--- a/docs/downloads/2026-10-15/bursa-report-2026-10-15.xlsx
+++ b/docs/downloads/2026-10-15/bursa-report-2026-10-15.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-15" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-15'!$A$1:$M$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-15'!$A$1:$M$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -78,12 +78,12 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -543,39 +543,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.665</v>
+        <v>0.06</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.064</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>30569500</v>
+        <v>31708000</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>1.21</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>76.18000000000001</v>
+        <v>22.58</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.596</v>
+        <v>0.138</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.517</v>
+        <v>0.347</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" s="7" t="inlineStr"/>
@@ -588,39 +588,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.45</v>
+        <v>0.905</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>-0.0426</v>
+        <v>-0.005500000000000001</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>6931400</v>
+        <v>19179100</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.2</v>
+        <v>0.29</v>
       </c>
       <c r="H3" t="n">
-        <v>39.27</v>
+        <v>67.23999999999999</v>
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.486</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.482</v>
+        <v>0.727</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" s="7" t="inlineStr"/>
@@ -633,39 +633,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0138</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ZETRIX</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.45</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>-0.0426</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>6526100</v>
+        <v>12377400</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.01</v>
+        <v>0.35</v>
       </c>
       <c r="H4" t="n">
-        <v>22.58</v>
-      </c>
-      <c r="I4" s="9" t="inlineStr">
+        <v>39.27</v>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.138</v>
+        <v>0.486</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.347</v>
+        <v>0.482</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="7" t="inlineStr"/>
@@ -678,27 +678,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0041</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AIMAX</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>0</v>
+        <v>0.79</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>-0.0125</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>5369600</v>
-      </c>
-      <c r="G5" s="5" t="n"/>
+        <v>11946500</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J5" s="2" t="n"/>
@@ -714,29 +716,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>0041</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>AIMAX</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="E6" s="8" t="n">
-        <v>-0.05</v>
+        <v>0.005</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>2700700</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>0.01</v>
-      </c>
+        <v>9349900</v>
+      </c>
+      <c r="G6" s="5" t="n"/>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J6" s="2" t="n"/>
@@ -752,39 +752,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.925</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>0.0165</v>
+        <v>0.415</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>2230800</v>
+        <v>9097200</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.03</v>
+        <v>0.25</v>
       </c>
       <c r="H7" t="n">
-        <v>69.56</v>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.373</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.727</v>
+        <v>0.263</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
@@ -812,15 +812,15 @@
         <v>-0.0147</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>2218000</v>
+        <v>8344600</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.03</v>
+        <v>0.11</v>
       </c>
       <c r="H8" t="n">
         <v>68.7</v>
       </c>
-      <c r="I8" s="6" t="inlineStr">
+      <c r="I8" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -842,39 +842,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>0.012</v>
+        <v>0.39</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>2042500</v>
+        <v>8225700</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.06</v>
+        <v>0.75</v>
       </c>
       <c r="H9" t="n">
-        <v>76.48999999999999</v>
+        <v>33.83</v>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.373</v>
+        <v>0.398</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.263</v>
+        <v>0.408</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
@@ -887,39 +887,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.315</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>-0.0156</v>
+        <v>0.675</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0.015</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1396200</v>
+        <v>7430700</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.19</v>
+        <v>0.29</v>
       </c>
       <c r="H10" t="n">
-        <v>63.92</v>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.301</v>
+        <v>0.604</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.279</v>
+        <v>0.521</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="7" t="inlineStr"/>
@@ -941,30 +941,30 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>-0.029</v>
+        <v>-0.0386</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>947600</v>
+        <v>6254000</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.03</v>
+        <v>0.21</v>
       </c>
       <c r="H11" t="n">
-        <v>59.07</v>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
+        <v>57.79</v>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.91</v>
+        <v>1.908</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1.713</v>
+        <v>1.712</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
@@ -977,45 +977,3582 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0117</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>SMRT</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.96</v>
+        <v>0.17</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.0052</v>
+        <v>0.0625</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>579400</v>
+        <v>6188600</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.1</v>
+        <v>1.92</v>
       </c>
       <c r="H12" t="n">
-        <v>66.63</v>
-      </c>
-      <c r="I12" s="9" t="inlineStr">
+        <v>41.24</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.918</v>
+        <v>0.179</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0.872</v>
+        <v>0.192</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>5311</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CEB</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>-0.0156</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>5318200</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H13" t="n">
+        <v>63.92</v>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>0.279</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0237</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>HAILY</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0.1143</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>4546900</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>18.06</v>
+      </c>
+      <c r="H14" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0476</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SLG</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>-0.0392</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>4148600</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="n"/>
+      <c r="K15" s="2" t="n"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>5161</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>JCY</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>-0.0348</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>4102700</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H16" t="n">
+        <v>47.34</v>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>0.536</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>7106</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SUPERMX</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>-0.0109</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>3651800</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H17" t="n">
+        <v>62.43</v>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>0.421</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0166</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>INARI</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>-0.0446</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>3401800</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H18" t="n">
+        <v>46.53</v>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>2.649</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>2.541</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0457</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>PENTECH</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>-0.0556</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>3278000</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H19" t="n">
+        <v>48.71</v>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0083</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NOTION</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>-0.0534</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>2959500</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H20" t="n">
+        <v>42.98</v>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>3182</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>GENTING</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0.0141</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>2918300</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H21" t="n">
+        <v>21.31</v>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>1.747</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>1.971</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0339</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CBHB</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>-0.0194</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>2642500</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H22" t="n">
+        <v>44.99</v>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>1.063</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>0.947</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>7121</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>2578800</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H23" t="n">
+        <v>58.28</v>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>0.8139999999999999</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>0.8090000000000001</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0198</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>GDB</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>-0.0122</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>2557200</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="H24" t="n">
+        <v>36.17</v>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>0.436</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0372</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CHEEDING</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>-0.0625</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>2523500</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="H25" t="n">
+        <v>33.38</v>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0024</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>JAG</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>2516000</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H26" t="n">
+        <v>61.88</v>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" s="7" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0248</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>YEWLEE</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>2328700</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H27" t="n">
+        <v>56.82</v>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0217</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>PWRWELL</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>-0.0252</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>2216100</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H28" t="n">
+        <v>52.79</v>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>1.091</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0251</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>SFPTECH</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>-0.0364</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>2030800</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H29" t="n">
+        <v>42.94</v>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>5151</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>HEXTAR</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="E30" s="8" t="n">
+        <v>-0.0064</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>2008900</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H30" t="n">
+        <v>50.18</v>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>5168</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>HARTA</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>-0.0179</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>1896200</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H31" t="n">
+        <v>54.37</v>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>1.075</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>1.043</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>5099</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CAPITALA</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>0.0233</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>1746100</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H32" t="n">
+        <v>33.69</v>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>0.239</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0278</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EDELTEQ</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>-0.05429999999999999</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>1692600</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H33" t="n">
+        <v>61.59</v>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0453</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EIPOWER</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="E34" s="8" t="n">
+        <v>-0.005699999999999999</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>1687100</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H34" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" s="7" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>UUE</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>-0.0395</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>1497800</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H35" t="n">
+        <v>50.68</v>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>0.743</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" s="7" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0471</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>PIONEER</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E36" s="8" t="n">
+        <v>-0.0141</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>1475900</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H36" t="n">
+        <v>63.15</v>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="K36" s="2" t="n"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" s="7" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>7579</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>AWC</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>0.0072</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>1426100</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H37" t="n">
+        <v>67.11</v>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>0.642</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>0.548</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0259</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>SNS</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="E38" s="8" t="n">
+        <v>-0.0101</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>1407300</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H38" t="n">
+        <v>40.63</v>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>0.514</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" s="7" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>-0.0156</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>1403600</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H39" t="n">
+        <v>48.11</v>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" s="7" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>3336</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>IJM</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>-0.0109</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>1403000</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H40" t="n">
+        <v>44.88</v>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>2.785</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>2.728</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" s="7" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0390</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ISF</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>-0.0186</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>1392400</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H41" t="n">
+        <v>45.85</v>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>0.822</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" s="7" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1295</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>PBBANK</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>-0.0063</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>1377700</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H42" t="n">
+        <v>47.63</v>
+      </c>
+      <c r="I42" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>4.718</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>4.863</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" s="7" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>7204</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>D&amp;O</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>-0.0278</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>1372000</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H43" t="n">
+        <v>53.55</v>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>0.454</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" s="7" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0181</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>AEMULUS</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>-0.0471</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>1344000</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H44" t="n">
+        <v>45.47</v>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" s="7" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>5301</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CTOS</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>1327700</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H45" t="n">
+        <v>28.41</v>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>0.626</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" s="7" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0345</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>SUNLOGY</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E46" s="8" t="n">
+        <v>-0.0118</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>1293300</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H46" t="n">
+        <v>43.93</v>
+      </c>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" s="7" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>6742</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>YTLPOWR</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="E47" s="8" t="n">
+        <v>-0.0292</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>1270200</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H47" t="n">
+        <v>40.17</v>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>5.579</v>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>5.412</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" s="7" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>7153</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>KOSSAN</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E48" s="8" t="n">
+        <v>-0.0164</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>1247100</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H48" t="n">
+        <v>54.83</v>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>1.131</v>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" s="7" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>8524</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>TALIWRK</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="E49" s="8" t="n">
+        <v>-0.0213</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>1241300</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H49" t="n">
+        <v>37.06</v>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>0.247</v>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>0.258</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" s="7" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>5932</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>BPURI</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="E50" s="8" t="n">
+        <v>-0.0227</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>1223900</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="H50" t="n">
+        <v>40.22</v>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" s="7" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>0246</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>CNERGEN</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E51" s="8" t="n">
+        <v>-0.0556</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>1203400</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H51" t="n">
+        <v>51.06</v>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>1.041</v>
+      </c>
+      <c r="K51" s="2" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" s="7" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>0450</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>MFGROUP</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>0.0351</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>1183700</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="H52" t="n">
+        <v>66.28</v>
+      </c>
+      <c r="I52" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" s="7" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>0196</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>QES</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="E53" s="8" t="n">
+        <v>-0.0407</v>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>1171900</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H53" t="n">
+        <v>48.81</v>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K53" s="2" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" s="7" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>5398</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>GAMUDA</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="E54" s="8" t="n">
+        <v>-0.004099999999999999</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>1161300</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H54" t="n">
+        <v>47.46</v>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>4.918</v>
+      </c>
+      <c r="K54" s="2" t="n">
+        <v>4.708</v>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" s="7" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>8052</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>CGB</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="E55" s="8" t="n">
+        <v>-0.005699999999999999</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>1155000</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H55" t="n">
+        <v>45.95</v>
+      </c>
+      <c r="I55" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>0.868</v>
+      </c>
+      <c r="K55" s="2" t="n">
+        <v>0.869</v>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" s="7" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>9776</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>RSSB</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="E56" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>1153800</v>
+      </c>
+      <c r="G56" s="5" t="n"/>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="n"/>
+      <c r="K56" s="2" t="n"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" s="7" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>0275</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>OPPSTAR</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="E57" s="8" t="n">
+        <v>-0.0222</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>1142900</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H57" t="n">
+        <v>44.67</v>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="K57" s="2" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" s="7" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>5238</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>AAGB</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>0.0222</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>1126400</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H58" t="n">
+        <v>27.43</v>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="K58" s="2" t="n">
+        <v>0.701</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" s="7" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>0455</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>BUSCAP</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E59" s="8" t="n">
+        <v>-0.0574</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>1123400</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H59" t="n">
+        <v>80.06</v>
+      </c>
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>0.803</v>
+      </c>
+      <c r="K59" s="2" t="n">
+        <v>0.544</v>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" s="7" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>0208</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>GREATEC</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="E60" s="8" t="n">
+        <v>-0.0426</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>1110900</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H60" t="n">
+        <v>40.24</v>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>2.613</v>
+      </c>
+      <c r="K60" s="2" t="n">
+        <v>2.599</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" s="7" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>5327</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>MEGAFB</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>0.0066</v>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>1102000</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H61" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="I61" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="n">
+        <v>2.769</v>
+      </c>
+      <c r="K61" s="2" t="n">
+        <v>2.382</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" s="7" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>CIMB</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="E62" s="8" t="n">
+        <v>-0.0013</v>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>1099700</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H62" t="n">
+        <v>44.06</v>
+      </c>
+      <c r="I62" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>7.579</v>
+      </c>
+      <c r="K62" s="2" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" s="7" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>0104</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>GENETEC</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E63" s="8" t="n">
+        <v>-0.0164</v>
+      </c>
+      <c r="F63" s="4" t="n">
+        <v>1088300</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H63" t="n">
+        <v>38.46</v>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="K63" s="2" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" s="7" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>8583</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>MAHSING</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E64" s="8" t="n">
+        <v>-0.0106</v>
+      </c>
+      <c r="F64" s="4" t="n">
+        <v>1080500</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H64" t="n">
+        <v>27.89</v>
+      </c>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="n">
+        <v>0.979</v>
+      </c>
+      <c r="K64" s="2" t="n">
+        <v>1.059</v>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" s="7" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>0318</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ELRIDGE</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="E65" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="4" t="n">
+        <v>1043400</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H65" t="n">
+        <v>65.59</v>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="n">
+        <v>0.917</v>
+      </c>
+      <c r="K65" s="2" t="n">
+        <v>0.872</v>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" s="7" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>5210</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ARMADA</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>0.0308</v>
+      </c>
+      <c r="F66" s="4" t="n">
+        <v>1038200</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H66" t="n">
+        <v>47.07</v>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="K66" s="2" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" s="7" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>4677</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>YTL</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="E67" s="8" t="n">
+        <v>-0.024</v>
+      </c>
+      <c r="F67" s="4" t="n">
+        <v>1036100</v>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H67" t="n">
+        <v>33.92</v>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="n">
+        <v>2.175</v>
+      </c>
+      <c r="K67" s="2" t="n">
+        <v>2.228</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" s="7" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>5352</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>MTTSL</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v>1022800</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H68" t="n">
+        <v>62.46</v>
+      </c>
+      <c r="I68" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>1.184</v>
+      </c>
+      <c r="K68" s="2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" s="7" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>SCGBHD</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E69" s="8" t="n">
+        <v>-0.0246</v>
+      </c>
+      <c r="F69" s="4" t="n">
+        <v>993400</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H69" t="n">
+        <v>50.67</v>
+      </c>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="n">
+        <v>2.795</v>
+      </c>
+      <c r="K69" s="2" t="n">
+        <v>2.647</v>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" s="7" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>5286</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="E70" s="8" t="n">
+        <v>-0.0522</v>
+      </c>
+      <c r="F70" s="4" t="n">
+        <v>972800</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H70" t="n">
+        <v>55.06</v>
+      </c>
+      <c r="I70" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>6.097</v>
+      </c>
+      <c r="K70" s="2" t="n">
+        <v>5.875</v>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" s="7" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>0245</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>MNHLDG</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="E71" s="8" t="n">
+        <v>-0.026</v>
+      </c>
+      <c r="F71" s="4" t="n">
+        <v>883400</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H71" t="n">
+        <v>45.59</v>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="K71" s="2" t="n">
+        <v>3.646</v>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" s="7" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0127</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>JHM</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E72" s="8" t="n">
+        <v>-0.0579</v>
+      </c>
+      <c r="F72" s="4" t="n">
+        <v>877600</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H72" t="n">
+        <v>55.34</v>
+      </c>
+      <c r="I72" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="K72" s="2" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" s="7" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>8907</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="E73" s="8" t="n">
+        <v>-0.0291</v>
+      </c>
+      <c r="F73" s="4" t="n">
+        <v>862400</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H73" t="n">
+        <v>39.48</v>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="K73" s="2" t="n">
+        <v>1.771</v>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" s="7" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>0296</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>HEGROUP</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="E74" s="8" t="n">
+        <v>-0.0441</v>
+      </c>
+      <c r="F74" s="4" t="n">
+        <v>858900</v>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H74" t="n">
+        <v>42.79</v>
+      </c>
+      <c r="I74" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="n">
+        <v>1.049</v>
+      </c>
+      <c r="K74" s="2" t="n">
+        <v>0.926</v>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" s="7" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>0271</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>WELLS</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>0.0091</v>
+      </c>
+      <c r="F75" s="4" t="n">
+        <v>842000</v>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H75" t="n">
+        <v>39.65</v>
+      </c>
+      <c r="I75" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="K75" s="2" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" s="7" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>0236</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>RAMSSOL</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E76" s="8" t="n">
+        <v>-0.013</v>
+      </c>
+      <c r="F76" s="4" t="n">
+        <v>817400</v>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H76" t="n">
+        <v>44.91</v>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="K76" s="2" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" s="7" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>0167</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>MCLEAN</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="E77" s="8" t="n">
+        <v>-0.0432</v>
+      </c>
+      <c r="F77" s="4" t="n">
+        <v>792400</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H77" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="n">
+        <v>0.738</v>
+      </c>
+      <c r="K77" s="2" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" s="7" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>7233</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>DUFU</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="E78" s="8" t="n">
+        <v>-0.0387</v>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>791100</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H78" t="n">
+        <v>50.16</v>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>3.026</v>
+      </c>
+      <c r="K78" s="2" t="n">
+        <v>2.846</v>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" s="7" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>0146</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>JFTECH</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="E79" s="8" t="n">
+        <v>-0.0513</v>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>743400</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H79" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="n">
+        <v>0.728</v>
+      </c>
+      <c r="K79" s="2" t="n">
+        <v>0.701</v>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" s="7" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>0376</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>IAB</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="E80" s="8" t="n">
+        <v>-0.0354</v>
+      </c>
+      <c r="F80" s="4" t="n">
+        <v>707200</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H80" t="n">
+        <v>34.68</v>
+      </c>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>1.232</v>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v>1.303</v>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" s="7" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>0459</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E81" s="8" t="n">
+        <v>-0.0429</v>
+      </c>
+      <c r="F81" s="4" t="n">
+        <v>699400</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H81" t="n">
+        <v>56.59</v>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="K81" s="2" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" s="7" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>0240</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>CORAZA</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="E82" s="8" t="n">
+        <v>-0.0677</v>
+      </c>
+      <c r="F82" s="4" t="n">
+        <v>689400</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H82" t="n">
+        <v>51.76</v>
+      </c>
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>1.246</v>
+      </c>
+      <c r="K82" s="2" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" s="7" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>5264</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>MALAKOF</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="E83" s="8" t="n">
+        <v>-0.0066</v>
+      </c>
+      <c r="F83" s="4" t="n">
+        <v>631700</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H83" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>0.783</v>
+      </c>
+      <c r="K83" s="2" t="n">
+        <v>0.803</v>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" s="7" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>GCB</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>0.007800000000000001</v>
+      </c>
+      <c r="F84" s="4" t="n">
+        <v>629200</v>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H84" t="n">
+        <v>46.61</v>
+      </c>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="K84" s="2" t="n">
+        <v>1.314</v>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" s="7" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>4715</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>GENM</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="F85" s="4" t="n">
+        <v>584000</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H85" t="n">
+        <v>25.55</v>
+      </c>
+      <c r="I85" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>1.425</v>
+      </c>
+      <c r="K85" s="2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" s="7" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>7241</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>NGGB</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="E86" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="4" t="n">
+        <v>567100</v>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H86" t="n">
+        <v>59.74</v>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="K86" s="2" t="n">
+        <v>0.718</v>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" s="7" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>0368</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>OXB</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="E87" s="8" t="n">
+        <v>-0.0374</v>
+      </c>
+      <c r="F87" s="4" t="n">
+        <v>548400</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H87" t="n">
+        <v>58.21</v>
+      </c>
+      <c r="I87" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="n">
+        <v>0.493</v>
+      </c>
+      <c r="K87" s="2" t="n">
+        <v>0.461</v>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" s="7" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>AMBANK</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="E88" s="8" t="n">
+        <v>-0.0016</v>
+      </c>
+      <c r="F88" s="4" t="n">
+        <v>518300</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H88" t="n">
+        <v>41.19</v>
+      </c>
+      <c r="I88" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="K88" s="2" t="n">
+        <v>6.789</v>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" s="7" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>4324</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>HENGYUAN</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="E89" s="8" t="n">
+        <v>-0.0159</v>
+      </c>
+      <c r="F89" s="4" t="n">
+        <v>517000</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H89" t="n">
+        <v>55.89</v>
+      </c>
+      <c r="I89" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>3.623</v>
+      </c>
+      <c r="K89" s="2" t="n">
+        <v>2.918</v>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" s="7" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>0292</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>JTGROUP</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="E90" s="8" t="n">
+        <v>-0.0484</v>
+      </c>
+      <c r="F90" s="4" t="n">
+        <v>510600</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H90" t="n">
+        <v>47.61</v>
+      </c>
+      <c r="I90" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>1.248</v>
+      </c>
+      <c r="K90" s="2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" s="7" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>5357</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>SKYECHIP</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E91" s="8" t="n">
+        <v>-0.0385</v>
+      </c>
+      <c r="F91" s="4" t="n">
+        <v>509000</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H91" t="n">
+        <v>36.96</v>
+      </c>
+      <c r="I91" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="n">
+        <v>2.922</v>
+      </c>
+      <c r="K91" s="2" t="n">
+        <v>3.023</v>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M12"/>
+  <autoFilter ref="A1:M91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-15/bursa-report-2026-10-15.xlsx
+++ b/docs/downloads/2026-10-15/bursa-report-2026-10-15.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-15" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-15'!$A$1:$M$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-15'!$A$1:$M$122</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M91"/>
+  <dimension ref="A1:M122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -558,10 +558,10 @@
         <v>0.09089999999999999</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>31708000</v>
+        <v>36768000</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H2" t="n">
         <v>22.58</v>
@@ -597,19 +597,19 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.905</v>
+        <v>0.895</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>-0.005500000000000001</v>
+        <v>-0.0165</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>19179100</v>
+        <v>26739300</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.29</v>
+        <v>0.4</v>
       </c>
       <c r="H3" t="n">
-        <v>67.23999999999999</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>0.727</v>
@@ -633,40 +633,33 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E4" s="8" t="n">
-        <v>-0.0426</v>
+        <v>0.825</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0.0312</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>12377400</v>
+        <v>19022100</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="H4" t="n">
-        <v>39.27</v>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>0.486</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>0.482</v>
-      </c>
+        <v>0.1</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="7" t="inlineStr"/>
     </row>
@@ -678,33 +671,40 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.79</v>
+        <v>0.45</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>-0.0125</v>
+        <v>-0.0426</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>11946500</v>
+        <v>16931500</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I5" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="n"/>
-      <c r="K5" s="2" t="n"/>
+        <v>0.48</v>
+      </c>
+      <c r="H5" t="n">
+        <v>39.27</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>0.486</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0.482</v>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
     </row>
@@ -716,31 +716,40 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0041</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AIMAX</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="E6" s="10" t="n">
-        <v>0</v>
+        <v>0.335</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>-0.0147</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>9349900</v>
-      </c>
-      <c r="G6" s="5" t="n"/>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="n"/>
-      <c r="K6" s="2" t="n"/>
+        <v>15180100</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H6" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>0.253</v>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr"/>
     </row>
@@ -761,19 +770,19 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>0</v>
+        <v>0.425</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0.0241</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>9097200</v>
+        <v>13290200</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.25</v>
+        <v>0.36</v>
       </c>
       <c r="H7" t="n">
-        <v>75.59999999999999</v>
+        <v>77.33</v>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
@@ -781,7 +790,7 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.373</v>
+        <v>0.374</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0.263</v>
@@ -797,28 +806,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>-0.0147</v>
+        <v>0.665</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>8344600</v>
+        <v>12961000</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.11</v>
+        <v>0.5</v>
       </c>
       <c r="H8" t="n">
-        <v>68.7</v>
+        <v>76.18000000000001</v>
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
@@ -826,10 +835,10 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.297</v>
+        <v>0.603</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.253</v>
+        <v>0.521</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
@@ -842,39 +851,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>0096</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>NEXGRAM</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.39</v>
+        <v>0.055</v>
       </c>
       <c r="E9" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>8225700</v>
+        <v>11717300</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.75</v>
+        <v>6.85</v>
       </c>
       <c r="H9" t="n">
-        <v>33.83</v>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.25</v>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.398</v>
+        <v>0.044</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.408</v>
+        <v>0.047</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
@@ -887,40 +896,31 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0041</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>AIMAX</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>0.015</v>
+        <v>0.005</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>7430700</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="H10" t="n">
-        <v>77.59999999999999</v>
-      </c>
-      <c r="I10" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>0.604</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>0.521</v>
-      </c>
+        <v>10997900</v>
+      </c>
+      <c r="G10" s="5" t="n"/>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n"/>
+      <c r="K10" s="2" t="n"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="7" t="inlineStr"/>
     </row>
@@ -932,39 +932,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1.99</v>
+        <v>0.26</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>-0.0386</v>
+        <v>-0.0189</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>6254000</v>
+        <v>10085300</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.21</v>
+        <v>1.29</v>
       </c>
       <c r="H11" t="n">
-        <v>57.79</v>
-      </c>
-      <c r="I11" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>26.18</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.908</v>
+        <v>0.281</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1.712</v>
+        <v>0.304</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
@@ -977,28 +977,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0117</t>
+          <t>1643</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SMRT</t>
+          <t>LANDMRK</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.17</v>
+        <v>0.04</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.0625</v>
+        <v>0.3333</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>6188600</v>
+        <v>8708000</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>1.92</v>
+        <v>6.96</v>
       </c>
       <c r="H12" t="n">
-        <v>41.24</v>
+        <v>37.75</v>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.179</v>
+        <v>0.048</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0.192</v>
+        <v>0.064</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
@@ -1022,28 +1022,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.315</v>
+        <v>2</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>-0.0156</v>
+        <v>-0.0338</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>5318200</v>
+        <v>8629300</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.72</v>
+        <v>0.29</v>
       </c>
       <c r="H13" t="n">
-        <v>63.92</v>
+        <v>58.43</v>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.301</v>
+        <v>1.909</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0.279</v>
+        <v>1.713</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
@@ -1067,39 +1067,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0237</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>HAILY</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.195</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>0.1143</v>
+        <v>0.39</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>4546900</v>
+        <v>8292200</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>18.06</v>
+        <v>0.76</v>
       </c>
       <c r="H14" t="n">
-        <v>73.09999999999999</v>
-      </c>
-      <c r="I14" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.83</v>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.167</v>
+        <v>0.398</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0.166</v>
+        <v>0.408</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="7" t="inlineStr"/>
@@ -1121,20 +1121,20 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.245</v>
+        <v>0.25</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>-0.0392</v>
+        <v>-0.0196</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>4148600</v>
+        <v>7662600</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>0.28</v>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J15" s="2" t="n"/>
@@ -1150,28 +1150,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0117</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>SMRT</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E16" s="8" t="n">
-        <v>-0.0348</v>
+        <v>0.17</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>0.0625</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>4102700</v>
+        <v>7650600</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.2</v>
+        <v>2.37</v>
       </c>
       <c r="H16" t="n">
-        <v>47.34</v>
+        <v>41.24</v>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.58</v>
+        <v>0.179</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.536</v>
+        <v>0.192</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
@@ -1195,28 +1195,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.455</v>
+        <v>0.315</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>-0.0109</v>
+        <v>-0.0156</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>3651800</v>
+        <v>6625500</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.18</v>
+        <v>0.89</v>
       </c>
       <c r="H17" t="n">
-        <v>62.43</v>
+        <v>63.92</v>
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.421</v>
+        <v>0.301</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.361</v>
+        <v>0.279</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
@@ -1240,28 +1240,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>2.57</v>
+        <v>0.45</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>-0.0446</v>
+        <v>-0.0217</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>3401800</v>
+        <v>5991000</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.19</v>
+        <v>0.29</v>
       </c>
       <c r="H18" t="n">
-        <v>46.53</v>
+        <v>60.9</v>
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
@@ -1269,10 +1269,10 @@
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>2.649</v>
+        <v>0.42</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>2.541</v>
+        <v>0.361</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
@@ -1285,39 +1285,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0237</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>HAILY</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="E19" s="8" t="n">
-        <v>-0.0556</v>
+        <v>0.19</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>0.0857</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>3278000</v>
+        <v>5591500</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.37</v>
+        <v>22.21</v>
       </c>
       <c r="H19" t="n">
-        <v>48.71</v>
-      </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.90000000000001</v>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.349</v>
+        <v>0.167</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0.331</v>
+        <v>0.166</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
@@ -1330,28 +1330,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.62</v>
+        <v>0.55</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>-0.0534</v>
+        <v>-0.0435</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2959500</v>
+        <v>5368200</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="H20" t="n">
-        <v>42.98</v>
+        <v>46.48</v>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
@@ -1359,10 +1359,10 @@
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.665</v>
+        <v>0.579</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.619</v>
+        <v>0.536</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
@@ -1375,39 +1375,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>0.0141</v>
+        <v>2.58</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>-0.0409</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>2918300</v>
+        <v>5289400</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="H21" t="n">
-        <v>21.31</v>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.09</v>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.747</v>
+        <v>2.65</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>1.971</v>
+        <v>2.541</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
@@ -1420,39 +1420,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="E22" s="8" t="n">
-        <v>-0.0194</v>
+        <v>0.82</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2642500</v>
+        <v>5132800</v>
       </c>
       <c r="G22" s="5" t="n">
         <v>0.32</v>
       </c>
       <c r="H22" t="n">
-        <v>44.99</v>
-      </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.28</v>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.063</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0.947</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
@@ -1465,39 +1465,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>0</v>
+        <v>1.43</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>0.006999999999999999</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2578800</v>
+        <v>4941200</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.16</v>
+        <v>0.48</v>
       </c>
       <c r="H23" t="n">
-        <v>58.28</v>
-      </c>
-      <c r="I23" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>20.13</v>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.8139999999999999</v>
+        <v>1.746</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.8090000000000001</v>
+        <v>1.971</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
@@ -1510,28 +1510,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.405</v>
+        <v>0.345</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>-0.0122</v>
+        <v>-0.0417</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>2557200</v>
+        <v>4806500</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>1.37</v>
+        <v>0.55</v>
       </c>
       <c r="H24" t="n">
-        <v>36.17</v>
+        <v>50.66</v>
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
@@ -1539,10 +1539,10 @@
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.417</v>
+        <v>0.349</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.436</v>
+        <v>0.331</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
@@ -1555,39 +1555,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="E25" s="8" t="n">
-        <v>-0.0625</v>
+        <v>1.28</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>0.0159</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>2523500</v>
+        <v>4736800</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.62</v>
+        <v>0.8</v>
       </c>
       <c r="H25" t="n">
-        <v>33.38</v>
-      </c>
-      <c r="I25" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.38</v>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.597</v>
+        <v>1.185</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.604</v>
+        <v>1.181</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
@@ -1600,39 +1600,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E26" s="10" t="n">
-        <v>0</v>
+        <v>0.615</v>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>-0.0611</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2516000</v>
+        <v>4390600</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.35</v>
+        <v>0.49</v>
       </c>
       <c r="H26" t="n">
-        <v>61.88</v>
-      </c>
-      <c r="I26" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.21</v>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.371</v>
+        <v>0.664</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.369</v>
+        <v>0.619</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
@@ -1645,28 +1645,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>0</v>
+        <v>0.775</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>-0.0064</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2328700</v>
+        <v>4176100</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.21</v>
+        <v>0.28</v>
       </c>
       <c r="H27" t="n">
-        <v>56.82</v>
+        <v>50.18</v>
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.615</v>
+        <v>0.775</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.614</v>
+        <v>0.776</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
@@ -1690,39 +1690,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="E28" s="8" t="n">
-        <v>-0.0252</v>
+        <v>0.625</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2216100</v>
+        <v>3748200</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.54</v>
+        <v>0.34</v>
       </c>
       <c r="H28" t="n">
-        <v>52.79</v>
-      </c>
-      <c r="I28" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.82</v>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.163</v>
+        <v>0.615</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>1.091</v>
+        <v>0.614</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
@@ -1735,39 +1735,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E29" s="8" t="n">
-        <v>-0.0364</v>
+        <v>0.385</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>0.0132</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>2030800</v>
+        <v>3610400</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.24</v>
+        <v>0.5</v>
       </c>
       <c r="H29" t="n">
-        <v>42.94</v>
-      </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.54000000000001</v>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.277</v>
+        <v>0.371</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.298</v>
+        <v>0.369</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1780,39 +1780,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.775</v>
+        <v>0.515</v>
       </c>
       <c r="E30" s="8" t="n">
-        <v>-0.0064</v>
+        <v>-0.08039999999999999</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2008900</v>
+        <v>3206900</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.13</v>
+        <v>0.79</v>
       </c>
       <c r="H30" t="n">
-        <v>50.18</v>
-      </c>
-      <c r="I30" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.06</v>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.775</v>
+        <v>0.596</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.776</v>
+        <v>0.603</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1825,28 +1825,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>-0.0179</v>
+        <v>-0.0291</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1896200</v>
+        <v>3205500</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.19</v>
+        <v>0.38</v>
       </c>
       <c r="H31" t="n">
-        <v>54.37</v>
+        <v>43.73</v>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
@@ -1854,10 +1854,10 @@
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.075</v>
+        <v>1.062</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>1.043</v>
+        <v>0.947</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1870,28 +1870,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>0.0233</v>
+        <v>1.1</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>-0.0179</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>1746100</v>
+        <v>3099300</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.31</v>
       </c>
       <c r="H32" t="n">
-        <v>33.69</v>
+        <v>54.37</v>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.239</v>
+        <v>1.075</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0.292</v>
+        <v>1.043</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
@@ -1915,28 +1915,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.435</v>
+        <v>0.415</v>
       </c>
       <c r="E33" s="8" t="n">
-        <v>-0.05429999999999999</v>
+        <v>-0.0235</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1692600</v>
+        <v>2749900</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.32</v>
+        <v>0.26</v>
       </c>
       <c r="H33" t="n">
-        <v>61.59</v>
+        <v>42.82</v>
       </c>
       <c r="I33" s="9" t="inlineStr">
         <is>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.383</v>
+        <v>0.443</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.357</v>
+        <v>0.432</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1960,28 +1960,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.87</v>
+        <v>1.27</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>1687100</v>
+        <v>2744800</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.2</v>
+        <v>0.28</v>
       </c>
       <c r="H34" t="n">
-        <v>41.5</v>
+        <v>43.81</v>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.308</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.84</v>
+        <v>1.313</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2005,28 +2005,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.73</v>
+        <v>0.26</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>-0.0395</v>
+        <v>-0.0545</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>1497800</v>
+        <v>2713100</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.21</v>
+        <v>0.32</v>
       </c>
       <c r="H35" t="n">
-        <v>50.68</v>
+        <v>41</v>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
@@ -2034,10 +2034,10 @@
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.743</v>
+        <v>0.276</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.669</v>
+        <v>0.298</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2050,38 +2050,40 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.35</v>
+        <v>0.405</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>-0.0141</v>
+        <v>-0.0122</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>1475900</v>
+        <v>2557200</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.16</v>
+        <v>1.37</v>
       </c>
       <c r="H36" t="n">
-        <v>63.15</v>
-      </c>
-      <c r="I36" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.17</v>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.311</v>
-      </c>
-      <c r="K36" s="2" t="n"/>
+        <v>0.417</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>0.436</v>
+      </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
     </row>
@@ -2093,28 +2095,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>0.0072</v>
+        <v>0.445</v>
+      </c>
+      <c r="E37" s="8" t="n">
+        <v>-0.0326</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>1426100</v>
+        <v>2440300</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.6</v>
+        <v>0.47</v>
       </c>
       <c r="H37" t="n">
-        <v>67.11</v>
+        <v>63.86</v>
       </c>
       <c r="I37" s="9" t="inlineStr">
         <is>
@@ -2122,10 +2124,10 @@
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.642</v>
+        <v>0.384</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0.548</v>
+        <v>0.357</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2138,40 +2140,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="E38" s="8" t="n">
-        <v>-0.0101</v>
+        <v>0.36</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>0.0141</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>1407300</v>
+        <v>2349100</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="H38" t="n">
-        <v>40.63</v>
-      </c>
-      <c r="I38" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.45</v>
+      </c>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.514</v>
-      </c>
-      <c r="K38" s="2" t="n">
-        <v>0.527</v>
-      </c>
+        <v>0.312</v>
+      </c>
+      <c r="K38" s="2" t="n"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
     </row>
@@ -2183,28 +2183,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>0.63</v>
+        <v>1.16</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>-0.0156</v>
+        <v>-0.0252</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>1403600</v>
+        <v>2316700</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="H39" t="n">
-        <v>48.11</v>
+        <v>52.79</v>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.637</v>
+        <v>1.163</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0.619</v>
+        <v>1.091</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2228,28 +2228,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="E40" s="8" t="n">
-        <v>-0.0109</v>
+        <v>0.215</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>1403000</v>
+        <v>2287400</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="H40" t="n">
-        <v>44.88</v>
+        <v>30.1</v>
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
@@ -2257,10 +2257,10 @@
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>2.785</v>
+        <v>0.238</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>2.728</v>
+        <v>0.292</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2273,39 +2273,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>0.79</v>
+        <v>1.15</v>
       </c>
       <c r="E41" s="8" t="n">
-        <v>-0.0186</v>
+        <v>-0.0574</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>1392400</v>
+        <v>2286300</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.37</v>
+        <v>0.59</v>
       </c>
       <c r="H41" t="n">
-        <v>45.85</v>
-      </c>
-      <c r="I41" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>80.06</v>
+      </c>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.822</v>
+        <v>0.803</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0.773</v>
+        <v>0.544</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2318,28 +2318,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>4.72</v>
+        <v>0.31</v>
       </c>
       <c r="E42" s="8" t="n">
-        <v>-0.0063</v>
+        <v>-0.0159</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>1377700</v>
+        <v>2267400</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="H42" t="n">
-        <v>47.63</v>
+        <v>54.53</v>
       </c>
       <c r="I42" s="9" t="inlineStr">
         <is>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>4.718</v>
+        <v>0.308</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>4.863</v>
+        <v>0.298</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2363,28 +2363,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>0.525</v>
+        <v>0.87</v>
       </c>
       <c r="E43" s="8" t="n">
-        <v>-0.0278</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>1372000</v>
+        <v>2182200</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.09</v>
+        <v>0.26</v>
       </c>
       <c r="H43" t="n">
-        <v>53.55</v>
+        <v>41.5</v>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
@@ -2392,10 +2392,10 @@
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.52</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0.454</v>
+        <v>0.84</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2408,28 +2408,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.405</v>
+        <v>5.32</v>
       </c>
       <c r="E44" s="8" t="n">
-        <v>-0.0471</v>
+        <v>-0.0292</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>1344000</v>
+        <v>2052200</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="H44" t="n">
-        <v>45.47</v>
+        <v>40.17</v>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
@@ -2437,10 +2437,10 @@
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.425</v>
+        <v>5.579</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.416</v>
+        <v>5.412</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2453,39 +2453,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>0.48</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="E45" s="8" t="n">
-        <v>-0.04</v>
+        <v>-0.0072</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>1327700</v>
+        <v>2027100</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.18</v>
+        <v>0.85</v>
       </c>
       <c r="H45" t="n">
-        <v>28.41</v>
-      </c>
-      <c r="I45" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.88</v>
+      </c>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.556</v>
+        <v>0.641</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.626</v>
+        <v>0.547</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2498,39 +2498,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>0.42</v>
+        <v>2.74</v>
       </c>
       <c r="E46" s="8" t="n">
-        <v>-0.0118</v>
+        <v>-0.0352</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>1293300</v>
+        <v>2023100</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.12</v>
+        <v>0.23</v>
       </c>
       <c r="H46" t="n">
-        <v>43.93</v>
-      </c>
-      <c r="I46" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.73</v>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.444</v>
+        <v>2.793</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0.432</v>
+        <v>2.646</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2543,39 +2543,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>5.32</v>
-      </c>
-      <c r="E47" s="8" t="n">
-        <v>-0.0292</v>
+        <v>3.07</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>0.0066</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>1270200</v>
+        <v>1949900</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.09</v>
+        <v>0.6</v>
       </c>
       <c r="H47" t="n">
-        <v>40.17</v>
-      </c>
-      <c r="I47" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>81.5</v>
+      </c>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>5.579</v>
+        <v>2.769</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>5.412</v>
+        <v>2.382</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2588,28 +2588,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>1.2</v>
+        <v>0.79</v>
       </c>
       <c r="E48" s="8" t="n">
-        <v>-0.0164</v>
+        <v>-0.0186</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>1247100</v>
+        <v>1938200</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.17</v>
+        <v>0.52</v>
       </c>
       <c r="H48" t="n">
-        <v>54.83</v>
+        <v>45.85</v>
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.169</v>
+        <v>0.822</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>1.131</v>
+        <v>0.773</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2633,28 +2633,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>8524</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>TALIWRK</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="E49" s="8" t="n">
+        <v>-0.0202</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>1925200</v>
+      </c>
+      <c r="G49" s="5" t="n">
         <v>0.23</v>
       </c>
-      <c r="E49" s="8" t="n">
-        <v>-0.0213</v>
-      </c>
-      <c r="F49" s="4" t="n">
-        <v>1241300</v>
-      </c>
-      <c r="G49" s="5" t="n">
-        <v>0.6</v>
-      </c>
       <c r="H49" t="n">
-        <v>37.06</v>
+        <v>39.31</v>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
@@ -2662,10 +2662,10 @@
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.247</v>
+        <v>0.514</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0.258</v>
+        <v>0.527</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
@@ -2678,28 +2678,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>BPURI</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>0.215</v>
+        <v>0.41</v>
       </c>
       <c r="E50" s="8" t="n">
-        <v>-0.0227</v>
+        <v>-0.0353</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>1223900</v>
+        <v>1904800</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>2.35</v>
+        <v>0.28</v>
       </c>
       <c r="H50" t="n">
-        <v>40.22</v>
+        <v>46.73</v>
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
@@ -2707,10 +2707,10 @@
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.225</v>
+        <v>0.425</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0.233</v>
+        <v>0.416</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2723,39 +2723,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>1.02</v>
+        <v>4.73</v>
       </c>
       <c r="E51" s="8" t="n">
-        <v>-0.0556</v>
+        <v>-0.0042</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>1203400</v>
+        <v>1895500</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.3</v>
+        <v>0.11</v>
       </c>
       <c r="H51" t="n">
-        <v>51.06</v>
-      </c>
-      <c r="I51" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.54</v>
+      </c>
+      <c r="I51" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.041</v>
+        <v>4.719</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0.895</v>
+        <v>4.863</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2768,28 +2768,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E52" s="3" t="n">
-        <v>0.0351</v>
+        <v>0.865</v>
+      </c>
+      <c r="E52" s="8" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>1183700</v>
+        <v>1893700</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>1.24</v>
+        <v>0.1</v>
       </c>
       <c r="H52" t="n">
-        <v>66.28</v>
+        <v>45.95</v>
       </c>
       <c r="I52" s="9" t="inlineStr">
         <is>
@@ -2797,10 +2797,10 @@
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.275</v>
+        <v>0.868</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0.267</v>
+        <v>0.869</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2813,28 +2813,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>0.59</v>
+        <v>0.73</v>
       </c>
       <c r="E53" s="8" t="n">
-        <v>-0.0407</v>
+        <v>-0.0395</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>1171900</v>
+        <v>1872200</v>
       </c>
       <c r="G53" s="5" t="n">
         <v>0.27</v>
       </c>
       <c r="H53" t="n">
-        <v>48.81</v>
+        <v>50.68</v>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
@@ -2842,10 +2842,10 @@
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.6</v>
+        <v>0.743</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0.585</v>
+        <v>0.669</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2858,28 +2858,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>4.83</v>
-      </c>
-      <c r="E54" s="8" t="n">
-        <v>-0.004099999999999999</v>
+        <v>0.455</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>0.0111</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>1161300</v>
+        <v>1854800</v>
       </c>
       <c r="G54" s="5" t="n">
         <v>0.05</v>
       </c>
       <c r="H54" t="n">
-        <v>47.46</v>
+        <v>25.8</v>
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>4.918</v>
+        <v>0.518</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>4.708</v>
+        <v>0.701</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2903,39 +2903,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>0.865</v>
+        <v>2.02</v>
       </c>
       <c r="E55" s="8" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.0288</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>1155000</v>
+        <v>1807400</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="H55" t="n">
-        <v>45.95</v>
-      </c>
-      <c r="I55" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.29</v>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.868</v>
+        <v>2.174</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0.869</v>
+        <v>2.228</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2948,31 +2948,40 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>9776</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>RSSB</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="E56" s="10" t="n">
-        <v>0</v>
+        <v>2.69</v>
+      </c>
+      <c r="E56" s="8" t="n">
+        <v>-0.0182</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>1153800</v>
-      </c>
-      <c r="G56" s="5" t="n"/>
+        <v>1752000</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H56" t="n">
+        <v>43.52</v>
+      </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="n"/>
-      <c r="K56" s="2" t="n"/>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>2.783</v>
+      </c>
+      <c r="K56" s="2" t="n">
+        <v>2.728</v>
+      </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
     </row>
@@ -2984,28 +2993,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>0.66</v>
+        <v>1.01</v>
       </c>
       <c r="E57" s="8" t="n">
-        <v>-0.0222</v>
+        <v>-0.06480000000000001</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>1142900</v>
+        <v>1740900</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.13</v>
+        <v>0.43</v>
       </c>
       <c r="H57" t="n">
-        <v>44.67</v>
+        <v>50.15</v>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
@@ -3013,10 +3022,10 @@
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.6879999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.894</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3029,28 +3038,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="E58" s="3" t="n">
-        <v>0.0222</v>
+        <v>0.52</v>
+      </c>
+      <c r="E58" s="8" t="n">
+        <v>-0.03700000000000001</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>1126400</v>
+        <v>1662300</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.03</v>
+        <v>0.11</v>
       </c>
       <c r="H58" t="n">
-        <v>27.43</v>
+        <v>52.58</v>
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
@@ -3058,10 +3067,10 @@
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.518</v>
+        <v>0.52</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0.701</v>
+        <v>0.454</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3074,39 +3083,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>VANTNRG</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>1.15</v>
+        <v>0.3</v>
       </c>
       <c r="E59" s="8" t="n">
-        <v>-0.0574</v>
+        <v>-0.0164</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>1123400</v>
+        <v>1649100</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.29</v>
+        <v>0.52</v>
       </c>
       <c r="H59" t="n">
-        <v>80.06</v>
-      </c>
-      <c r="I59" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.9</v>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.803</v>
+        <v>0.324</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0.544</v>
+        <v>0.332</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3119,28 +3128,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>2.47</v>
+        <v>0.655</v>
       </c>
       <c r="E60" s="8" t="n">
-        <v>-0.0426</v>
+        <v>-0.0296</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>1110900</v>
+        <v>1629600</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="H60" t="n">
-        <v>40.24</v>
+        <v>43.84</v>
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
@@ -3148,10 +3157,10 @@
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>2.613</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>2.599</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
@@ -3164,39 +3173,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="E61" s="3" t="n">
-        <v>0.0066</v>
+        <v>4.83</v>
+      </c>
+      <c r="E61" s="8" t="n">
+        <v>-0.004099999999999999</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>1102000</v>
+        <v>1593400</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.34</v>
+        <v>0.06</v>
       </c>
       <c r="H61" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="I61" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.46</v>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>2.769</v>
+        <v>4.918</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>2.382</v>
+        <v>4.708</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3209,28 +3218,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>7.49</v>
+        <v>6.36</v>
       </c>
       <c r="E62" s="8" t="n">
-        <v>-0.0013</v>
+        <v>-0.0507</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>1099700</v>
+        <v>1549000</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.28</v>
       </c>
       <c r="H62" t="n">
-        <v>44.06</v>
+        <v>55.22</v>
       </c>
       <c r="I62" s="9" t="inlineStr">
         <is>
@@ -3238,10 +3247,10 @@
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>7.579</v>
+        <v>6.098</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>7.71</v>
+        <v>5.875</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
@@ -3254,28 +3263,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>0.3</v>
+        <v>0.48</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>-0.0164</v>
+        <v>-0.04</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>1088300</v>
+        <v>1524100</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="H63" t="n">
-        <v>38.46</v>
+        <v>28.41</v>
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
@@ -3283,10 +3292,10 @@
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.319</v>
+        <v>0.556</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0.338</v>
+        <v>0.626</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
@@ -3299,28 +3308,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>0.9350000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="E64" s="8" t="n">
-        <v>-0.0106</v>
+        <v>-0.0164</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>1080500</v>
+        <v>1450500</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.28</v>
+        <v>0.19</v>
       </c>
       <c r="H64" t="n">
-        <v>27.89</v>
+        <v>54.83</v>
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
@@ -3328,10 +3337,10 @@
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.979</v>
+        <v>1.169</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>1.059</v>
+        <v>1.131</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
@@ -3344,28 +3353,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>0.955</v>
-      </c>
-      <c r="E65" s="10" t="n">
-        <v>0</v>
+        <v>0.585</v>
+      </c>
+      <c r="E65" s="8" t="n">
+        <v>-0.0488</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>1043400</v>
+        <v>1434400</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.19</v>
+        <v>0.34</v>
       </c>
       <c r="H65" t="n">
-        <v>65.59</v>
+        <v>47.76</v>
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
@@ -3373,10 +3382,10 @@
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.917</v>
+        <v>0.6</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0.872</v>
+        <v>0.585</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3389,28 +3398,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>TALIWRK</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E66" s="3" t="n">
-        <v>0.0308</v>
+        <v>0.23</v>
+      </c>
+      <c r="E66" s="8" t="n">
+        <v>-0.0213</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>1038200</v>
+        <v>1424500</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.2</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H66" t="n">
-        <v>47.07</v>
+        <v>37.06</v>
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
@@ -3418,10 +3427,10 @@
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.336</v>
+        <v>0.247</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0.343</v>
+        <v>0.258</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3434,28 +3443,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>2.03</v>
+        <v>0.63</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>-0.024</v>
+        <v>-0.0156</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>1036100</v>
+        <v>1408900</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="H67" t="n">
-        <v>33.92</v>
+        <v>48.11</v>
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
@@ -3463,10 +3472,10 @@
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>2.175</v>
+        <v>0.637</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>2.228</v>
+        <v>0.619</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
@@ -3479,28 +3488,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E68" s="3" t="n">
-        <v>0.007900000000000001</v>
+        <v>7.49</v>
+      </c>
+      <c r="E68" s="8" t="n">
+        <v>-0.0013</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>1022800</v>
+        <v>1390600</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.17</v>
+        <v>0.09</v>
       </c>
       <c r="H68" t="n">
-        <v>62.46</v>
+        <v>44.06</v>
       </c>
       <c r="I68" s="9" t="inlineStr">
         <is>
@@ -3508,10 +3517,10 @@
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1.184</v>
+        <v>7.579</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>1.18</v>
+        <v>7.71</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
@@ -3524,28 +3533,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>2.77</v>
+        <v>0.76</v>
       </c>
       <c r="E69" s="8" t="n">
-        <v>-0.0246</v>
+        <v>-0.013</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>993400</v>
+        <v>1359400</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="H69" t="n">
-        <v>50.67</v>
+        <v>44.91</v>
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
@@ -3553,10 +3562,10 @@
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>2.795</v>
+        <v>0.777</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>2.647</v>
+        <v>0.773</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
@@ -3569,39 +3578,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>6.35</v>
+        <v>2.47</v>
       </c>
       <c r="E70" s="8" t="n">
-        <v>-0.0522</v>
+        <v>-0.0426</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>972800</v>
+        <v>1345800</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="H70" t="n">
-        <v>55.06</v>
-      </c>
-      <c r="I70" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.24</v>
+      </c>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>6.097</v>
+        <v>2.613</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>5.875</v>
+        <v>2.599</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
@@ -3614,28 +3623,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>3.74</v>
+        <v>0.98</v>
       </c>
       <c r="E71" s="8" t="n">
-        <v>-0.026</v>
+        <v>-0.0392</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>883400</v>
+        <v>1298500</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="H71" t="n">
-        <v>45.59</v>
+        <v>43.38</v>
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
@@ -3643,10 +3652,10 @@
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>3.86</v>
+        <v>1.049</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>3.646</v>
+        <v>0.927</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
@@ -3659,28 +3668,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>0.57</v>
+        <v>0.3</v>
       </c>
       <c r="E72" s="8" t="n">
-        <v>-0.0579</v>
+        <v>-0.0164</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>877600</v>
+        <v>1280400</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="H72" t="n">
-        <v>55.34</v>
+        <v>38.46</v>
       </c>
       <c r="I72" s="6" t="inlineStr">
         <is>
@@ -3688,10 +3697,10 @@
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.319</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0.51</v>
+        <v>0.338</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
@@ -3704,28 +3713,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>1.67</v>
+        <v>0.67</v>
       </c>
       <c r="E73" s="8" t="n">
-        <v>-0.0291</v>
+        <v>-0.036</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>862400</v>
+        <v>1273400</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="H73" t="n">
-        <v>39.48</v>
+        <v>35.17</v>
       </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
@@ -3733,10 +3742,10 @@
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1.74</v>
+        <v>0.738</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>1.771</v>
+        <v>0.746</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
@@ -3749,28 +3758,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>BPURI</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>0.975</v>
+        <v>0.215</v>
       </c>
       <c r="E74" s="8" t="n">
-        <v>-0.0441</v>
+        <v>-0.0227</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>858900</v>
+        <v>1223900</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.19</v>
+        <v>2.35</v>
       </c>
       <c r="H74" t="n">
-        <v>42.79</v>
+        <v>40.22</v>
       </c>
       <c r="I74" s="6" t="inlineStr">
         <is>
@@ -3778,10 +3787,10 @@
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>1.049</v>
+        <v>0.225</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0.926</v>
+        <v>0.233</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr"/>
@@ -3794,39 +3803,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E75" s="3" t="n">
-        <v>0.0091</v>
+        <v>1.68</v>
+      </c>
+      <c r="E75" s="8" t="n">
+        <v>-0.0233</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>842000</v>
+        <v>1213000</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="H75" t="n">
-        <v>39.65</v>
-      </c>
-      <c r="I75" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.51</v>
+      </c>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.573</v>
+        <v>1.741</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0.615</v>
+        <v>1.772</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr"/>
@@ -3839,28 +3848,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>0.76</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="E76" s="8" t="n">
-        <v>-0.013</v>
+        <v>-0.0106</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>817400</v>
+        <v>1197200</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.1</v>
+        <v>0.31</v>
       </c>
       <c r="H76" t="n">
-        <v>44.91</v>
+        <v>27.89</v>
       </c>
       <c r="I76" s="6" t="inlineStr">
         <is>
@@ -3868,10 +3877,10 @@
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.777</v>
+        <v>0.979</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0.773</v>
+        <v>1.059</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
@@ -3884,28 +3893,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>0.665</v>
-      </c>
-      <c r="E77" s="8" t="n">
-        <v>-0.0432</v>
+        <v>0.335</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>0.0308</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>792400</v>
+        <v>1189800</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="H77" t="n">
-        <v>34.5</v>
+        <v>47.07</v>
       </c>
       <c r="I77" s="6" t="inlineStr">
         <is>
@@ -3913,10 +3922,10 @@
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.738</v>
+        <v>0.336</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0.746</v>
+        <v>0.343</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
@@ -3929,39 +3938,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="E78" s="8" t="n">
-        <v>-0.0387</v>
+        <v>0.295</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>0.0351</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>791100</v>
+        <v>1183700</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.25</v>
+        <v>1.24</v>
       </c>
       <c r="H78" t="n">
-        <v>50.16</v>
-      </c>
-      <c r="I78" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.28</v>
+      </c>
+      <c r="I78" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>3.026</v>
+        <v>0.275</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>2.846</v>
+        <v>0.267</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
@@ -3974,28 +3983,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>0.74</v>
+        <v>0.785</v>
       </c>
       <c r="E79" s="8" t="n">
-        <v>-0.0513</v>
+        <v>-0.0368</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>743400</v>
+        <v>1179900</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.32</v>
+        <v>0.19</v>
       </c>
       <c r="H79" t="n">
-        <v>53.4</v>
+        <v>57.66</v>
       </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
@@ -4003,10 +4012,10 @@
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.728</v>
+        <v>0.768</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0.701</v>
+        <v>0.68</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
@@ -4019,28 +4028,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>0272</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>TTVHB</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>1.09</v>
+        <v>0.235</v>
       </c>
       <c r="E80" s="8" t="n">
-        <v>-0.0354</v>
+        <v>-0.0208</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>707200</v>
+        <v>1177000</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.3</v>
+        <v>0.49</v>
       </c>
       <c r="H80" t="n">
-        <v>34.68</v>
+        <v>44.1</v>
       </c>
       <c r="I80" s="6" t="inlineStr">
         <is>
@@ -4048,10 +4057,10 @@
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>1.232</v>
+        <v>0.248</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>1.303</v>
+        <v>0.255</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
@@ -4064,28 +4073,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>0.78</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>-0.0429</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>699400</v>
+        <v>1167000</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.11</v>
+        <v>0.22</v>
       </c>
       <c r="H81" t="n">
-        <v>56.59</v>
+        <v>54.07</v>
       </c>
       <c r="I81" s="6" t="inlineStr">
         <is>
@@ -4093,10 +4102,10 @@
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.767</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0.68</v>
+        <v>0.51</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
@@ -4109,28 +4118,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="E82" s="8" t="n">
-        <v>-0.0677</v>
+        <v>0.955</v>
+      </c>
+      <c r="E82" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>689400</v>
+        <v>1162500</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.3</v>
+        <v>0.21</v>
       </c>
       <c r="H82" t="n">
-        <v>51.76</v>
+        <v>65.59</v>
       </c>
       <c r="I82" s="6" t="inlineStr">
         <is>
@@ -4138,10 +4147,10 @@
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>1.246</v>
+        <v>0.917</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>1.167</v>
+        <v>0.872</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr"/>
@@ -4154,40 +4163,31 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>9776</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MALAKOF</t>
+          <t>RSSB</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="E83" s="8" t="n">
-        <v>-0.0066</v>
+        <v>0.325</v>
+      </c>
+      <c r="E83" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>631700</v>
-      </c>
-      <c r="G83" s="5" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="H83" t="n">
-        <v>40.15</v>
-      </c>
+        <v>1153800</v>
+      </c>
+      <c r="G83" s="5" t="n"/>
       <c r="I83" s="6" t="inlineStr">
         <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J83" s="2" t="n">
-        <v>0.783</v>
-      </c>
-      <c r="K83" s="2" t="n">
-        <v>0.803</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="n"/>
+      <c r="K83" s="2" t="n"/>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
     </row>
@@ -4199,28 +4199,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E84" s="3" t="n">
-        <v>0.007800000000000001</v>
+        <v>3.7</v>
+      </c>
+      <c r="E84" s="8" t="n">
+        <v>-0.0365</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>629200</v>
+        <v>1139600</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.06</v>
+        <v>0.4</v>
       </c>
       <c r="H84" t="n">
-        <v>46.61</v>
+        <v>43.72</v>
       </c>
       <c r="I84" s="6" t="inlineStr">
         <is>
@@ -4228,10 +4228,10 @@
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>1.31</v>
+        <v>3.856</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>1.314</v>
+        <v>3.646</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
@@ -4244,28 +4244,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E85" s="3" t="n">
-        <v>0.007900000000000001</v>
+        <v>1.18</v>
+      </c>
+      <c r="E85" s="8" t="n">
+        <v>-0.0484</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>584000</v>
+        <v>1113100</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.14</v>
+        <v>0.31</v>
       </c>
       <c r="H85" t="n">
-        <v>25.55</v>
+        <v>47.61</v>
       </c>
       <c r="I85" s="6" t="inlineStr">
         <is>
@@ -4273,10 +4273,10 @@
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.425</v>
+        <v>1.248</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>1.58</v>
+        <v>1.05</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr"/>
@@ -4289,28 +4289,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>NGGB</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="E86" s="10" t="n">
-        <v>0</v>
+        <v>2.72</v>
+      </c>
+      <c r="E86" s="8" t="n">
+        <v>-0.0251</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>567100</v>
+        <v>1102300</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.36</v>
+        <v>0.23</v>
       </c>
       <c r="H86" t="n">
-        <v>59.74</v>
+        <v>53.26</v>
       </c>
       <c r="I86" s="6" t="inlineStr">
         <is>
@@ -4318,10 +4318,10 @@
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.741</v>
+        <v>2.758</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0.718</v>
+        <v>2.156</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
@@ -4334,28 +4334,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>0.515</v>
+        <v>2.1</v>
       </c>
       <c r="E87" s="8" t="n">
-        <v>-0.0374</v>
+        <v>-0.009399999999999999</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>548400</v>
+        <v>1066900</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.14</v>
+        <v>0.05</v>
       </c>
       <c r="H87" t="n">
-        <v>58.21</v>
+        <v>49.15</v>
       </c>
       <c r="I87" s="9" t="inlineStr">
         <is>
@@ -4363,10 +4363,10 @@
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.493</v>
+        <v>2.109</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0.461</v>
+        <v>2.097</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
@@ -4379,28 +4379,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>6.33</v>
-      </c>
-      <c r="E88" s="8" t="n">
-        <v>-0.0016</v>
+        <v>0.88</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>0.0353</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>518300</v>
+        <v>1061100</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.08</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H88" t="n">
-        <v>41.19</v>
+        <v>46.12</v>
       </c>
       <c r="I88" s="6" t="inlineStr">
         <is>
@@ -4408,10 +4408,10 @@
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>6.41</v>
+        <v>0.913</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>6.789</v>
+        <v>0.865</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr"/>
@@ -4424,28 +4424,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>3.72</v>
+        <v>0.225</v>
       </c>
       <c r="E89" s="8" t="n">
-        <v>-0.0159</v>
+        <v>-0.0426</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>517000</v>
+        <v>1020600</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.05</v>
+        <v>0.21</v>
       </c>
       <c r="H89" t="n">
-        <v>55.89</v>
+        <v>41.8</v>
       </c>
       <c r="I89" s="6" t="inlineStr">
         <is>
@@ -4453,10 +4453,10 @@
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>3.623</v>
+        <v>0.247</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>2.918</v>
+        <v>0.223</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
@@ -4469,39 +4469,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0337</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>1.18</v>
+        <v>0.24</v>
       </c>
       <c r="E90" s="8" t="n">
-        <v>-0.0484</v>
+        <v>-0.04</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>510600</v>
+        <v>1010400</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.14</v>
+        <v>0.54</v>
       </c>
       <c r="H90" t="n">
-        <v>47.61</v>
-      </c>
-      <c r="I90" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.37</v>
+      </c>
+      <c r="I90" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>1.248</v>
+        <v>0.24</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>1.05</v>
+        <v>0.243</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr"/>
@@ -4514,28 +4514,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>2.75</v>
+        <v>0.74</v>
       </c>
       <c r="E91" s="8" t="n">
-        <v>-0.0385</v>
+        <v>-0.0513</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>509000</v>
+        <v>1008200</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.16</v>
+        <v>0.44</v>
       </c>
       <c r="H91" t="n">
-        <v>36.96</v>
+        <v>53.4</v>
       </c>
       <c r="I91" s="6" t="inlineStr">
         <is>
@@ -4543,16 +4543,1411 @@
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>2.922</v>
+        <v>0.728</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>3.023</v>
+        <v>0.701</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr"/>
     </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>7233</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>DUFU</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="E92" s="8" t="n">
+        <v>-0.0484</v>
+      </c>
+      <c r="F92" s="4" t="n">
+        <v>991700</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H92" t="n">
+        <v>48.85</v>
+      </c>
+      <c r="I92" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>3.023</v>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>2.846</v>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" s="7" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>5199</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>HIBISCS</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="E93" s="8" t="n">
+        <v>-0.013</v>
+      </c>
+      <c r="F93" s="4" t="n">
+        <v>985400</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H93" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="I93" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>2.208</v>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>2.152</v>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" s="7" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>0240</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>CORAZA</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="E94" s="8" t="n">
+        <v>-0.07519999999999999</v>
+      </c>
+      <c r="F94" s="4" t="n">
+        <v>980300</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H94" t="n">
+        <v>50.82</v>
+      </c>
+      <c r="I94" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>1.246</v>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>1.166</v>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" s="7" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>AMBANK</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="E95" s="8" t="n">
+        <v>-0.0016</v>
+      </c>
+      <c r="F95" s="4" t="n">
+        <v>964100</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H95" t="n">
+        <v>41.19</v>
+      </c>
+      <c r="I95" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="K95" s="2" t="n">
+        <v>6.789</v>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" s="7" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>0321</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>SDCG</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="E96" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" s="4" t="n">
+        <v>960100</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H96" t="n">
+        <v>66.89</v>
+      </c>
+      <c r="I96" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="K96" s="2" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" s="7" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>0376</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>IAB</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E97" s="8" t="n">
+        <v>-0.0442</v>
+      </c>
+      <c r="F97" s="4" t="n">
+        <v>934700</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H97" t="n">
+        <v>34.06</v>
+      </c>
+      <c r="I97" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>1.231</v>
+      </c>
+      <c r="K97" s="2" t="n">
+        <v>1.303</v>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" s="7" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>4715</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>GENM</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="F98" s="4" t="n">
+        <v>925100</v>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H98" t="n">
+        <v>25.55</v>
+      </c>
+      <c r="I98" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>1.425</v>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" s="7" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>RHBBANK</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="E99" s="8" t="n">
+        <v>-0.008199999999999999</v>
+      </c>
+      <c r="F99" s="4" t="n">
+        <v>922200</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H99" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="I99" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>7.497</v>
+      </c>
+      <c r="K99" s="2" t="n">
+        <v>8.002000000000001</v>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" s="7" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>4324</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>HENGYUAN</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="E100" s="8" t="n">
+        <v>-0.0291</v>
+      </c>
+      <c r="F100" s="4" t="n">
+        <v>914600</v>
+      </c>
+      <c r="G100" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H100" t="n">
+        <v>54.51</v>
+      </c>
+      <c r="I100" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>3.618</v>
+      </c>
+      <c r="K100" s="2" t="n">
+        <v>2.917</v>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" s="7" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>5264</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>MALAKOF</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E101" s="8" t="n">
+        <v>-0.0132</v>
+      </c>
+      <c r="F101" s="4" t="n">
+        <v>881500</v>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H101" t="n">
+        <v>39.04</v>
+      </c>
+      <c r="I101" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>0.783</v>
+      </c>
+      <c r="K101" s="2" t="n">
+        <v>0.803</v>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" s="7" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>5292</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>UWC</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="E102" s="8" t="n">
+        <v>-0.0556</v>
+      </c>
+      <c r="F102" s="4" t="n">
+        <v>843400</v>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H102" t="n">
+        <v>51.38</v>
+      </c>
+      <c r="I102" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="n">
+        <v>7.374</v>
+      </c>
+      <c r="K102" s="2" t="n">
+        <v>6.867</v>
+      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" s="7" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>0271</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>WELLS</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>0.0091</v>
+      </c>
+      <c r="F103" s="4" t="n">
+        <v>842000</v>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H103" t="n">
+        <v>39.65</v>
+      </c>
+      <c r="I103" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="K103" s="2" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" s="7" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>0239</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>ECOMATE</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="E104" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" s="4" t="n">
+        <v>774000</v>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H104" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="I104" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="K104" s="2" t="n">
+        <v>0.859</v>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" s="7" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>5357</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>SKYECHIP</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E105" s="8" t="n">
+        <v>-0.0385</v>
+      </c>
+      <c r="F105" s="4" t="n">
+        <v>741100</v>
+      </c>
+      <c r="G105" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H105" t="n">
+        <v>36.96</v>
+      </c>
+      <c r="I105" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>2.922</v>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>3.023</v>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" s="7" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>5317</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>CPETECH</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="E106" s="8" t="n">
+        <v>-0.0472</v>
+      </c>
+      <c r="F106" s="4" t="n">
+        <v>739300</v>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H106" t="n">
+        <v>44.54</v>
+      </c>
+      <c r="I106" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="n">
+        <v>1.285</v>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>1.217</v>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" s="7" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>5248</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>BAUTO</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="E107" s="8" t="n">
+        <v>-0.005600000000000001</v>
+      </c>
+      <c r="F107" s="4" t="n">
+        <v>722700</v>
+      </c>
+      <c r="G107" s="5" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H107" t="n">
+        <v>37.09</v>
+      </c>
+      <c r="I107" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="n">
+        <v>0.914</v>
+      </c>
+      <c r="K107" s="2" t="n">
+        <v>0.931</v>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" s="7" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>0391</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>AMBEST</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="E108" s="8" t="n">
+        <v>-0.0294</v>
+      </c>
+      <c r="F108" s="4" t="n">
+        <v>681600</v>
+      </c>
+      <c r="G108" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H108" t="n">
+        <v>48.94</v>
+      </c>
+      <c r="I108" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="n">
+        <v>1.341</v>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>1.274</v>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" s="7" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>0120</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>VIS</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E109" s="8" t="n">
+        <v>-0.0458</v>
+      </c>
+      <c r="F109" s="4" t="n">
+        <v>678700</v>
+      </c>
+      <c r="G109" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H109" t="n">
+        <v>62.58</v>
+      </c>
+      <c r="I109" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="K109" s="2" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" s="7" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>5184</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>CYPARK</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="E110" s="8" t="n">
+        <v>-0.0274</v>
+      </c>
+      <c r="F110" s="4" t="n">
+        <v>650200</v>
+      </c>
+      <c r="G110" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H110" t="n">
+        <v>43.13</v>
+      </c>
+      <c r="I110" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="n">
+        <v>0.764</v>
+      </c>
+      <c r="K110" s="2" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" s="7" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>0368</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>OXB</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E111" s="8" t="n">
+        <v>-0.028</v>
+      </c>
+      <c r="F111" s="4" t="n">
+        <v>642600</v>
+      </c>
+      <c r="G111" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H111" t="n">
+        <v>59.64</v>
+      </c>
+      <c r="I111" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="n">
+        <v>0.494</v>
+      </c>
+      <c r="K111" s="2" t="n">
+        <v>0.461</v>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" s="7" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>0375</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>THMY</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E112" s="8" t="n">
+        <v>-0.0566</v>
+      </c>
+      <c r="F112" s="4" t="n">
+        <v>630900</v>
+      </c>
+      <c r="G112" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H112" t="n">
+        <v>45.65</v>
+      </c>
+      <c r="I112" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="n">
+        <v>2.107</v>
+      </c>
+      <c r="K112" s="2" t="n">
+        <v>1.983</v>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" s="7" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>0215</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>SLVEST</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="E113" s="8" t="n">
+        <v>-0.0207</v>
+      </c>
+      <c r="F113" s="4" t="n">
+        <v>589400</v>
+      </c>
+      <c r="G113" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H113" t="n">
+        <v>46.67</v>
+      </c>
+      <c r="I113" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="n">
+        <v>3.969</v>
+      </c>
+      <c r="K113" s="2" t="n">
+        <v>3.522</v>
+      </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" s="7" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>0097</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>VITROX</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>10.16</v>
+      </c>
+      <c r="E114" s="8" t="n">
+        <v>-0.0451</v>
+      </c>
+      <c r="F114" s="4" t="n">
+        <v>577700</v>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H114" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="I114" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>10.372</v>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>9.689</v>
+      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" s="7" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>4197</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>SIME</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="E115" s="8" t="n">
+        <v>-0.0122</v>
+      </c>
+      <c r="F115" s="4" t="n">
+        <v>573700</v>
+      </c>
+      <c r="G115" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H115" t="n">
+        <v>47.92</v>
+      </c>
+      <c r="I115" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>2.458</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>2.374</v>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" s="7" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>7241</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>NGGB</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="E116" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="4" t="n">
+        <v>567100</v>
+      </c>
+      <c r="G116" s="5" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H116" t="n">
+        <v>59.74</v>
+      </c>
+      <c r="I116" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>0.718</v>
+      </c>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" s="7" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>5347</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>TENAGA</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>12.98</v>
+      </c>
+      <c r="E117" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="4" t="n">
+        <v>565900</v>
+      </c>
+      <c r="G117" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H117" t="n">
+        <v>44.06</v>
+      </c>
+      <c r="I117" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>13.021</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>13.468</v>
+      </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" s="7" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>7277</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>DIALOG</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="E118" s="8" t="n">
+        <v>-0.0104</v>
+      </c>
+      <c r="F118" s="4" t="n">
+        <v>559800</v>
+      </c>
+      <c r="G118" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H118" t="n">
+        <v>45.87</v>
+      </c>
+      <c r="I118" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="n">
+        <v>1.924</v>
+      </c>
+      <c r="K118" s="2" t="n">
+        <v>1.952</v>
+      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" s="7" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>5183</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>PCHEM</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="E119" s="8" t="n">
+        <v>-0.0248</v>
+      </c>
+      <c r="F119" s="4" t="n">
+        <v>525700</v>
+      </c>
+      <c r="G119" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H119" t="n">
+        <v>47.32</v>
+      </c>
+      <c r="I119" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="K119" s="2" t="n">
+        <v>4.438</v>
+      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" s="7" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>0291</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>CHB</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="E120" s="8" t="n">
+        <v>-0.0498</v>
+      </c>
+      <c r="F120" s="4" t="n">
+        <v>518300</v>
+      </c>
+      <c r="G120" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H120" t="n">
+        <v>51.32</v>
+      </c>
+      <c r="I120" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="n">
+        <v>2.526</v>
+      </c>
+      <c r="K120" s="2" t="n">
+        <v>2.223</v>
+      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" s="7" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>0338</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>KOPI</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="E121" s="8" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="F121" s="4" t="n">
+        <v>514100</v>
+      </c>
+      <c r="G121" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H121" t="n">
+        <v>41.27</v>
+      </c>
+      <c r="I121" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="K121" s="2" t="n">
+        <v>0.958</v>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" s="7" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>5356</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>STRATUS</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="E122" s="8" t="n">
+        <v>-0.0333</v>
+      </c>
+      <c r="F122" s="4" t="n">
+        <v>508000</v>
+      </c>
+      <c r="G122" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H122" t="n">
+        <v>35.52</v>
+      </c>
+      <c r="I122" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="n">
+        <v>2.878</v>
+      </c>
+      <c r="K122" s="2" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M91"/>
+  <autoFilter ref="A1:M122"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-15/bursa-report-2026-10-15.xlsx
+++ b/docs/downloads/2026-10-15/bursa-report-2026-10-15.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-15" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-15'!$A$1:$M$122</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-15'!$A$1:$M$142</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M122"/>
+  <dimension ref="A1:M142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -552,19 +552,19 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.06</v>
+        <v>0.065</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.1818</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>36768000</v>
+        <v>76581100</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.08</v>
+        <v>0.18</v>
       </c>
       <c r="H2" t="n">
-        <v>22.58</v>
+        <v>24.2</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.138</v>
+        <v>0.139</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0.347</v>
@@ -597,19 +597,19 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.895</v>
+        <v>0.9</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>-0.0165</v>
+        <v>-0.011</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>26739300</v>
+        <v>29887700</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="H3" t="n">
-        <v>65.34999999999999</v>
+        <v>66.28</v>
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.825</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.0312</v>
+        <v>0.0125</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>19022100</v>
+        <v>21032200</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I4" s="9" t="inlineStr">
         <is>
@@ -671,39 +671,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>-0.0426</v>
+        <v>0.425</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0.0241</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>16931500</v>
+        <v>20716600</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.48</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>39.27</v>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>77.33</v>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.486</v>
+        <v>0.374</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.482</v>
+        <v>0.263</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
@@ -731,10 +731,10 @@
         <v>-0.0147</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>15180100</v>
+        <v>19414800</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.21</v>
+        <v>0.26</v>
       </c>
       <c r="H6" t="n">
         <v>68.7</v>
@@ -761,28 +761,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>0.0241</v>
+        <v>0.665</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>13290200</v>
+        <v>17835200</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.36</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>77.33</v>
+        <v>76.18000000000001</v>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.374</v>
+        <v>0.603</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.263</v>
+        <v>0.521</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
@@ -806,39 +806,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.665</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>0</v>
+        <v>0.45</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>-0.0426</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>12961000</v>
+        <v>17097000</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="H8" t="n">
-        <v>76.18000000000001</v>
-      </c>
-      <c r="I8" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.27</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.603</v>
+        <v>0.486</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.521</v>
+        <v>0.482</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
@@ -851,28 +851,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0096</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NEXGRAM</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>0</v>
+        <v>1.99</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>-0.0386</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>11717300</v>
+        <v>12901900</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>6.85</v>
+        <v>0.43</v>
       </c>
       <c r="H9" t="n">
-        <v>69.25</v>
+        <v>57.79</v>
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
@@ -880,10 +880,10 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.044</v>
+        <v>1.908</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.047</v>
+        <v>1.712</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
@@ -896,31 +896,40 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0041</t>
+          <t>0096</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AIMAX</t>
+          <t>NEXGRAM</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.005</v>
+        <v>0.055</v>
       </c>
       <c r="E10" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>10997900</v>
-      </c>
-      <c r="G10" s="5" t="n"/>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n"/>
-      <c r="K10" s="2" t="n"/>
+        <v>12462100</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="H10" t="n">
+        <v>69.25</v>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>0.047</v>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="7" t="inlineStr"/>
     </row>
@@ -947,10 +956,10 @@
         <v>-0.0189</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>10085300</v>
+        <v>12247700</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="H11" t="n">
         <v>26.18</v>
@@ -977,40 +986,33 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1643</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LANDMRK</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>0.3333</v>
+        <v>0.25</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>-0.0196</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>8708000</v>
+        <v>12158800</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>6.96</v>
-      </c>
-      <c r="H12" t="n">
-        <v>37.75</v>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="K12" s="2" t="n">
-        <v>0.064</v>
-      </c>
+        <v>0.45</v>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="2" t="n"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
     </row>
@@ -1022,40 +1024,31 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>0041</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>AIMAX</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>-0.0338</v>
+        <v>0.005</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>8629300</v>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="H13" t="n">
-        <v>58.43</v>
-      </c>
-      <c r="I13" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="n">
-        <v>1.909</v>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>1.713</v>
-      </c>
+        <v>11712900</v>
+      </c>
+      <c r="G13" s="5" t="n"/>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n"/>
+      <c r="K13" s="2" t="n"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
     </row>
@@ -1067,28 +1060,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>7036</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>BORNOIL</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.39</v>
+        <v>0.005</v>
       </c>
       <c r="E14" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>8292200</v>
+        <v>10500000</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.76</v>
+        <v>16.58</v>
       </c>
       <c r="H14" t="n">
-        <v>33.83</v>
+        <v>48.15</v>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
@@ -1096,10 +1089,10 @@
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.398</v>
+        <v>0.005</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0.408</v>
+        <v>0.005</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="7" t="inlineStr"/>
@@ -1112,33 +1105,40 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>1643</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>LANDMRK</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E15" s="8" t="n">
-        <v>-0.0196</v>
+        <v>0.045</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0.5</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>7662600</v>
+        <v>10387200</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="n"/>
-      <c r="K15" s="2" t="n"/>
+        <v>8.300000000000001</v>
+      </c>
+      <c r="H15" t="n">
+        <v>43.11</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>0.064</v>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
     </row>
@@ -1150,39 +1150,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0117</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SMRT</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>0.0625</v>
+        <v>0.31</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>-0.0313</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>7650600</v>
+        <v>9177600</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>2.37</v>
+        <v>1.23</v>
       </c>
       <c r="H16" t="n">
-        <v>41.24</v>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.95</v>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.179</v>
+        <v>0.3</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.192</v>
+        <v>0.279</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
@@ -1195,39 +1195,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.315</v>
-      </c>
-      <c r="E17" s="8" t="n">
-        <v>-0.0156</v>
+        <v>0.39</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>6625500</v>
+        <v>8358200</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.89</v>
+        <v>0.77</v>
       </c>
       <c r="H17" t="n">
-        <v>63.92</v>
-      </c>
-      <c r="I17" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.83</v>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.301</v>
+        <v>0.398</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.279</v>
+        <v>0.408</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
@@ -1240,39 +1240,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E18" s="8" t="n">
-        <v>-0.0217</v>
+        <v>1.43</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>0.006999999999999999</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>5991000</v>
+        <v>7824800</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.29</v>
+        <v>0.76</v>
       </c>
       <c r="H18" t="n">
-        <v>60.9</v>
-      </c>
-      <c r="I18" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>20.13</v>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.42</v>
+        <v>1.746</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.361</v>
+        <v>1.971</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
@@ -1285,39 +1285,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0237</t>
+          <t>0117</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>HAILY</t>
+          <t>SMRT</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>0.0857</v>
+        <v>0.0625</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>5591500</v>
+        <v>7699400</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>22.21</v>
+        <v>2.38</v>
       </c>
       <c r="H19" t="n">
-        <v>70.90000000000001</v>
-      </c>
-      <c r="I19" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.24</v>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.167</v>
+        <v>0.179</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0.166</v>
+        <v>0.192</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
@@ -1330,39 +1330,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.55</v>
+        <v>0.445</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>-0.0435</v>
+        <v>-0.0326</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>5368200</v>
+        <v>6826800</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="H20" t="n">
-        <v>46.48</v>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.44</v>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.579</v>
+        <v>0.42</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.536</v>
+        <v>0.361</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
@@ -1375,39 +1375,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="E21" s="8" t="n">
-        <v>-0.0409</v>
+        <v>0.23</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0.0698</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>5289400</v>
+        <v>6633400</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="H21" t="n">
-        <v>47.09</v>
-      </c>
-      <c r="I21" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.85</v>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>2.65</v>
+        <v>0.24</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>2.541</v>
+        <v>0.292</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
@@ -1420,28 +1420,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0237</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>HAILY</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E22" s="10" t="n">
-        <v>0</v>
+        <v>0.185</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0.0571</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>5132800</v>
+        <v>6554900</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.32</v>
+        <v>26.04</v>
       </c>
       <c r="H22" t="n">
-        <v>58.28</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.166</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.166</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
@@ -1465,39 +1465,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>0.006999999999999999</v>
+        <v>1.26</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>4941200</v>
+        <v>6509600</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.48</v>
+        <v>1.1</v>
       </c>
       <c r="H23" t="n">
-        <v>20.13</v>
-      </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.5</v>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.746</v>
+        <v>1.183</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>1.971</v>
+        <v>1.18</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
@@ -1510,39 +1510,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="E24" s="8" t="n">
-        <v>-0.0417</v>
+        <v>0.82</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>4806500</v>
+        <v>6507800</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.55</v>
+        <v>0.4</v>
       </c>
       <c r="H24" t="n">
-        <v>50.66</v>
-      </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.28</v>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.349</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.331</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
@@ -1555,28 +1555,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>0.0159</v>
+        <v>2.58</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>-0.0409</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>4736800</v>
+        <v>6415000</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.8</v>
+        <v>0.35</v>
       </c>
       <c r="H25" t="n">
-        <v>63.38</v>
+        <v>47.09</v>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
@@ -1584,10 +1584,10 @@
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.185</v>
+        <v>2.65</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>1.181</v>
+        <v>2.541</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
@@ -1600,39 +1600,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.615</v>
+        <v>0.31</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>-0.0611</v>
+        <v>-0.0159</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>4390600</v>
+        <v>6125800</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.49</v>
+        <v>0.32</v>
       </c>
       <c r="H26" t="n">
-        <v>42.21</v>
-      </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.53</v>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.664</v>
+        <v>0.308</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.619</v>
+        <v>0.298</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
@@ -1645,39 +1645,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.775</v>
+        <v>0.545</v>
       </c>
       <c r="E27" s="8" t="n">
-        <v>-0.0064</v>
+        <v>-0.0522</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>4176100</v>
+        <v>6124200</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="H27" t="n">
-        <v>50.18</v>
-      </c>
-      <c r="I27" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.65</v>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.775</v>
+        <v>0.579</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.776</v>
+        <v>0.536</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
@@ -1690,39 +1690,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E28" s="10" t="n">
-        <v>0</v>
+        <v>0.615</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>-0.0611</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>3748200</v>
+        <v>5655100</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.34</v>
+        <v>0.64</v>
       </c>
       <c r="H28" t="n">
-        <v>56.82</v>
-      </c>
-      <c r="I28" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.21</v>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.615</v>
+        <v>0.664</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0.614</v>
+        <v>0.619</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
@@ -1735,28 +1735,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>0.0132</v>
+        <v>0.625</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>3610400</v>
+        <v>5555400</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="H29" t="n">
-        <v>65.54000000000001</v>
+        <v>56.82</v>
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
@@ -1764,10 +1764,10 @@
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.371</v>
+        <v>0.615</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.369</v>
+        <v>0.614</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1780,28 +1780,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.515</v>
+        <v>0.345</v>
       </c>
       <c r="E30" s="8" t="n">
-        <v>-0.08039999999999999</v>
+        <v>-0.0417</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>3206900</v>
+        <v>5332400</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.79</v>
+        <v>0.61</v>
       </c>
       <c r="H30" t="n">
-        <v>32.06</v>
+        <v>50.66</v>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.596</v>
+        <v>0.349</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.603</v>
+        <v>0.331</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1825,39 +1825,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>1</v>
+        <v>0.775</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>-0.0291</v>
+        <v>-0.0064</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3205500</v>
+        <v>4982200</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="H31" t="n">
-        <v>43.73</v>
-      </c>
-      <c r="I31" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.18</v>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.062</v>
+        <v>0.775</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.947</v>
+        <v>0.776</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1879,19 +1879,19 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>-0.0179</v>
+        <v>-0.0357</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3099300</v>
+        <v>4579800</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.31</v>
+        <v>0.45</v>
       </c>
       <c r="H32" t="n">
-        <v>54.37</v>
+        <v>51.54</v>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.075</v>
+        <v>1.073</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>1.043</v>
+        <v>1.042</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
@@ -1915,39 +1915,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.415</v>
+        <v>1</v>
       </c>
       <c r="E33" s="8" t="n">
-        <v>-0.0235</v>
+        <v>-0.0291</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>2749900</v>
+        <v>3868200</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.26</v>
+        <v>0.46</v>
       </c>
       <c r="H33" t="n">
-        <v>42.82</v>
-      </c>
-      <c r="I33" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.73</v>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.443</v>
+        <v>1.062</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.432</v>
+        <v>0.947</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1960,39 +1960,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E34" s="8" t="n">
-        <v>-0.007800000000000001</v>
+        <v>0.38</v>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>2744800</v>
+        <v>3852500</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.28</v>
+        <v>0.53</v>
       </c>
       <c r="H34" t="n">
-        <v>43.81</v>
-      </c>
-      <c r="I34" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.88</v>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.308</v>
+        <v>0.371</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>1.313</v>
+        <v>0.369</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2005,28 +2005,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.26</v>
+        <v>0.295</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>-0.0545</v>
+        <v>-0.0484</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>2713100</v>
+        <v>3830500</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.32</v>
+        <v>0.76</v>
       </c>
       <c r="H35" t="n">
-        <v>41</v>
+        <v>21.54</v>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
@@ -2034,10 +2034,10 @@
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.276</v>
+        <v>0.345</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.298</v>
+        <v>0.377</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2050,39 +2050,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.405</v>
+        <v>0.865</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>-0.0122</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>2557200</v>
+        <v>3669600</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>1.37</v>
+        <v>0.19</v>
       </c>
       <c r="H36" t="n">
-        <v>36.17</v>
-      </c>
-      <c r="I36" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.95</v>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.417</v>
+        <v>0.868</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0.436</v>
+        <v>0.869</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
@@ -2095,39 +2095,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.445</v>
+        <v>0.52</v>
       </c>
       <c r="E37" s="8" t="n">
-        <v>-0.0326</v>
+        <v>-0.07139999999999999</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>2440300</v>
+        <v>3401500</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.47</v>
+        <v>0.84</v>
       </c>
       <c r="H37" t="n">
-        <v>63.86</v>
-      </c>
-      <c r="I37" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.71</v>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.384</v>
+        <v>0.597</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0.357</v>
+        <v>0.603</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2140,38 +2140,40 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>0.0141</v>
+        <v>5.3</v>
+      </c>
+      <c r="E38" s="8" t="n">
+        <v>-0.0328</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>2349100</v>
+        <v>3357200</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="H38" t="n">
-        <v>66.45</v>
-      </c>
-      <c r="I38" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.55</v>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.312</v>
-      </c>
-      <c r="K38" s="2" t="n"/>
+        <v>5.577</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>5.412</v>
+      </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
     </row>
@@ -2183,28 +2185,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>1.16</v>
+        <v>0.415</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>-0.0252</v>
+        <v>-0.0235</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>2316700</v>
+        <v>3205400</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.57</v>
+        <v>0.3</v>
       </c>
       <c r="H39" t="n">
-        <v>52.79</v>
+        <v>42.82</v>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
@@ -2212,10 +2214,10 @@
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.163</v>
+        <v>0.443</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>1.091</v>
+        <v>0.432</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2228,39 +2230,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>0.215</v>
+        <v>4.75</v>
       </c>
       <c r="E40" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>2287400</v>
+        <v>3122900</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.09</v>
+        <v>0.18</v>
       </c>
       <c r="H40" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="I40" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.45</v>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.238</v>
+        <v>4.721</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0.292</v>
+        <v>4.863</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2273,39 +2275,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="E41" s="8" t="n">
-        <v>-0.0574</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>2286300</v>
+        <v>3062500</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.59</v>
+        <v>0.32</v>
       </c>
       <c r="H41" t="n">
-        <v>80.06</v>
-      </c>
-      <c r="I41" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.81</v>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.803</v>
+        <v>1.308</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0.544</v>
+        <v>1.313</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2318,28 +2320,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>0.31</v>
+        <v>0.44</v>
       </c>
       <c r="E42" s="8" t="n">
-        <v>-0.0159</v>
+        <v>-0.0435</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>2267400</v>
+        <v>2954500</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.12</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H42" t="n">
-        <v>54.53</v>
+        <v>62.7</v>
       </c>
       <c r="I42" s="9" t="inlineStr">
         <is>
@@ -2347,10 +2349,10 @@
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.308</v>
+        <v>0.384</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0.298</v>
+        <v>0.357</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2363,28 +2365,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>0.87</v>
+        <v>2.75</v>
       </c>
       <c r="E43" s="8" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.0317</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>2182200</v>
+        <v>2944200</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.26</v>
+        <v>0.33</v>
       </c>
       <c r="H43" t="n">
-        <v>41.5</v>
+        <v>49.36</v>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
@@ -2392,10 +2394,10 @@
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.794</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0.84</v>
+        <v>2.646</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2408,28 +2410,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>5.32</v>
+        <v>0.27</v>
       </c>
       <c r="E44" s="8" t="n">
-        <v>-0.0292</v>
+        <v>-0.0182</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>2052200</v>
+        <v>2824300</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.15</v>
+        <v>0.34</v>
       </c>
       <c r="H44" t="n">
-        <v>40.17</v>
+        <v>45.07</v>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
@@ -2437,10 +2439,10 @@
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>5.579</v>
+        <v>0.277</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>5.412</v>
+        <v>0.298</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2453,39 +2455,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>0.6850000000000001</v>
-      </c>
-      <c r="E45" s="8" t="n">
-        <v>-0.0072</v>
+        <v>0.465</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>0.0333</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>2027100</v>
+        <v>2813100</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.85</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H45" t="n">
-        <v>64.88</v>
-      </c>
-      <c r="I45" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.99</v>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.641</v>
+        <v>0.519</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.547</v>
+        <v>0.701</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2498,40 +2500,38 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="E46" s="8" t="n">
-        <v>-0.0352</v>
+        <v>0.355</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>2023100</v>
+        <v>2646800</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="H46" t="n">
-        <v>48.73</v>
-      </c>
-      <c r="I46" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.3</v>
+      </c>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>2.793</v>
-      </c>
-      <c r="K46" s="2" t="n">
-        <v>2.646</v>
-      </c>
+        <v>0.311</v>
+      </c>
+      <c r="K46" s="2" t="n"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
     </row>
@@ -2543,39 +2543,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="E47" s="3" t="n">
-        <v>0.0066</v>
+        <v>0.405</v>
+      </c>
+      <c r="E47" s="8" t="n">
+        <v>-0.0122</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>1949900</v>
+        <v>2587200</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.6</v>
+        <v>1.39</v>
       </c>
       <c r="H47" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="I47" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.17</v>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>2.769</v>
+        <v>0.417</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>2.382</v>
+        <v>0.436</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2588,28 +2588,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>0.79</v>
+        <v>2.71</v>
       </c>
       <c r="E48" s="8" t="n">
-        <v>-0.0186</v>
+        <v>-0.0109</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>1938200</v>
+        <v>2550700</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.52</v>
+        <v>0.19</v>
       </c>
       <c r="H48" t="n">
-        <v>45.85</v>
+        <v>44.88</v>
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.822</v>
+        <v>2.785</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0.773</v>
+        <v>2.728</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2633,28 +2633,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="E49" s="8" t="n">
-        <v>-0.0202</v>
+        <v>0.875</v>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>1925200</v>
+        <v>2516100</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="H49" t="n">
-        <v>39.31</v>
+        <v>42.13</v>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
@@ -2662,10 +2662,10 @@
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.514</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0.527</v>
+        <v>0.84</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
@@ -2678,39 +2678,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E50" s="8" t="n">
-        <v>-0.0353</v>
+        <v>3.07</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>0.0066</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>1904800</v>
+        <v>2494600</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.28</v>
+        <v>0.77</v>
       </c>
       <c r="H50" t="n">
-        <v>46.73</v>
-      </c>
-      <c r="I50" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>81.5</v>
+      </c>
+      <c r="I50" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.425</v>
+        <v>2.769</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0.416</v>
+        <v>2.382</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2723,39 +2723,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="E51" s="8" t="n">
-        <v>-0.0042</v>
+        <v>4.86</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>0.0021</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>1895500</v>
+        <v>2365500</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="H51" t="n">
-        <v>48.54</v>
-      </c>
-      <c r="I51" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.97</v>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>4.719</v>
+        <v>4.921</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>4.863</v>
+        <v>4.709</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2768,39 +2768,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>0.865</v>
+        <v>1.16</v>
       </c>
       <c r="E52" s="8" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.0252</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>1893700</v>
+        <v>2359700</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.1</v>
+        <v>0.58</v>
       </c>
       <c r="H52" t="n">
-        <v>45.95</v>
-      </c>
-      <c r="I52" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.79</v>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.868</v>
+        <v>1.163</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0.869</v>
+        <v>1.091</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2813,39 +2813,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>0.73</v>
+        <v>1.16</v>
       </c>
       <c r="E53" s="8" t="n">
-        <v>-0.0395</v>
+        <v>-0.0492</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>1872200</v>
+        <v>2325200</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.27</v>
+        <v>0.6</v>
       </c>
       <c r="H53" t="n">
-        <v>50.68</v>
-      </c>
-      <c r="I53" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>81.16</v>
+      </c>
+      <c r="I53" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.743</v>
+        <v>0.804</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0.669</v>
+        <v>0.544</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2858,39 +2858,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="E54" s="3" t="n">
-        <v>0.0111</v>
+        <v>6.5</v>
+      </c>
+      <c r="E54" s="8" t="n">
+        <v>-0.0299</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>1854800</v>
+        <v>2265300</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.05</v>
+        <v>0.41</v>
       </c>
       <c r="H54" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="I54" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.47</v>
+      </c>
+      <c r="I54" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.518</v>
+        <v>6.111</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0.701</v>
+        <v>5.878</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2903,28 +2903,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>2.02</v>
+        <v>0.79</v>
       </c>
       <c r="E55" s="8" t="n">
-        <v>-0.0288</v>
+        <v>-0.0186</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>1807400</v>
+        <v>2221200</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.12</v>
+        <v>0.6</v>
       </c>
       <c r="H55" t="n">
-        <v>33.29</v>
+        <v>45.85</v>
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>2.174</v>
+        <v>0.822</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>2.228</v>
+        <v>0.773</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2948,28 +2948,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>2.69</v>
+        <v>2.03</v>
       </c>
       <c r="E56" s="8" t="n">
-        <v>-0.0182</v>
+        <v>-0.024</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>1752000</v>
+        <v>2155500</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="H56" t="n">
-        <v>43.52</v>
+        <v>33.92</v>
       </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>2.783</v>
+        <v>2.175</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>2.728</v>
+        <v>2.228</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -2993,39 +2993,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="E57" s="8" t="n">
-        <v>-0.06480000000000001</v>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E57" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>1740900</v>
+        <v>2089500</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.43</v>
+        <v>0.88</v>
       </c>
       <c r="H57" t="n">
-        <v>50.15</v>
-      </c>
-      <c r="I57" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.36</v>
+      </c>
+      <c r="I57" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>1.04</v>
+        <v>0.642</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0.894</v>
+        <v>0.548</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3038,28 +3038,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>0.52</v>
+        <v>0.735</v>
       </c>
       <c r="E58" s="8" t="n">
-        <v>-0.03700000000000001</v>
+        <v>-0.0329</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>1662300</v>
+        <v>2072000</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.11</v>
+        <v>0.3</v>
       </c>
       <c r="H58" t="n">
-        <v>52.58</v>
+        <v>51.56</v>
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.52</v>
+        <v>0.743</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0.454</v>
+        <v>0.669</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3083,28 +3083,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5218</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>VANTNRG</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>0.3</v>
+        <v>1.02</v>
       </c>
       <c r="E59" s="8" t="n">
-        <v>-0.0164</v>
+        <v>-0.0556</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>1649100</v>
+        <v>2016500</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="H59" t="n">
-        <v>28.9</v>
+        <v>51.06</v>
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
@@ -3112,10 +3112,10 @@
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.324</v>
+        <v>1.041</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0.332</v>
+        <v>0.895</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3128,39 +3128,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="E60" s="8" t="n">
-        <v>-0.0296</v>
+        <v>7.52</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>0.0027</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>1629600</v>
+        <v>1990500</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.18</v>
+        <v>0.13</v>
       </c>
       <c r="H60" t="n">
-        <v>43.84</v>
-      </c>
-      <c r="I60" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.48</v>
+      </c>
+      <c r="I60" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.6879999999999999</v>
+        <v>7.582</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0.6879999999999999</v>
+        <v>7.711</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
@@ -3173,28 +3173,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>4.83</v>
+        <v>0.41</v>
       </c>
       <c r="E61" s="8" t="n">
-        <v>-0.004099999999999999</v>
+        <v>-0.0353</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>1593400</v>
+        <v>1972800</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.06</v>
+        <v>0.29</v>
       </c>
       <c r="H61" t="n">
-        <v>47.46</v>
+        <v>46.73</v>
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>4.918</v>
+        <v>0.425</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>4.708</v>
+        <v>0.416</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3218,39 +3218,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>6.36</v>
+        <v>0.485</v>
       </c>
       <c r="E62" s="8" t="n">
-        <v>-0.0507</v>
+        <v>-0.0202</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>1549000</v>
+        <v>1950400</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.28</v>
+        <v>0.23</v>
       </c>
       <c r="H62" t="n">
-        <v>55.22</v>
-      </c>
-      <c r="I62" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.31</v>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>6.098</v>
+        <v>0.514</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>5.875</v>
+        <v>0.527</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
@@ -3263,28 +3263,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>0.48</v>
+        <v>0.57</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>-0.04</v>
+        <v>-0.0579</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>1524100</v>
+        <v>1897400</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.2</v>
+        <v>0.37</v>
       </c>
       <c r="H63" t="n">
-        <v>28.41</v>
+        <v>55.34</v>
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
@@ -3292,10 +3292,10 @@
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.556</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0.626</v>
+        <v>0.51</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
@@ -3308,28 +3308,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>1.2</v>
+        <v>0.585</v>
       </c>
       <c r="E64" s="8" t="n">
-        <v>-0.0164</v>
+        <v>-0.0488</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>1450500</v>
+        <v>1845200</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.19</v>
+        <v>0.43</v>
       </c>
       <c r="H64" t="n">
-        <v>54.83</v>
+        <v>47.76</v>
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.169</v>
+        <v>0.6</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>1.131</v>
+        <v>0.585</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
@@ -3353,28 +3353,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="E65" s="8" t="n">
-        <v>-0.0488</v>
+        <v>6.35</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>0.0016</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>1434400</v>
+        <v>1821300</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.34</v>
+        <v>0.3</v>
       </c>
       <c r="H65" t="n">
-        <v>47.76</v>
+        <v>42.34</v>
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
@@ -3382,10 +3382,10 @@
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.6</v>
+        <v>6.412</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0.585</v>
+        <v>6.789</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3398,28 +3398,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>8524</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>TALIWRK</t>
+          <t>VANTNRG</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>0.23</v>
+        <v>0.3</v>
       </c>
       <c r="E66" s="8" t="n">
-        <v>-0.0213</v>
+        <v>-0.0164</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>1424500</v>
+        <v>1767900</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.55</v>
       </c>
       <c r="H66" t="n">
-        <v>37.06</v>
+        <v>28.9</v>
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.247</v>
+        <v>0.324</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0.258</v>
+        <v>0.332</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3443,28 +3443,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>0.63</v>
+        <v>2.46</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>-0.0156</v>
+        <v>-0.04650000000000001</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>1408900</v>
+        <v>1745200</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.59</v>
+        <v>0.29</v>
       </c>
       <c r="H67" t="n">
-        <v>48.11</v>
+        <v>39.72</v>
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.637</v>
+        <v>2.612</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0.619</v>
+        <v>2.599</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
@@ -3488,39 +3488,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>7.49</v>
+        <v>0.52</v>
       </c>
       <c r="E68" s="8" t="n">
-        <v>-0.0013</v>
+        <v>-0.03700000000000001</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>1390600</v>
+        <v>1724600</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="H68" t="n">
-        <v>44.06</v>
-      </c>
-      <c r="I68" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.58</v>
+      </c>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>7.579</v>
+        <v>0.52</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>7.71</v>
+        <v>0.454</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
@@ -3533,28 +3533,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>0.76</v>
+        <v>2.77</v>
       </c>
       <c r="E69" s="8" t="n">
-        <v>-0.013</v>
+        <v>-0.0072</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>1359400</v>
+        <v>1702200</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.16</v>
+        <v>0.35</v>
       </c>
       <c r="H69" t="n">
-        <v>44.91</v>
+        <v>55.23</v>
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
@@ -3562,10 +3562,10 @@
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.777</v>
+        <v>2.763</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0.773</v>
+        <v>2.157</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
@@ -3578,28 +3578,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>2.47</v>
+        <v>0.655</v>
       </c>
       <c r="E70" s="8" t="n">
-        <v>-0.0426</v>
+        <v>-0.0296</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>1345800</v>
+        <v>1685100</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="H70" t="n">
-        <v>40.24</v>
+        <v>43.84</v>
       </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
@@ -3607,10 +3607,10 @@
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>2.613</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>2.599</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
@@ -3623,28 +3623,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>0.98</v>
+        <v>0.46</v>
       </c>
       <c r="E71" s="8" t="n">
-        <v>-0.0392</v>
+        <v>-0.0316</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>1298500</v>
+        <v>1682000</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.28</v>
+        <v>0.22</v>
       </c>
       <c r="H71" t="n">
-        <v>43.38</v>
+        <v>26.61</v>
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
@@ -3652,10 +3652,10 @@
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.049</v>
+        <v>0.507</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0.927</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
@@ -3668,28 +3668,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E72" s="8" t="n">
-        <v>-0.0164</v>
+        <v>1.44</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>0.006999999999999999</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>1280400</v>
+        <v>1636800</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.21</v>
+        <v>0.4</v>
       </c>
       <c r="H72" t="n">
-        <v>38.46</v>
+        <v>44.83</v>
       </c>
       <c r="I72" s="6" t="inlineStr">
         <is>
@@ -3697,10 +3697,10 @@
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.319</v>
+        <v>1.452</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0.338</v>
+        <v>1.466</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
@@ -3713,28 +3713,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>0.67</v>
+        <v>0.78</v>
       </c>
       <c r="E73" s="8" t="n">
-        <v>-0.036</v>
+        <v>-0.0429</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>1273400</v>
+        <v>1617600</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.4</v>
+        <v>0.26</v>
       </c>
       <c r="H73" t="n">
-        <v>35.17</v>
+        <v>56.59</v>
       </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
@@ -3742,10 +3742,10 @@
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.738</v>
+        <v>0.767</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0.746</v>
+        <v>0.68</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
@@ -3758,28 +3758,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BPURI</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>0.215</v>
+        <v>1.19</v>
       </c>
       <c r="E74" s="8" t="n">
-        <v>-0.0227</v>
+        <v>-0.0246</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>1223900</v>
+        <v>1615000</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>2.35</v>
+        <v>0.21</v>
       </c>
       <c r="H74" t="n">
-        <v>40.22</v>
+        <v>53.56</v>
       </c>
       <c r="I74" s="6" t="inlineStr">
         <is>
@@ -3787,10 +3787,10 @@
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.225</v>
+        <v>1.169</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0.233</v>
+        <v>1.131</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr"/>
@@ -3803,28 +3803,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>1.68</v>
+        <v>0.48</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>-0.0233</v>
+        <v>-0.04</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>1213000</v>
+        <v>1601800</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="H75" t="n">
-        <v>40.51</v>
+        <v>28.41</v>
       </c>
       <c r="I75" s="6" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1.741</v>
+        <v>0.556</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>1.772</v>
+        <v>0.626</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr"/>
@@ -3848,28 +3848,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.975</v>
       </c>
       <c r="E76" s="8" t="n">
-        <v>-0.0106</v>
+        <v>-0.0441</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>1197200</v>
+        <v>1574100</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.31</v>
+        <v>0.34</v>
       </c>
       <c r="H76" t="n">
-        <v>27.89</v>
+        <v>42.79</v>
       </c>
       <c r="I76" s="6" t="inlineStr">
         <is>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.979</v>
+        <v>1.049</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>1.059</v>
+        <v>0.926</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
@@ -3893,39 +3893,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E77" s="3" t="n">
-        <v>0.0308</v>
+        <v>0.805</v>
+      </c>
+      <c r="E77" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>1189800</v>
+        <v>1542100</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="H77" t="n">
-        <v>47.07</v>
-      </c>
-      <c r="I77" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.89</v>
+      </c>
+      <c r="I77" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.336</v>
+        <v>0.792</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0.343</v>
+        <v>0.769</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
@@ -3938,39 +3938,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>TALIWRK</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E78" s="3" t="n">
-        <v>0.0351</v>
+        <v>0.23</v>
+      </c>
+      <c r="E78" s="8" t="n">
+        <v>-0.0213</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>1183700</v>
+        <v>1454300</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>1.24</v>
+        <v>0.71</v>
       </c>
       <c r="H78" t="n">
-        <v>66.28</v>
-      </c>
-      <c r="I78" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.06</v>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.275</v>
+        <v>0.247</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0.267</v>
+        <v>0.258</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
@@ -3983,28 +3983,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>0.785</v>
+        <v>7.31</v>
       </c>
       <c r="E79" s="8" t="n">
-        <v>-0.0368</v>
+        <v>-0.0027</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>1179900</v>
+        <v>1427900</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
       <c r="H79" t="n">
-        <v>57.66</v>
+        <v>33.47</v>
       </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
@@ -4012,10 +4012,10 @@
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.768</v>
+        <v>7.5</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0.68</v>
+        <v>8.003</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
@@ -4028,28 +4028,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0272</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>TTVHB</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E80" s="8" t="n">
-        <v>-0.0208</v>
+        <v>0.865</v>
+      </c>
+      <c r="E80" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>1177000</v>
+        <v>1420800</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.49</v>
+        <v>0.45</v>
       </c>
       <c r="H80" t="n">
-        <v>44.1</v>
+        <v>51.9</v>
       </c>
       <c r="I80" s="6" t="inlineStr">
         <is>
@@ -4057,10 +4057,10 @@
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.248</v>
+        <v>0.865</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0.255</v>
+        <v>0.859</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
@@ -4073,28 +4073,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>-0.06610000000000001</v>
+        <v>-0.0052</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>1167000</v>
+        <v>1409000</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="H81" t="n">
-        <v>54.07</v>
+        <v>63.6</v>
       </c>
       <c r="I81" s="6" t="inlineStr">
         <is>
@@ -4102,10 +4102,10 @@
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.917</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0.51</v>
+        <v>0.871</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
@@ -4118,28 +4118,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>0.955</v>
-      </c>
-      <c r="E82" s="10" t="n">
-        <v>0</v>
+        <v>0.63</v>
+      </c>
+      <c r="E82" s="8" t="n">
+        <v>-0.0156</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>1162500</v>
+        <v>1408900</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.21</v>
+        <v>0.59</v>
       </c>
       <c r="H82" t="n">
-        <v>65.59</v>
+        <v>48.11</v>
       </c>
       <c r="I82" s="6" t="inlineStr">
         <is>
@@ -4147,10 +4147,10 @@
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.917</v>
+        <v>0.637</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0.872</v>
+        <v>0.619</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr"/>
@@ -4163,31 +4163,40 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>9776</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>RSSB</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="E83" s="10" t="n">
-        <v>0</v>
+        <v>3.71</v>
+      </c>
+      <c r="E83" s="8" t="n">
+        <v>-0.0339</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>1153800</v>
-      </c>
-      <c r="G83" s="5" t="n"/>
+        <v>1399000</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H83" t="n">
+        <v>44.17</v>
+      </c>
       <c r="I83" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J83" s="2" t="n"/>
-      <c r="K83" s="2" t="n"/>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>3.857</v>
+      </c>
+      <c r="K83" s="2" t="n">
+        <v>3.646</v>
+      </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
     </row>
@@ -4199,28 +4208,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>3.7</v>
+        <v>7.33</v>
       </c>
       <c r="E84" s="8" t="n">
-        <v>-0.0365</v>
+        <v>-0.0517</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>1139600</v>
+        <v>1397900</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="H84" t="n">
-        <v>43.72</v>
+        <v>52.06</v>
       </c>
       <c r="I84" s="6" t="inlineStr">
         <is>
@@ -4228,10 +4237,10 @@
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>3.856</v>
+        <v>7.377</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>3.646</v>
+        <v>6.867</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
@@ -4244,28 +4253,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="E85" s="8" t="n">
-        <v>-0.0484</v>
+        <v>0.335</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>0.0308</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>1113100</v>
+        <v>1378600</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.31</v>
+        <v>0.26</v>
       </c>
       <c r="H85" t="n">
-        <v>47.61</v>
+        <v>47.07</v>
       </c>
       <c r="I85" s="6" t="inlineStr">
         <is>
@@ -4273,10 +4282,10 @@
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.248</v>
+        <v>0.336</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>1.05</v>
+        <v>0.343</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr"/>
@@ -4289,28 +4298,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>2.72</v>
+        <v>1.24</v>
       </c>
       <c r="E86" s="8" t="n">
-        <v>-0.0251</v>
+        <v>-0.0677</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>1102300</v>
+        <v>1367600</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.23</v>
+        <v>0.6</v>
       </c>
       <c r="H86" t="n">
-        <v>53.26</v>
+        <v>51.76</v>
       </c>
       <c r="I86" s="6" t="inlineStr">
         <is>
@@ -4318,10 +4327,10 @@
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>2.758</v>
+        <v>1.246</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>2.156</v>
+        <v>1.167</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
@@ -4334,39 +4343,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>2.1</v>
+        <v>0.76</v>
       </c>
       <c r="E87" s="8" t="n">
-        <v>-0.009399999999999999</v>
+        <v>-0.013</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>1066900</v>
+        <v>1359400</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.05</v>
+        <v>0.16</v>
       </c>
       <c r="H87" t="n">
-        <v>49.15</v>
-      </c>
-      <c r="I87" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.91</v>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>2.109</v>
+        <v>0.777</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>2.097</v>
+        <v>0.773</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
@@ -4379,28 +4388,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="E88" s="3" t="n">
-        <v>0.0353</v>
+        <v>0.305</v>
+      </c>
+      <c r="E88" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>1061100</v>
+        <v>1354200</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.22</v>
       </c>
       <c r="H88" t="n">
-        <v>46.12</v>
+        <v>40.5</v>
       </c>
       <c r="I88" s="6" t="inlineStr">
         <is>
@@ -4408,10 +4417,10 @@
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.913</v>
+        <v>0.32</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0.865</v>
+        <v>0.338</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr"/>
@@ -4424,28 +4433,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>0.225</v>
+        <v>0.75</v>
       </c>
       <c r="E89" s="8" t="n">
-        <v>-0.0426</v>
+        <v>-0.0132</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>1020600</v>
+        <v>1352900</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.21</v>
+        <v>0.3</v>
       </c>
       <c r="H89" t="n">
-        <v>41.8</v>
+        <v>39.04</v>
       </c>
       <c r="I89" s="6" t="inlineStr">
         <is>
@@ -4453,10 +4462,10 @@
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.247</v>
+        <v>0.783</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0.223</v>
+        <v>0.803</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
@@ -4469,39 +4478,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0337</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E90" s="8" t="n">
-        <v>-0.04</v>
+        <v>1.26</v>
+      </c>
+      <c r="E90" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>1010400</v>
+        <v>1346800</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.54</v>
+        <v>0.32</v>
       </c>
       <c r="H90" t="n">
-        <v>50.37</v>
-      </c>
-      <c r="I90" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>23.74</v>
+      </c>
+      <c r="I90" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.24</v>
+        <v>1.424</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0.243</v>
+        <v>1.58</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr"/>
@@ -4514,28 +4523,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>0.74</v>
+        <v>0.66</v>
       </c>
       <c r="E91" s="8" t="n">
-        <v>-0.0513</v>
+        <v>-0.0504</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>1008200</v>
+        <v>1334400</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="H91" t="n">
-        <v>53.4</v>
+        <v>33.87</v>
       </c>
       <c r="I91" s="6" t="inlineStr">
         <is>
@@ -4543,10 +4552,10 @@
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.728</v>
+        <v>0.737</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0.701</v>
+        <v>0.746</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr"/>
@@ -4559,28 +4568,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>2.95</v>
+        <v>3.66</v>
       </c>
       <c r="E92" s="8" t="n">
-        <v>-0.0484</v>
+        <v>-0.0317</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>991700</v>
+        <v>1318400</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0.32</v>
+        <v>0.14</v>
       </c>
       <c r="H92" t="n">
-        <v>48.85</v>
+        <v>54.25</v>
       </c>
       <c r="I92" s="6" t="inlineStr">
         <is>
@@ -4588,10 +4597,10 @@
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>3.023</v>
+        <v>3.617</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>2.846</v>
+        <v>2.917</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="7" t="inlineStr"/>
@@ -4604,39 +4613,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>2.28</v>
+        <v>1.69</v>
       </c>
       <c r="E93" s="8" t="n">
-        <v>-0.013</v>
+        <v>-0.0174</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>985400</v>
+        <v>1304400</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="H93" t="n">
-        <v>57.14</v>
-      </c>
-      <c r="I93" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.59</v>
+      </c>
+      <c r="I93" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>2.208</v>
+        <v>1.742</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>2.152</v>
+        <v>1.772</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="7" t="inlineStr"/>
@@ -4649,28 +4658,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>1.23</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="E94" s="8" t="n">
-        <v>-0.07519999999999999</v>
+        <v>-0.0106</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>980300</v>
+        <v>1290600</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>0.43</v>
+        <v>0.34</v>
       </c>
       <c r="H94" t="n">
-        <v>50.82</v>
+        <v>27.89</v>
       </c>
       <c r="I94" s="6" t="inlineStr">
         <is>
@@ -4678,10 +4687,10 @@
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1.246</v>
+        <v>0.979</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>1.166</v>
+        <v>1.059</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="7" t="inlineStr"/>
@@ -4694,28 +4703,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>2054</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>TDM</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>6.33</v>
-      </c>
-      <c r="E95" s="8" t="n">
-        <v>-0.0016</v>
+        <v>0.2</v>
+      </c>
+      <c r="E95" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>964100</v>
+        <v>1283200</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.16</v>
+        <v>2.61</v>
       </c>
       <c r="H95" t="n">
-        <v>41.19</v>
+        <v>27.29</v>
       </c>
       <c r="I95" s="6" t="inlineStr">
         <is>
@@ -4723,10 +4732,10 @@
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>6.41</v>
+        <v>0.208</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>6.789</v>
+        <v>0.217</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="7" t="inlineStr"/>
@@ -4739,39 +4748,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E96" s="10" t="n">
-        <v>0</v>
+        <v>2.77</v>
+      </c>
+      <c r="E96" s="8" t="n">
+        <v>-0.0315</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>960100</v>
+        <v>1246700</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.16</v>
+        <v>0.38</v>
       </c>
       <c r="H96" t="n">
-        <v>66.89</v>
-      </c>
-      <c r="I96" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.93</v>
+      </c>
+      <c r="I96" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.792</v>
+        <v>2.924</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0.769</v>
+        <v>3.023</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="7" t="inlineStr"/>
@@ -4784,28 +4793,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>0272</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>TTVHB</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>1.08</v>
+        <v>0.235</v>
       </c>
       <c r="E97" s="8" t="n">
-        <v>-0.0442</v>
+        <v>-0.0208</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>934700</v>
+        <v>1227200</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>0.4</v>
+        <v>0.51</v>
       </c>
       <c r="H97" t="n">
-        <v>34.06</v>
+        <v>44.1</v>
       </c>
       <c r="I97" s="6" t="inlineStr">
         <is>
@@ -4813,10 +4822,10 @@
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>1.231</v>
+        <v>0.248</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>1.303</v>
+        <v>0.255</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="7" t="inlineStr"/>
@@ -4829,28 +4838,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>BPURI</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E98" s="3" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.215</v>
+      </c>
+      <c r="E98" s="8" t="n">
+        <v>-0.0227</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>925100</v>
+        <v>1223900</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>0.22</v>
+        <v>2.35</v>
       </c>
       <c r="H98" t="n">
-        <v>25.55</v>
+        <v>40.22</v>
       </c>
       <c r="I98" s="6" t="inlineStr">
         <is>
@@ -4858,10 +4867,10 @@
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>1.425</v>
+        <v>0.225</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>1.58</v>
+        <v>0.233</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr"/>
@@ -4874,28 +4883,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>7.27</v>
+        <v>1.2</v>
       </c>
       <c r="E99" s="8" t="n">
-        <v>-0.008199999999999999</v>
+        <v>-0.0323</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>922200</v>
+        <v>1218000</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0.09</v>
+        <v>0.34</v>
       </c>
       <c r="H99" t="n">
-        <v>32.1</v>
+        <v>49.35</v>
       </c>
       <c r="I99" s="6" t="inlineStr">
         <is>
@@ -4903,10 +4912,10 @@
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>7.497</v>
+        <v>1.25</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>8.002000000000001</v>
+        <v>1.05</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="7" t="inlineStr"/>
@@ -4919,39 +4928,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>3.67</v>
+        <v>2.08</v>
       </c>
       <c r="E100" s="8" t="n">
-        <v>-0.0291</v>
+        <v>-0.0189</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>914600</v>
+        <v>1203900</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="H100" t="n">
-        <v>54.51</v>
-      </c>
-      <c r="I100" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.32</v>
+      </c>
+      <c r="I100" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>3.618</v>
+        <v>2.107</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>2.917</v>
+        <v>2.096</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr"/>
@@ -4964,28 +4973,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>MALAKOF</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E101" s="8" t="n">
-        <v>-0.0132</v>
+        <v>0.885</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>0.0412</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>881500</v>
+        <v>1202100</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>0.2</v>
+        <v>0.78</v>
       </c>
       <c r="H101" t="n">
-        <v>39.04</v>
+        <v>46.91</v>
       </c>
       <c r="I101" s="6" t="inlineStr">
         <is>
@@ -4993,10 +5002,10 @@
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.783</v>
+        <v>0.914</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0.803</v>
+        <v>0.865</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="7" t="inlineStr"/>
@@ -5009,28 +5018,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>7.3</v>
+        <v>0.745</v>
       </c>
       <c r="E102" s="8" t="n">
-        <v>-0.0556</v>
+        <v>-0.0449</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>843400</v>
+        <v>1188400</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0.21</v>
+        <v>0.52</v>
       </c>
       <c r="H102" t="n">
-        <v>51.38</v>
+        <v>54.2</v>
       </c>
       <c r="I102" s="6" t="inlineStr">
         <is>
@@ -5038,10 +5047,10 @@
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>7.374</v>
+        <v>0.729</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>6.867</v>
+        <v>0.701</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="7" t="inlineStr"/>
@@ -5054,40 +5063,31 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>9776</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>RSSB</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E103" s="3" t="n">
-        <v>0.0091</v>
+        <v>0.33</v>
+      </c>
+      <c r="E103" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>842000</v>
-      </c>
-      <c r="G103" s="5" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H103" t="n">
-        <v>39.65</v>
-      </c>
-      <c r="I103" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J103" s="2" t="n">
-        <v>0.573</v>
-      </c>
-      <c r="K103" s="2" t="n">
-        <v>0.615</v>
-      </c>
+        <v>1183800</v>
+      </c>
+      <c r="G103" s="5" t="n"/>
+      <c r="I103" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="n"/>
+      <c r="K103" s="2" t="n"/>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="7" t="inlineStr"/>
     </row>
@@ -5099,39 +5099,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E104" s="10" t="n">
-        <v>0</v>
+        <v>0.295</v>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>0.0351</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>774000</v>
+        <v>1183700</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>0.25</v>
+        <v>1.24</v>
       </c>
       <c r="H104" t="n">
-        <v>51.9</v>
-      </c>
-      <c r="I104" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.28</v>
+      </c>
+      <c r="I104" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.865</v>
+        <v>0.275</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0.859</v>
+        <v>0.267</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="7" t="inlineStr"/>
@@ -5144,28 +5144,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>2.75</v>
+        <v>2.99</v>
       </c>
       <c r="E105" s="8" t="n">
-        <v>-0.0385</v>
+        <v>-0.0355</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>741100</v>
+        <v>1169800</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>0.23</v>
+        <v>0.37</v>
       </c>
       <c r="H105" t="n">
-        <v>36.96</v>
+        <v>50.62</v>
       </c>
       <c r="I105" s="6" t="inlineStr">
         <is>
@@ -5173,10 +5173,10 @@
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>2.922</v>
+        <v>3.027</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>3.023</v>
+        <v>2.846</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="7" t="inlineStr"/>
@@ -5189,39 +5189,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>1.21</v>
+        <v>2.26</v>
       </c>
       <c r="E106" s="8" t="n">
-        <v>-0.0472</v>
+        <v>-0.0216</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>739300</v>
+        <v>1103600</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="H106" t="n">
-        <v>44.54</v>
-      </c>
-      <c r="I106" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.35</v>
+      </c>
+      <c r="I106" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>1.285</v>
+        <v>2.206</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>1.217</v>
+        <v>2.151</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="7" t="inlineStr"/>
@@ -5234,28 +5234,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>BAUTO</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>0.89</v>
+        <v>1.08</v>
       </c>
       <c r="E107" s="8" t="n">
-        <v>-0.005600000000000001</v>
+        <v>-0.0442</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>722700</v>
+        <v>1098400</v>
       </c>
       <c r="G107" s="5" t="n">
         <v>0.46</v>
       </c>
       <c r="H107" t="n">
-        <v>37.09</v>
+        <v>34.06</v>
       </c>
       <c r="I107" s="6" t="inlineStr">
         <is>
@@ -5263,10 +5263,10 @@
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.914</v>
+        <v>1.231</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0.931</v>
+        <v>1.303</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="7" t="inlineStr"/>
@@ -5279,28 +5279,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>1.32</v>
+        <v>10.28</v>
       </c>
       <c r="E108" s="8" t="n">
-        <v>-0.0294</v>
+        <v>-0.0338</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>681600</v>
+        <v>1093800</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="H108" t="n">
-        <v>48.94</v>
+        <v>51.56</v>
       </c>
       <c r="I108" s="6" t="inlineStr">
         <is>
@@ -5308,10 +5308,10 @@
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>1.341</v>
+        <v>10.384</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>1.274</v>
+        <v>9.692</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="7" t="inlineStr"/>
@@ -5324,28 +5324,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>5120</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>AMFIRST</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>0.625</v>
+        <v>0.33</v>
       </c>
       <c r="E109" s="8" t="n">
-        <v>-0.0458</v>
+        <v>-0.0294</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>678700</v>
+        <v>1091100</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>0.12</v>
+        <v>3.72</v>
       </c>
       <c r="H109" t="n">
-        <v>62.58</v>
+        <v>26.77</v>
       </c>
       <c r="I109" s="6" t="inlineStr">
         <is>
@@ -5353,10 +5353,10 @@
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.344</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0.462</v>
+        <v>0.345</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="7" t="inlineStr"/>
@@ -5369,28 +5369,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>0.71</v>
+        <v>0.23</v>
       </c>
       <c r="E110" s="8" t="n">
-        <v>-0.0274</v>
+        <v>-0.0213</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>650200</v>
+        <v>1088100</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>0.04</v>
+        <v>0.22</v>
       </c>
       <c r="H110" t="n">
-        <v>43.13</v>
+        <v>43.72</v>
       </c>
       <c r="I110" s="6" t="inlineStr">
         <is>
@@ -5398,10 +5398,10 @@
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.764</v>
+        <v>0.247</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0.722</v>
+        <v>0.223</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="7" t="inlineStr"/>
@@ -5414,39 +5414,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>0466</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>SRKKAI</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>0.52</v>
+        <v>0.495</v>
       </c>
       <c r="E111" s="8" t="n">
-        <v>-0.028</v>
+        <v>-0.0294</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>642600</v>
+        <v>1084100</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>0.17</v>
+        <v>0.91</v>
       </c>
       <c r="H111" t="n">
-        <v>59.64</v>
-      </c>
-      <c r="I111" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.16</v>
+      </c>
+      <c r="I111" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.494</v>
+        <v>0.518</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0.461</v>
+        <v>0.531</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="7" t="inlineStr"/>
@@ -5459,39 +5459,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>0337</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>THMY</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>2</v>
+        <v>0.24</v>
       </c>
       <c r="E112" s="8" t="n">
-        <v>-0.0566</v>
+        <v>-0.04</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>630900</v>
+        <v>1050000</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>0.26</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H112" t="n">
-        <v>45.65</v>
-      </c>
-      <c r="I112" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.37</v>
+      </c>
+      <c r="I112" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>2.107</v>
+        <v>0.24</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>1.983</v>
+        <v>0.243</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="7" t="inlineStr"/>
@@ -5504,28 +5504,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>3.79</v>
+        <v>2.62</v>
       </c>
       <c r="E113" s="8" t="n">
-        <v>-0.0207</v>
+        <v>-0.0296</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>589400</v>
+        <v>1046400</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>0.06</v>
+        <v>0.21</v>
       </c>
       <c r="H113" t="n">
-        <v>46.67</v>
+        <v>35.88</v>
       </c>
       <c r="I113" s="6" t="inlineStr">
         <is>
@@ -5533,10 +5533,10 @@
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>3.969</v>
+        <v>2.879</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>3.522</v>
+        <v>2.87</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="7" t="inlineStr"/>
@@ -5549,28 +5549,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>6181</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>MALTON</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>10.16</v>
+        <v>0.2</v>
       </c>
       <c r="E114" s="8" t="n">
-        <v>-0.0451</v>
+        <v>-0.0698</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>577700</v>
+        <v>1037400</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>0.16</v>
+        <v>1.49</v>
       </c>
       <c r="H114" t="n">
-        <v>49.4</v>
+        <v>32.72</v>
       </c>
       <c r="I114" s="6" t="inlineStr">
         <is>
@@ -5578,10 +5578,10 @@
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>10.372</v>
+        <v>0.218</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>9.689</v>
+        <v>0.225</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="7" t="inlineStr"/>
@@ -5594,28 +5594,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>2.43</v>
+        <v>1.21</v>
       </c>
       <c r="E115" s="8" t="n">
-        <v>-0.0122</v>
+        <v>-0.0472</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>573700</v>
+        <v>981000</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
       <c r="H115" t="n">
-        <v>47.92</v>
+        <v>44.54</v>
       </c>
       <c r="I115" s="6" t="inlineStr">
         <is>
@@ -5623,10 +5623,10 @@
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>2.458</v>
+        <v>1.285</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>2.374</v>
+        <v>1.217</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="7" t="inlineStr"/>
@@ -5639,28 +5639,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>NGGB</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="E116" s="10" t="n">
-        <v>0</v>
+        <v>3.78</v>
+      </c>
+      <c r="E116" s="8" t="n">
+        <v>-0.0233</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>567100</v>
+        <v>923700</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>0.36</v>
+        <v>0.09</v>
       </c>
       <c r="H116" t="n">
-        <v>59.74</v>
+        <v>46.36</v>
       </c>
       <c r="I116" s="6" t="inlineStr">
         <is>
@@ -5668,10 +5668,10 @@
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.741</v>
+        <v>3.968</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>0.718</v>
+        <v>3.522</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="7" t="inlineStr"/>
@@ -5684,39 +5684,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>12.98</v>
-      </c>
-      <c r="E117" s="10" t="n">
-        <v>0</v>
+        <v>0.87</v>
+      </c>
+      <c r="E117" s="8" t="n">
+        <v>-0.0169</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>565900</v>
+        <v>912700</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>0.06</v>
+        <v>0.36</v>
       </c>
       <c r="H117" t="n">
-        <v>44.06</v>
-      </c>
-      <c r="I117" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>20.42</v>
+      </c>
+      <c r="I117" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>13.021</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>13.468</v>
+        <v>0.98</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="7" t="inlineStr"/>
@@ -5729,39 +5729,39 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>BAUTO</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>1.91</v>
+        <v>0.885</v>
       </c>
       <c r="E118" s="8" t="n">
-        <v>-0.0104</v>
+        <v>-0.0112</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>559800</v>
+        <v>882400</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>0.09</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H118" t="n">
-        <v>45.87</v>
-      </c>
-      <c r="I118" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.62</v>
+      </c>
+      <c r="I118" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>1.924</v>
+        <v>0.914</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>1.952</v>
+        <v>0.931</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="7" t="inlineStr"/>
@@ -5774,39 +5774,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>4.32</v>
+        <v>2.43</v>
       </c>
       <c r="E119" s="8" t="n">
-        <v>-0.0248</v>
+        <v>-0.0122</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>525700</v>
+        <v>860100</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H119" t="n">
-        <v>47.32</v>
-      </c>
-      <c r="I119" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.92</v>
+      </c>
+      <c r="I119" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>4.36</v>
+        <v>2.458</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>4.438</v>
+        <v>2.374</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="7" t="inlineStr"/>
@@ -5819,39 +5819,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0291</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>CHB</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="E120" s="8" t="n">
-        <v>-0.0498</v>
+        <v>0.555</v>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>0.0091</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>518300</v>
+        <v>842000</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>0.31</v>
+        <v>0.75</v>
       </c>
       <c r="H120" t="n">
-        <v>51.32</v>
-      </c>
-      <c r="I120" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>39.65</v>
+      </c>
+      <c r="I120" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>2.526</v>
+        <v>0.573</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>2.223</v>
+        <v>0.615</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="7" t="inlineStr"/>
@@ -5864,28 +5864,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>0.895</v>
+        <v>0.63</v>
       </c>
       <c r="E121" s="8" t="n">
-        <v>-0.011</v>
+        <v>-0.0382</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>514100</v>
+        <v>823500</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="H121" t="n">
-        <v>41.27</v>
+        <v>63.4</v>
       </c>
       <c r="I121" s="6" t="inlineStr">
         <is>
@@ -5893,10 +5893,10 @@
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.909</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0.958</v>
+        <v>0.463</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="7" t="inlineStr"/>
@@ -5909,28 +5909,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0375</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>THMY</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>2.61</v>
+        <v>2.04</v>
       </c>
       <c r="E122" s="8" t="n">
-        <v>-0.0333</v>
+        <v>-0.0377</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>508000</v>
+        <v>772000</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>0.1</v>
+        <v>0.32</v>
       </c>
       <c r="H122" t="n">
-        <v>35.52</v>
+        <v>47.7</v>
       </c>
       <c r="I122" s="6" t="inlineStr">
         <is>
@@ -5938,16 +5938,916 @@
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>2.878</v>
+        <v>2.111</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>2.87</v>
+        <v>1.983</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="7" t="inlineStr"/>
     </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>5246</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>WPRTS</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>0.0059</v>
+      </c>
+      <c r="F123" s="4" t="n">
+        <v>759000</v>
+      </c>
+      <c r="G123" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H123" t="n">
+        <v>51.24</v>
+      </c>
+      <c r="I123" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="n">
+        <v>6.761</v>
+      </c>
+      <c r="K123" s="2" t="n">
+        <v>6.835</v>
+      </c>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" s="7" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>0391</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>AMBEST</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E124" s="8" t="n">
+        <v>-0.0441</v>
+      </c>
+      <c r="F124" s="4" t="n">
+        <v>749900</v>
+      </c>
+      <c r="G124" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H124" t="n">
+        <v>46.63</v>
+      </c>
+      <c r="I124" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="n">
+        <v>1.339</v>
+      </c>
+      <c r="K124" s="2" t="n">
+        <v>1.273</v>
+      </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" s="7" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>5347</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>TENAGA</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>12.98</v>
+      </c>
+      <c r="E125" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="4" t="n">
+        <v>738900</v>
+      </c>
+      <c r="G125" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H125" t="n">
+        <v>44.06</v>
+      </c>
+      <c r="I125" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="n">
+        <v>13.021</v>
+      </c>
+      <c r="K125" s="2" t="n">
+        <v>13.468</v>
+      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" s="7" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>MAYBANK</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>10.04</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="F126" s="4" t="n">
+        <v>724400</v>
+      </c>
+      <c r="G126" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H126" t="n">
+        <v>49.55</v>
+      </c>
+      <c r="I126" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="K126" s="2" t="n">
+        <v>10.168</v>
+      </c>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" s="7" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>6947</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E127" s="8" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="F127" s="4" t="n">
+        <v>719900</v>
+      </c>
+      <c r="G127" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H127" t="n">
+        <v>36.45</v>
+      </c>
+      <c r="I127" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" s="7" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>5183</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>PCHEM</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E128" s="8" t="n">
+        <v>-0.0293</v>
+      </c>
+      <c r="F128" s="4" t="n">
+        <v>702300</v>
+      </c>
+      <c r="G128" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H128" t="n">
+        <v>46.61</v>
+      </c>
+      <c r="I128" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="n">
+        <v>4.358</v>
+      </c>
+      <c r="K128" s="2" t="n">
+        <v>4.438</v>
+      </c>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" s="7" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>0368</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>OXB</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="E129" s="8" t="n">
+        <v>-0.0187</v>
+      </c>
+      <c r="F129" s="4" t="n">
+        <v>693000</v>
+      </c>
+      <c r="G129" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H129" t="n">
+        <v>61.14</v>
+      </c>
+      <c r="I129" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="n">
+        <v>0.494</v>
+      </c>
+      <c r="K129" s="2" t="n">
+        <v>0.461</v>
+      </c>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" s="7" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>5184</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>CYPARK</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="E130" s="8" t="n">
+        <v>-0.0274</v>
+      </c>
+      <c r="F130" s="4" t="n">
+        <v>676000</v>
+      </c>
+      <c r="G130" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H130" t="n">
+        <v>43.13</v>
+      </c>
+      <c r="I130" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="n">
+        <v>0.764</v>
+      </c>
+      <c r="K130" s="2" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" s="7" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>7277</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>DIALOG</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="E131" s="8" t="n">
+        <v>-0.0104</v>
+      </c>
+      <c r="F131" s="4" t="n">
+        <v>673000</v>
+      </c>
+      <c r="G131" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H131" t="n">
+        <v>45.87</v>
+      </c>
+      <c r="I131" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="n">
+        <v>1.924</v>
+      </c>
+      <c r="K131" s="2" t="n">
+        <v>1.952</v>
+      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" s="7" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>0291</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>CHB</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="E132" s="8" t="n">
+        <v>-0.0383</v>
+      </c>
+      <c r="F132" s="4" t="n">
+        <v>661700</v>
+      </c>
+      <c r="G132" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H132" t="n">
+        <v>52.87</v>
+      </c>
+      <c r="I132" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="n">
+        <v>2.528</v>
+      </c>
+      <c r="K132" s="2" t="n">
+        <v>2.223</v>
+      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" s="7" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>6971</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>KOBAY</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>0.0152</v>
+      </c>
+      <c r="F133" s="4" t="n">
+        <v>643000</v>
+      </c>
+      <c r="G133" s="5" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H133" t="n">
+        <v>36.94</v>
+      </c>
+      <c r="I133" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="n">
+        <v>2.135</v>
+      </c>
+      <c r="K133" s="2" t="n">
+        <v>2.291</v>
+      </c>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" s="7" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>0151</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>KGB</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="E134" s="8" t="n">
+        <v>-0.0288</v>
+      </c>
+      <c r="F134" s="4" t="n">
+        <v>636600</v>
+      </c>
+      <c r="G134" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H134" t="n">
+        <v>44.12</v>
+      </c>
+      <c r="I134" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="n">
+        <v>8.682</v>
+      </c>
+      <c r="K134" s="2" t="n">
+        <v>8.707000000000001</v>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" s="7" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>5249</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>IOIPG</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="E135" s="8" t="n">
+        <v>-0.0152</v>
+      </c>
+      <c r="F135" s="4" t="n">
+        <v>588600</v>
+      </c>
+      <c r="G135" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H135" t="n">
+        <v>29.47</v>
+      </c>
+      <c r="I135" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="n">
+        <v>3.405</v>
+      </c>
+      <c r="K135" s="2" t="n">
+        <v>3.623</v>
+      </c>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" s="7" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>7241</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>NGGB</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="E136" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" s="4" t="n">
+        <v>567100</v>
+      </c>
+      <c r="G136" s="5" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H136" t="n">
+        <v>59.74</v>
+      </c>
+      <c r="I136" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="K136" s="2" t="n">
+        <v>0.718</v>
+      </c>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" s="7" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>0325</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="E137" s="8" t="n">
+        <v>-0.0194</v>
+      </c>
+      <c r="F137" s="4" t="n">
+        <v>550800</v>
+      </c>
+      <c r="G137" s="5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H137" t="n">
+        <v>37.27</v>
+      </c>
+      <c r="I137" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="n">
+        <v>1.092</v>
+      </c>
+      <c r="K137" s="2" t="n">
+        <v>1.095</v>
+      </c>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" s="7" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>0338</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>KOPI</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="E138" s="8" t="n">
+        <v>-0.0166</v>
+      </c>
+      <c r="F138" s="4" t="n">
+        <v>543900</v>
+      </c>
+      <c r="G138" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H138" t="n">
+        <v>39.69</v>
+      </c>
+      <c r="I138" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="K138" s="2" t="n">
+        <v>0.958</v>
+      </c>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" s="7" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>0293</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>KJTS</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="E139" s="8" t="n">
+        <v>-0.038</v>
+      </c>
+      <c r="F139" s="4" t="n">
+        <v>536300</v>
+      </c>
+      <c r="G139" s="5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H139" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="I139" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="n">
+        <v>0.979</v>
+      </c>
+      <c r="K139" s="2" t="n">
+        <v>1.029</v>
+      </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" s="7" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>5878</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>KPJ</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="E140" s="8" t="n">
+        <v>-0.0119</v>
+      </c>
+      <c r="F140" s="4" t="n">
+        <v>530500</v>
+      </c>
+      <c r="G140" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H140" t="n">
+        <v>40.83</v>
+      </c>
+      <c r="I140" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="n">
+        <v>2.564</v>
+      </c>
+      <c r="K140" s="2" t="n">
+        <v>2.739</v>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" s="7" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>5328</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>LWSABAH</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E141" s="8" t="n">
+        <v>-0.0272</v>
+      </c>
+      <c r="F141" s="4" t="n">
+        <v>521100</v>
+      </c>
+      <c r="G141" s="5" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="H141" t="n">
+        <v>32.63</v>
+      </c>
+      <c r="I141" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="K141" s="2" t="n">
+        <v>1.631</v>
+      </c>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" s="7" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>7293</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>YINSON</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="E142" s="3" t="n">
+        <v>0.0141</v>
+      </c>
+      <c r="F142" s="4" t="n">
+        <v>516800</v>
+      </c>
+      <c r="G142" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H142" t="n">
+        <v>58.07</v>
+      </c>
+      <c r="I142" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="n">
+        <v>2.107</v>
+      </c>
+      <c r="K142" s="2" t="n">
+        <v>2.055</v>
+      </c>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M122"/>
+  <autoFilter ref="A1:M142"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-15/bursa-report-2026-10-15.xlsx
+++ b/docs/downloads/2026-10-15/bursa-report-2026-10-15.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-15" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-15'!$A$1:$M$142</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-15'!$A$1:$M$163</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M142"/>
+  <dimension ref="A1:M163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -558,10 +558,10 @@
         <v>0.1818</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>76581100</v>
+        <v>88230800</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="H2" t="n">
         <v>24.2</v>
@@ -597,19 +597,19 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.9</v>
+        <v>0.895</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>-0.011</v>
+        <v>-0.0165</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>29887700</v>
+        <v>37070800</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.45</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>66.28</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
@@ -633,33 +633,40 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>0.0125</v>
+        <v>0.34</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>21032200</v>
+        <v>25737600</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.11</v>
+        <v>0.35</v>
+      </c>
+      <c r="H4" t="n">
+        <v>71.22</v>
       </c>
       <c r="I4" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J4" s="2" t="n"/>
-      <c r="K4" s="2" t="n"/>
+      <c r="J4" s="2" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>0.253</v>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="7" t="inlineStr"/>
     </row>
@@ -671,40 +678,33 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>0.0241</v>
+        <v>0.79</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>-0.0125</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>20716600</v>
+        <v>22890000</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="H5" t="n">
-        <v>77.33</v>
+        <v>0.12</v>
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J5" s="2" t="n">
-        <v>0.374</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>0.263</v>
-      </c>
+      <c r="J5" s="2" t="n"/>
+      <c r="K5" s="2" t="n"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
     </row>
@@ -716,28 +716,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E6" s="8" t="n">
-        <v>-0.0147</v>
+        <v>0.425</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0.0241</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>19414800</v>
+        <v>21062500</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.26</v>
+        <v>0.57</v>
       </c>
       <c r="H6" t="n">
-        <v>68.7</v>
+        <v>77.33</v>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.297</v>
+        <v>0.374</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.253</v>
+        <v>0.263</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr"/>
@@ -761,39 +761,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.665</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>0</v>
+        <v>0.445</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>-0.0532</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>17835200</v>
+        <v>20219900</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.57</v>
       </c>
       <c r="H7" t="n">
-        <v>76.18000000000001</v>
-      </c>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.13</v>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.603</v>
+        <v>0.485</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.521</v>
+        <v>0.482</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
@@ -806,39 +806,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>-0.0426</v>
+        <v>0.665</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>17097000</v>
+        <v>19013700</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.48</v>
+        <v>0.74</v>
       </c>
       <c r="H8" t="n">
-        <v>39.27</v>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>76.18000000000001</v>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.486</v>
+        <v>0.603</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.482</v>
+        <v>0.521</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
@@ -851,39 +851,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>7036</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>BORNOIL</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>-0.0386</v>
+        <v>0.005</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>12901900</v>
+        <v>15500500</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.43</v>
+        <v>24.48</v>
       </c>
       <c r="H9" t="n">
-        <v>57.79</v>
-      </c>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.15</v>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.908</v>
+        <v>0.005</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>1.712</v>
+        <v>0.005</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
@@ -896,28 +896,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0096</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NEXGRAM</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>-0.0338</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>12462100</v>
+        <v>14694200</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>7.28</v>
+        <v>0.49</v>
       </c>
       <c r="H10" t="n">
-        <v>69.25</v>
+        <v>58.43</v>
       </c>
       <c r="I10" s="9" t="inlineStr">
         <is>
@@ -925,10 +925,10 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.044</v>
+        <v>1.909</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.047</v>
+        <v>1.713</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="7" t="inlineStr"/>
@@ -956,10 +956,10 @@
         <v>-0.0189</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>12247700</v>
+        <v>13315300</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="H11" t="n">
         <v>26.18</v>
@@ -986,33 +986,40 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>0096</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>NEXGRAM</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>-0.0196</v>
+        <v>0.055</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>12158800</v>
+        <v>12944500</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.45</v>
+        <v>7.56</v>
+      </c>
+      <c r="H12" t="n">
+        <v>69.25</v>
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J12" s="2" t="n"/>
-      <c r="K12" s="2" t="n"/>
+      <c r="J12" s="2" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>0.047</v>
+      </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
     </row>
@@ -1039,7 +1046,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>11712900</v>
+        <v>12500400</v>
       </c>
       <c r="G13" s="5" t="n"/>
       <c r="I13" s="6" t="inlineStr">
@@ -1060,40 +1067,33 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7036</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BORNOIL</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>0</v>
+        <v>0.25</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>-0.0196</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>10500000</v>
+        <v>12270700</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>16.58</v>
-      </c>
-      <c r="H14" t="n">
-        <v>48.15</v>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="K14" s="2" t="n">
-        <v>0.005</v>
-      </c>
+        <v>0.45</v>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="2" t="n"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="7" t="inlineStr"/>
     </row>
@@ -1114,19 +1114,19 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.045</v>
+        <v>0.05</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0.5</v>
+        <v>0.6667000000000001</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>10387200</v>
+        <v>10889400</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>8.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>43.11</v>
+        <v>47.61</v>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
@@ -1150,28 +1150,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.31</v>
+        <v>0.44</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>-0.0313</v>
+        <v>-0.0435</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>9177600</v>
+        <v>10536300</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>1.23</v>
+        <v>0.52</v>
       </c>
       <c r="H16" t="n">
-        <v>59.95</v>
+        <v>58.06</v>
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.3</v>
+        <v>0.419</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.279</v>
+        <v>0.36</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
@@ -1195,39 +1195,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>0</v>
+        <v>0.305</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>-0.0469</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>8358200</v>
+        <v>9323900</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.77</v>
+        <v>1.25</v>
       </c>
       <c r="H17" t="n">
-        <v>33.83</v>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.44</v>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.398</v>
+        <v>0.3</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.408</v>
+        <v>0.279</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
@@ -1240,39 +1240,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.31</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>-0.0159</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>7824800</v>
+        <v>8663800</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.76</v>
+        <v>0.45</v>
       </c>
       <c r="H18" t="n">
-        <v>20.13</v>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.53</v>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.746</v>
+        <v>0.308</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>1.971</v>
+        <v>0.298</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
@@ -1285,39 +1285,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0117</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SMRT</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>0.0625</v>
+        <v>0.82</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>7699400</v>
+        <v>8647500</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>2.38</v>
+        <v>0.54</v>
       </c>
       <c r="H19" t="n">
-        <v>41.24</v>
-      </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.28</v>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.179</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0.192</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
@@ -1330,39 +1330,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="E20" s="8" t="n">
-        <v>-0.0326</v>
+        <v>1.44</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>0.0141</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>6826800</v>
+        <v>8409500</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.33</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>59.44</v>
-      </c>
-      <c r="I20" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>21.31</v>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.42</v>
+        <v>1.747</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.361</v>
+        <v>1.971</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
@@ -1375,28 +1375,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>0.0698</v>
+        <v>0.39</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>6633400</v>
+        <v>8358200</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.25</v>
+        <v>0.77</v>
       </c>
       <c r="H21" t="n">
-        <v>39.85</v>
+        <v>33.83</v>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.24</v>
+        <v>0.398</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0.292</v>
+        <v>0.408</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
@@ -1420,28 +1420,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0237</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>HAILY</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>0.0571</v>
+        <v>0.775</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>-0.0064</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>6554900</v>
+        <v>8028200</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>26.04</v>
+        <v>0.53</v>
       </c>
       <c r="H22" t="n">
-        <v>68.31999999999999</v>
+        <v>50.18</v>
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.166</v>
+        <v>0.775</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0.166</v>
+        <v>0.776</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
@@ -1465,39 +1465,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0117</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>SMRT</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>0</v>
+        <v>0.17</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>0.0625</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>6509600</v>
+        <v>7737800</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="H23" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="I23" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.24</v>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.183</v>
+        <v>0.179</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>1.18</v>
+        <v>0.192</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
@@ -1510,28 +1510,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E24" s="10" t="n">
-        <v>0</v>
+        <v>2.59</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>-0.0372</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>6507800</v>
+        <v>7439500</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="H24" t="n">
-        <v>58.28</v>
+        <v>47.68</v>
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
@@ -1539,10 +1539,10 @@
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.8139999999999999</v>
+        <v>2.651</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.8090000000000001</v>
+        <v>2.541</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
@@ -1555,39 +1555,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="E25" s="8" t="n">
-        <v>-0.0409</v>
+        <v>0.225</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>0.04650000000000001</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>6415000</v>
+        <v>7281000</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.35</v>
+        <v>0.28</v>
       </c>
       <c r="H25" t="n">
-        <v>47.09</v>
-      </c>
-      <c r="I25" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.92</v>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>2.65</v>
+        <v>0.239</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>2.541</v>
+        <v>0.292</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
@@ -1600,28 +1600,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.31</v>
+        <v>1.25</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>-0.0159</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>6125800</v>
+        <v>7239200</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.32</v>
+        <v>1.22</v>
       </c>
       <c r="H26" t="n">
-        <v>54.53</v>
+        <v>59.95</v>
       </c>
       <c r="I26" s="9" t="inlineStr">
         <is>
@@ -1629,10 +1629,10 @@
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.308</v>
+        <v>1.182</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.298</v>
+        <v>1.18</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
@@ -1654,19 +1654,19 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.545</v>
+        <v>0.55</v>
       </c>
       <c r="E27" s="8" t="n">
-        <v>-0.0522</v>
+        <v>-0.0435</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>6124200</v>
+        <v>7209400</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="H27" t="n">
-        <v>45.65</v>
+        <v>46.48</v>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
@@ -1690,39 +1690,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0237</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>HAILY</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="E28" s="8" t="n">
-        <v>-0.0611</v>
+        <v>0.185</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>0.0571</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>5655100</v>
+        <v>6781900</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.64</v>
+        <v>26.94</v>
       </c>
       <c r="H28" t="n">
-        <v>42.21</v>
-      </c>
-      <c r="I28" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.31999999999999</v>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.664</v>
+        <v>0.166</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0.619</v>
+        <v>0.166</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
@@ -1750,10 +1750,10 @@
         <v>0</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>5555400</v>
+        <v>6068600</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.51</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H29" t="n">
         <v>56.82</v>
@@ -1780,28 +1780,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.345</v>
+        <v>0.62</v>
       </c>
       <c r="E30" s="8" t="n">
-        <v>-0.0417</v>
+        <v>-0.0534</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>5332400</v>
+        <v>6062400</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.61</v>
+        <v>0.68</v>
       </c>
       <c r="H30" t="n">
-        <v>50.66</v>
+        <v>42.98</v>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.349</v>
+        <v>0.665</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.331</v>
+        <v>0.619</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1825,39 +1825,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.775</v>
+        <v>0.35</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>-0.0064</v>
+        <v>-0.0278</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>4982200</v>
+        <v>5672800</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.33</v>
+        <v>0.64</v>
       </c>
       <c r="H31" t="n">
-        <v>50.18</v>
-      </c>
-      <c r="I31" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.78</v>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.775</v>
+        <v>0.349</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.776</v>
+        <v>0.332</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1870,39 +1870,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>1.08</v>
+        <v>0.865</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>-0.0357</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4579800</v>
+        <v>5592600</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.45</v>
+        <v>0.28</v>
       </c>
       <c r="H32" t="n">
-        <v>51.54</v>
-      </c>
-      <c r="I32" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.95</v>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.073</v>
+        <v>0.868</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>1.042</v>
+        <v>0.869</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
@@ -1915,28 +1915,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0051</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>CUSCAPI</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" s="8" t="n">
-        <v>-0.0291</v>
+        <v>0.045</v>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3868200</v>
+        <v>5469400</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.46</v>
+        <v>0.38</v>
       </c>
       <c r="H33" t="n">
-        <v>43.73</v>
+        <v>38.84</v>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1.062</v>
+        <v>0.05</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.947</v>
+        <v>0.066</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1960,39 +1960,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.38</v>
+        <v>0.18</v>
       </c>
       <c r="E34" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3852500</v>
+        <v>5274100</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.53</v>
+        <v>0.22</v>
       </c>
       <c r="H34" t="n">
-        <v>61.88</v>
-      </c>
-      <c r="I34" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.99</v>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.371</v>
+        <v>0.192</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.369</v>
+        <v>0.185</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2020,10 +2020,10 @@
         <v>-0.0484</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>3830500</v>
+        <v>5003500</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.76</v>
+        <v>0.99</v>
       </c>
       <c r="H35" t="n">
         <v>21.54</v>
@@ -2050,39 +2050,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.865</v>
+        <v>1.08</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.0357</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>3669600</v>
+        <v>4728600</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.19</v>
+        <v>0.47</v>
       </c>
       <c r="H36" t="n">
-        <v>45.95</v>
-      </c>
-      <c r="I36" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.54</v>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.868</v>
+        <v>1.073</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0.869</v>
+        <v>1.042</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
@@ -2095,28 +2095,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.52</v>
+        <v>5.29</v>
       </c>
       <c r="E37" s="8" t="n">
-        <v>-0.07139999999999999</v>
+        <v>-0.0347</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>3401500</v>
+        <v>4357500</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.84</v>
+        <v>0.31</v>
       </c>
       <c r="H37" t="n">
-        <v>32.71</v>
+        <v>39.25</v>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.597</v>
+        <v>5.576</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0.603</v>
+        <v>5.412</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2140,28 +2140,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="E38" s="8" t="n">
-        <v>-0.0328</v>
+        <v>-0.0194</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>3357200</v>
+        <v>4340700</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.24</v>
+        <v>0.52</v>
       </c>
       <c r="H38" t="n">
-        <v>39.55</v>
+        <v>44.99</v>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>5.577</v>
+        <v>1.063</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>5.412</v>
+        <v>0.947</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
@@ -2185,39 +2185,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E39" s="8" t="n">
-        <v>-0.0235</v>
+        <v>0.385</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>0.0132</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>3205400</v>
+        <v>4337700</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="H39" t="n">
-        <v>42.82</v>
-      </c>
-      <c r="I39" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.54000000000001</v>
+      </c>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.443</v>
+        <v>0.371</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0.432</v>
+        <v>0.369</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         <v>0</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>3122900</v>
+        <v>3692300</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
       <c r="H40" t="n">
         <v>50.45</v>
@@ -2275,28 +2275,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>1.27</v>
+        <v>0.52</v>
       </c>
       <c r="E41" s="8" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.07139999999999999</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>3062500</v>
+        <v>3522300</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.32</v>
+        <v>0.87</v>
       </c>
       <c r="H41" t="n">
-        <v>43.81</v>
+        <v>32.71</v>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.308</v>
+        <v>0.597</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>1.313</v>
+        <v>0.603</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2320,39 +2320,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>0.44</v>
+        <v>1.27</v>
       </c>
       <c r="E42" s="8" t="n">
-        <v>-0.0435</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>2954500</v>
+        <v>3451900</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.36</v>
       </c>
       <c r="H42" t="n">
-        <v>62.7</v>
-      </c>
-      <c r="I42" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.81</v>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.384</v>
+        <v>1.308</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0.357</v>
+        <v>1.313</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2380,10 +2380,10 @@
         <v>-0.0317</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>2944200</v>
+        <v>3447000</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.33</v>
+        <v>0.39</v>
       </c>
       <c r="H43" t="n">
         <v>49.36</v>
@@ -2410,28 +2410,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.27</v>
+        <v>0.415</v>
       </c>
       <c r="E44" s="8" t="n">
-        <v>-0.0182</v>
+        <v>-0.0235</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>2824300</v>
+        <v>3384800</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="H44" t="n">
-        <v>45.07</v>
+        <v>42.82</v>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
@@ -2439,10 +2439,10 @@
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.277</v>
+        <v>0.443</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.298</v>
+        <v>0.432</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2455,28 +2455,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>0.0333</v>
+        <v>0.22</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>2813100</v>
+        <v>3334200</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="H45" t="n">
-        <v>28.99</v>
+        <v>44.76</v>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
@@ -2484,10 +2484,10 @@
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.519</v>
+        <v>0.223</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.701</v>
+        <v>0.239</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2500,28 +2500,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="E46" s="10" t="n">
-        <v>0</v>
+        <v>1.1</v>
+      </c>
+      <c r="E46" s="8" t="n">
+        <v>-0.0984</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>2646800</v>
+        <v>3295300</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.28</v>
+        <v>0.85</v>
       </c>
       <c r="H46" t="n">
-        <v>65.3</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="I46" s="9" t="inlineStr">
         <is>
@@ -2529,9 +2529,11 @@
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.311</v>
-      </c>
-      <c r="K46" s="2" t="n"/>
+        <v>0.798</v>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>0.543</v>
+      </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
     </row>
@@ -2543,28 +2545,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>0.405</v>
+        <v>0.125</v>
       </c>
       <c r="E47" s="8" t="n">
-        <v>-0.0122</v>
+        <v>-0.0385</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>2587200</v>
+        <v>3264700</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>1.39</v>
+        <v>0.14</v>
       </c>
       <c r="H47" t="n">
-        <v>36.17</v>
+        <v>36.74</v>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
@@ -2572,10 +2574,10 @@
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.417</v>
+        <v>0.148</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0.436</v>
+        <v>0.148</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2588,28 +2590,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="E48" s="8" t="n">
-        <v>-0.0109</v>
+        <v>0.15</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>0.0345</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>2550700</v>
+        <v>3211900</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.19</v>
+        <v>0.04</v>
       </c>
       <c r="H48" t="n">
-        <v>44.88</v>
+        <v>46.24</v>
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
@@ -2617,10 +2619,10 @@
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>2.785</v>
+        <v>0.163</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>2.728</v>
+        <v>0.137</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2633,39 +2635,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="E49" s="10" t="n">
-        <v>0</v>
+        <v>0.44</v>
+      </c>
+      <c r="E49" s="8" t="n">
+        <v>-0.0435</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>2516100</v>
+        <v>3172000</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.29</v>
+        <v>0.61</v>
       </c>
       <c r="H49" t="n">
-        <v>42.13</v>
-      </c>
-      <c r="I49" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.7</v>
+      </c>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.384</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0.84</v>
+        <v>0.357</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
@@ -2678,39 +2680,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="E50" s="3" t="n">
-        <v>0.0066</v>
+        <v>0.735</v>
+      </c>
+      <c r="E50" s="8" t="n">
+        <v>-0.0329</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>2494600</v>
+        <v>3036900</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.77</v>
+        <v>0.67</v>
       </c>
       <c r="H50" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="I50" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.06</v>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>2.769</v>
+        <v>0.781</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>2.382</v>
+        <v>0.803</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2723,28 +2725,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>4.86</v>
-      </c>
-      <c r="E51" s="3" t="n">
-        <v>0.0021</v>
+        <v>0.265</v>
+      </c>
+      <c r="E51" s="8" t="n">
+        <v>-0.0364</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>2365500</v>
+        <v>3033100</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.09</v>
+        <v>0.36</v>
       </c>
       <c r="H51" t="n">
-        <v>48.97</v>
+        <v>42.94</v>
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
@@ -2752,10 +2754,10 @@
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>4.921</v>
+        <v>0.277</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>4.709</v>
+        <v>0.298</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2768,28 +2770,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="E52" s="8" t="n">
-        <v>-0.0252</v>
+        <v>2.74</v>
+      </c>
+      <c r="E52" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>2359700</v>
+        <v>2949500</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.58</v>
+        <v>0.22</v>
       </c>
       <c r="H52" t="n">
-        <v>52.79</v>
+        <v>47.1</v>
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
@@ -2797,10 +2799,10 @@
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1.163</v>
+        <v>2.788</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>1.091</v>
+        <v>2.729</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2813,39 +2815,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="E53" s="8" t="n">
-        <v>-0.0492</v>
+        <v>0.46</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>0.0222</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>2325200</v>
+        <v>2897200</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.6</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H53" t="n">
-        <v>81.16</v>
-      </c>
-      <c r="I53" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.43</v>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.804</v>
+        <v>0.518</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0.544</v>
+        <v>0.701</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2858,39 +2860,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E54" s="8" t="n">
-        <v>-0.0299</v>
+        <v>0.89</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>0.0171</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>2265300</v>
+        <v>2882000</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.41</v>
+        <v>0.34</v>
       </c>
       <c r="H54" t="n">
-        <v>57.47</v>
-      </c>
-      <c r="I54" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.65</v>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>6.111</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>5.878</v>
+        <v>0.84</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2903,28 +2905,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E55" s="8" t="n">
-        <v>-0.0186</v>
+        <v>4.88</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>0.0062</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>2221200</v>
+        <v>2853000</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.6</v>
+        <v>0.11</v>
       </c>
       <c r="H55" t="n">
-        <v>45.85</v>
+        <v>49.99</v>
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
@@ -2932,10 +2934,10 @@
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.822</v>
+        <v>4.923</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0.773</v>
+        <v>4.709</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2948,40 +2950,38 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="E56" s="8" t="n">
-        <v>-0.024</v>
+        <v>0.355</v>
+      </c>
+      <c r="E56" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>2155500</v>
+        <v>2743000</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.15</v>
+        <v>0.29</v>
       </c>
       <c r="H56" t="n">
-        <v>33.92</v>
-      </c>
-      <c r="I56" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.3</v>
+      </c>
+      <c r="I56" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>2.175</v>
-      </c>
-      <c r="K56" s="2" t="n">
-        <v>2.228</v>
-      </c>
+        <v>0.311</v>
+      </c>
+      <c r="K56" s="2" t="n"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
     </row>
@@ -2993,39 +2993,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="E57" s="10" t="n">
-        <v>0</v>
+        <v>7.37</v>
+      </c>
+      <c r="E57" s="8" t="n">
+        <v>-0.0466</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>2089500</v>
+        <v>2700300</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.88</v>
+        <v>0.68</v>
       </c>
       <c r="H57" t="n">
-        <v>66.36</v>
-      </c>
-      <c r="I57" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.98</v>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.642</v>
+        <v>7.381</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0.548</v>
+        <v>6.868</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3047,19 +3047,19 @@
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>0.735</v>
+        <v>0.74</v>
       </c>
       <c r="E58" s="8" t="n">
-        <v>-0.0329</v>
+        <v>-0.0263</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>2072000</v>
+        <v>2646500</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.3</v>
+        <v>0.38</v>
       </c>
       <c r="H58" t="n">
-        <v>51.56</v>
+        <v>52.48</v>
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.743</v>
+        <v>0.744</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0.669</v>
+        <v>0.67</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3083,39 +3083,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="E59" s="8" t="n">
-        <v>-0.0556</v>
+        <v>3.07</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>0.0066</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>2016500</v>
+        <v>2642600</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.5</v>
+        <v>0.82</v>
       </c>
       <c r="H59" t="n">
-        <v>51.06</v>
-      </c>
-      <c r="I59" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>81.5</v>
+      </c>
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.041</v>
+        <v>2.769</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0.895</v>
+        <v>2.382</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3128,39 +3128,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>7.52</v>
-      </c>
-      <c r="E60" s="3" t="n">
-        <v>0.0027</v>
+        <v>2.03</v>
+      </c>
+      <c r="E60" s="8" t="n">
+        <v>-0.024</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>1990500</v>
+        <v>2596300</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="H60" t="n">
-        <v>45.48</v>
-      </c>
-      <c r="I60" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.92</v>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>7.582</v>
+        <v>2.175</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>7.711</v>
+        <v>2.228</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
@@ -3182,19 +3182,19 @@
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>0.41</v>
+        <v>0.405</v>
       </c>
       <c r="E61" s="8" t="n">
-        <v>-0.0353</v>
+        <v>-0.0471</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>1972800</v>
+        <v>2595000</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="H61" t="n">
-        <v>46.73</v>
+        <v>45.47</v>
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
@@ -3218,28 +3218,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>0.485</v>
+        <v>0.4</v>
       </c>
       <c r="E62" s="8" t="n">
-        <v>-0.0202</v>
+        <v>-0.0244</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>1950400</v>
+        <v>2587900</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.23</v>
+        <v>1.39</v>
       </c>
       <c r="H62" t="n">
-        <v>39.31</v>
+        <v>33.55</v>
       </c>
       <c r="I62" s="6" t="inlineStr">
         <is>
@@ -3247,10 +3247,10 @@
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.514</v>
+        <v>0.417</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0.527</v>
+        <v>0.436</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
@@ -3263,39 +3263,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>0.57</v>
+        <v>6.46</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>-0.0579</v>
+        <v>-0.0358</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>1897400</v>
+        <v>2444100</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.37</v>
+        <v>0.44</v>
       </c>
       <c r="H63" t="n">
-        <v>55.34</v>
-      </c>
-      <c r="I63" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.81</v>
+      </c>
+      <c r="I63" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.5610000000000001</v>
+        <v>6.107</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0.51</v>
+        <v>5.877</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
@@ -3308,28 +3308,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>0.585</v>
+        <v>4.57</v>
       </c>
       <c r="E64" s="8" t="n">
-        <v>-0.0488</v>
+        <v>-0.0151</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>1845200</v>
+        <v>2432400</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.43</v>
+        <v>0.25</v>
       </c>
       <c r="H64" t="n">
-        <v>47.76</v>
+        <v>42.88</v>
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.6</v>
+        <v>4.645</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0.585</v>
+        <v>4.636</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
@@ -3353,28 +3353,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="E65" s="3" t="n">
-        <v>0.0016</v>
+        <v>2.5</v>
+      </c>
+      <c r="E65" s="8" t="n">
+        <v>-0.031</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>1821300</v>
+        <v>2423700</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.3</v>
+        <v>0.41</v>
       </c>
       <c r="H65" t="n">
-        <v>42.34</v>
+        <v>41.91</v>
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
@@ -3382,10 +3382,10 @@
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>6.412</v>
+        <v>2.616</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>6.789</v>
+        <v>2.6</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3398,28 +3398,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5218</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>VANTNRG</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>0.3</v>
+        <v>0.795</v>
       </c>
       <c r="E66" s="8" t="n">
-        <v>-0.0164</v>
+        <v>-0.0124</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>1767900</v>
+        <v>2387500</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="H66" t="n">
-        <v>28.9</v>
+        <v>46.65</v>
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.324</v>
+        <v>0.823</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0.332</v>
+        <v>0.773</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3443,28 +3443,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>2.46</v>
+        <v>1.16</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>-0.04650000000000001</v>
+        <v>-0.0252</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>1745200</v>
+        <v>2365000</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.29</v>
+        <v>0.58</v>
       </c>
       <c r="H67" t="n">
-        <v>39.72</v>
+        <v>52.79</v>
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>2.612</v>
+        <v>1.163</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>2.599</v>
+        <v>1.091</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
@@ -3488,28 +3488,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>VANTNRG</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>0.52</v>
+        <v>0.295</v>
       </c>
       <c r="E68" s="8" t="n">
-        <v>-0.03700000000000001</v>
+        <v>-0.0328</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>1724600</v>
+        <v>2343000</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.12</v>
+        <v>0.73</v>
       </c>
       <c r="H68" t="n">
-        <v>52.58</v>
+        <v>26.9</v>
       </c>
       <c r="I68" s="6" t="inlineStr">
         <is>
@@ -3517,10 +3517,10 @@
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.52</v>
+        <v>0.323</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0.454</v>
+        <v>0.332</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
@@ -3533,28 +3533,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>2.77</v>
+        <v>6.32</v>
       </c>
       <c r="E69" s="8" t="n">
-        <v>-0.0072</v>
+        <v>-0.0032</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>1702200</v>
+        <v>2270700</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
       <c r="H69" t="n">
-        <v>55.23</v>
+        <v>40.73</v>
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
@@ -3562,10 +3562,10 @@
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>2.763</v>
+        <v>6.409</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>2.157</v>
+        <v>6.789</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
@@ -3578,28 +3578,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>0.655</v>
+        <v>1.02</v>
       </c>
       <c r="E70" s="8" t="n">
-        <v>-0.0296</v>
+        <v>-0.0556</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>1685100</v>
+        <v>2251800</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.19</v>
+        <v>0.55</v>
       </c>
       <c r="H70" t="n">
-        <v>43.84</v>
+        <v>51.06</v>
       </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
@@ -3607,10 +3607,10 @@
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.6879999999999999</v>
+        <v>1.041</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.895</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
@@ -3623,39 +3623,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="E71" s="8" t="n">
-        <v>-0.0316</v>
+        <v>7.51</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>0.0013</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>1682000</v>
+        <v>2213300</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.22</v>
+        <v>0.15</v>
       </c>
       <c r="H71" t="n">
-        <v>26.61</v>
-      </c>
-      <c r="I71" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.98</v>
+      </c>
+      <c r="I71" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.507</v>
+        <v>7.581</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0.5620000000000001</v>
+        <v>7.71</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
@@ -3668,39 +3668,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="E72" s="3" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E72" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>1636800</v>
+        <v>2165700</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.4</v>
+        <v>0.91</v>
       </c>
       <c r="H72" t="n">
-        <v>44.83</v>
-      </c>
-      <c r="I72" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.36</v>
+      </c>
+      <c r="I72" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1.452</v>
+        <v>0.642</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>1.466</v>
+        <v>0.548</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
@@ -3713,39 +3713,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E73" s="8" t="n">
-        <v>-0.0429</v>
+        <v>0.405</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>0.0125</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>1617600</v>
+        <v>2153500</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.26</v>
+        <v>0.17</v>
       </c>
       <c r="H73" t="n">
-        <v>56.59</v>
-      </c>
-      <c r="I73" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.8</v>
+      </c>
+      <c r="I73" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.767</v>
+        <v>0.391</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0.68</v>
+        <v>0.378</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
@@ -3758,28 +3758,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E74" s="8" t="n">
-        <v>-0.0246</v>
+        <v>2.8</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>0.0036</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>1615000</v>
+        <v>2126400</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.21</v>
+        <v>0.44</v>
       </c>
       <c r="H74" t="n">
-        <v>53.56</v>
+        <v>56.38</v>
       </c>
       <c r="I74" s="6" t="inlineStr">
         <is>
@@ -3787,10 +3787,10 @@
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>1.169</v>
+        <v>2.766</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>1.131</v>
+        <v>2.158</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr"/>
@@ -3803,28 +3803,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>0.48</v>
+        <v>0.575</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>-0.04</v>
+        <v>-0.0496</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>1601800</v>
+        <v>2106400</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.22</v>
+        <v>0.41</v>
       </c>
       <c r="H75" t="n">
-        <v>28.41</v>
+        <v>56.68</v>
       </c>
       <c r="I75" s="6" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.556</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0.626</v>
+        <v>0.51</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr"/>
@@ -3848,39 +3848,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>0.975</v>
+        <v>2.09</v>
       </c>
       <c r="E76" s="8" t="n">
-        <v>-0.0441</v>
+        <v>-0.0142</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>1574100</v>
+        <v>2024600</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.34</v>
+        <v>0.1</v>
       </c>
       <c r="H76" t="n">
-        <v>42.79</v>
-      </c>
-      <c r="I76" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.7</v>
+      </c>
+      <c r="I76" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1.049</v>
+        <v>2.108</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0.926</v>
+        <v>2.097</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
@@ -3893,39 +3893,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E77" s="10" t="n">
-        <v>0</v>
+        <v>0.46</v>
+      </c>
+      <c r="E77" s="8" t="n">
+        <v>-0.0316</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>1542100</v>
+        <v>2021300</v>
       </c>
       <c r="G77" s="5" t="n">
         <v>0.26</v>
       </c>
       <c r="H77" t="n">
-        <v>66.89</v>
-      </c>
-      <c r="I77" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>26.61</v>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.792</v>
+        <v>0.507</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0.769</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
@@ -3938,28 +3938,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>8524</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>TALIWRK</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E78" s="8" t="n">
-        <v>-0.0213</v>
+        <v>0.865</v>
+      </c>
+      <c r="E78" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>1454300</v>
+        <v>1992800</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.71</v>
+        <v>0.64</v>
       </c>
       <c r="H78" t="n">
-        <v>37.06</v>
+        <v>51.9</v>
       </c>
       <c r="I78" s="6" t="inlineStr">
         <is>
@@ -3967,10 +3967,10 @@
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.247</v>
+        <v>0.865</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0.258</v>
+        <v>0.859</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
@@ -3983,28 +3983,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>7.31</v>
+        <v>0.49</v>
       </c>
       <c r="E79" s="8" t="n">
-        <v>-0.0027</v>
+        <v>-0.0101</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>1427900</v>
+        <v>1986400</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.14</v>
+        <v>0.23</v>
       </c>
       <c r="H79" t="n">
-        <v>33.47</v>
+        <v>40.63</v>
       </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
@@ -4012,10 +4012,10 @@
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>7.5</v>
+        <v>0.514</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>8.003</v>
+        <v>0.527</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
@@ -4028,28 +4028,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E80" s="10" t="n">
-        <v>0</v>
+        <v>0.59</v>
+      </c>
+      <c r="E80" s="8" t="n">
+        <v>-0.0407</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>1420800</v>
+        <v>1985500</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="H80" t="n">
-        <v>51.9</v>
+        <v>48.81</v>
       </c>
       <c r="I80" s="6" t="inlineStr">
         <is>
@@ -4057,10 +4057,10 @@
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.865</v>
+        <v>0.6</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0.859</v>
+        <v>0.585</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
@@ -4073,28 +4073,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>0.95</v>
+        <v>0.52</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>-0.0052</v>
+        <v>-0.03700000000000001</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>1409000</v>
+        <v>1961800</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.25</v>
+        <v>0.13</v>
       </c>
       <c r="H81" t="n">
-        <v>63.6</v>
+        <v>52.58</v>
       </c>
       <c r="I81" s="6" t="inlineStr">
         <is>
@@ -4102,10 +4102,10 @@
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.917</v>
+        <v>0.52</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0.871</v>
+        <v>0.454</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
@@ -4118,28 +4118,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="E82" s="8" t="n">
-        <v>-0.0156</v>
+        <v>-0.0222</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>1408900</v>
+        <v>1893400</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.59</v>
+        <v>0.21</v>
       </c>
       <c r="H82" t="n">
-        <v>48.11</v>
+        <v>44.67</v>
       </c>
       <c r="I82" s="6" t="inlineStr">
         <is>
@@ -4147,10 +4147,10 @@
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.637</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0.619</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr"/>
@@ -4163,28 +4163,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>3.71</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="E83" s="8" t="n">
-        <v>-0.0339</v>
+        <v>-0.0106</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>1399000</v>
+        <v>1858700</v>
       </c>
       <c r="G83" s="5" t="n">
         <v>0.49</v>
       </c>
       <c r="H83" t="n">
-        <v>44.17</v>
+        <v>27.89</v>
       </c>
       <c r="I83" s="6" t="inlineStr">
         <is>
@@ -4192,10 +4192,10 @@
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>3.857</v>
+        <v>0.979</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>3.646</v>
+        <v>1.059</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
@@ -4208,28 +4208,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>7.33</v>
+        <v>0.95</v>
       </c>
       <c r="E84" s="8" t="n">
-        <v>-0.0517</v>
+        <v>-0.0052</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>1397900</v>
+        <v>1795000</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.35</v>
+        <v>0.32</v>
       </c>
       <c r="H84" t="n">
-        <v>52.06</v>
+        <v>63.6</v>
       </c>
       <c r="I84" s="6" t="inlineStr">
         <is>
@@ -4237,10 +4237,10 @@
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>7.377</v>
+        <v>0.917</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>6.867</v>
+        <v>0.871</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
@@ -4253,28 +4253,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E85" s="3" t="n">
-        <v>0.0308</v>
+        <v>1.18</v>
+      </c>
+      <c r="E85" s="8" t="n">
+        <v>-0.0328</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>1378600</v>
+        <v>1753800</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
       <c r="H85" t="n">
-        <v>47.07</v>
+        <v>52.34</v>
       </c>
       <c r="I85" s="6" t="inlineStr">
         <is>
@@ -4282,10 +4282,10 @@
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.336</v>
+        <v>1.168</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0.343</v>
+        <v>1.13</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr"/>
@@ -4298,28 +4298,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>1.24</v>
+        <v>0.975</v>
       </c>
       <c r="E86" s="8" t="n">
-        <v>-0.0677</v>
+        <v>-0.0441</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>1367600</v>
+        <v>1748800</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.6</v>
+        <v>0.38</v>
       </c>
       <c r="H86" t="n">
-        <v>51.76</v>
+        <v>42.79</v>
       </c>
       <c r="I86" s="6" t="inlineStr">
         <is>
@@ -4327,10 +4327,10 @@
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.246</v>
+        <v>1.049</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>1.167</v>
+        <v>0.926</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
@@ -4343,28 +4343,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>0.76</v>
+        <v>7.3</v>
       </c>
       <c r="E87" s="8" t="n">
-        <v>-0.013</v>
+        <v>-0.004099999999999999</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>1359400</v>
+        <v>1722300</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="H87" t="n">
-        <v>44.91</v>
+        <v>33.12</v>
       </c>
       <c r="I87" s="6" t="inlineStr">
         <is>
@@ -4372,10 +4372,10 @@
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.777</v>
+        <v>7.499</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0.773</v>
+        <v>8.003</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
@@ -4388,28 +4388,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E88" s="10" t="n">
-        <v>0</v>
+        <v>2.79</v>
+      </c>
+      <c r="E88" s="8" t="n">
+        <v>-0.0245</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>1354200</v>
+        <v>1712100</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.22</v>
+        <v>0.52</v>
       </c>
       <c r="H88" t="n">
-        <v>40.5</v>
+        <v>38.96</v>
       </c>
       <c r="I88" s="6" t="inlineStr">
         <is>
@@ -4417,10 +4417,10 @@
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.32</v>
+        <v>2.926</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0.338</v>
+        <v>3.024</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr"/>
@@ -4433,28 +4433,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MALAKOF</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>0.75</v>
+        <v>3.74</v>
       </c>
       <c r="E89" s="8" t="n">
-        <v>-0.0132</v>
+        <v>-0.026</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>1352900</v>
+        <v>1711600</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="H89" t="n">
-        <v>39.04</v>
+        <v>45.59</v>
       </c>
       <c r="I89" s="6" t="inlineStr">
         <is>
@@ -4462,10 +4462,10 @@
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.783</v>
+        <v>3.86</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0.803</v>
+        <v>3.646</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
@@ -4478,28 +4478,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E90" s="10" t="n">
-        <v>0</v>
+        <v>0.78</v>
+      </c>
+      <c r="E90" s="8" t="n">
+        <v>-0.0429</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>1346800</v>
+        <v>1698200</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.32</v>
+        <v>0.27</v>
       </c>
       <c r="H90" t="n">
-        <v>23.74</v>
+        <v>56.59</v>
       </c>
       <c r="I90" s="6" t="inlineStr">
         <is>
@@ -4507,10 +4507,10 @@
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>1.424</v>
+        <v>0.767</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>1.58</v>
+        <v>0.68</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr"/>
@@ -4523,39 +4523,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="E91" s="8" t="n">
-        <v>-0.0504</v>
+        <v>0.805</v>
+      </c>
+      <c r="E91" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>1334400</v>
+        <v>1686800</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.42</v>
+        <v>0.29</v>
       </c>
       <c r="H91" t="n">
-        <v>33.87</v>
-      </c>
-      <c r="I91" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.89</v>
+      </c>
+      <c r="I91" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.737</v>
+        <v>0.792</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0.746</v>
+        <v>0.769</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr"/>
@@ -4568,28 +4568,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>3.66</v>
+        <v>0.48</v>
       </c>
       <c r="E92" s="8" t="n">
-        <v>-0.0317</v>
+        <v>-0.04</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>1318400</v>
+        <v>1685900</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0.14</v>
+        <v>0.23</v>
       </c>
       <c r="H92" t="n">
-        <v>54.25</v>
+        <v>28.41</v>
       </c>
       <c r="I92" s="6" t="inlineStr">
         <is>
@@ -4597,10 +4597,10 @@
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>3.617</v>
+        <v>0.556</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>2.917</v>
+        <v>0.626</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="7" t="inlineStr"/>
@@ -4613,28 +4613,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="E93" s="8" t="n">
-        <v>-0.0174</v>
+        <v>1.44</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>0.006999999999999999</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>1304400</v>
+        <v>1672600</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.27</v>
+        <v>0.41</v>
       </c>
       <c r="H93" t="n">
-        <v>41.59</v>
+        <v>44.83</v>
       </c>
       <c r="I93" s="6" t="inlineStr">
         <is>
@@ -4642,10 +4642,10 @@
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>1.742</v>
+        <v>1.452</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>1.772</v>
+        <v>1.466</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="7" t="inlineStr"/>
@@ -4658,28 +4658,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>0.9350000000000001</v>
+        <v>2.61</v>
       </c>
       <c r="E94" s="8" t="n">
-        <v>-0.0106</v>
+        <v>-0.0333</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>1290600</v>
+        <v>1640800</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="H94" t="n">
-        <v>27.89</v>
+        <v>35.52</v>
       </c>
       <c r="I94" s="6" t="inlineStr">
         <is>
@@ -4687,10 +4687,10 @@
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.979</v>
+        <v>2.878</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>1.059</v>
+        <v>2.87</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="7" t="inlineStr"/>
@@ -4703,28 +4703,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>TDM</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E95" s="10" t="n">
-        <v>0</v>
+        <v>1.27</v>
+      </c>
+      <c r="E95" s="8" t="n">
+        <v>-0.0451</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>1283200</v>
+        <v>1606800</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>2.61</v>
+        <v>0.71</v>
       </c>
       <c r="H95" t="n">
-        <v>27.29</v>
+        <v>54.81</v>
       </c>
       <c r="I95" s="6" t="inlineStr">
         <is>
@@ -4732,10 +4732,10 @@
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.208</v>
+        <v>1.249</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0.217</v>
+        <v>1.167</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="7" t="inlineStr"/>
@@ -4748,39 +4748,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="E96" s="8" t="n">
-        <v>-0.0315</v>
+        <v>1.93</v>
+      </c>
+      <c r="E96" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>1246700</v>
+        <v>1577800</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.38</v>
+        <v>0.26</v>
       </c>
       <c r="H96" t="n">
-        <v>37.93</v>
-      </c>
-      <c r="I96" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.34</v>
+      </c>
+      <c r="I96" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>2.924</v>
+        <v>1.926</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>3.023</v>
+        <v>1.953</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="7" t="inlineStr"/>
@@ -4793,28 +4793,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0272</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>TTVHB</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E97" s="8" t="n">
-        <v>-0.0208</v>
+        <v>0.335</v>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>0.0308</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>1227200</v>
+        <v>1549700</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>0.51</v>
+        <v>0.3</v>
       </c>
       <c r="H97" t="n">
-        <v>44.1</v>
+        <v>47.07</v>
       </c>
       <c r="I97" s="6" t="inlineStr">
         <is>
@@ -4822,10 +4822,10 @@
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.248</v>
+        <v>0.336</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0.255</v>
+        <v>0.343</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="7" t="inlineStr"/>
@@ -4838,28 +4838,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>BPURI</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E98" s="8" t="n">
-        <v>-0.0227</v>
+        <v>1.26</v>
+      </c>
+      <c r="E98" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>1223900</v>
+        <v>1536400</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>2.35</v>
+        <v>0.37</v>
       </c>
       <c r="H98" t="n">
-        <v>40.22</v>
+        <v>23.74</v>
       </c>
       <c r="I98" s="6" t="inlineStr">
         <is>
@@ -4867,10 +4867,10 @@
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.225</v>
+        <v>1.424</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0.233</v>
+        <v>1.58</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr"/>
@@ -4883,28 +4883,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>1.2</v>
+        <v>0.71</v>
       </c>
       <c r="E99" s="8" t="n">
-        <v>-0.0323</v>
+        <v>-0.0274</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>1218000</v>
+        <v>1499800</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0.34</v>
+        <v>0.1</v>
       </c>
       <c r="H99" t="n">
-        <v>49.35</v>
+        <v>43.13</v>
       </c>
       <c r="I99" s="6" t="inlineStr">
         <is>
@@ -4912,10 +4912,10 @@
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1.25</v>
+        <v>0.764</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>1.05</v>
+        <v>0.722</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="7" t="inlineStr"/>
@@ -4928,28 +4928,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="E100" s="8" t="n">
-        <v>-0.0189</v>
+        <v>12.98</v>
+      </c>
+      <c r="E100" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>1203900</v>
+        <v>1498600</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>0.06</v>
+        <v>0.17</v>
       </c>
       <c r="H100" t="n">
-        <v>46.32</v>
+        <v>44.06</v>
       </c>
       <c r="I100" s="9" t="inlineStr">
         <is>
@@ -4957,10 +4957,10 @@
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>2.107</v>
+        <v>13.021</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>2.096</v>
+        <v>13.468</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr"/>
@@ -4973,28 +4973,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="E101" s="3" t="n">
-        <v>0.0412</v>
+        <v>3.71</v>
+      </c>
+      <c r="E101" s="8" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>1202100</v>
+        <v>1493400</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>0.78</v>
+        <v>0.15</v>
       </c>
       <c r="H101" t="n">
-        <v>46.91</v>
+        <v>55.61</v>
       </c>
       <c r="I101" s="6" t="inlineStr">
         <is>
@@ -5002,10 +5002,10 @@
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.914</v>
+        <v>3.622</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0.865</v>
+        <v>2.918</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="7" t="inlineStr"/>
@@ -5018,28 +5018,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>0.745</v>
+        <v>2.98</v>
       </c>
       <c r="E102" s="8" t="n">
-        <v>-0.0449</v>
+        <v>-0.0387</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>1188400</v>
+        <v>1463300</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0.52</v>
+        <v>0.47</v>
       </c>
       <c r="H102" t="n">
-        <v>54.2</v>
+        <v>50.16</v>
       </c>
       <c r="I102" s="6" t="inlineStr">
         <is>
@@ -5047,10 +5047,10 @@
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.729</v>
+        <v>3.026</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0.701</v>
+        <v>2.846</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="7" t="inlineStr"/>
@@ -5063,31 +5063,40 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>9776</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>RSSB</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E103" s="10" t="n">
-        <v>0</v>
+        <v>0.76</v>
+      </c>
+      <c r="E103" s="8" t="n">
+        <v>-0.013</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>1183800</v>
-      </c>
-      <c r="G103" s="5" t="n"/>
+        <v>1461500</v>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H103" t="n">
+        <v>44.91</v>
+      </c>
       <c r="I103" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J103" s="2" t="n"/>
-      <c r="K103" s="2" t="n"/>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="K103" s="2" t="n">
+        <v>0.773</v>
+      </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="7" t="inlineStr"/>
     </row>
@@ -5099,39 +5108,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>TALIWRK</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E104" s="3" t="n">
-        <v>0.0351</v>
+        <v>0.23</v>
+      </c>
+      <c r="E104" s="8" t="n">
+        <v>-0.0213</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>1183700</v>
+        <v>1461500</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>1.24</v>
+        <v>0.71</v>
       </c>
       <c r="H104" t="n">
-        <v>66.28</v>
-      </c>
-      <c r="I104" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.06</v>
+      </c>
+      <c r="I104" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.275</v>
+        <v>0.247</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0.267</v>
+        <v>0.258</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="7" t="inlineStr"/>
@@ -5144,28 +5153,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>0272</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>TTVHB</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>2.99</v>
+        <v>0.235</v>
       </c>
       <c r="E105" s="8" t="n">
-        <v>-0.0355</v>
+        <v>-0.0208</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>1169800</v>
+        <v>1436900</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>0.37</v>
+        <v>0.59</v>
       </c>
       <c r="H105" t="n">
-        <v>50.62</v>
+        <v>44.1</v>
       </c>
       <c r="I105" s="6" t="inlineStr">
         <is>
@@ -5173,10 +5182,10 @@
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>3.027</v>
+        <v>0.248</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>2.846</v>
+        <v>0.255</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="7" t="inlineStr"/>
@@ -5189,39 +5198,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>2.26</v>
+        <v>0.63</v>
       </c>
       <c r="E106" s="8" t="n">
-        <v>-0.0216</v>
+        <v>-0.0156</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>1103600</v>
+        <v>1408900</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>0.29</v>
+        <v>0.59</v>
       </c>
       <c r="H106" t="n">
-        <v>55.35</v>
-      </c>
-      <c r="I106" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.11</v>
+      </c>
+      <c r="I106" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>2.206</v>
+        <v>0.637</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>2.151</v>
+        <v>0.619</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="7" t="inlineStr"/>
@@ -5234,28 +5243,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="E107" s="8" t="n">
-        <v>-0.0442</v>
+        <v>0.305</v>
+      </c>
+      <c r="E107" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>1098400</v>
+        <v>1393500</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>0.46</v>
+        <v>0.22</v>
       </c>
       <c r="H107" t="n">
-        <v>34.06</v>
+        <v>40.5</v>
       </c>
       <c r="I107" s="6" t="inlineStr">
         <is>
@@ -5263,10 +5272,10 @@
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>1.231</v>
+        <v>0.32</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>1.303</v>
+        <v>0.338</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="7" t="inlineStr"/>
@@ -5279,28 +5288,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>10.28</v>
+        <v>0.665</v>
       </c>
       <c r="E108" s="8" t="n">
-        <v>-0.0338</v>
+        <v>-0.0432</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>1093800</v>
+        <v>1377500</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>0.3</v>
+        <v>0.44</v>
       </c>
       <c r="H108" t="n">
-        <v>51.56</v>
+        <v>34.5</v>
       </c>
       <c r="I108" s="6" t="inlineStr">
         <is>
@@ -5308,10 +5317,10 @@
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>10.384</v>
+        <v>0.738</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>9.692</v>
+        <v>0.746</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="7" t="inlineStr"/>
@@ -5324,28 +5333,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>5120</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>AMFIRST</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E109" s="8" t="n">
-        <v>-0.0294</v>
+        <v>0.89</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>0.0471</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>1091100</v>
+        <v>1372900</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>3.72</v>
+        <v>0.9</v>
       </c>
       <c r="H109" t="n">
-        <v>26.77</v>
+        <v>47.67</v>
       </c>
       <c r="I109" s="6" t="inlineStr">
         <is>
@@ -5353,10 +5362,10 @@
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.344</v>
+        <v>0.914</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0.345</v>
+        <v>0.865</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="7" t="inlineStr"/>
@@ -5369,39 +5378,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>7173</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>TOYOVEN</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E110" s="8" t="n">
-        <v>-0.0213</v>
+        <v>0.255</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>0.0851</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>1088100</v>
+        <v>1350100</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>0.22</v>
+        <v>2.08</v>
       </c>
       <c r="H110" t="n">
-        <v>43.72</v>
-      </c>
-      <c r="I110" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.08</v>
+      </c>
+      <c r="I110" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.247</v>
+        <v>0.217</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0.223</v>
+        <v>0.209</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="7" t="inlineStr"/>
@@ -5414,28 +5423,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0466</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>SRKKAI</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>0.495</v>
+        <v>1.68</v>
       </c>
       <c r="E111" s="8" t="n">
-        <v>-0.0294</v>
+        <v>-0.0233</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>1084100</v>
+        <v>1343800</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>0.91</v>
+        <v>0.28</v>
       </c>
       <c r="H111" t="n">
-        <v>39.16</v>
+        <v>40.51</v>
       </c>
       <c r="I111" s="6" t="inlineStr">
         <is>
@@ -5443,10 +5452,10 @@
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.518</v>
+        <v>1.741</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0.531</v>
+        <v>1.772</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="7" t="inlineStr"/>
@@ -5459,39 +5468,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0337</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>0.24</v>
+        <v>3.81</v>
       </c>
       <c r="E112" s="8" t="n">
-        <v>-0.04</v>
+        <v>-0.0155</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>1050000</v>
+        <v>1309800</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="H112" t="n">
-        <v>50.37</v>
-      </c>
-      <c r="I112" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.3</v>
+      </c>
+      <c r="I112" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.24</v>
+        <v>3.971</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0.243</v>
+        <v>3.522</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="7" t="inlineStr"/>
@@ -5504,28 +5513,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>2.62</v>
+        <v>0.75</v>
       </c>
       <c r="E113" s="8" t="n">
-        <v>-0.0296</v>
+        <v>-0.0385</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>1046400</v>
+        <v>1293800</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>0.21</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H113" t="n">
-        <v>35.88</v>
+        <v>55.01</v>
       </c>
       <c r="I113" s="6" t="inlineStr">
         <is>
@@ -5533,10 +5542,10 @@
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>2.879</v>
+        <v>0.729</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>2.87</v>
+        <v>0.701</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="7" t="inlineStr"/>
@@ -5549,28 +5558,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>6181</t>
+          <t>2054</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>MALTON</t>
+          <t>TDM</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="E114" s="8" t="n">
-        <v>-0.0698</v>
+      <c r="E114" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>1037400</v>
+        <v>1286500</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>1.49</v>
+        <v>2.62</v>
       </c>
       <c r="H114" t="n">
-        <v>32.72</v>
+        <v>27.29</v>
       </c>
       <c r="I114" s="6" t="inlineStr">
         <is>
@@ -5578,10 +5587,10 @@
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.218</v>
+        <v>0.208</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0.225</v>
+        <v>0.217</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="7" t="inlineStr"/>
@@ -5594,28 +5603,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="E115" s="8" t="n">
-        <v>-0.0472</v>
+        <v>-0.0403</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>981000</v>
+        <v>1273200</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="H115" t="n">
-        <v>44.54</v>
+        <v>48.47</v>
       </c>
       <c r="I115" s="6" t="inlineStr">
         <is>
@@ -5623,10 +5632,10 @@
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>1.285</v>
+        <v>1.249</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>1.217</v>
+        <v>1.05</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="7" t="inlineStr"/>
@@ -5639,28 +5648,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>3.78</v>
+        <v>0.35</v>
       </c>
       <c r="E116" s="8" t="n">
-        <v>-0.0233</v>
+        <v>-0.0141</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>923700</v>
+        <v>1249800</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="H116" t="n">
-        <v>46.36</v>
+        <v>50.37</v>
       </c>
       <c r="I116" s="6" t="inlineStr">
         <is>
@@ -5668,10 +5677,10 @@
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>3.968</v>
+        <v>0.355</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>3.522</v>
+        <v>0.326</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="7" t="inlineStr"/>
@@ -5684,28 +5693,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>0.87</v>
+        <v>1.23</v>
       </c>
       <c r="E117" s="8" t="n">
-        <v>-0.0169</v>
+        <v>-0.0315</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>912700</v>
+        <v>1247300</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="H117" t="n">
-        <v>20.42</v>
+        <v>46.1</v>
       </c>
       <c r="I117" s="6" t="inlineStr">
         <is>
@@ -5713,10 +5722,10 @@
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.9330000000000001</v>
+        <v>1.287</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>0.98</v>
+        <v>1.217</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="7" t="inlineStr"/>
@@ -5729,28 +5738,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>BAUTO</t>
+          <t>BPURI</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>0.885</v>
+        <v>0.215</v>
       </c>
       <c r="E118" s="8" t="n">
-        <v>-0.0112</v>
+        <v>-0.0227</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>882400</v>
+        <v>1223900</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>2.35</v>
       </c>
       <c r="H118" t="n">
-        <v>35.62</v>
+        <v>40.22</v>
       </c>
       <c r="I118" s="6" t="inlineStr">
         <is>
@@ -5758,10 +5767,10 @@
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.914</v>
+        <v>0.225</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>0.931</v>
+        <v>0.233</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="7" t="inlineStr"/>
@@ -5774,28 +5783,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>2.43</v>
+        <v>0.87</v>
       </c>
       <c r="E119" s="8" t="n">
-        <v>-0.0122</v>
+        <v>-0.0169</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>860100</v>
+        <v>1208400</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.47</v>
       </c>
       <c r="H119" t="n">
-        <v>47.92</v>
+        <v>20.42</v>
       </c>
       <c r="I119" s="6" t="inlineStr">
         <is>
@@ -5803,10 +5812,10 @@
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>2.458</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>2.374</v>
+        <v>0.98</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="7" t="inlineStr"/>
@@ -5819,39 +5828,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E120" s="3" t="n">
-        <v>0.0091</v>
+        <v>1.09</v>
+      </c>
+      <c r="E120" s="8" t="n">
+        <v>-0.0354</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>842000</v>
+        <v>1202900</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>0.75</v>
+        <v>0.51</v>
       </c>
       <c r="H120" t="n">
-        <v>39.65</v>
-      </c>
-      <c r="I120" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.68</v>
+      </c>
+      <c r="I120" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.573</v>
+        <v>1.232</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0.615</v>
+        <v>1.303</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="7" t="inlineStr"/>
@@ -5864,28 +5873,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>0.63</v>
+        <v>10.42</v>
       </c>
       <c r="E121" s="8" t="n">
-        <v>-0.0382</v>
+        <v>-0.0207</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>823500</v>
+        <v>1202000</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>0.15</v>
+        <v>0.33</v>
       </c>
       <c r="H121" t="n">
-        <v>63.4</v>
+        <v>54.34</v>
       </c>
       <c r="I121" s="6" t="inlineStr">
         <is>
@@ -5893,10 +5902,10 @@
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.5620000000000001</v>
+        <v>10.397</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0.463</v>
+        <v>9.694000000000001</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="7" t="inlineStr"/>
@@ -5909,40 +5918,31 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>9776</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>THMY</t>
+          <t>RSSB</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="E122" s="8" t="n">
-        <v>-0.0377</v>
+        <v>0.325</v>
+      </c>
+      <c r="E122" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>772000</v>
-      </c>
-      <c r="G122" s="5" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="H122" t="n">
-        <v>47.7</v>
-      </c>
+        <v>1193800</v>
+      </c>
+      <c r="G122" s="5" t="n"/>
       <c r="I122" s="6" t="inlineStr">
         <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J122" s="2" t="n">
-        <v>2.111</v>
-      </c>
-      <c r="K122" s="2" t="n">
-        <v>1.983</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="n"/>
+      <c r="K122" s="2" t="n"/>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="7" t="inlineStr"/>
     </row>
@@ -5954,39 +5954,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>6.78</v>
+        <v>0.295</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>0.0059</v>
+        <v>0.0351</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>759000</v>
+        <v>1183700</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>0.17</v>
+        <v>1.24</v>
       </c>
       <c r="H123" t="n">
-        <v>51.24</v>
-      </c>
-      <c r="I123" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.28</v>
+      </c>
+      <c r="I123" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>6.761</v>
+        <v>0.275</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>6.835</v>
+        <v>0.267</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="7" t="inlineStr"/>
@@ -5999,39 +5999,39 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E124" s="8" t="n">
-        <v>-0.0441</v>
+        <v>2.51</v>
+      </c>
+      <c r="E124" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>749900</v>
+        <v>1174200</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>0.32</v>
+        <v>0.37</v>
       </c>
       <c r="H124" t="n">
-        <v>46.63</v>
-      </c>
-      <c r="I124" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>37.53</v>
+      </c>
+      <c r="I124" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>1.339</v>
+        <v>2.561</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>1.273</v>
+        <v>2.7</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="7" t="inlineStr"/>
@@ -6044,28 +6044,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>12.98</v>
-      </c>
-      <c r="E125" s="10" t="n">
-        <v>0</v>
+        <v>2.27</v>
+      </c>
+      <c r="E125" s="8" t="n">
+        <v>-0.0173</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>738900</v>
+        <v>1157600</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>0.08</v>
+        <v>0.3</v>
       </c>
       <c r="H125" t="n">
-        <v>44.06</v>
+        <v>56.23</v>
       </c>
       <c r="I125" s="9" t="inlineStr">
         <is>
@@ -6073,10 +6073,10 @@
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>13.021</v>
+        <v>2.207</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>13.468</v>
+        <v>2.152</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="7" t="inlineStr"/>
@@ -6089,39 +6089,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>10.04</v>
+        <v>1.64</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>0.006</v>
+        <v>0.0123</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>724400</v>
+        <v>1156500</v>
       </c>
       <c r="G126" s="5" t="n">
-        <v>0.05</v>
+        <v>0.17</v>
       </c>
       <c r="H126" t="n">
-        <v>49.55</v>
-      </c>
-      <c r="I126" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.81</v>
+      </c>
+      <c r="I126" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>10.01</v>
+        <v>1.616</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>10.168</v>
+        <v>1.703</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="7" t="inlineStr"/>
@@ -6134,39 +6134,39 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>0466</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>SRKKAI</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>2.5</v>
+        <v>0.49</v>
       </c>
       <c r="E127" s="8" t="n">
-        <v>-0.004</v>
+        <v>-0.0392</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>719900</v>
+        <v>1122800</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>0.23</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H127" t="n">
-        <v>36.45</v>
-      </c>
-      <c r="I127" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.73</v>
+      </c>
+      <c r="I127" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>2.56</v>
+        <v>0.518</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>2.7</v>
+        <v>0.531</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="7" t="inlineStr"/>
@@ -6179,39 +6179,39 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>5120</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>AMFIRST</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>4.3</v>
+        <v>0.33</v>
       </c>
       <c r="E128" s="8" t="n">
-        <v>-0.0293</v>
+        <v>-0.0294</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>702300</v>
+        <v>1111100</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>0.11</v>
+        <v>3.79</v>
       </c>
       <c r="H128" t="n">
-        <v>46.61</v>
-      </c>
-      <c r="I128" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>26.77</v>
+      </c>
+      <c r="I128" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>4.358</v>
+        <v>0.344</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>4.438</v>
+        <v>0.345</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="7" t="inlineStr"/>
@@ -6224,39 +6224,39 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>0.525</v>
+        <v>0.23</v>
       </c>
       <c r="E129" s="8" t="n">
-        <v>-0.0187</v>
+        <v>-0.0213</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>693000</v>
+        <v>1090600</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="H129" t="n">
-        <v>61.14</v>
-      </c>
-      <c r="I129" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.72</v>
+      </c>
+      <c r="I129" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>0.494</v>
+        <v>0.247</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>0.461</v>
+        <v>0.223</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="7" t="inlineStr"/>
@@ -6269,28 +6269,28 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>BAUTO</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="E130" s="8" t="n">
-        <v>-0.0274</v>
+        <v>0.895</v>
+      </c>
+      <c r="E130" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>676000</v>
+        <v>1087900</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>0.05</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H130" t="n">
-        <v>43.13</v>
+        <v>38.7</v>
       </c>
       <c r="I130" s="6" t="inlineStr">
         <is>
@@ -6298,10 +6298,10 @@
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>0.764</v>
+        <v>0.915</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>0.722</v>
+        <v>0.931</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="7" t="inlineStr"/>
@@ -6314,39 +6314,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>6181</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>MALTON</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>1.91</v>
+        <v>0.205</v>
       </c>
       <c r="E131" s="8" t="n">
-        <v>-0.0104</v>
+        <v>-0.04650000000000001</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>673000</v>
+        <v>1072500</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>0.11</v>
+        <v>1.54</v>
       </c>
       <c r="H131" t="n">
-        <v>45.87</v>
-      </c>
-      <c r="I131" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.59</v>
+      </c>
+      <c r="I131" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>1.924</v>
+        <v>0.218</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>1.952</v>
+        <v>0.226</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="7" t="inlineStr"/>
@@ -6359,39 +6359,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0291</t>
+          <t>0337</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>CHB</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>2.51</v>
+        <v>0.24</v>
       </c>
       <c r="E132" s="8" t="n">
-        <v>-0.0383</v>
+        <v>-0.04</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>661700</v>
+        <v>1070300</v>
       </c>
       <c r="G132" s="5" t="n">
-        <v>0.4</v>
+        <v>0.57</v>
       </c>
       <c r="H132" t="n">
-        <v>52.87</v>
-      </c>
-      <c r="I132" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.37</v>
+      </c>
+      <c r="I132" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>2.528</v>
+        <v>0.24</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>2.223</v>
+        <v>0.243</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="7" t="inlineStr"/>
@@ -6404,28 +6404,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>KOBAY</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E133" s="3" t="n">
-        <v>0.0152</v>
+        <v>2.44</v>
+      </c>
+      <c r="E133" s="8" t="n">
+        <v>-0.008100000000000001</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>643000</v>
+        <v>1057000</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>0.57</v>
+        <v>0.08</v>
       </c>
       <c r="H133" t="n">
-        <v>36.94</v>
+        <v>49.39</v>
       </c>
       <c r="I133" s="6" t="inlineStr">
         <is>
@@ -6433,10 +6433,10 @@
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>2.135</v>
+        <v>2.459</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>2.291</v>
+        <v>2.375</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="7" t="inlineStr"/>
@@ -6449,39 +6449,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0151</t>
+          <t>0328</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>KGB</t>
+          <t>3REN</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>8.43</v>
+        <v>0.39</v>
       </c>
       <c r="E134" s="8" t="n">
-        <v>-0.0288</v>
+        <v>-0.0127</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>636600</v>
+        <v>1049000</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>0.3</v>
+        <v>0.46</v>
       </c>
       <c r="H134" t="n">
-        <v>44.12</v>
-      </c>
-      <c r="I134" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.92</v>
+      </c>
+      <c r="I134" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>8.682</v>
+        <v>0.388</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>8.707000000000001</v>
+        <v>0.391</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="7" t="inlineStr"/>
@@ -6494,28 +6494,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>NGGB</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="E135" s="8" t="n">
-        <v>-0.0152</v>
+        <v>0.76</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>0.0066</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>588600</v>
+        <v>980100</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>0.09</v>
+        <v>0.63</v>
       </c>
       <c r="H135" t="n">
-        <v>29.47</v>
+        <v>61.61</v>
       </c>
       <c r="I135" s="6" t="inlineStr">
         <is>
@@ -6523,10 +6523,10 @@
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>3.405</v>
+        <v>0.742</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>3.623</v>
+        <v>0.718</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="7" t="inlineStr"/>
@@ -6539,28 +6539,28 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>NGGB</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="E136" s="10" t="n">
-        <v>0</v>
+        <v>1.19</v>
+      </c>
+      <c r="E136" s="8" t="n">
+        <v>-0.0083</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>567100</v>
+        <v>958800</v>
       </c>
       <c r="G136" s="5" t="n">
-        <v>0.36</v>
+        <v>0.13</v>
       </c>
       <c r="H136" t="n">
-        <v>59.74</v>
+        <v>35.65</v>
       </c>
       <c r="I136" s="6" t="inlineStr">
         <is>
@@ -6568,10 +6568,10 @@
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>0.741</v>
+        <v>1.241</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>0.718</v>
+        <v>1.334</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="7" t="inlineStr"/>
@@ -6584,28 +6584,28 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0325</t>
+          <t>0375</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>THMY</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="E137" s="8" t="n">
-        <v>-0.0194</v>
+        <v>-0.0283</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>550800</v>
+        <v>942500</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>0.34</v>
+        <v>0.39</v>
       </c>
       <c r="H137" t="n">
-        <v>37.27</v>
+        <v>48.8</v>
       </c>
       <c r="I137" s="6" t="inlineStr">
         <is>
@@ -6613,10 +6613,10 @@
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>1.092</v>
+        <v>2.112</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>1.095</v>
+        <v>1.984</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="7" t="inlineStr"/>
@@ -6629,39 +6629,39 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>5106</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>AXREIT</t>
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>0.89</v>
+        <v>1.84</v>
       </c>
       <c r="E138" s="8" t="n">
-        <v>-0.0166</v>
+        <v>-0.0054</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>543900</v>
+        <v>883100</v>
       </c>
       <c r="G138" s="5" t="n">
-        <v>0.19</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H138" t="n">
-        <v>39.69</v>
-      </c>
-      <c r="I138" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.86</v>
+      </c>
+      <c r="I138" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>0.908</v>
+        <v>1.83</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>0.958</v>
+        <v>1.828</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="7" t="inlineStr"/>
@@ -6674,28 +6674,28 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0293</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>KJTS</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="E139" s="8" t="n">
-        <v>-0.038</v>
+        <v>6.78</v>
+      </c>
+      <c r="E139" s="3" t="n">
+        <v>0.0059</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>536300</v>
+        <v>853200</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>0.45</v>
+        <v>0.19</v>
       </c>
       <c r="H139" t="n">
-        <v>34.95</v>
+        <v>51.24</v>
       </c>
       <c r="I139" s="6" t="inlineStr">
         <is>
@@ -6703,10 +6703,10 @@
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>0.979</v>
+        <v>6.761</v>
       </c>
       <c r="K139" s="2" t="n">
-        <v>1.029</v>
+        <v>6.835</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="7" t="inlineStr"/>
@@ -6719,28 +6719,28 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>2.49</v>
+        <v>0.625</v>
       </c>
       <c r="E140" s="8" t="n">
-        <v>-0.0119</v>
+        <v>-0.0458</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>530500</v>
+        <v>846200</v>
       </c>
       <c r="G140" s="5" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="H140" t="n">
-        <v>40.83</v>
+        <v>62.58</v>
       </c>
       <c r="I140" s="6" t="inlineStr">
         <is>
@@ -6748,10 +6748,10 @@
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>2.564</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>2.739</v>
+        <v>0.462</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="7" t="inlineStr"/>
@@ -6764,39 +6764,39 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>LWSABAH</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E141" s="8" t="n">
-        <v>-0.0272</v>
+        <v>0.555</v>
+      </c>
+      <c r="E141" s="3" t="n">
+        <v>0.0091</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>521100</v>
+        <v>842000</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>0.48</v>
+        <v>0.75</v>
       </c>
       <c r="H141" t="n">
-        <v>32.63</v>
-      </c>
-      <c r="I141" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>39.65</v>
+      </c>
+      <c r="I141" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>1.625</v>
+        <v>0.573</v>
       </c>
       <c r="K141" s="2" t="n">
-        <v>1.631</v>
+        <v>0.615</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="7" t="inlineStr"/>
@@ -6809,45 +6809,990 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>2.16</v>
+        <v>10.04</v>
       </c>
       <c r="E142" s="3" t="n">
-        <v>0.0141</v>
+        <v>0.006</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>516800</v>
+        <v>795800</v>
       </c>
       <c r="G142" s="5" t="n">
-        <v>0.24</v>
+        <v>0.06</v>
       </c>
       <c r="H142" t="n">
-        <v>58.07</v>
-      </c>
-      <c r="I142" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.55</v>
+      </c>
+      <c r="I142" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>2.107</v>
+        <v>10.01</v>
       </c>
       <c r="K142" s="2" t="n">
-        <v>2.055</v>
+        <v>10.168</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="7" t="inlineStr"/>
     </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>5183</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>PCHEM</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E143" s="8" t="n">
+        <v>-0.0293</v>
+      </c>
+      <c r="F143" s="4" t="n">
+        <v>771500</v>
+      </c>
+      <c r="G143" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H143" t="n">
+        <v>46.61</v>
+      </c>
+      <c r="I143" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="n">
+        <v>4.358</v>
+      </c>
+      <c r="K143" s="2" t="n">
+        <v>4.438</v>
+      </c>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" s="7" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>0291</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>CHB</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="E144" s="8" t="n">
+        <v>-0.0498</v>
+      </c>
+      <c r="F144" s="4" t="n">
+        <v>770800</v>
+      </c>
+      <c r="G144" s="5" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H144" t="n">
+        <v>51.32</v>
+      </c>
+      <c r="I144" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="n">
+        <v>2.526</v>
+      </c>
+      <c r="K144" s="2" t="n">
+        <v>2.223</v>
+      </c>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" s="7" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>0391</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>AMBEST</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E145" s="8" t="n">
+        <v>-0.0441</v>
+      </c>
+      <c r="F145" s="4" t="n">
+        <v>761900</v>
+      </c>
+      <c r="G145" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H145" t="n">
+        <v>46.63</v>
+      </c>
+      <c r="I145" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="n">
+        <v>1.339</v>
+      </c>
+      <c r="K145" s="2" t="n">
+        <v>1.273</v>
+      </c>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" s="7" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>6971</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>KOBAY</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="E146" s="3" t="n">
+        <v>0.0203</v>
+      </c>
+      <c r="F146" s="4" t="n">
+        <v>745100</v>
+      </c>
+      <c r="G146" s="5" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H146" t="n">
+        <v>37.84</v>
+      </c>
+      <c r="I146" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="n">
+        <v>2.136</v>
+      </c>
+      <c r="K146" s="2" t="n">
+        <v>2.291</v>
+      </c>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" s="7" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>0151</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>KGB</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="E147" s="8" t="n">
+        <v>-0.0288</v>
+      </c>
+      <c r="F147" s="4" t="n">
+        <v>735900</v>
+      </c>
+      <c r="G147" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H147" t="n">
+        <v>44.12</v>
+      </c>
+      <c r="I147" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="n">
+        <v>8.682</v>
+      </c>
+      <c r="K147" s="2" t="n">
+        <v>8.707000000000001</v>
+      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" s="7" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>0368</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>OXB</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="E148" s="8" t="n">
+        <v>-0.0187</v>
+      </c>
+      <c r="F148" s="4" t="n">
+        <v>701200</v>
+      </c>
+      <c r="G148" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H148" t="n">
+        <v>61.14</v>
+      </c>
+      <c r="I148" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="n">
+        <v>0.494</v>
+      </c>
+      <c r="K148" s="2" t="n">
+        <v>0.461</v>
+      </c>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" s="7" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>0056</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>NCT</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E149" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F149" s="4" t="n">
+        <v>700000</v>
+      </c>
+      <c r="G149" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H149" t="n">
+        <v>48.26</v>
+      </c>
+      <c r="I149" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="K149" s="2" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" s="7" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>8869</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>PMETAL</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="E150" s="8" t="n">
+        <v>-0.0042</v>
+      </c>
+      <c r="F150" s="4" t="n">
+        <v>671700</v>
+      </c>
+      <c r="G150" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H150" t="n">
+        <v>35.67</v>
+      </c>
+      <c r="I150" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="n">
+        <v>7.346</v>
+      </c>
+      <c r="K150" s="2" t="n">
+        <v>7.669</v>
+      </c>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" s="7" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>5878</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>KPJ</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="E151" s="8" t="n">
+        <v>-0.0119</v>
+      </c>
+      <c r="F151" s="4" t="n">
+        <v>656600</v>
+      </c>
+      <c r="G151" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H151" t="n">
+        <v>40.83</v>
+      </c>
+      <c r="I151" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="n">
+        <v>2.564</v>
+      </c>
+      <c r="K151" s="2" t="n">
+        <v>2.739</v>
+      </c>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" s="7" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>5249</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>IOIPG</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="E152" s="8" t="n">
+        <v>-0.0152</v>
+      </c>
+      <c r="F152" s="4" t="n">
+        <v>622200</v>
+      </c>
+      <c r="G152" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H152" t="n">
+        <v>29.47</v>
+      </c>
+      <c r="I152" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="n">
+        <v>3.405</v>
+      </c>
+      <c r="K152" s="2" t="n">
+        <v>3.623</v>
+      </c>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" s="7" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>7160</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>PENTA</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="E153" s="8" t="n">
+        <v>-0.0269</v>
+      </c>
+      <c r="F153" s="4" t="n">
+        <v>617700</v>
+      </c>
+      <c r="G153" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H153" t="n">
+        <v>48.86</v>
+      </c>
+      <c r="I153" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="n">
+        <v>5.507</v>
+      </c>
+      <c r="K153" s="2" t="n">
+        <v>5.392</v>
+      </c>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" s="7" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>0128</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>FRONTKN</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E154" s="8" t="n">
+        <v>-0.0058</v>
+      </c>
+      <c r="F154" s="4" t="n">
+        <v>587000</v>
+      </c>
+      <c r="G154" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H154" t="n">
+        <v>53.09</v>
+      </c>
+      <c r="I154" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="n">
+        <v>5.071</v>
+      </c>
+      <c r="K154" s="2" t="n">
+        <v>5.064</v>
+      </c>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" s="7" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>0325</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="E155" s="8" t="n">
+        <v>-0.0194</v>
+      </c>
+      <c r="F155" s="4" t="n">
+        <v>562600</v>
+      </c>
+      <c r="G155" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H155" t="n">
+        <v>37.27</v>
+      </c>
+      <c r="I155" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="n">
+        <v>1.092</v>
+      </c>
+      <c r="K155" s="2" t="n">
+        <v>1.095</v>
+      </c>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" s="7" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>0338</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>KOPI</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="E156" s="8" t="n">
+        <v>-0.0166</v>
+      </c>
+      <c r="F156" s="4" t="n">
+        <v>552200</v>
+      </c>
+      <c r="G156" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H156" t="n">
+        <v>39.69</v>
+      </c>
+      <c r="I156" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="K156" s="2" t="n">
+        <v>0.958</v>
+      </c>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" s="7" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>5236</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>MATRIX</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="E157" s="3" t="n">
+        <v>0.009300000000000001</v>
+      </c>
+      <c r="F157" s="4" t="n">
+        <v>546700</v>
+      </c>
+      <c r="G157" s="5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H157" t="n">
+        <v>45.93</v>
+      </c>
+      <c r="I157" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="n">
+        <v>1.096</v>
+      </c>
+      <c r="K157" s="2" t="n">
+        <v>1.138</v>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" s="7" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>7293</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>YINSON</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="E158" s="3" t="n">
+        <v>0.0141</v>
+      </c>
+      <c r="F158" s="4" t="n">
+        <v>543900</v>
+      </c>
+      <c r="G158" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H158" t="n">
+        <v>58.07</v>
+      </c>
+      <c r="I158" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="n">
+        <v>2.107</v>
+      </c>
+      <c r="K158" s="2" t="n">
+        <v>2.055</v>
+      </c>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" s="7" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>5328</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>LWSABAH</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E159" s="8" t="n">
+        <v>-0.0272</v>
+      </c>
+      <c r="F159" s="4" t="n">
+        <v>543600</v>
+      </c>
+      <c r="G159" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H159" t="n">
+        <v>32.63</v>
+      </c>
+      <c r="I159" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="K159" s="2" t="n">
+        <v>1.631</v>
+      </c>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" s="7" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>0293</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>KJTS</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="E160" s="8" t="n">
+        <v>-0.0326</v>
+      </c>
+      <c r="F160" s="4" t="n">
+        <v>541700</v>
+      </c>
+      <c r="G160" s="5" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H160" t="n">
+        <v>35.43</v>
+      </c>
+      <c r="I160" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="K160" s="2" t="n">
+        <v>1.029</v>
+      </c>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" s="7" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>0233</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>PEKAT</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="E161" s="8" t="n">
+        <v>-0.0075</v>
+      </c>
+      <c r="F161" s="4" t="n">
+        <v>514000</v>
+      </c>
+      <c r="G161" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H161" t="n">
+        <v>54.47</v>
+      </c>
+      <c r="I161" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="n">
+        <v>2.669</v>
+      </c>
+      <c r="K161" s="2" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" s="7" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>1171</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>MBSB</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="E162" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F162" s="4" t="n">
+        <v>512000</v>
+      </c>
+      <c r="G162" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H162" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="I162" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="n">
+        <v>0.547</v>
+      </c>
+      <c r="K162" s="2" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" s="7" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>5302</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>ATECH</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="E163" s="8" t="n">
+        <v>-0.0248</v>
+      </c>
+      <c r="F163" s="4" t="n">
+        <v>509100</v>
+      </c>
+      <c r="G163" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H163" t="n">
+        <v>52.65</v>
+      </c>
+      <c r="I163" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="K163" s="2" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M142"/>
+  <autoFilter ref="A1:M163"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-15/bursa-report-2026-10-15.xlsx
+++ b/docs/downloads/2026-10-15/bursa-report-2026-10-15.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-15" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-15'!$A$1:$M$163</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-15'!$A$1:$M$177</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M163"/>
+  <dimension ref="A1:M177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -558,10 +558,10 @@
         <v>0.1818</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>88230800</v>
+        <v>96396500</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="H2" t="n">
         <v>24.2</v>
@@ -597,19 +597,19 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.895</v>
+        <v>0.89</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>-0.0165</v>
+        <v>-0.022</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>37070800</v>
+        <v>39741100</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="H3" t="n">
-        <v>65.34999999999999</v>
+        <v>64.45</v>
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>0.727</v>
@@ -642,19 +642,19 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="E4" s="10" t="n">
-        <v>0</v>
+        <v>0.335</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>-0.0147</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>25737600</v>
+        <v>33307100</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="H4" t="n">
-        <v>71.22</v>
+        <v>68.7</v>
       </c>
       <c r="I4" s="9" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.298</v>
+        <v>0.297</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0.253</v>
@@ -687,16 +687,16 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>-0.0125</v>
+        <v>0.8</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>22890000</v>
+        <v>24102300</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
@@ -716,39 +716,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>0.0241</v>
+        <v>0.445</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>-0.0532</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>21062500</v>
+        <v>22450500</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="H6" t="n">
-        <v>77.33</v>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.13</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.374</v>
+        <v>0.485</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.263</v>
+        <v>0.482</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr"/>
@@ -761,39 +761,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>-0.0532</v>
+        <v>0.425</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0.0241</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>20219900</v>
+        <v>22151900</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="H7" t="n">
-        <v>38.13</v>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>77.33</v>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.485</v>
+        <v>0.374</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.482</v>
+        <v>0.263</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
@@ -806,39 +806,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>7036</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>BORNOIL</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.665</v>
+        <v>0.005</v>
       </c>
       <c r="E8" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>19013700</v>
+        <v>19500500</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.74</v>
+        <v>30.8</v>
       </c>
       <c r="H8" t="n">
-        <v>76.18000000000001</v>
-      </c>
-      <c r="I8" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.15</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.603</v>
+        <v>0.005</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.521</v>
+        <v>0.005</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
@@ -851,39 +851,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7036</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BORNOIL</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>0</v>
+        <v>0.67</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0.0075</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>15500500</v>
+        <v>19156400</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>24.48</v>
+        <v>0.74</v>
       </c>
       <c r="H9" t="n">
-        <v>48.15</v>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>76.91</v>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.005</v>
+        <v>0.603</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.005</v>
+        <v>0.521</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
@@ -905,19 +905,19 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>-0.0338</v>
+        <v>-0.029</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>14694200</v>
+        <v>16780200</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.49</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>58.43</v>
+        <v>59.07</v>
       </c>
       <c r="I10" s="9" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.909</v>
+        <v>1.91</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>1.713</v>
@@ -941,28 +941,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.26</v>
+        <v>0.295</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>-0.0189</v>
+        <v>-0.0781</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>13315300</v>
+        <v>16077100</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>1.71</v>
+        <v>2.16</v>
       </c>
       <c r="H11" t="n">
-        <v>26.18</v>
+        <v>50.53</v>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
@@ -970,10 +970,10 @@
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.281</v>
+        <v>0.299</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0.304</v>
+        <v>0.279</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
@@ -986,39 +986,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0096</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NEXGRAM</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>0</v>
+        <v>0.26</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>-0.0189</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>12944500</v>
+        <v>13514000</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>7.56</v>
+        <v>1.73</v>
       </c>
       <c r="H12" t="n">
-        <v>69.25</v>
-      </c>
-      <c r="I12" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>26.18</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.044</v>
+        <v>0.281</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0.047</v>
+        <v>0.304</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
@@ -1031,31 +1031,40 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0041</t>
+          <t>0096</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AIMAX</t>
+          <t>NEXGRAM</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="E13" s="10" t="n">
-        <v>0</v>
+        <v>0.05</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>-0.09089999999999999</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>12500400</v>
-      </c>
-      <c r="G13" s="5" t="n"/>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="n"/>
-      <c r="K13" s="2" t="n"/>
+        <v>12969500</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="H13" t="n">
+        <v>59.29</v>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>0.047</v>
+      </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
     </row>
@@ -1067,29 +1076,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>0041</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>AIMAX</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>-0.0196</v>
+        <v>0.005</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>12270700</v>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="I14" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>12630400</v>
+      </c>
+      <c r="G14" s="5" t="n"/>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="J14" s="2" t="n"/>
@@ -1105,40 +1112,33 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1643</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>LANDMRK</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>0.6667000000000001</v>
+        <v>0.25</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>-0.0196</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>10889400</v>
+        <v>12272300</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="H15" t="n">
-        <v>47.61</v>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>0.049</v>
-      </c>
-      <c r="K15" s="2" t="n">
-        <v>0.064</v>
-      </c>
+        <v>0.45</v>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="n"/>
+      <c r="K15" s="2" t="n"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
     </row>
@@ -1159,19 +1159,19 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.44</v>
+        <v>0.445</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>-0.0435</v>
+        <v>-0.0326</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>10536300</v>
+        <v>11674800</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.52</v>
+        <v>0.57</v>
       </c>
       <c r="H16" t="n">
-        <v>58.06</v>
+        <v>59.44</v>
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.419</v>
+        <v>0.42</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.36</v>
+        <v>0.361</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
@@ -1195,39 +1195,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>1643</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>LANDMRK</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E17" s="8" t="n">
-        <v>-0.0469</v>
+        <v>0.045</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0.5</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>9323900</v>
+        <v>10952400</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>1.25</v>
+        <v>8.75</v>
       </c>
       <c r="H17" t="n">
-        <v>56.44</v>
-      </c>
-      <c r="I17" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.11</v>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.3</v>
+        <v>0.049</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.279</v>
+        <v>0.064</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
@@ -1255,10 +1255,10 @@
         <v>-0.0159</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>8663800</v>
+        <v>10273800</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.45</v>
+        <v>0.54</v>
       </c>
       <c r="H18" t="n">
         <v>54.53</v>
@@ -1300,10 +1300,10 @@
         <v>0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>8647500</v>
+        <v>10026700</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.54</v>
+        <v>0.62</v>
       </c>
       <c r="H19" t="n">
         <v>58.28</v>
@@ -1330,39 +1330,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>0.0141</v>
+        <v>0.775</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>-0.0064</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>8409500</v>
+        <v>9837900</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H20" t="n">
-        <v>21.31</v>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.18</v>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.747</v>
+        <v>0.775</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>1.971</v>
+        <v>0.776</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
@@ -1375,28 +1375,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E21" s="10" t="n">
-        <v>0</v>
+        <v>1.43</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0.006999999999999999</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>8358200</v>
+        <v>9506500</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.77</v>
+        <v>0.92</v>
       </c>
       <c r="H21" t="n">
-        <v>33.83</v>
+        <v>20.13</v>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.398</v>
+        <v>1.746</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0.408</v>
+        <v>1.971</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
@@ -1420,28 +1420,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.775</v>
+        <v>2.57</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>-0.0064</v>
+        <v>-0.0446</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>8028200</v>
+        <v>8365900</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.53</v>
+        <v>0.46</v>
       </c>
       <c r="H22" t="n">
-        <v>50.18</v>
+        <v>46.53</v>
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.775</v>
+        <v>2.649</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0.776</v>
+        <v>2.541</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
@@ -1465,28 +1465,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0117</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SMRT</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>0.0625</v>
+        <v>0.39</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>7737800</v>
+        <v>8358200</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>2.4</v>
+        <v>0.77</v>
       </c>
       <c r="H23" t="n">
-        <v>41.24</v>
+        <v>33.83</v>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.179</v>
+        <v>0.398</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.192</v>
+        <v>0.408</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
@@ -1510,28 +1510,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>2.59</v>
+        <v>0.865</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>-0.0372</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>7439500</v>
+        <v>8009400</v>
       </c>
       <c r="G24" s="5" t="n">
         <v>0.41</v>
       </c>
       <c r="H24" t="n">
-        <v>47.68</v>
+        <v>45.95</v>
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
@@ -1539,10 +1539,10 @@
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>2.651</v>
+        <v>0.868</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>2.541</v>
+        <v>0.869</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
@@ -1555,28 +1555,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0117</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>SMRT</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.225</v>
+        <v>0.17</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>0.04650000000000001</v>
+        <v>0.0625</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>7281000</v>
+        <v>7824000</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.28</v>
+        <v>2.42</v>
       </c>
       <c r="H25" t="n">
-        <v>36.92</v>
+        <v>41.24</v>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
@@ -1584,10 +1584,10 @@
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.239</v>
+        <v>0.179</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.292</v>
+        <v>0.192</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
@@ -1609,19 +1609,19 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E26" s="8" t="n">
-        <v>-0.007900000000000001</v>
+        <v>1.26</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>7239200</v>
+        <v>7816500</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="H26" t="n">
-        <v>59.95</v>
+        <v>61.5</v>
       </c>
       <c r="I26" s="9" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.182</v>
+        <v>1.183</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>1.18</v>
@@ -1654,19 +1654,19 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.55</v>
+        <v>0.555</v>
       </c>
       <c r="E27" s="8" t="n">
-        <v>-0.0435</v>
+        <v>-0.0348</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>7209400</v>
+        <v>7502000</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="H27" t="n">
-        <v>46.48</v>
+        <v>47.34</v>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.579</v>
+        <v>0.58</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0.536</v>
@@ -1690,39 +1690,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0237</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>HAILY</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.185</v>
+        <v>0.225</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.0571</v>
+        <v>0.04650000000000001</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>6781900</v>
+        <v>7401400</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>26.94</v>
+        <v>0.28</v>
       </c>
       <c r="H28" t="n">
-        <v>68.31999999999999</v>
-      </c>
-      <c r="I28" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.92</v>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.166</v>
+        <v>0.239</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0.166</v>
+        <v>0.292</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
@@ -1735,28 +1735,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0237</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>HAILY</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>0</v>
+        <v>0.18</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>0.0286</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>6068600</v>
+        <v>7220400</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>28.68</v>
       </c>
       <c r="H29" t="n">
-        <v>56.82</v>
+        <v>65.22</v>
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
@@ -1764,10 +1764,10 @@
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.615</v>
+        <v>0.166</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.614</v>
+        <v>0.165</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1780,39 +1780,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E30" s="8" t="n">
-        <v>-0.0534</v>
+        <v>0.625</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>6062400</v>
+        <v>7189400</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="H30" t="n">
-        <v>42.98</v>
-      </c>
-      <c r="I30" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.82</v>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.665</v>
+        <v>0.615</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.619</v>
+        <v>0.614</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1825,28 +1825,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.35</v>
+        <v>0.62</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>-0.0278</v>
+        <v>-0.0534</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5672800</v>
+        <v>6244100</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="H31" t="n">
-        <v>52.78</v>
+        <v>42.98</v>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
@@ -1854,10 +1854,10 @@
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.349</v>
+        <v>0.665</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.332</v>
+        <v>0.619</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1870,39 +1870,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.865</v>
+        <v>5.31</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.031</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>5592600</v>
+        <v>6154500</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.28</v>
+        <v>0.44</v>
       </c>
       <c r="H32" t="n">
-        <v>45.95</v>
-      </c>
-      <c r="I32" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.86</v>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.868</v>
+        <v>5.578</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0.869</v>
+        <v>5.412</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
@@ -1915,28 +1915,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0051</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CUSCAPI</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.045</v>
+        <v>0.155</v>
       </c>
       <c r="E33" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>5469400</v>
+        <v>5900100</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.38</v>
+        <v>0.17</v>
       </c>
       <c r="H33" t="n">
-        <v>38.84</v>
+        <v>48.59</v>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.05</v>
+        <v>0.155</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.066</v>
+        <v>0.157</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1960,39 +1960,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.18</v>
+        <v>0.38</v>
       </c>
       <c r="E34" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>5274100</v>
+        <v>5861000</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.22</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H34" t="n">
-        <v>42.99</v>
-      </c>
-      <c r="I34" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.88</v>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.192</v>
+        <v>0.371</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.185</v>
+        <v>0.369</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2020,10 +2020,10 @@
         <v>-0.0484</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>5003500</v>
+        <v>5707500</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.99</v>
+        <v>1.13</v>
       </c>
       <c r="H35" t="n">
         <v>21.54</v>
@@ -2050,28 +2050,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>1.08</v>
+        <v>0.35</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>-0.0357</v>
+        <v>-0.0278</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>4728600</v>
+        <v>5678600</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.47</v>
+        <v>0.65</v>
       </c>
       <c r="H36" t="n">
-        <v>51.54</v>
+        <v>52.78</v>
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.073</v>
+        <v>0.349</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>1.042</v>
+        <v>0.332</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
@@ -2095,28 +2095,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0051</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>CUSCAPI</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="E37" s="8" t="n">
-        <v>-0.0347</v>
+        <v>0.045</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>4357500</v>
+        <v>5569500</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.31</v>
+        <v>0.39</v>
       </c>
       <c r="H37" t="n">
-        <v>39.25</v>
+        <v>38.84</v>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>5.576</v>
+        <v>0.05</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>5.412</v>
+        <v>0.066</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2140,28 +2140,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>1.01</v>
+        <v>0.175</v>
       </c>
       <c r="E38" s="8" t="n">
-        <v>-0.0194</v>
+        <v>-0.0278</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>4340700</v>
+        <v>5331400</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.52</v>
+        <v>0.23</v>
       </c>
       <c r="H38" t="n">
-        <v>44.99</v>
+        <v>40.54</v>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.063</v>
+        <v>0.191</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0.947</v>
+        <v>0.185</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
@@ -2185,39 +2185,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>0.0132</v>
+        <v>1.08</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>-0.0357</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>4337700</v>
+        <v>4846300</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.6</v>
+        <v>0.48</v>
       </c>
       <c r="H39" t="n">
-        <v>65.54000000000001</v>
-      </c>
-      <c r="I39" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.54</v>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.371</v>
+        <v>1.073</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0.369</v>
+        <v>1.042</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2239,19 +2239,19 @@
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="E40" s="10" t="n">
-        <v>0</v>
+        <v>4.76</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>0.0021</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>3692300</v>
+        <v>4808600</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.21</v>
+        <v>0.27</v>
       </c>
       <c r="H40" t="n">
-        <v>50.45</v>
+        <v>51.4</v>
       </c>
       <c r="I40" s="9" t="inlineStr">
         <is>
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>4.721</v>
+        <v>4.722</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>4.863</v>
+        <v>4.864</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2275,28 +2275,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>0.52</v>
+        <v>1.01</v>
       </c>
       <c r="E41" s="8" t="n">
-        <v>-0.07139999999999999</v>
+        <v>-0.0194</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>3522300</v>
+        <v>4577900</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.87</v>
+        <v>0.55</v>
       </c>
       <c r="H41" t="n">
-        <v>32.71</v>
+        <v>44.99</v>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.597</v>
+        <v>1.063</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0.603</v>
+        <v>0.947</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2320,39 +2320,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>1.27</v>
+        <v>0.455</v>
       </c>
       <c r="E42" s="8" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.0109</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>3451900</v>
+        <v>4152900</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.36</v>
+        <v>0.79</v>
       </c>
       <c r="H42" t="n">
-        <v>43.81</v>
-      </c>
-      <c r="I42" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.3</v>
+      </c>
+      <c r="I42" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.308</v>
+        <v>0.385</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>1.313</v>
+        <v>0.357</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2365,28 +2365,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="E43" s="8" t="n">
-        <v>-0.0317</v>
+        <v>1.29</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>0.007800000000000001</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>3447000</v>
+        <v>4070000</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="H43" t="n">
-        <v>49.36</v>
+        <v>46.61</v>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
@@ -2394,10 +2394,10 @@
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>2.794</v>
+        <v>1.31</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>2.646</v>
+        <v>1.314</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2410,28 +2410,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E44" s="8" t="n">
-        <v>-0.0235</v>
+        <v>0.225</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>0.0227</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>3384800</v>
+        <v>4055900</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.32</v>
+        <v>0.19</v>
       </c>
       <c r="H44" t="n">
-        <v>42.82</v>
+        <v>48.68</v>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
@@ -2439,10 +2439,10 @@
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.443</v>
+        <v>0.223</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.432</v>
+        <v>0.24</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2455,28 +2455,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>0.22</v>
+        <v>0.13</v>
       </c>
       <c r="E45" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>3334200</v>
+        <v>3862500</v>
       </c>
       <c r="G45" s="5" t="n">
         <v>0.16</v>
       </c>
       <c r="H45" t="n">
-        <v>44.76</v>
+        <v>38.74</v>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
@@ -2484,10 +2484,10 @@
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.223</v>
+        <v>0.148</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.239</v>
+        <v>0.148</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2500,39 +2500,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>1.1</v>
+        <v>0.475</v>
       </c>
       <c r="E46" s="8" t="n">
-        <v>-0.0984</v>
+        <v>-0.05</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>3295300</v>
+        <v>3852100</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.85</v>
+        <v>0.52</v>
       </c>
       <c r="H46" t="n">
-        <v>74.98999999999999</v>
-      </c>
-      <c r="I46" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.8</v>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.798</v>
+        <v>0.556</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0.543</v>
+        <v>0.626</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2545,28 +2545,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>0.125</v>
+        <v>2.76</v>
       </c>
       <c r="E47" s="8" t="n">
-        <v>-0.0385</v>
+        <v>-0.0282</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>3264700</v>
+        <v>3819700</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.14</v>
+        <v>0.43</v>
       </c>
       <c r="H47" t="n">
-        <v>36.74</v>
+        <v>50</v>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
@@ -2574,10 +2574,10 @@
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.148</v>
+        <v>2.795</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0.148</v>
+        <v>2.646</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2590,28 +2590,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E48" s="3" t="n">
-        <v>0.0345</v>
+        <v>0.465</v>
+      </c>
+      <c r="E48" s="8" t="n">
+        <v>-0.0211</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>3211900</v>
+        <v>3750800</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.04</v>
+        <v>0.48</v>
       </c>
       <c r="H48" t="n">
-        <v>46.24</v>
+        <v>27.64</v>
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.163</v>
+        <v>0.507</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0.137</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2635,39 +2635,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>0.44</v>
+        <v>0.52</v>
       </c>
       <c r="E49" s="8" t="n">
-        <v>-0.0435</v>
+        <v>-0.07139999999999999</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>3172000</v>
+        <v>3625100</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.61</v>
+        <v>0.89</v>
       </c>
       <c r="H49" t="n">
-        <v>62.7</v>
-      </c>
-      <c r="I49" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.71</v>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.384</v>
+        <v>0.597</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0.357</v>
+        <v>0.603</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
@@ -2680,39 +2680,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MALAKOF</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="E50" s="8" t="n">
-        <v>-0.0329</v>
+        <v>0.405</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>0.0125</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>3036900</v>
+        <v>3562300</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.67</v>
+        <v>0.28</v>
       </c>
       <c r="H50" t="n">
-        <v>36.06</v>
-      </c>
-      <c r="I50" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.8</v>
+      </c>
+      <c r="I50" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.781</v>
+        <v>0.391</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0.803</v>
+        <v>0.378</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2725,39 +2725,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>0.265</v>
+        <v>1.1</v>
       </c>
       <c r="E51" s="8" t="n">
-        <v>-0.0364</v>
+        <v>-0.0984</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>3033100</v>
+        <v>3469600</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.36</v>
+        <v>0.9</v>
       </c>
       <c r="H51" t="n">
-        <v>42.94</v>
-      </c>
-      <c r="I51" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>74.98999999999999</v>
+      </c>
+      <c r="I51" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.277</v>
+        <v>0.798</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0.298</v>
+        <v>0.543</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2770,28 +2770,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="E52" s="10" t="n">
-        <v>0</v>
+        <v>0.89</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>0.0171</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>2949500</v>
+        <v>3444700</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.22</v>
+        <v>0.4</v>
       </c>
       <c r="H52" t="n">
-        <v>47.1</v>
+        <v>44.65</v>
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
@@ -2799,10 +2799,10 @@
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>2.788</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>2.729</v>
+        <v>0.84</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2815,28 +2815,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="E53" s="3" t="n">
-        <v>0.0222</v>
+        <v>0.415</v>
+      </c>
+      <c r="E53" s="8" t="n">
+        <v>-0.0235</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>2897200</v>
+        <v>3413300</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.32</v>
       </c>
       <c r="H53" t="n">
-        <v>27.43</v>
+        <v>42.82</v>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.518</v>
+        <v>0.443</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0.701</v>
+        <v>0.432</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2860,28 +2860,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>0.89</v>
+        <v>4.9</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>0.0171</v>
+        <v>0.0103</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>2882000</v>
+        <v>3336000</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.34</v>
+        <v>0.13</v>
       </c>
       <c r="H54" t="n">
-        <v>44.65</v>
+        <v>50.98</v>
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.9419999999999999</v>
+        <v>4.925</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0.84</v>
+        <v>4.71</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2905,28 +2905,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="E55" s="3" t="n">
-        <v>0.0062</v>
+        <v>2.04</v>
+      </c>
+      <c r="E55" s="8" t="n">
+        <v>-0.0192</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>2853000</v>
+        <v>3306100</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.11</v>
+        <v>0.23</v>
       </c>
       <c r="H55" t="n">
-        <v>49.99</v>
+        <v>34.57</v>
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
@@ -2934,10 +2934,10 @@
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>4.923</v>
+        <v>2.176</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>4.709</v>
+        <v>2.229</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2950,38 +2950,40 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="E56" s="10" t="n">
-        <v>0</v>
+        <v>0.15</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>0.0345</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>2743000</v>
+        <v>3298900</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.29</v>
+        <v>0.05</v>
       </c>
       <c r="H56" t="n">
-        <v>65.3</v>
-      </c>
-      <c r="I56" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.24</v>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.311</v>
-      </c>
-      <c r="K56" s="2" t="n"/>
+        <v>0.163</v>
+      </c>
+      <c r="K56" s="2" t="n">
+        <v>0.137</v>
+      </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
     </row>
@@ -2993,39 +2995,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>7.37</v>
-      </c>
-      <c r="E57" s="8" t="n">
-        <v>-0.0466</v>
+        <v>3.07</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>0.0066</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>2700300</v>
+        <v>3257600</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.68</v>
+        <v>1.01</v>
       </c>
       <c r="H57" t="n">
-        <v>52.98</v>
-      </c>
-      <c r="I57" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>81.5</v>
+      </c>
+      <c r="I57" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>7.381</v>
+        <v>2.769</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>6.868</v>
+        <v>2.382</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3038,28 +3040,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="E58" s="8" t="n">
-        <v>-0.0263</v>
+        <v>-0.0132</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>2646500</v>
+        <v>3251900</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.38</v>
+        <v>0.72</v>
       </c>
       <c r="H58" t="n">
-        <v>52.48</v>
+        <v>39.04</v>
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
@@ -3067,10 +3069,10 @@
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.744</v>
+        <v>0.783</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0.67</v>
+        <v>0.803</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3083,39 +3085,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="E59" s="3" t="n">
-        <v>0.0066</v>
+        <v>7.36</v>
+      </c>
+      <c r="E59" s="8" t="n">
+        <v>-0.0479</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>2642600</v>
+        <v>3251800</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H59" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="I59" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.75</v>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>2.769</v>
+        <v>7.38</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>2.382</v>
+        <v>6.868</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3128,28 +3130,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="E60" s="8" t="n">
-        <v>-0.024</v>
+        <v>0.46</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>0.0222</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>2596300</v>
+        <v>3206700</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.18</v>
+        <v>0.08</v>
       </c>
       <c r="H60" t="n">
-        <v>33.92</v>
+        <v>27.43</v>
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
@@ -3157,10 +3159,10 @@
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>2.175</v>
+        <v>0.518</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>2.228</v>
+        <v>0.701</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
@@ -3173,28 +3175,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>0.405</v>
+        <v>0.265</v>
       </c>
       <c r="E61" s="8" t="n">
-        <v>-0.0471</v>
+        <v>-0.0364</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>2595000</v>
+        <v>3095600</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="H61" t="n">
-        <v>45.47</v>
+        <v>42.94</v>
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
@@ -3202,10 +3204,10 @@
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.425</v>
+        <v>0.277</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0.416</v>
+        <v>0.298</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3218,28 +3220,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E62" s="8" t="n">
-        <v>-0.0244</v>
+        <v>2.74</v>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>2587900</v>
+        <v>3013700</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>1.39</v>
+        <v>0.22</v>
       </c>
       <c r="H62" t="n">
-        <v>33.55</v>
+        <v>47.1</v>
       </c>
       <c r="I62" s="6" t="inlineStr">
         <is>
@@ -3247,10 +3249,10 @@
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.417</v>
+        <v>2.788</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0.436</v>
+        <v>2.729</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
@@ -3263,28 +3265,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>6.46</v>
+        <v>0.35</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>-0.0358</v>
+        <v>-0.0141</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>2444100</v>
+        <v>2847400</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.44</v>
+        <v>0.31</v>
       </c>
       <c r="H63" t="n">
-        <v>56.81</v>
+        <v>63.15</v>
       </c>
       <c r="I63" s="9" t="inlineStr">
         <is>
@@ -3292,11 +3294,9 @@
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>6.107</v>
-      </c>
-      <c r="K63" s="2" t="n">
-        <v>5.877</v>
-      </c>
+        <v>0.311</v>
+      </c>
+      <c r="K63" s="2" t="n"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
     </row>
@@ -3308,39 +3308,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>4.57</v>
+        <v>6.51</v>
       </c>
       <c r="E64" s="8" t="n">
-        <v>-0.0151</v>
+        <v>-0.0284</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>2432400</v>
+        <v>2834300</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.25</v>
+        <v>0.52</v>
       </c>
       <c r="H64" t="n">
-        <v>42.88</v>
-      </c>
-      <c r="I64" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.64</v>
+      </c>
+      <c r="I64" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>4.645</v>
+        <v>6.112</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>4.636</v>
+        <v>5.878</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
@@ -3353,28 +3353,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>2.5</v>
+        <v>0.745</v>
       </c>
       <c r="E65" s="8" t="n">
-        <v>-0.031</v>
+        <v>-0.0197</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>2423700</v>
+        <v>2816700</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="H65" t="n">
-        <v>41.91</v>
+        <v>53.43</v>
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
@@ -3382,10 +3382,10 @@
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>2.616</v>
+        <v>0.744</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>2.6</v>
+        <v>0.67</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3398,28 +3398,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>0.795</v>
+        <v>0.52</v>
       </c>
       <c r="E66" s="8" t="n">
-        <v>-0.0124</v>
+        <v>-0.03700000000000001</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>2387500</v>
+        <v>2786400</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.64</v>
+        <v>0.19</v>
       </c>
       <c r="H66" t="n">
-        <v>46.65</v>
+        <v>52.58</v>
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.823</v>
+        <v>0.52</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0.773</v>
+        <v>0.454</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3443,28 +3443,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>1.16</v>
+        <v>4.57</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>-0.0252</v>
+        <v>-0.0151</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>2365000</v>
+        <v>2754300</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.58</v>
+        <v>0.28</v>
       </c>
       <c r="H67" t="n">
-        <v>52.79</v>
+        <v>42.88</v>
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.163</v>
+        <v>4.645</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>1.091</v>
+        <v>4.636</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
@@ -3488,28 +3488,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>5218</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>VANTNRG</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>0.295</v>
+        <v>0.985</v>
       </c>
       <c r="E68" s="8" t="n">
-        <v>-0.0328</v>
+        <v>-0.0343</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>2343000</v>
+        <v>2715100</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.73</v>
+        <v>0.59</v>
       </c>
       <c r="H68" t="n">
-        <v>26.9</v>
+        <v>43.98</v>
       </c>
       <c r="I68" s="6" t="inlineStr">
         <is>
@@ -3517,10 +3517,10 @@
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.323</v>
+        <v>1.05</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0.332</v>
+        <v>0.927</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
@@ -3533,39 +3533,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>6.32</v>
-      </c>
-      <c r="E69" s="8" t="n">
-        <v>-0.0032</v>
+        <v>7.52</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>0.0027</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>2270700</v>
+        <v>2707000</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.37</v>
+        <v>0.18</v>
       </c>
       <c r="H69" t="n">
-        <v>40.73</v>
-      </c>
-      <c r="I69" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.48</v>
+      </c>
+      <c r="I69" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>6.409</v>
+        <v>7.582</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>6.789</v>
+        <v>7.711</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
@@ -3578,28 +3578,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>1.02</v>
+        <v>0.41</v>
       </c>
       <c r="E70" s="8" t="n">
-        <v>-0.0556</v>
+        <v>-0.0353</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>2251800</v>
+        <v>2676900</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.55</v>
+        <v>0.39</v>
       </c>
       <c r="H70" t="n">
-        <v>51.06</v>
+        <v>46.73</v>
       </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
@@ -3607,10 +3607,10 @@
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1.041</v>
+        <v>0.425</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0.895</v>
+        <v>0.416</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
@@ -3623,39 +3623,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>7.51</v>
-      </c>
-      <c r="E71" s="3" t="n">
-        <v>0.0013</v>
+        <v>6.33</v>
+      </c>
+      <c r="E71" s="8" t="n">
+        <v>-0.0016</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>2213300</v>
+        <v>2653900</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.15</v>
+        <v>0.43</v>
       </c>
       <c r="H71" t="n">
-        <v>44.98</v>
-      </c>
-      <c r="I71" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.19</v>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>7.581</v>
+        <v>6.41</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>7.71</v>
+        <v>6.789</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
@@ -3668,39 +3668,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="E72" s="10" t="n">
-        <v>0</v>
+        <v>2.5</v>
+      </c>
+      <c r="E72" s="8" t="n">
+        <v>-0.031</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>2165700</v>
+        <v>2629100</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.91</v>
+        <v>0.44</v>
       </c>
       <c r="H72" t="n">
-        <v>66.36</v>
-      </c>
-      <c r="I72" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.91</v>
+      </c>
+      <c r="I72" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.642</v>
+        <v>2.616</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0.548</v>
+        <v>2.6</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
@@ -3713,39 +3713,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="E73" s="3" t="n">
-        <v>0.0125</v>
+        <v>0.4</v>
+      </c>
+      <c r="E73" s="8" t="n">
+        <v>-0.0244</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>2153500</v>
+        <v>2587900</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.17</v>
+        <v>1.39</v>
       </c>
       <c r="H73" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="I73" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.55</v>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.391</v>
+        <v>0.417</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0.378</v>
+        <v>0.436</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
@@ -3758,28 +3758,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="E74" s="3" t="n">
-        <v>0.0036</v>
+        <v>0.79</v>
+      </c>
+      <c r="E74" s="8" t="n">
+        <v>-0.0186</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>2126400</v>
+        <v>2473300</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.44</v>
+        <v>0.66</v>
       </c>
       <c r="H74" t="n">
-        <v>56.38</v>
+        <v>45.85</v>
       </c>
       <c r="I74" s="6" t="inlineStr">
         <is>
@@ -3787,10 +3787,10 @@
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>2.766</v>
+        <v>0.822</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>2.158</v>
+        <v>0.773</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr"/>
@@ -3803,28 +3803,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>0.575</v>
+        <v>1.03</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>-0.0496</v>
+        <v>-0.0463</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>2106400</v>
+        <v>2468400</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.41</v>
+        <v>0.61</v>
       </c>
       <c r="H75" t="n">
-        <v>56.68</v>
+        <v>52</v>
       </c>
       <c r="I75" s="6" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.5620000000000001</v>
+        <v>1.042</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0.51</v>
+        <v>0.895</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr"/>
@@ -3848,39 +3848,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>2.09</v>
+        <v>1.16</v>
       </c>
       <c r="E76" s="8" t="n">
-        <v>-0.0142</v>
+        <v>-0.0252</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>2024600</v>
+        <v>2410100</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.1</v>
+        <v>0.59</v>
       </c>
       <c r="H76" t="n">
-        <v>47.7</v>
-      </c>
-      <c r="I76" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.79</v>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>2.108</v>
+        <v>1.163</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>2.097</v>
+        <v>1.091</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
@@ -3893,28 +3893,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="E77" s="8" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="F77" s="4" t="n">
+        <v>2374600</v>
+      </c>
+      <c r="G77" s="5" t="n">
         <v>0.46</v>
       </c>
-      <c r="E77" s="8" t="n">
-        <v>-0.0316</v>
-      </c>
-      <c r="F77" s="4" t="n">
-        <v>2021300</v>
-      </c>
-      <c r="G77" s="5" t="n">
-        <v>0.26</v>
-      </c>
       <c r="H77" t="n">
-        <v>26.61</v>
+        <v>56.68</v>
       </c>
       <c r="I77" s="6" t="inlineStr">
         <is>
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.507</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
@@ -3938,28 +3938,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E78" s="10" t="n">
-        <v>0</v>
+        <v>1.27</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>0.007900000000000001</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>1992800</v>
+        <v>2366200</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="H78" t="n">
-        <v>51.9</v>
+        <v>25.55</v>
       </c>
       <c r="I78" s="6" t="inlineStr">
         <is>
@@ -3967,10 +3967,10 @@
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.865</v>
+        <v>1.425</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0.859</v>
+        <v>1.58</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
@@ -3983,28 +3983,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>VANTNRG</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>0.49</v>
+        <v>0.295</v>
       </c>
       <c r="E79" s="8" t="n">
-        <v>-0.0101</v>
+        <v>-0.0328</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>1986400</v>
+        <v>2363500</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.23</v>
+        <v>0.74</v>
       </c>
       <c r="H79" t="n">
-        <v>40.63</v>
+        <v>26.9</v>
       </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
@@ -4012,10 +4012,10 @@
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.514</v>
+        <v>0.323</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0.527</v>
+        <v>0.332</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
@@ -4028,28 +4028,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>0.59</v>
+        <v>0.49</v>
       </c>
       <c r="E80" s="8" t="n">
-        <v>-0.0407</v>
+        <v>-0.0101</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>1985500</v>
+        <v>2353100</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.46</v>
+        <v>0.28</v>
       </c>
       <c r="H80" t="n">
-        <v>48.81</v>
+        <v>40.63</v>
       </c>
       <c r="I80" s="6" t="inlineStr">
         <is>
@@ -4057,10 +4057,10 @@
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.6</v>
+        <v>0.514</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0.585</v>
+        <v>0.527</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
@@ -4073,39 +4073,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>0.52</v>
+        <v>2.09</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>-0.03700000000000001</v>
+        <v>-0.0142</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>1961800</v>
+        <v>2303700</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="H81" t="n">
-        <v>52.58</v>
-      </c>
-      <c r="I81" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.7</v>
+      </c>
+      <c r="I81" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.52</v>
+        <v>2.108</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0.454</v>
+        <v>2.097</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
@@ -4118,28 +4118,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>0.66</v>
+        <v>2.42</v>
       </c>
       <c r="E82" s="8" t="n">
-        <v>-0.0222</v>
+        <v>-0.0163</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>1893400</v>
+        <v>2264500</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="H82" t="n">
-        <v>44.67</v>
+        <v>46.53</v>
       </c>
       <c r="I82" s="6" t="inlineStr">
         <is>
@@ -4147,10 +4147,10 @@
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.6879999999999999</v>
+        <v>2.457</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0.6879999999999999</v>
+        <v>2.374</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr"/>
@@ -4163,28 +4163,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>0.9350000000000001</v>
+        <v>2.62</v>
       </c>
       <c r="E83" s="8" t="n">
-        <v>-0.0106</v>
+        <v>-0.0296</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>1858700</v>
+        <v>2255000</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.49</v>
+        <v>0.45</v>
       </c>
       <c r="H83" t="n">
-        <v>27.89</v>
+        <v>35.88</v>
       </c>
       <c r="I83" s="6" t="inlineStr">
         <is>
@@ -4192,10 +4192,10 @@
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.979</v>
+        <v>2.879</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>1.059</v>
+        <v>2.87</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
@@ -4208,28 +4208,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>0.95</v>
+        <v>7.29</v>
       </c>
       <c r="E84" s="8" t="n">
-        <v>-0.0052</v>
+        <v>-0.005500000000000001</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>1795000</v>
+        <v>2225100</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.32</v>
+        <v>0.22</v>
       </c>
       <c r="H84" t="n">
-        <v>63.6</v>
+        <v>32.77</v>
       </c>
       <c r="I84" s="6" t="inlineStr">
         <is>
@@ -4237,10 +4237,10 @@
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.917</v>
+        <v>7.499</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0.871</v>
+        <v>8.003</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
@@ -4253,28 +4253,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>1.18</v>
+        <v>0.585</v>
       </c>
       <c r="E85" s="8" t="n">
-        <v>-0.0328</v>
+        <v>-0.0488</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>1753800</v>
+        <v>2208900</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.23</v>
+        <v>0.52</v>
       </c>
       <c r="H85" t="n">
-        <v>52.34</v>
+        <v>47.76</v>
       </c>
       <c r="I85" s="6" t="inlineStr">
         <is>
@@ -4282,10 +4282,10 @@
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.168</v>
+        <v>0.6</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>1.13</v>
+        <v>0.585</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr"/>
@@ -4298,39 +4298,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>0.975</v>
-      </c>
-      <c r="E86" s="8" t="n">
-        <v>-0.0441</v>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E86" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>1748800</v>
+        <v>2180200</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.38</v>
+        <v>0.92</v>
       </c>
       <c r="H86" t="n">
-        <v>42.79</v>
-      </c>
-      <c r="I86" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.36</v>
+      </c>
+      <c r="I86" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.049</v>
+        <v>0.642</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0.926</v>
+        <v>0.548</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
@@ -4343,28 +4343,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="E87" s="8" t="n">
-        <v>-0.004099999999999999</v>
+        <v>2.79</v>
+      </c>
+      <c r="E87" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>1722300</v>
+        <v>2175200</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.17</v>
+        <v>0.45</v>
       </c>
       <c r="H87" t="n">
-        <v>33.12</v>
+        <v>56.06</v>
       </c>
       <c r="I87" s="6" t="inlineStr">
         <is>
@@ -4372,10 +4372,10 @@
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>7.499</v>
+        <v>2.765</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>8.003</v>
+        <v>2.158</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
@@ -4388,39 +4388,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="E88" s="8" t="n">
-        <v>-0.0245</v>
+        <v>13.04</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>0.0046</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>1712100</v>
+        <v>2164200</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.52</v>
+        <v>0.24</v>
       </c>
       <c r="H88" t="n">
-        <v>38.96</v>
-      </c>
-      <c r="I88" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.07</v>
+      </c>
+      <c r="I88" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>2.926</v>
+        <v>13.027</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>3.024</v>
+        <v>13.469</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr"/>
@@ -4433,28 +4433,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>3.74</v>
+        <v>2.8</v>
       </c>
       <c r="E89" s="8" t="n">
-        <v>-0.026</v>
+        <v>-0.021</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>1711600</v>
+        <v>2140800</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="H89" t="n">
-        <v>45.59</v>
+        <v>39.49</v>
       </c>
       <c r="I89" s="6" t="inlineStr">
         <is>
@@ -4462,10 +4462,10 @@
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>3.86</v>
+        <v>2.927</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>3.646</v>
+        <v>3.024</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
@@ -4478,28 +4478,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E90" s="8" t="n">
-        <v>-0.0429</v>
+        <v>0.865</v>
+      </c>
+      <c r="E90" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>1698200</v>
+        <v>1992800</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.27</v>
+        <v>0.64</v>
       </c>
       <c r="H90" t="n">
-        <v>56.59</v>
+        <v>51.9</v>
       </c>
       <c r="I90" s="6" t="inlineStr">
         <is>
@@ -4507,10 +4507,10 @@
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.767</v>
+        <v>0.865</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0.68</v>
+        <v>0.859</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr"/>
@@ -4523,39 +4523,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E91" s="10" t="n">
-        <v>0</v>
+        <v>0.66</v>
+      </c>
+      <c r="E91" s="8" t="n">
+        <v>-0.0222</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>1686800</v>
+        <v>1973400</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.29</v>
+        <v>0.22</v>
       </c>
       <c r="H91" t="n">
-        <v>66.89</v>
-      </c>
-      <c r="I91" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.67</v>
+      </c>
+      <c r="I91" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.792</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0.769</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr"/>
@@ -4568,39 +4568,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>0.48</v>
+        <v>0.8</v>
       </c>
       <c r="E92" s="8" t="n">
-        <v>-0.04</v>
+        <v>-0.0062</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>1685900</v>
+        <v>1931700</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0.23</v>
+        <v>0.33</v>
       </c>
       <c r="H92" t="n">
-        <v>28.41</v>
-      </c>
-      <c r="I92" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.65</v>
+      </c>
+      <c r="I92" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.556</v>
+        <v>0.792</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0.626</v>
+        <v>0.769</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="7" t="inlineStr"/>
@@ -4613,28 +4613,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="E93" s="3" t="n">
-        <v>0.006999999999999999</v>
+        <v>1.18</v>
+      </c>
+      <c r="E93" s="8" t="n">
+        <v>-0.0328</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>1672600</v>
+        <v>1916600</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.41</v>
+        <v>0.26</v>
       </c>
       <c r="H93" t="n">
-        <v>44.83</v>
+        <v>52.34</v>
       </c>
       <c r="I93" s="6" t="inlineStr">
         <is>
@@ -4642,10 +4642,10 @@
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>1.452</v>
+        <v>1.168</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>1.466</v>
+        <v>1.13</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="7" t="inlineStr"/>
@@ -4658,28 +4658,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>2.61</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="E94" s="8" t="n">
-        <v>-0.0333</v>
+        <v>-0.0106</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>1640800</v>
+        <v>1912000</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="H94" t="n">
-        <v>35.52</v>
+        <v>27.89</v>
       </c>
       <c r="I94" s="6" t="inlineStr">
         <is>
@@ -4687,10 +4687,10 @@
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>2.878</v>
+        <v>0.979</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>2.87</v>
+        <v>1.059</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="7" t="inlineStr"/>
@@ -4703,28 +4703,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>1.27</v>
+        <v>3.74</v>
       </c>
       <c r="E95" s="8" t="n">
-        <v>-0.0451</v>
+        <v>-0.026</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>1606800</v>
+        <v>1904200</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="H95" t="n">
-        <v>54.81</v>
+        <v>45.59</v>
       </c>
       <c r="I95" s="6" t="inlineStr">
         <is>
@@ -4732,10 +4732,10 @@
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>1.249</v>
+        <v>3.86</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>1.167</v>
+        <v>3.646</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="7" t="inlineStr"/>
@@ -4748,39 +4748,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="E96" s="10" t="n">
-        <v>0</v>
+        <v>0.775</v>
+      </c>
+      <c r="E96" s="8" t="n">
+        <v>-0.0491</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>1577800</v>
+        <v>1860600</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="H96" t="n">
-        <v>49.34</v>
-      </c>
-      <c r="I96" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.55</v>
+      </c>
+      <c r="I96" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1.926</v>
+        <v>0.767</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>1.953</v>
+        <v>0.68</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="7" t="inlineStr"/>
@@ -4793,39 +4793,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E97" s="3" t="n">
-        <v>0.0308</v>
+        <v>1.93</v>
+      </c>
+      <c r="E97" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>1549700</v>
+        <v>1854600</v>
       </c>
       <c r="G97" s="5" t="n">
         <v>0.3</v>
       </c>
       <c r="H97" t="n">
-        <v>47.07</v>
-      </c>
-      <c r="I97" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.34</v>
+      </c>
+      <c r="I97" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.336</v>
+        <v>1.926</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0.343</v>
+        <v>1.953</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="7" t="inlineStr"/>
@@ -4838,28 +4838,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E98" s="10" t="n">
-        <v>0</v>
+        <v>0.33</v>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>0.0154</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>1536400</v>
+        <v>1821800</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="H98" t="n">
-        <v>23.74</v>
+        <v>41.84</v>
       </c>
       <c r="I98" s="6" t="inlineStr">
         <is>
@@ -4867,10 +4867,10 @@
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>1.424</v>
+        <v>0.335</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>1.58</v>
+        <v>0.343</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr"/>
@@ -4883,28 +4883,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>0.71</v>
+        <v>0.95</v>
       </c>
       <c r="E99" s="8" t="n">
-        <v>-0.0274</v>
+        <v>-0.0052</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>1499800</v>
+        <v>1820100</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0.1</v>
+        <v>0.33</v>
       </c>
       <c r="H99" t="n">
-        <v>43.13</v>
+        <v>63.6</v>
       </c>
       <c r="I99" s="6" t="inlineStr">
         <is>
@@ -4912,10 +4912,10 @@
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.764</v>
+        <v>0.917</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0.722</v>
+        <v>0.871</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="7" t="inlineStr"/>
@@ -4928,39 +4928,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>12.98</v>
-      </c>
-      <c r="E100" s="10" t="n">
-        <v>0</v>
+        <v>3.74</v>
+      </c>
+      <c r="E100" s="8" t="n">
+        <v>-0.0106</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>1498600</v>
+        <v>1738100</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="H100" t="n">
-        <v>44.06</v>
-      </c>
-      <c r="I100" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.45</v>
+      </c>
+      <c r="I100" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>13.021</v>
+        <v>3.625</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>13.468</v>
+        <v>2.918</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr"/>
@@ -4973,28 +4973,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="E101" s="8" t="n">
-        <v>-0.0185</v>
+        <v>1.44</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>0.006999999999999999</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>1493400</v>
+        <v>1725500</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>0.15</v>
+        <v>0.42</v>
       </c>
       <c r="H101" t="n">
-        <v>55.61</v>
+        <v>44.83</v>
       </c>
       <c r="I101" s="6" t="inlineStr">
         <is>
@@ -5002,10 +5002,10 @@
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>3.622</v>
+        <v>1.452</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>2.918</v>
+        <v>1.466</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="7" t="inlineStr"/>
@@ -5018,39 +5018,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>7173</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>TOYOVEN</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="E102" s="8" t="n">
-        <v>-0.0387</v>
+        <v>0.255</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>0.0851</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>1463300</v>
+        <v>1665100</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0.47</v>
+        <v>2.57</v>
       </c>
       <c r="H102" t="n">
-        <v>50.16</v>
-      </c>
-      <c r="I102" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.08</v>
+      </c>
+      <c r="I102" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>3.026</v>
+        <v>0.217</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>2.846</v>
+        <v>0.209</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="7" t="inlineStr"/>
@@ -5072,19 +5072,19 @@
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>0.76</v>
+        <v>0.755</v>
       </c>
       <c r="E103" s="8" t="n">
-        <v>-0.013</v>
+        <v>-0.0195</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>1461500</v>
+        <v>1661600</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="H103" t="n">
-        <v>44.91</v>
+        <v>43.62</v>
       </c>
       <c r="I103" s="6" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.777</v>
+        <v>0.776</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0.773</v>
@@ -5108,28 +5108,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>8524</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>TALIWRK</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>0.23</v>
+        <v>1.26</v>
       </c>
       <c r="E104" s="8" t="n">
-        <v>-0.0213</v>
+        <v>-0.0526</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>1461500</v>
+        <v>1654400</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="H104" t="n">
-        <v>37.06</v>
+        <v>53.76</v>
       </c>
       <c r="I104" s="6" t="inlineStr">
         <is>
@@ -5137,10 +5137,10 @@
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.247</v>
+        <v>1.248</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0.258</v>
+        <v>1.167</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="7" t="inlineStr"/>
@@ -5153,28 +5153,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0272</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>TTVHB</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>0.235</v>
+        <v>2.98</v>
       </c>
       <c r="E105" s="8" t="n">
-        <v>-0.0208</v>
+        <v>-0.0387</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>1436900</v>
+        <v>1628400</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>0.59</v>
+        <v>0.52</v>
       </c>
       <c r="H105" t="n">
-        <v>44.1</v>
+        <v>50.16</v>
       </c>
       <c r="I105" s="6" t="inlineStr">
         <is>
@@ -5182,10 +5182,10 @@
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.248</v>
+        <v>3.026</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0.255</v>
+        <v>2.846</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="7" t="inlineStr"/>
@@ -5198,28 +5198,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>0.63</v>
+        <v>3.79</v>
       </c>
       <c r="E106" s="8" t="n">
-        <v>-0.0156</v>
+        <v>-0.0207</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>1408900</v>
+        <v>1613500</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>0.59</v>
+        <v>0.16</v>
       </c>
       <c r="H106" t="n">
-        <v>48.11</v>
+        <v>46.67</v>
       </c>
       <c r="I106" s="6" t="inlineStr">
         <is>
@@ -5227,10 +5227,10 @@
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.637</v>
+        <v>3.969</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0.619</v>
+        <v>3.522</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="7" t="inlineStr"/>
@@ -5243,39 +5243,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>0.305</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E107" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>1393500</v>
+        <v>1569000</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>0.22</v>
+        <v>0.73</v>
       </c>
       <c r="H107" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="I107" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.26</v>
+      </c>
+      <c r="I107" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.32</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0.338</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="7" t="inlineStr"/>
@@ -5288,39 +5288,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>0.665</v>
-      </c>
-      <c r="E108" s="8" t="n">
-        <v>-0.0432</v>
+        <v>1.63</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>0.0062</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>1377500</v>
+        <v>1541300</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>0.44</v>
+        <v>0.23</v>
       </c>
       <c r="H108" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="I108" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.49</v>
+      </c>
+      <c r="I108" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.738</v>
+        <v>1.615</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0.746</v>
+        <v>1.703</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="7" t="inlineStr"/>
@@ -5333,28 +5333,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="E109" s="3" t="n">
-        <v>0.0471</v>
+        <v>1.24</v>
+      </c>
+      <c r="E109" s="8" t="n">
+        <v>-0.0236</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>1372900</v>
+        <v>1537500</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>0.9</v>
+        <v>0.48</v>
       </c>
       <c r="H109" t="n">
-        <v>47.67</v>
+        <v>46.92</v>
       </c>
       <c r="I109" s="6" t="inlineStr">
         <is>
@@ -5362,10 +5362,10 @@
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.914</v>
+        <v>1.288</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0.865</v>
+        <v>1.217</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="7" t="inlineStr"/>
@@ -5378,39 +5378,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>7173</t>
+          <t>0272</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>TOYOVEN</t>
+          <t>TTVHB</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="E110" s="8" t="n">
+        <v>-0.0208</v>
+      </c>
+      <c r="F110" s="4" t="n">
+        <v>1519200</v>
+      </c>
+      <c r="G110" s="5" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="H110" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="I110" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="K110" s="2" t="n">
         <v>0.255</v>
-      </c>
-      <c r="E110" s="3" t="n">
-        <v>0.0851</v>
-      </c>
-      <c r="F110" s="4" t="n">
-        <v>1350100</v>
-      </c>
-      <c r="G110" s="5" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="H110" t="n">
-        <v>75.08</v>
-      </c>
-      <c r="I110" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J110" s="2" t="n">
-        <v>0.217</v>
-      </c>
-      <c r="K110" s="2" t="n">
-        <v>0.209</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="7" t="inlineStr"/>
@@ -5423,39 +5423,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="E111" s="8" t="n">
-        <v>-0.0233</v>
+        <v>2.51</v>
+      </c>
+      <c r="E111" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>1343800</v>
+        <v>1517600</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>0.28</v>
+        <v>0.48</v>
       </c>
       <c r="H111" t="n">
-        <v>40.51</v>
-      </c>
-      <c r="I111" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>37.53</v>
+      </c>
+      <c r="I111" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>1.741</v>
+        <v>2.561</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>1.772</v>
+        <v>2.7</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="7" t="inlineStr"/>
@@ -5468,28 +5468,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="E112" s="8" t="n">
-        <v>-0.0155</v>
+        <v>0.905</v>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>0.06469999999999999</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>1309800</v>
+        <v>1512700</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>0.13</v>
+        <v>0.99</v>
       </c>
       <c r="H112" t="n">
-        <v>47.3</v>
+        <v>49.82</v>
       </c>
       <c r="I112" s="6" t="inlineStr">
         <is>
@@ -5497,10 +5497,10 @@
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>3.971</v>
+        <v>0.916</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>3.522</v>
+        <v>0.866</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="7" t="inlineStr"/>
@@ -5513,28 +5513,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="E113" s="8" t="n">
-        <v>-0.0385</v>
+        <v>-0.0274</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>1293800</v>
+        <v>1509500</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="H113" t="n">
-        <v>55.01</v>
+        <v>43.13</v>
       </c>
       <c r="I113" s="6" t="inlineStr">
         <is>
@@ -5542,10 +5542,10 @@
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.729</v>
+        <v>0.764</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0.701</v>
+        <v>0.722</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="7" t="inlineStr"/>
@@ -5558,28 +5558,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>TDM</t>
+          <t>TALIWRK</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E114" s="10" t="n">
-        <v>0</v>
+        <v>0.23</v>
+      </c>
+      <c r="E114" s="8" t="n">
+        <v>-0.0213</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>1286500</v>
+        <v>1479500</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>2.62</v>
+        <v>0.72</v>
       </c>
       <c r="H114" t="n">
-        <v>27.29</v>
+        <v>37.06</v>
       </c>
       <c r="I114" s="6" t="inlineStr">
         <is>
@@ -5587,10 +5587,10 @@
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.208</v>
+        <v>0.247</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0.217</v>
+        <v>0.258</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="7" t="inlineStr"/>
@@ -5603,28 +5603,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>1.19</v>
+        <v>0.3</v>
       </c>
       <c r="E115" s="8" t="n">
-        <v>-0.0403</v>
+        <v>-0.0164</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>1273200</v>
+        <v>1468700</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>0.36</v>
+        <v>0.24</v>
       </c>
       <c r="H115" t="n">
-        <v>48.47</v>
+        <v>38.46</v>
       </c>
       <c r="I115" s="6" t="inlineStr">
         <is>
@@ -5632,10 +5632,10 @@
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>1.249</v>
+        <v>0.319</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>1.05</v>
+        <v>0.338</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="7" t="inlineStr"/>
@@ -5648,28 +5648,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>0.35</v>
+        <v>1.69</v>
       </c>
       <c r="E116" s="8" t="n">
-        <v>-0.0141</v>
+        <v>-0.0174</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>1249800</v>
+        <v>1464600</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>0.14</v>
+        <v>0.3</v>
       </c>
       <c r="H116" t="n">
-        <v>50.37</v>
+        <v>41.59</v>
       </c>
       <c r="I116" s="6" t="inlineStr">
         <is>
@@ -5677,10 +5677,10 @@
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.355</v>
+        <v>1.742</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>0.326</v>
+        <v>1.772</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="7" t="inlineStr"/>
@@ -5693,28 +5693,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>1.23</v>
+        <v>0.75</v>
       </c>
       <c r="E117" s="8" t="n">
-        <v>-0.0315</v>
+        <v>-0.0385</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>1247300</v>
+        <v>1415500</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>0.39</v>
+        <v>0.62</v>
       </c>
       <c r="H117" t="n">
-        <v>46.1</v>
+        <v>55.01</v>
       </c>
       <c r="I117" s="6" t="inlineStr">
         <is>
@@ -5722,10 +5722,10 @@
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>1.287</v>
+        <v>0.729</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>1.217</v>
+        <v>0.701</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="7" t="inlineStr"/>
@@ -5738,28 +5738,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>BPURI</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>0.215</v>
+        <v>0.67</v>
       </c>
       <c r="E118" s="8" t="n">
-        <v>-0.0227</v>
+        <v>-0.036</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>1223900</v>
+        <v>1412000</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>2.35</v>
+        <v>0.45</v>
       </c>
       <c r="H118" t="n">
-        <v>40.22</v>
+        <v>35.17</v>
       </c>
       <c r="I118" s="6" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.225</v>
+        <v>0.738</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>0.233</v>
+        <v>0.746</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="7" t="inlineStr"/>
@@ -5783,28 +5783,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>0.87</v>
+        <v>0.63</v>
       </c>
       <c r="E119" s="8" t="n">
-        <v>-0.0169</v>
+        <v>-0.0156</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>1208400</v>
+        <v>1408900</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>0.47</v>
+        <v>0.59</v>
       </c>
       <c r="H119" t="n">
-        <v>20.42</v>
+        <v>48.11</v>
       </c>
       <c r="I119" s="6" t="inlineStr">
         <is>
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.637</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>0.98</v>
+        <v>0.619</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="7" t="inlineStr"/>
@@ -5828,28 +5828,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>2054</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>TDM</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E120" s="8" t="n">
-        <v>-0.0354</v>
+        <v>0.2</v>
+      </c>
+      <c r="E120" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>1202900</v>
+        <v>1383200</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>0.51</v>
+        <v>2.81</v>
       </c>
       <c r="H120" t="n">
-        <v>34.68</v>
+        <v>27.29</v>
       </c>
       <c r="I120" s="6" t="inlineStr">
         <is>
@@ -5857,10 +5857,10 @@
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>1.232</v>
+        <v>0.208</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>1.303</v>
+        <v>0.217</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="7" t="inlineStr"/>
@@ -5873,28 +5873,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>10.42</v>
+        <v>0.875</v>
       </c>
       <c r="E121" s="8" t="n">
-        <v>-0.0207</v>
+        <v>-0.0113</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>1202000</v>
+        <v>1369700</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>0.33</v>
+        <v>0.53</v>
       </c>
       <c r="H121" t="n">
-        <v>54.34</v>
+        <v>21.19</v>
       </c>
       <c r="I121" s="6" t="inlineStr">
         <is>
@@ -5902,10 +5902,10 @@
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>10.397</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>9.694000000000001</v>
+        <v>0.98</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="7" t="inlineStr"/>
@@ -5918,31 +5918,40 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>9776</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>RSSB</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="E122" s="10" t="n">
-        <v>0</v>
+        <v>1.2</v>
+      </c>
+      <c r="E122" s="8" t="n">
+        <v>-0.0323</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>1193800</v>
-      </c>
-      <c r="G122" s="5" t="n"/>
+        <v>1350400</v>
+      </c>
+      <c r="G122" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H122" t="n">
+        <v>49.35</v>
+      </c>
       <c r="I122" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J122" s="2" t="n"/>
-      <c r="K122" s="2" t="n"/>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K122" s="2" t="n">
+        <v>1.05</v>
+      </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="7" t="inlineStr"/>
     </row>
@@ -5954,39 +5963,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>6181</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>MALTON</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E123" s="3" t="n">
-        <v>0.0351</v>
+        <v>0.205</v>
+      </c>
+      <c r="E123" s="8" t="n">
+        <v>-0.04650000000000001</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>1183700</v>
+        <v>1339300</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>1.24</v>
+        <v>1.92</v>
       </c>
       <c r="H123" t="n">
-        <v>66.28</v>
-      </c>
-      <c r="I123" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.59</v>
+      </c>
+      <c r="I123" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.275</v>
+        <v>0.218</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>0.267</v>
+        <v>0.226</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="7" t="inlineStr"/>
@@ -5999,39 +6008,39 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>0466</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>SRKKAI</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="E124" s="10" t="n">
-        <v>0</v>
+        <v>0.485</v>
+      </c>
+      <c r="E124" s="8" t="n">
+        <v>-0.049</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>1174200</v>
+        <v>1328200</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>0.37</v>
+        <v>1.12</v>
       </c>
       <c r="H124" t="n">
-        <v>37.53</v>
-      </c>
-      <c r="I124" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.4</v>
+      </c>
+      <c r="I124" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>2.561</v>
+        <v>0.517</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>2.7</v>
+        <v>0.531</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="7" t="inlineStr"/>
@@ -6044,39 +6053,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="E125" s="8" t="n">
-        <v>-0.0173</v>
+        <v>0.355</v>
+      </c>
+      <c r="E125" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>1157600</v>
+        <v>1291700</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>0.3</v>
+        <v>0.14</v>
       </c>
       <c r="H125" t="n">
-        <v>56.23</v>
-      </c>
-      <c r="I125" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.59</v>
+      </c>
+      <c r="I125" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>2.207</v>
+        <v>0.356</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>2.152</v>
+        <v>0.326</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="7" t="inlineStr"/>
@@ -6089,39 +6098,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="E126" s="3" t="n">
-        <v>0.0123</v>
+        <v>10.42</v>
+      </c>
+      <c r="E126" s="8" t="n">
+        <v>-0.0207</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>1156500</v>
+        <v>1289700</v>
       </c>
       <c r="G126" s="5" t="n">
-        <v>0.17</v>
+        <v>0.36</v>
       </c>
       <c r="H126" t="n">
-        <v>50.81</v>
-      </c>
-      <c r="I126" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.34</v>
+      </c>
+      <c r="I126" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>1.616</v>
+        <v>10.397</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>1.703</v>
+        <v>9.694000000000001</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="7" t="inlineStr"/>
@@ -6134,28 +6143,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0466</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>SRKKAI</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>0.49</v>
+        <v>1.09</v>
       </c>
       <c r="E127" s="8" t="n">
-        <v>-0.0392</v>
+        <v>-0.0354</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>1122800</v>
+        <v>1258900</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.53</v>
       </c>
       <c r="H127" t="n">
-        <v>37.73</v>
+        <v>34.68</v>
       </c>
       <c r="I127" s="6" t="inlineStr">
         <is>
@@ -6163,10 +6172,10 @@
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.518</v>
+        <v>1.232</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>0.531</v>
+        <v>1.303</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="7" t="inlineStr"/>
@@ -6179,28 +6188,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>5120</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>AMFIRST</t>
+          <t>BPURI</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>0.33</v>
+        <v>0.21</v>
       </c>
       <c r="E128" s="8" t="n">
-        <v>-0.0294</v>
+        <v>-0.0455</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>1111100</v>
+        <v>1229000</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>3.79</v>
+        <v>2.36</v>
       </c>
       <c r="H128" t="n">
-        <v>26.77</v>
+        <v>37.42</v>
       </c>
       <c r="I128" s="6" t="inlineStr">
         <is>
@@ -6208,10 +6217,10 @@
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.344</v>
+        <v>0.224</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>0.345</v>
+        <v>0.233</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="7" t="inlineStr"/>
@@ -6224,40 +6233,31 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>9776</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>RSSB</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E129" s="8" t="n">
-        <v>-0.0213</v>
+        <v>0.33</v>
+      </c>
+      <c r="E129" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>1090600</v>
-      </c>
-      <c r="G129" s="5" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="H129" t="n">
-        <v>43.72</v>
-      </c>
+        <v>1208800</v>
+      </c>
+      <c r="G129" s="5" t="n"/>
       <c r="I129" s="6" t="inlineStr">
         <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J129" s="2" t="n">
-        <v>0.247</v>
-      </c>
-      <c r="K129" s="2" t="n">
-        <v>0.223</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="n"/>
+      <c r="K129" s="2" t="n"/>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="7" t="inlineStr"/>
     </row>
@@ -6278,19 +6278,19 @@
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>0.895</v>
-      </c>
-      <c r="E130" s="10" t="n">
-        <v>0</v>
+        <v>0.885</v>
+      </c>
+      <c r="E130" s="8" t="n">
+        <v>-0.0112</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>1087900</v>
+        <v>1206900</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.77</v>
       </c>
       <c r="H130" t="n">
-        <v>38.7</v>
+        <v>35.62</v>
       </c>
       <c r="I130" s="6" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>0.915</v>
+        <v>0.914</v>
       </c>
       <c r="K130" s="2" t="n">
         <v>0.931</v>
@@ -6314,39 +6314,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>6181</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>MALTON</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>0.205</v>
+        <v>2.28</v>
       </c>
       <c r="E131" s="8" t="n">
-        <v>-0.04650000000000001</v>
+        <v>-0.013</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>1072500</v>
+        <v>1198100</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>1.54</v>
+        <v>0.32</v>
       </c>
       <c r="H131" t="n">
-        <v>35.59</v>
-      </c>
-      <c r="I131" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.14</v>
+      </c>
+      <c r="I131" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>0.218</v>
+        <v>2.208</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>0.226</v>
+        <v>2.152</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="7" t="inlineStr"/>
@@ -6359,28 +6359,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0337</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E132" s="8" t="n">
-        <v>-0.04</v>
+        <v>0.29</v>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>0.0175</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>1070300</v>
+        <v>1184300</v>
       </c>
       <c r="G132" s="5" t="n">
-        <v>0.57</v>
+        <v>1.24</v>
       </c>
       <c r="H132" t="n">
-        <v>50.37</v>
+        <v>63.79</v>
       </c>
       <c r="I132" s="9" t="inlineStr">
         <is>
@@ -6388,10 +6388,10 @@
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>0.24</v>
+        <v>0.275</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>0.243</v>
+        <v>0.267</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="7" t="inlineStr"/>
@@ -6404,28 +6404,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>2.44</v>
+        <v>1.18</v>
       </c>
       <c r="E133" s="8" t="n">
-        <v>-0.008100000000000001</v>
+        <v>-0.0167</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>1057000</v>
+        <v>1179400</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="H133" t="n">
-        <v>49.39</v>
+        <v>34.37</v>
       </c>
       <c r="I133" s="6" t="inlineStr">
         <is>
@@ -6433,10 +6433,10 @@
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>2.459</v>
+        <v>1.24</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>2.375</v>
+        <v>1.334</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="7" t="inlineStr"/>
@@ -6449,39 +6449,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0328</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>3REN</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>0.39</v>
+        <v>7.17</v>
       </c>
       <c r="E134" s="8" t="n">
-        <v>-0.0127</v>
+        <v>-0.005500000000000001</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>1049000</v>
+        <v>1130900</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>0.46</v>
+        <v>0.15</v>
       </c>
       <c r="H134" t="n">
-        <v>50.92</v>
-      </c>
-      <c r="I134" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.27</v>
+      </c>
+      <c r="I134" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>0.388</v>
+        <v>7.345</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>0.391</v>
+        <v>7.669</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="7" t="inlineStr"/>
@@ -6494,28 +6494,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>NGGB</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>0.76</v>
+        <v>6.78</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>0.0066</v>
+        <v>0.0059</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>980100</v>
+        <v>1122100</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>0.63</v>
+        <v>0.26</v>
       </c>
       <c r="H135" t="n">
-        <v>61.61</v>
+        <v>51.24</v>
       </c>
       <c r="I135" s="6" t="inlineStr">
         <is>
@@ -6523,10 +6523,10 @@
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>0.742</v>
+        <v>6.761</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>0.718</v>
+        <v>6.835</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="7" t="inlineStr"/>
@@ -6539,28 +6539,28 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>5120</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>AMFIRST</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>1.19</v>
+        <v>0.335</v>
       </c>
       <c r="E136" s="8" t="n">
-        <v>-0.0083</v>
+        <v>-0.0147</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>958800</v>
+        <v>1121100</v>
       </c>
       <c r="G136" s="5" t="n">
-        <v>0.13</v>
+        <v>3.82</v>
       </c>
       <c r="H136" t="n">
-        <v>35.65</v>
+        <v>31.64</v>
       </c>
       <c r="I136" s="6" t="inlineStr">
         <is>
@@ -6568,10 +6568,10 @@
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>1.241</v>
+        <v>0.344</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>1.334</v>
+        <v>0.345</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="7" t="inlineStr"/>
@@ -6584,28 +6584,28 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>THMY</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>2.06</v>
+        <v>0.225</v>
       </c>
       <c r="E137" s="8" t="n">
-        <v>-0.0283</v>
+        <v>-0.0426</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>942500</v>
+        <v>1110700</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>0.39</v>
+        <v>0.23</v>
       </c>
       <c r="H137" t="n">
-        <v>48.8</v>
+        <v>41.8</v>
       </c>
       <c r="I137" s="6" t="inlineStr">
         <is>
@@ -6613,10 +6613,10 @@
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>2.112</v>
+        <v>0.247</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>1.984</v>
+        <v>0.223</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="7" t="inlineStr"/>
@@ -6629,39 +6629,39 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>5106</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>AXREIT</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>1.84</v>
+        <v>0.635</v>
       </c>
       <c r="E138" s="8" t="n">
-        <v>-0.0054</v>
+        <v>-0.0305</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>883100</v>
+        <v>1098100</v>
       </c>
       <c r="G138" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="H138" t="n">
-        <v>51.86</v>
-      </c>
-      <c r="I138" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>64.23999999999999</v>
+      </c>
+      <c r="I138" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>1.83</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>1.828</v>
+        <v>0.463</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="7" t="inlineStr"/>
@@ -6674,39 +6674,39 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>0337</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>6.78</v>
-      </c>
-      <c r="E139" s="3" t="n">
-        <v>0.0059</v>
+        <v>0.24</v>
+      </c>
+      <c r="E139" s="8" t="n">
+        <v>-0.04</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>853200</v>
+        <v>1093300</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>0.19</v>
+        <v>0.58</v>
       </c>
       <c r="H139" t="n">
-        <v>51.24</v>
-      </c>
-      <c r="I139" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.37</v>
+      </c>
+      <c r="I139" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>6.761</v>
+        <v>0.24</v>
       </c>
       <c r="K139" s="2" t="n">
-        <v>6.835</v>
+        <v>0.243</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="7" t="inlineStr"/>
@@ -6719,39 +6719,39 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>0328</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>3REN</t>
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>0.625</v>
+        <v>0.39</v>
       </c>
       <c r="E140" s="8" t="n">
-        <v>-0.0458</v>
+        <v>-0.0127</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>846200</v>
+        <v>1070700</v>
       </c>
       <c r="G140" s="5" t="n">
-        <v>0.16</v>
+        <v>0.47</v>
       </c>
       <c r="H140" t="n">
-        <v>62.58</v>
-      </c>
-      <c r="I140" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.92</v>
+      </c>
+      <c r="I140" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.388</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>0.462</v>
+        <v>0.391</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="7" t="inlineStr"/>
@@ -6764,39 +6764,39 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>4634</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>POS</t>
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>0.555</v>
+        <v>0.255</v>
       </c>
       <c r="E141" s="3" t="n">
-        <v>0.0091</v>
+        <v>0.0408</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>842000</v>
+        <v>1025300</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>0.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H141" t="n">
-        <v>39.65</v>
-      </c>
-      <c r="I141" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.86</v>
+      </c>
+      <c r="I141" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>0.573</v>
+        <v>0.249</v>
       </c>
       <c r="K141" s="2" t="n">
-        <v>0.615</v>
+        <v>0.251</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="7" t="inlineStr"/>
@@ -6809,28 +6809,28 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0291</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>CHB</t>
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>10.04</v>
-      </c>
-      <c r="E142" s="3" t="n">
-        <v>0.006</v>
+        <v>2.52</v>
+      </c>
+      <c r="E142" s="8" t="n">
+        <v>-0.0345</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>795800</v>
+        <v>1023500</v>
       </c>
       <c r="G142" s="5" t="n">
-        <v>0.06</v>
+        <v>0.62</v>
       </c>
       <c r="H142" t="n">
-        <v>49.55</v>
+        <v>53.41</v>
       </c>
       <c r="I142" s="6" t="inlineStr">
         <is>
@@ -6838,10 +6838,10 @@
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>10.01</v>
+        <v>2.529</v>
       </c>
       <c r="K142" s="2" t="n">
-        <v>10.168</v>
+        <v>2.224</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="7" t="inlineStr"/>
@@ -6854,39 +6854,39 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="E143" s="8" t="n">
-        <v>-0.0293</v>
+        <v>10.04</v>
+      </c>
+      <c r="E143" s="3" t="n">
+        <v>0.006</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>771500</v>
+        <v>1017700</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="H143" t="n">
-        <v>46.61</v>
-      </c>
-      <c r="I143" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.55</v>
+      </c>
+      <c r="I143" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>4.358</v>
+        <v>10.01</v>
       </c>
       <c r="K143" s="2" t="n">
-        <v>4.438</v>
+        <v>10.168</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="7" t="inlineStr"/>
@@ -6899,28 +6899,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0291</t>
+          <t>0375</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>CHB</t>
+          <t>THMY</t>
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>2.48</v>
+        <v>2.05</v>
       </c>
       <c r="E144" s="8" t="n">
-        <v>-0.0498</v>
+        <v>-0.033</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>770800</v>
+        <v>1015800</v>
       </c>
       <c r="G144" s="5" t="n">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="H144" t="n">
-        <v>51.32</v>
+        <v>48.24</v>
       </c>
       <c r="I144" s="6" t="inlineStr">
         <is>
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>2.526</v>
+        <v>2.112</v>
       </c>
       <c r="K144" s="2" t="n">
-        <v>2.223</v>
+        <v>1.984</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="7" t="inlineStr"/>
@@ -6944,28 +6944,28 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>KOBAY</t>
         </is>
       </c>
       <c r="D145" s="2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E145" s="8" t="n">
-        <v>-0.0441</v>
+        <v>2.01</v>
+      </c>
+      <c r="E145" s="3" t="n">
+        <v>0.0203</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>761900</v>
+        <v>1000700</v>
       </c>
       <c r="G145" s="5" t="n">
-        <v>0.32</v>
+        <v>0.88</v>
       </c>
       <c r="H145" t="n">
-        <v>46.63</v>
+        <v>37.84</v>
       </c>
       <c r="I145" s="6" t="inlineStr">
         <is>
@@ -6973,10 +6973,10 @@
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>1.339</v>
+        <v>2.136</v>
       </c>
       <c r="K145" s="2" t="n">
-        <v>1.273</v>
+        <v>2.291</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="7" t="inlineStr"/>
@@ -6989,28 +6989,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>KOBAY</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D146" s="2" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="E146" s="3" t="n">
-        <v>0.0203</v>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E146" s="8" t="n">
+        <v>-0.0072</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>745100</v>
+        <v>989900</v>
       </c>
       <c r="G146" s="5" t="n">
-        <v>0.66</v>
+        <v>0.14</v>
       </c>
       <c r="H146" t="n">
-        <v>37.84</v>
+        <v>30.53</v>
       </c>
       <c r="I146" s="6" t="inlineStr">
         <is>
@@ -7018,10 +7018,10 @@
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>2.136</v>
+        <v>0.735</v>
       </c>
       <c r="K146" s="2" t="n">
-        <v>2.291</v>
+        <v>0.801</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="7" t="inlineStr"/>
@@ -7034,28 +7034,28 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>0151</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>KGB</t>
+          <t>NGGB</t>
         </is>
       </c>
       <c r="D147" s="2" t="n">
-        <v>8.43</v>
-      </c>
-      <c r="E147" s="8" t="n">
-        <v>-0.0288</v>
+        <v>0.76</v>
+      </c>
+      <c r="E147" s="3" t="n">
+        <v>0.0066</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>735900</v>
+        <v>980100</v>
       </c>
       <c r="G147" s="5" t="n">
-        <v>0.35</v>
+        <v>0.63</v>
       </c>
       <c r="H147" t="n">
-        <v>44.12</v>
+        <v>61.61</v>
       </c>
       <c r="I147" s="6" t="inlineStr">
         <is>
@@ -7063,10 +7063,10 @@
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>8.682</v>
+        <v>0.742</v>
       </c>
       <c r="K147" s="2" t="n">
-        <v>8.707000000000001</v>
+        <v>0.718</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="7" t="inlineStr"/>
@@ -7079,28 +7079,28 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D148" s="2" t="n">
-        <v>0.525</v>
+        <v>4.32</v>
       </c>
       <c r="E148" s="8" t="n">
-        <v>-0.0187</v>
+        <v>-0.0248</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>701200</v>
+        <v>948300</v>
       </c>
       <c r="G148" s="5" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="H148" t="n">
-        <v>61.14</v>
+        <v>47.32</v>
       </c>
       <c r="I148" s="9" t="inlineStr">
         <is>
@@ -7108,10 +7108,10 @@
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>0.494</v>
+        <v>4.36</v>
       </c>
       <c r="K148" s="2" t="n">
-        <v>0.461</v>
+        <v>4.438</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="7" t="inlineStr"/>
@@ -7124,28 +7124,28 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>5106</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>AXREIT</t>
         </is>
       </c>
       <c r="D149" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.85</v>
       </c>
       <c r="E149" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>700000</v>
+        <v>891700</v>
       </c>
       <c r="G149" s="5" t="n">
-        <v>0.33</v>
+        <v>0.7</v>
       </c>
       <c r="H149" t="n">
-        <v>48.26</v>
+        <v>53.66</v>
       </c>
       <c r="I149" s="9" t="inlineStr">
         <is>
@@ -7153,10 +7153,10 @@
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>0.5620000000000001</v>
+        <v>1.831</v>
       </c>
       <c r="K149" s="2" t="n">
-        <v>0.5620000000000001</v>
+        <v>1.829</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="7" t="inlineStr"/>
@@ -7169,28 +7169,28 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D150" s="2" t="n">
-        <v>7.18</v>
+        <v>5.09</v>
       </c>
       <c r="E150" s="8" t="n">
-        <v>-0.0042</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>671700</v>
+        <v>866500</v>
       </c>
       <c r="G150" s="5" t="n">
-        <v>0.09</v>
+        <v>0.2</v>
       </c>
       <c r="H150" t="n">
-        <v>35.67</v>
+        <v>52.38</v>
       </c>
       <c r="I150" s="6" t="inlineStr">
         <is>
@@ -7198,10 +7198,10 @@
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>7.346</v>
+        <v>5.07</v>
       </c>
       <c r="K150" s="2" t="n">
-        <v>7.669</v>
+        <v>5.064</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="7" t="inlineStr"/>
@@ -7214,28 +7214,28 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>0151</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>KGB</t>
         </is>
       </c>
       <c r="D151" s="2" t="n">
-        <v>2.49</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="E151" s="8" t="n">
-        <v>-0.0119</v>
+        <v>-0.0265</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>656600</v>
+        <v>845800</v>
       </c>
       <c r="G151" s="5" t="n">
-        <v>0.12</v>
+        <v>0.4</v>
       </c>
       <c r="H151" t="n">
-        <v>40.83</v>
+        <v>44.52</v>
       </c>
       <c r="I151" s="6" t="inlineStr">
         <is>
@@ -7243,10 +7243,10 @@
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>2.564</v>
+        <v>8.683999999999999</v>
       </c>
       <c r="K151" s="2" t="n">
-        <v>2.739</v>
+        <v>8.708</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="7" t="inlineStr"/>
@@ -7259,39 +7259,39 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D152" s="2" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="E152" s="8" t="n">
-        <v>-0.0152</v>
+        <v>0.555</v>
+      </c>
+      <c r="E152" s="3" t="n">
+        <v>0.0091</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>622200</v>
+        <v>842000</v>
       </c>
       <c r="G152" s="5" t="n">
-        <v>0.1</v>
+        <v>0.75</v>
       </c>
       <c r="H152" t="n">
-        <v>29.47</v>
-      </c>
-      <c r="I152" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>39.65</v>
+      </c>
+      <c r="I152" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>3.405</v>
+        <v>0.573</v>
       </c>
       <c r="K152" s="2" t="n">
-        <v>3.623</v>
+        <v>0.615</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="7" t="inlineStr"/>
@@ -7313,19 +7313,19 @@
         </is>
       </c>
       <c r="D153" s="2" t="n">
-        <v>5.42</v>
+        <v>5.41</v>
       </c>
       <c r="E153" s="8" t="n">
-        <v>-0.0269</v>
+        <v>-0.0287</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>617700</v>
+        <v>834600</v>
       </c>
       <c r="G153" s="5" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="H153" t="n">
-        <v>48.86</v>
+        <v>48.62</v>
       </c>
       <c r="I153" s="9" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         </is>
       </c>
       <c r="J153" s="2" t="n">
-        <v>5.507</v>
+        <v>5.506</v>
       </c>
       <c r="K153" s="2" t="n">
         <v>5.392</v>
@@ -7349,39 +7349,39 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D154" s="2" t="n">
-        <v>5.1</v>
+        <v>0.525</v>
       </c>
       <c r="E154" s="8" t="n">
-        <v>-0.0058</v>
+        <v>-0.0187</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>587000</v>
+        <v>828900</v>
       </c>
       <c r="G154" s="5" t="n">
-        <v>0.14</v>
+        <v>0.22</v>
       </c>
       <c r="H154" t="n">
-        <v>53.09</v>
-      </c>
-      <c r="I154" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.14</v>
+      </c>
+      <c r="I154" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>5.071</v>
+        <v>0.494</v>
       </c>
       <c r="K154" s="2" t="n">
-        <v>5.064</v>
+        <v>0.461</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="7" t="inlineStr"/>
@@ -7394,28 +7394,28 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>0325</t>
+          <t>0293</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>KJTS</t>
         </is>
       </c>
       <c r="D155" s="2" t="n">
-        <v>1.01</v>
+        <v>0.88</v>
       </c>
       <c r="E155" s="8" t="n">
-        <v>-0.0194</v>
+        <v>-0.0435</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>562600</v>
+        <v>820100</v>
       </c>
       <c r="G155" s="5" t="n">
-        <v>0.35</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H155" t="n">
-        <v>37.27</v>
+        <v>34.48</v>
       </c>
       <c r="I155" s="6" t="inlineStr">
         <is>
@@ -7423,10 +7423,10 @@
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>1.092</v>
+        <v>0.979</v>
       </c>
       <c r="K155" s="2" t="n">
-        <v>1.095</v>
+        <v>1.028</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="7" t="inlineStr"/>
@@ -7439,28 +7439,28 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D156" s="2" t="n">
-        <v>0.89</v>
+        <v>1.29</v>
       </c>
       <c r="E156" s="8" t="n">
-        <v>-0.0166</v>
+        <v>-0.0515</v>
       </c>
       <c r="F156" s="4" t="n">
-        <v>552200</v>
+        <v>775000</v>
       </c>
       <c r="G156" s="5" t="n">
-        <v>0.19</v>
+        <v>0.33</v>
       </c>
       <c r="H156" t="n">
-        <v>39.69</v>
+        <v>45.56</v>
       </c>
       <c r="I156" s="6" t="inlineStr">
         <is>
@@ -7468,10 +7468,10 @@
         </is>
       </c>
       <c r="J156" s="2" t="n">
-        <v>0.908</v>
+        <v>1.338</v>
       </c>
       <c r="K156" s="2" t="n">
-        <v>0.958</v>
+        <v>1.273</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="7" t="inlineStr"/>
@@ -7484,39 +7484,39 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>MATRIX</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D157" s="2" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E157" s="3" t="n">
-        <v>0.009300000000000001</v>
+        <v>3.24</v>
+      </c>
+      <c r="E157" s="8" t="n">
+        <v>-0.0122</v>
       </c>
       <c r="F157" s="4" t="n">
-        <v>546700</v>
+        <v>758900</v>
       </c>
       <c r="G157" s="5" t="n">
-        <v>0.43</v>
+        <v>0.12</v>
       </c>
       <c r="H157" t="n">
-        <v>45.93</v>
-      </c>
-      <c r="I157" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.99</v>
+      </c>
+      <c r="I157" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J157" s="2" t="n">
-        <v>1.096</v>
+        <v>3.406</v>
       </c>
       <c r="K157" s="2" t="n">
-        <v>1.138</v>
+        <v>3.624</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="7" t="inlineStr"/>
@@ -7529,39 +7529,39 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D158" s="2" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="E158" s="3" t="n">
-        <v>0.0141</v>
+        <v>2.5</v>
+      </c>
+      <c r="E158" s="8" t="n">
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F158" s="4" t="n">
-        <v>543900</v>
+        <v>755200</v>
       </c>
       <c r="G158" s="5" t="n">
-        <v>0.25</v>
+        <v>0.14</v>
       </c>
       <c r="H158" t="n">
-        <v>58.07</v>
-      </c>
-      <c r="I158" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.47</v>
+      </c>
+      <c r="I158" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J158" s="2" t="n">
-        <v>2.107</v>
+        <v>2.565</v>
       </c>
       <c r="K158" s="2" t="n">
-        <v>2.055</v>
+        <v>2.739</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="7" t="inlineStr"/>
@@ -7574,28 +7574,28 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>LWSABAH</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D159" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E159" s="8" t="n">
-        <v>-0.0272</v>
+        <v>6</v>
+      </c>
+      <c r="E159" s="3" t="n">
+        <v>0.005</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v>543600</v>
+        <v>662300</v>
       </c>
       <c r="G159" s="5" t="n">
-        <v>0.5</v>
+        <v>0.08</v>
       </c>
       <c r="H159" t="n">
-        <v>32.63</v>
+        <v>40.06</v>
       </c>
       <c r="I159" s="6" t="inlineStr">
         <is>
@@ -7603,10 +7603,10 @@
         </is>
       </c>
       <c r="J159" s="2" t="n">
-        <v>1.625</v>
+        <v>6.097</v>
       </c>
       <c r="K159" s="2" t="n">
-        <v>1.631</v>
+        <v>6.351</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="7" t="inlineStr"/>
@@ -7619,28 +7619,28 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>0293</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>KJTS</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D160" s="2" t="n">
-        <v>0.89</v>
+        <v>0.625</v>
       </c>
       <c r="E160" s="8" t="n">
-        <v>-0.0326</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F160" s="4" t="n">
-        <v>541700</v>
+        <v>610800</v>
       </c>
       <c r="G160" s="5" t="n">
-        <v>0.46</v>
+        <v>0.53</v>
       </c>
       <c r="H160" t="n">
-        <v>35.43</v>
+        <v>35.74</v>
       </c>
       <c r="I160" s="6" t="inlineStr">
         <is>
@@ -7648,10 +7648,10 @@
         </is>
       </c>
       <c r="J160" s="2" t="n">
-        <v>0.98</v>
+        <v>0.631</v>
       </c>
       <c r="K160" s="2" t="n">
-        <v>1.029</v>
+        <v>0.63</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="7" t="inlineStr"/>
@@ -7664,28 +7664,28 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D161" s="2" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="E161" s="8" t="n">
-        <v>-0.0075</v>
+        <v>0.535</v>
+      </c>
+      <c r="E161" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F161" s="4" t="n">
-        <v>514000</v>
+        <v>606800</v>
       </c>
       <c r="G161" s="5" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="H161" t="n">
-        <v>54.47</v>
+        <v>39.4</v>
       </c>
       <c r="I161" s="6" t="inlineStr">
         <is>
@@ -7693,10 +7693,10 @@
         </is>
       </c>
       <c r="J161" s="2" t="n">
-        <v>2.669</v>
+        <v>0.547</v>
       </c>
       <c r="K161" s="2" t="n">
-        <v>2.225</v>
+        <v>0.575</v>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" s="7" t="inlineStr"/>
@@ -7709,39 +7709,39 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D162" s="2" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E162" s="10" t="n">
-        <v>0</v>
+        <v>4.35</v>
+      </c>
+      <c r="E162" s="8" t="n">
+        <v>-0.0225</v>
       </c>
       <c r="F162" s="4" t="n">
-        <v>512000</v>
+        <v>602300</v>
       </c>
       <c r="G162" s="5" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
       <c r="H162" t="n">
-        <v>39.4</v>
-      </c>
-      <c r="I162" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>39.04</v>
+      </c>
+      <c r="I162" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J162" s="2" t="n">
-        <v>0.547</v>
+        <v>4.463</v>
       </c>
       <c r="K162" s="2" t="n">
-        <v>0.575</v>
+        <v>4.758</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="7" t="inlineStr"/>
@@ -7754,45 +7754,675 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>LWSABAH</t>
         </is>
       </c>
       <c r="D163" s="2" t="n">
-        <v>0.785</v>
+        <v>1.51</v>
       </c>
       <c r="E163" s="8" t="n">
-        <v>-0.0248</v>
+        <v>-0.0208</v>
       </c>
       <c r="F163" s="4" t="n">
-        <v>509100</v>
+        <v>590100</v>
       </c>
       <c r="G163" s="5" t="n">
-        <v>0.22</v>
+        <v>0.55</v>
       </c>
       <c r="H163" t="n">
-        <v>52.65</v>
-      </c>
-      <c r="I163" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.47</v>
+      </c>
+      <c r="I163" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J163" s="2" t="n">
-        <v>0.778</v>
+        <v>1.626</v>
       </c>
       <c r="K163" s="2" t="n">
-        <v>0.767</v>
+        <v>1.632</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="7" t="inlineStr"/>
     </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>0233</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>PEKAT</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="E164" s="8" t="n">
+        <v>-0.0037</v>
+      </c>
+      <c r="F164" s="4" t="n">
+        <v>589200</v>
+      </c>
+      <c r="G164" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H164" t="n">
+        <v>55.04</v>
+      </c>
+      <c r="I164" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="K164" s="2" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" s="7" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>5121</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>HEKTAR</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="E165" s="8" t="n">
+        <v>-0.0098</v>
+      </c>
+      <c r="F165" s="4" t="n">
+        <v>586700</v>
+      </c>
+      <c r="G165" s="5" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H165" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="I165" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="K165" s="2" t="n">
+        <v>0.488</v>
+      </c>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" s="7" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>5323</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>JPG</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="E166" s="8" t="n">
+        <v>-0.0117</v>
+      </c>
+      <c r="F166" s="4" t="n">
+        <v>584700</v>
+      </c>
+      <c r="G166" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H166" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="I166" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="n">
+        <v>1.785</v>
+      </c>
+      <c r="K166" s="2" t="n">
+        <v>1.902</v>
+      </c>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" s="7" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>5225</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>IHH</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="E167" s="3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F167" s="4" t="n">
+        <v>575200</v>
+      </c>
+      <c r="G167" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H167" t="n">
+        <v>58.53</v>
+      </c>
+      <c r="I167" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="n">
+        <v>7.908</v>
+      </c>
+      <c r="K167" s="2" t="n">
+        <v>7.984</v>
+      </c>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" s="7" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>0338</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>KOPI</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="E168" s="8" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="F168" s="4" t="n">
+        <v>573000</v>
+      </c>
+      <c r="G168" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H168" t="n">
+        <v>41.27</v>
+      </c>
+      <c r="I168" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="K168" s="2" t="n">
+        <v>0.958</v>
+      </c>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" s="7" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>5302</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>ATECH</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="E169" s="8" t="n">
+        <v>-0.0248</v>
+      </c>
+      <c r="F169" s="4" t="n">
+        <v>567300</v>
+      </c>
+      <c r="G169" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H169" t="n">
+        <v>52.65</v>
+      </c>
+      <c r="I169" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="K169" s="2" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" s="7" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>9059</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>TSH</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="E170" s="8" t="n">
+        <v>-0.008399999999999999</v>
+      </c>
+      <c r="F170" s="4" t="n">
+        <v>565900</v>
+      </c>
+      <c r="G170" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H170" t="n">
+        <v>31.79</v>
+      </c>
+      <c r="I170" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="n">
+        <v>1.254</v>
+      </c>
+      <c r="K170" s="2" t="n">
+        <v>1.309</v>
+      </c>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" s="7" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>0325</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="E171" s="8" t="n">
+        <v>-0.0194</v>
+      </c>
+      <c r="F171" s="4" t="n">
+        <v>565400</v>
+      </c>
+      <c r="G171" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H171" t="n">
+        <v>37.27</v>
+      </c>
+      <c r="I171" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="n">
+        <v>1.092</v>
+      </c>
+      <c r="K171" s="2" t="n">
+        <v>1.095</v>
+      </c>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" s="7" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>7293</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>YINSON</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="E172" s="3" t="n">
+        <v>0.0141</v>
+      </c>
+      <c r="F172" s="4" t="n">
+        <v>564200</v>
+      </c>
+      <c r="G172" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H172" t="n">
+        <v>58.07</v>
+      </c>
+      <c r="I172" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="n">
+        <v>2.107</v>
+      </c>
+      <c r="K172" s="2" t="n">
+        <v>2.055</v>
+      </c>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" s="7" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>5236</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>MATRIX</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="E173" s="3" t="n">
+        <v>0.009300000000000001</v>
+      </c>
+      <c r="F173" s="4" t="n">
+        <v>561800</v>
+      </c>
+      <c r="G173" s="5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H173" t="n">
+        <v>45.93</v>
+      </c>
+      <c r="I173" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="n">
+        <v>1.096</v>
+      </c>
+      <c r="K173" s="2" t="n">
+        <v>1.138</v>
+      </c>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" s="7" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>7081</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>PHARMA</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E174" s="8" t="n">
+        <v>-0.0178</v>
+      </c>
+      <c r="F174" s="4" t="n">
+        <v>556200</v>
+      </c>
+      <c r="G174" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H174" t="n">
+        <v>18.08</v>
+      </c>
+      <c r="I174" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="n">
+        <v>0.972</v>
+      </c>
+      <c r="K174" s="2" t="n">
+        <v>1.093</v>
+      </c>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" s="7" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>3905</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>MULPHA</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="E175" s="8" t="n">
+        <v>-0.0112</v>
+      </c>
+      <c r="F175" s="4" t="n">
+        <v>551300</v>
+      </c>
+      <c r="G175" s="5" t="n">
+        <v>67.81</v>
+      </c>
+      <c r="H175" t="n">
+        <v>37.45</v>
+      </c>
+      <c r="I175" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="n">
+        <v>2.728</v>
+      </c>
+      <c r="K175" s="2" t="n">
+        <v>2.822</v>
+      </c>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" s="7" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>5271</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>PECCA</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E176" s="3" t="n">
+        <v>0.0145</v>
+      </c>
+      <c r="F176" s="4" t="n">
+        <v>510200</v>
+      </c>
+      <c r="G176" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H176" t="n">
+        <v>63.39</v>
+      </c>
+      <c r="I176" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="K176" s="2" t="n">
+        <v>1.343</v>
+      </c>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" s="7" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>LGMS</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="E177" s="8" t="n">
+        <v>-0.0374</v>
+      </c>
+      <c r="F177" s="4" t="n">
+        <v>507400</v>
+      </c>
+      <c r="G177" s="5" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H177" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="I177" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="K177" s="2" t="n">
+        <v>0.506</v>
+      </c>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M163"/>
+  <autoFilter ref="A1:M177"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-15/bursa-report-2026-10-15.xlsx
+++ b/docs/downloads/2026-10-15/bursa-report-2026-10-15.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-15" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-15'!$A$1:$M$177</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-15'!$A$1:$M$196</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M177"/>
+  <dimension ref="A1:M196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -558,10 +558,10 @@
         <v>0.1818</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>96396500</v>
+        <v>102713300</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="H2" t="n">
         <v>24.2</v>
@@ -597,19 +597,19 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.89</v>
+        <v>0.885</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>-0.022</v>
+        <v>-0.0275</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>39741100</v>
+        <v>43900400</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.6</v>
+        <v>0.66</v>
       </c>
       <c r="H3" t="n">
-        <v>64.45</v>
+        <v>63.57</v>
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         <v>0.8110000000000001</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.727</v>
+        <v>0.726</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" s="7" t="inlineStr"/>
@@ -648,10 +648,10 @@
         <v>-0.0147</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>33307100</v>
+        <v>34404700</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="H4" t="n">
         <v>68.7</v>
@@ -687,13 +687,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>0</v>
+        <v>0.805</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0.0063</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>24102300</v>
+        <v>24539000</v>
       </c>
       <c r="G5" s="5" t="n">
         <v>0.13</v>
@@ -731,10 +731,10 @@
         <v>-0.0532</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>22450500</v>
+        <v>24021000</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.63</v>
+        <v>0.68</v>
       </c>
       <c r="H6" t="n">
         <v>38.13</v>
@@ -776,10 +776,10 @@
         <v>0.0241</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>22151900</v>
+        <v>22738700</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="H7" t="n">
         <v>77.33</v>
@@ -821,10 +821,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>19500500</v>
+        <v>22500500</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>30.8</v>
+        <v>35.54</v>
       </c>
       <c r="H8" t="n">
         <v>48.15</v>
@@ -866,7 +866,7 @@
         <v>0.0075</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>19156400</v>
+        <v>19186100</v>
       </c>
       <c r="G9" s="5" t="n">
         <v>0.74</v>
@@ -911,10 +911,10 @@
         <v>-0.029</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>16780200</v>
+        <v>17784600</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="H10" t="n">
         <v>59.07</v>
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.295</v>
+        <v>0.3</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>-0.0781</v>
+        <v>-0.0625</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>16077100</v>
+        <v>17202200</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>2.16</v>
+        <v>2.31</v>
       </c>
       <c r="H11" t="n">
-        <v>50.53</v>
+        <v>53.32</v>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
         <v>-0.0189</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>13514000</v>
+        <v>14901700</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="H12" t="n">
         <v>26.18</v>
@@ -1031,40 +1031,31 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0096</t>
+          <t>0041</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NEXGRAM</t>
+          <t>AIMAX</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>-0.09089999999999999</v>
+        <v>0.005</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>12969500</v>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>7.58</v>
-      </c>
-      <c r="H13" t="n">
-        <v>59.29</v>
-      </c>
-      <c r="I13" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="n">
-        <v>0.044</v>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>0.047</v>
-      </c>
+        <v>13330400</v>
+      </c>
+      <c r="G13" s="5" t="n"/>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n"/>
+      <c r="K13" s="2" t="n"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
     </row>
@@ -1076,31 +1067,40 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0041</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AIMAX</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.005</v>
+        <v>0.155</v>
       </c>
       <c r="E14" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>12630400</v>
-      </c>
-      <c r="G14" s="5" t="n"/>
+        <v>13330100</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H14" t="n">
+        <v>48.59</v>
+      </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="n"/>
-      <c r="K14" s="2" t="n"/>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>0.157</v>
+      </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="7" t="inlineStr"/>
     </row>
@@ -1112,33 +1112,40 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.25</v>
+        <v>0.445</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>-0.0196</v>
+        <v>-0.0326</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>12272300</v>
+        <v>13059000</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.45</v>
+        <v>0.64</v>
+      </c>
+      <c r="H15" t="n">
+        <v>59.44</v>
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J15" s="2" t="n"/>
-      <c r="K15" s="2" t="n"/>
+      <c r="J15" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>0.361</v>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
     </row>
@@ -1150,28 +1157,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0096</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>NEXGRAM</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.445</v>
+        <v>0.05</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>-0.0326</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>11674800</v>
+        <v>12989500</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.57</v>
+        <v>7.59</v>
       </c>
       <c r="H16" t="n">
-        <v>59.44</v>
+        <v>59.29</v>
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
@@ -1179,10 +1186,10 @@
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.42</v>
+        <v>0.044</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.361</v>
+        <v>0.047</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
@@ -1195,39 +1202,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1643</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>LANDMRK</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>0.5</v>
+        <v>0.31</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>-0.0159</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>10952400</v>
+        <v>12720800</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>8.75</v>
+        <v>0.67</v>
       </c>
       <c r="H17" t="n">
-        <v>43.11</v>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.53</v>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.049</v>
+        <v>0.308</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.064</v>
+        <v>0.298</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
@@ -1240,40 +1247,33 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.31</v>
+        <v>0.245</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>-0.0159</v>
+        <v>-0.0392</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>10273800</v>
+        <v>12275500</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="H18" t="n">
-        <v>54.53</v>
-      </c>
-      <c r="I18" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="n">
-        <v>0.308</v>
-      </c>
-      <c r="K18" s="2" t="n">
-        <v>0.298</v>
-      </c>
+        <v>0.45</v>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
     </row>
@@ -1300,10 +1300,10 @@
         <v>0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>10026700</v>
+        <v>12175000</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.62</v>
+        <v>0.75</v>
       </c>
       <c r="H19" t="n">
         <v>58.28</v>
@@ -1330,39 +1330,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>1643</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>LANDMRK</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E20" s="8" t="n">
-        <v>-0.0064</v>
+        <v>0.04</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>0.3333</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>9837900</v>
+        <v>11734800</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.65</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>50.18</v>
-      </c>
-      <c r="I20" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.75</v>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.775</v>
+        <v>0.048</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.776</v>
+        <v>0.064</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
@@ -1384,19 +1384,19 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>0.006999999999999999</v>
+        <v>1.42</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>9506500</v>
+        <v>11579900</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.92</v>
+        <v>1.12</v>
       </c>
       <c r="H21" t="n">
-        <v>20.13</v>
+        <v>18.91</v>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.746</v>
+        <v>1.745</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>1.971</v>
@@ -1435,10 +1435,10 @@
         <v>-0.0446</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>8365900</v>
+        <v>10466500</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.46</v>
+        <v>0.57</v>
       </c>
       <c r="H22" t="n">
         <v>46.53</v>
@@ -1465,39 +1465,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>0</v>
+        <v>0.865</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>8358200</v>
+        <v>10375600</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.77</v>
+        <v>0.53</v>
       </c>
       <c r="H23" t="n">
-        <v>33.83</v>
-      </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.95</v>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.398</v>
+        <v>0.868</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.408</v>
+        <v>0.869</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
@@ -1510,28 +1510,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.865</v>
+        <v>0.775</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.0064</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>8009400</v>
+        <v>10009300</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.41</v>
+        <v>0.66</v>
       </c>
       <c r="H24" t="n">
-        <v>45.95</v>
+        <v>50.18</v>
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
@@ -1539,10 +1539,10 @@
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.868</v>
+        <v>0.775</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.869</v>
+        <v>0.776</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
@@ -1555,28 +1555,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0117</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SMRT</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.17</v>
+        <v>0.225</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>0.0625</v>
+        <v>0.04650000000000001</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>7824000</v>
+        <v>9467500</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>2.42</v>
+        <v>0.36</v>
       </c>
       <c r="H25" t="n">
-        <v>41.24</v>
+        <v>36.92</v>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
@@ -1584,10 +1584,10 @@
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.179</v>
+        <v>0.239</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.192</v>
+        <v>0.292</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
@@ -1600,39 +1600,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E26" s="10" t="n">
-        <v>0</v>
+        <v>0.545</v>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>-0.0522</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>7816500</v>
+        <v>8623100</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>1.32</v>
+        <v>0.43</v>
       </c>
       <c r="H26" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="I26" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.65</v>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.183</v>
+        <v>0.579</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>1.18</v>
+        <v>0.536</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
@@ -1645,39 +1645,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.555</v>
+        <v>1.25</v>
       </c>
       <c r="E27" s="8" t="n">
-        <v>-0.0348</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>7502000</v>
+        <v>8595900</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.37</v>
+        <v>1.45</v>
       </c>
       <c r="H27" t="n">
-        <v>47.34</v>
-      </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.95</v>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.58</v>
+        <v>1.182</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.536</v>
+        <v>1.18</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
@@ -1690,28 +1690,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>0.04650000000000001</v>
+        <v>0.39</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>7401400</v>
+        <v>8358200</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.28</v>
+        <v>0.77</v>
       </c>
       <c r="H28" t="n">
-        <v>36.92</v>
+        <v>33.83</v>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
@@ -1719,10 +1719,10 @@
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.239</v>
+        <v>0.398</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0.292</v>
+        <v>0.408</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
@@ -1735,28 +1735,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0237</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>HAILY</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>0.0286</v>
+        <v>0.625</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>7220400</v>
+        <v>8249900</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>28.68</v>
+        <v>0.76</v>
       </c>
       <c r="H29" t="n">
-        <v>65.22</v>
+        <v>56.82</v>
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
@@ -1764,10 +1764,10 @@
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.166</v>
+        <v>0.615</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.165</v>
+        <v>0.614</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1780,39 +1780,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0117</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>SMRT</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>0</v>
+        <v>0.175</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>0.09369999999999999</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>7189400</v>
+        <v>7986800</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.66</v>
+        <v>2.47</v>
       </c>
       <c r="H30" t="n">
-        <v>56.82</v>
-      </c>
-      <c r="I30" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.05</v>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.615</v>
+        <v>0.18</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.614</v>
+        <v>0.192</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1825,39 +1825,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0237</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>HAILY</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E31" s="8" t="n">
-        <v>-0.0534</v>
+        <v>0.18</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>0.0286</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>6244100</v>
+        <v>7276600</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.7</v>
+        <v>28.91</v>
       </c>
       <c r="H31" t="n">
-        <v>42.98</v>
-      </c>
-      <c r="I31" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.22</v>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.665</v>
+        <v>0.166</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.619</v>
+        <v>0.165</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1870,28 +1870,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>5.31</v>
+        <v>0.615</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>-0.031</v>
+        <v>-0.0611</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>6154500</v>
+        <v>7261600</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.44</v>
+        <v>0.82</v>
       </c>
       <c r="H32" t="n">
-        <v>39.86</v>
+        <v>42.21</v>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>5.578</v>
+        <v>0.664</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>5.412</v>
+        <v>0.619</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
@@ -1915,28 +1915,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E33" s="10" t="n">
-        <v>0</v>
+        <v>5.3</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>-0.0328</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>5900100</v>
+        <v>7085100</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.17</v>
+        <v>0.5</v>
       </c>
       <c r="H33" t="n">
-        <v>48.59</v>
+        <v>39.55</v>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.155</v>
+        <v>5.577</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.157</v>
+        <v>5.412</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1960,39 +1960,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.38</v>
+        <v>0.19</v>
       </c>
       <c r="E34" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>5861000</v>
+        <v>6971600</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.9</v>
       </c>
       <c r="H34" t="n">
-        <v>61.88</v>
-      </c>
-      <c r="I34" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.74</v>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.371</v>
+        <v>0.202</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.369</v>
+        <v>0.208</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2005,39 +2005,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.295</v>
+        <v>4.74</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>-0.0484</v>
+        <v>-0.0021</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>5707500</v>
+        <v>6242100</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>1.13</v>
+        <v>0.35</v>
       </c>
       <c r="H35" t="n">
-        <v>21.54</v>
-      </c>
-      <c r="I35" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.47</v>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.345</v>
+        <v>4.72</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.377</v>
+        <v>4.863</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2059,19 +2059,19 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.35</v>
+        <v>0.345</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>-0.0278</v>
+        <v>-0.0417</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>5678600</v>
+        <v>6113400</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.65</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H36" t="n">
-        <v>52.78</v>
+        <v>50.66</v>
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>0.349</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0.332</v>
+        <v>0.331</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
@@ -2095,28 +2095,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0051</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CUSCAPI</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>0</v>
+        <v>0.3</v>
+      </c>
+      <c r="E37" s="8" t="n">
+        <v>-0.0323</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>5569500</v>
+        <v>6109700</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.39</v>
+        <v>1.21</v>
       </c>
       <c r="H37" t="n">
-        <v>38.84</v>
+        <v>22.57</v>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.05</v>
+        <v>0.346</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0.066</v>
+        <v>0.377</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2140,28 +2140,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="E38" s="8" t="n">
-        <v>-0.0278</v>
+        <v>0.47</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>0.0444</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>5331400</v>
+        <v>5980300</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.23</v>
+        <v>0.15</v>
       </c>
       <c r="H38" t="n">
-        <v>40.54</v>
+        <v>30.49</v>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.191</v>
+        <v>0.519</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0.185</v>
+        <v>0.701</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
@@ -2185,39 +2185,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="E39" s="8" t="n">
-        <v>-0.0357</v>
+        <v>7.5</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>4846300</v>
+        <v>5896900</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.48</v>
+        <v>0.39</v>
       </c>
       <c r="H39" t="n">
-        <v>51.54</v>
-      </c>
-      <c r="I39" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.47</v>
+      </c>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.073</v>
+        <v>7.58</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>1.042</v>
+        <v>7.71</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2230,28 +2230,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>0.0021</v>
+        <v>0.375</v>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>-0.0132</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>4808600</v>
+        <v>5895400</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.27</v>
+        <v>0.82</v>
       </c>
       <c r="H40" t="n">
-        <v>51.4</v>
+        <v>55.92</v>
       </c>
       <c r="I40" s="9" t="inlineStr">
         <is>
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>4.722</v>
+        <v>0.37</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>4.864</v>
+        <v>0.369</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2275,28 +2275,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0051</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>CUSCAPI</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="E41" s="8" t="n">
-        <v>-0.0194</v>
+        <v>0.045</v>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>4577900</v>
+        <v>5590500</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.55</v>
+        <v>0.39</v>
       </c>
       <c r="H41" t="n">
-        <v>44.99</v>
+        <v>38.84</v>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.063</v>
+        <v>0.05</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0.947</v>
+        <v>0.066</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2320,39 +2320,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>0.455</v>
+        <v>0.175</v>
       </c>
       <c r="E42" s="8" t="n">
-        <v>-0.0109</v>
+        <v>-0.0278</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>4152900</v>
+        <v>5444700</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.79</v>
+        <v>0.23</v>
       </c>
       <c r="H42" t="n">
-        <v>66.3</v>
-      </c>
-      <c r="I42" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.54</v>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.385</v>
+        <v>0.191</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0.357</v>
+        <v>0.185</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2365,28 +2365,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.46</v>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>-0.08</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>4070000</v>
+        <v>5431200</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.42</v>
+        <v>0.73</v>
       </c>
       <c r="H43" t="n">
-        <v>46.61</v>
+        <v>26.14</v>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
@@ -2394,10 +2394,10 @@
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.31</v>
+        <v>0.554</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>1.314</v>
+        <v>0.625</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2410,39 +2410,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.225</v>
+        <v>0.41</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>0.0227</v>
+        <v>0.025</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>4055900</v>
+        <v>5248100</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.19</v>
+        <v>0.41</v>
       </c>
       <c r="H44" t="n">
-        <v>48.68</v>
-      </c>
-      <c r="I44" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.13</v>
+      </c>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.223</v>
+        <v>0.391</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.24</v>
+        <v>0.378</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2455,39 +2455,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="E45" s="10" t="n">
-        <v>0</v>
+        <v>0.455</v>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>-0.0109</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>3862500</v>
+        <v>4964200</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.16</v>
+        <v>0.95</v>
       </c>
       <c r="H45" t="n">
-        <v>38.74</v>
-      </c>
-      <c r="I45" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.3</v>
+      </c>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.148</v>
+        <v>0.385</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.148</v>
+        <v>0.357</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2500,28 +2500,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="E46" s="8" t="n">
-        <v>-0.05</v>
+        <v>0.225</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>0.0227</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>3852100</v>
+        <v>4937100</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.52</v>
+        <v>0.23</v>
       </c>
       <c r="H46" t="n">
-        <v>27.8</v>
+        <v>48.68</v>
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.556</v>
+        <v>0.223</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0.626</v>
+        <v>0.24</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2545,28 +2545,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>2.76</v>
+        <v>1.08</v>
       </c>
       <c r="E47" s="8" t="n">
-        <v>-0.0282</v>
+        <v>-0.0357</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>3819700</v>
+        <v>4891700</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.43</v>
+        <v>0.49</v>
       </c>
       <c r="H47" t="n">
-        <v>50</v>
+        <v>51.54</v>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
@@ -2574,10 +2574,10 @@
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>2.795</v>
+        <v>1.073</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>2.646</v>
+        <v>1.042</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2590,28 +2590,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>0.465</v>
+        <v>1.01</v>
       </c>
       <c r="E48" s="8" t="n">
-        <v>-0.0211</v>
+        <v>-0.0194</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>3750800</v>
+        <v>4838300</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.48</v>
+        <v>0.58</v>
       </c>
       <c r="H48" t="n">
-        <v>27.64</v>
+        <v>44.99</v>
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.507</v>
+        <v>1.063</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.947</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2635,28 +2635,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E49" s="8" t="n">
-        <v>-0.07139999999999999</v>
+        <v>1.3</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>0.0156</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>3625100</v>
+        <v>4707800</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.89</v>
+        <v>0.49</v>
       </c>
       <c r="H49" t="n">
-        <v>32.71</v>
+        <v>48.06</v>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.597</v>
+        <v>1.311</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0.603</v>
+        <v>1.314</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
@@ -2680,39 +2680,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="E50" s="3" t="n">
-        <v>0.0125</v>
+        <v>0.46</v>
+      </c>
+      <c r="E50" s="8" t="n">
+        <v>-0.0316</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>3562300</v>
+        <v>4562100</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.28</v>
+        <v>0.58</v>
       </c>
       <c r="H50" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="I50" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>26.61</v>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.391</v>
+        <v>0.507</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0.378</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2725,39 +2725,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E51" s="8" t="n">
-        <v>-0.0984</v>
+        <v>4.86</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>0.0021</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>3469600</v>
+        <v>4541900</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.9</v>
+        <v>0.18</v>
       </c>
       <c r="H51" t="n">
-        <v>74.98999999999999</v>
-      </c>
-      <c r="I51" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.97</v>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.798</v>
+        <v>4.921</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0.543</v>
+        <v>4.709</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2770,28 +2770,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="E52" s="3" t="n">
-        <v>0.0171</v>
+        <v>2.75</v>
+      </c>
+      <c r="E52" s="8" t="n">
+        <v>-0.0317</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>3444700</v>
+        <v>4148300</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.4</v>
+        <v>0.47</v>
       </c>
       <c r="H52" t="n">
-        <v>44.65</v>
+        <v>49.36</v>
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
@@ -2799,10 +2799,10 @@
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.9419999999999999</v>
+        <v>2.794</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0.84</v>
+        <v>2.646</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2815,28 +2815,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>0.415</v>
+        <v>7.28</v>
       </c>
       <c r="E53" s="8" t="n">
-        <v>-0.0235</v>
+        <v>-0.0582</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>3413300</v>
+        <v>4078300</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.32</v>
+        <v>1.02</v>
       </c>
       <c r="H53" t="n">
-        <v>42.82</v>
+        <v>50.94</v>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.443</v>
+        <v>7.372</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0.432</v>
+        <v>6.866</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2860,28 +2860,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="E54" s="3" t="n">
-        <v>0.0103</v>
+        <v>0.125</v>
+      </c>
+      <c r="E54" s="8" t="n">
+        <v>-0.0385</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>3336000</v>
+        <v>4070900</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="H54" t="n">
-        <v>50.98</v>
+        <v>36.74</v>
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>4.925</v>
+        <v>0.148</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>4.71</v>
+        <v>0.148</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2905,28 +2905,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>2.04</v>
+        <v>0.52</v>
       </c>
       <c r="E55" s="8" t="n">
-        <v>-0.0192</v>
+        <v>-0.07139999999999999</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>3306100</v>
+        <v>3746500</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.23</v>
+        <v>0.92</v>
       </c>
       <c r="H55" t="n">
-        <v>34.57</v>
+        <v>32.71</v>
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
@@ -2934,10 +2934,10 @@
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>2.176</v>
+        <v>0.597</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>2.229</v>
+        <v>0.603</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2950,28 +2950,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E56" s="3" t="n">
-        <v>0.0345</v>
+        <v>0.415</v>
+      </c>
+      <c r="E56" s="8" t="n">
+        <v>-0.0235</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>3298900</v>
+        <v>3684700</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.05</v>
+        <v>0.35</v>
       </c>
       <c r="H56" t="n">
-        <v>46.24</v>
+        <v>42.82</v>
       </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.163</v>
+        <v>0.443</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0.137</v>
+        <v>0.432</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -2995,39 +2995,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>3.07</v>
+        <v>0.885</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0.0066</v>
+        <v>0.0114</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>3257600</v>
+        <v>3641900</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>1.01</v>
+        <v>0.43</v>
       </c>
       <c r="H57" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="I57" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.84</v>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>2.769</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>2.382</v>
+        <v>0.84</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3040,28 +3040,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MALAKOF</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>0.75</v>
+        <v>2.41</v>
       </c>
       <c r="E58" s="8" t="n">
-        <v>-0.0132</v>
+        <v>-0.0203</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>3251900</v>
+        <v>3635900</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.72</v>
+        <v>0.29</v>
       </c>
       <c r="H58" t="n">
-        <v>39.04</v>
+        <v>45.23</v>
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
@@ -3069,10 +3069,10 @@
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.783</v>
+        <v>2.456</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0.803</v>
+        <v>2.374</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3085,39 +3085,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>7.36</v>
+        <v>2.11</v>
       </c>
       <c r="E59" s="8" t="n">
-        <v>-0.0479</v>
+        <v>-0.004699999999999999</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>3251800</v>
+        <v>3549500</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="H59" t="n">
-        <v>52.75</v>
-      </c>
-      <c r="I59" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.7</v>
+      </c>
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>7.38</v>
+        <v>2.11</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>6.868</v>
+        <v>2.097</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3130,28 +3130,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="E60" s="3" t="n">
-        <v>0.0222</v>
+        <v>0.755</v>
+      </c>
+      <c r="E60" s="8" t="n">
+        <v>-0.0066</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>3206700</v>
+        <v>3548700</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.08</v>
+        <v>0.79</v>
       </c>
       <c r="H60" t="n">
-        <v>27.43</v>
+        <v>40.15</v>
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
@@ -3159,10 +3159,10 @@
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.518</v>
+        <v>0.783</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0.701</v>
+        <v>0.803</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
@@ -3175,39 +3175,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>0.265</v>
+        <v>1.1</v>
       </c>
       <c r="E61" s="8" t="n">
-        <v>-0.0364</v>
+        <v>-0.0984</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>3095600</v>
+        <v>3542400</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.37</v>
+        <v>0.92</v>
       </c>
       <c r="H61" t="n">
-        <v>42.94</v>
-      </c>
-      <c r="I61" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>74.98999999999999</v>
+      </c>
+      <c r="I61" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.277</v>
+        <v>0.798</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0.298</v>
+        <v>0.543</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3220,28 +3220,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="E62" s="10" t="n">
-        <v>0</v>
+        <v>2.04</v>
+      </c>
+      <c r="E62" s="8" t="n">
+        <v>-0.0192</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>3013700</v>
+        <v>3506300</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="H62" t="n">
-        <v>47.1</v>
+        <v>34.57</v>
       </c>
       <c r="I62" s="6" t="inlineStr">
         <is>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>2.788</v>
+        <v>2.176</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>2.729</v>
+        <v>2.229</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
@@ -3265,38 +3265,40 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E63" s="8" t="n">
-        <v>-0.0141</v>
+        <v>2.74</v>
+      </c>
+      <c r="E63" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>2847400</v>
+        <v>3479500</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.31</v>
+        <v>0.26</v>
       </c>
       <c r="H63" t="n">
-        <v>63.15</v>
-      </c>
-      <c r="I63" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.1</v>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.311</v>
-      </c>
-      <c r="K63" s="2" t="n"/>
+        <v>2.788</v>
+      </c>
+      <c r="K63" s="2" t="n">
+        <v>2.729</v>
+      </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
     </row>
@@ -3308,39 +3310,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>6.51</v>
+        <v>0.26</v>
       </c>
       <c r="E64" s="8" t="n">
-        <v>-0.0284</v>
+        <v>-0.0545</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>2834300</v>
+        <v>3479400</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.52</v>
+        <v>0.41</v>
       </c>
       <c r="H64" t="n">
-        <v>57.64</v>
-      </c>
-      <c r="I64" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41</v>
+      </c>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>6.112</v>
+        <v>0.276</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>5.878</v>
+        <v>0.298</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
@@ -3353,28 +3355,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="E65" s="8" t="n">
-        <v>-0.0197</v>
+        <v>6.36</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>0.0032</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>2816700</v>
+        <v>3452400</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.4</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H65" t="n">
-        <v>53.43</v>
+        <v>42.99</v>
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
@@ -3382,10 +3384,10 @@
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.744</v>
+        <v>6.413</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0.67</v>
+        <v>6.789</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3398,28 +3400,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E66" s="8" t="n">
-        <v>-0.03700000000000001</v>
+        <v>0.145</v>
+      </c>
+      <c r="E66" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>2786400</v>
+        <v>3444100</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.19</v>
+        <v>0.05</v>
       </c>
       <c r="H66" t="n">
-        <v>52.58</v>
+        <v>43.8</v>
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
@@ -3427,10 +3429,10 @@
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.52</v>
+        <v>0.162</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0.454</v>
+        <v>0.137</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3443,28 +3445,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>4.57</v>
+        <v>0.405</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>-0.0151</v>
+        <v>-0.0471</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>2754300</v>
+        <v>3382200</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.28</v>
+        <v>0.49</v>
       </c>
       <c r="H67" t="n">
-        <v>42.88</v>
+        <v>45.47</v>
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
@@ -3472,10 +3474,10 @@
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>4.645</v>
+        <v>0.425</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>4.636</v>
+        <v>0.416</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
@@ -3488,39 +3490,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>0.985</v>
-      </c>
-      <c r="E68" s="8" t="n">
-        <v>-0.0343</v>
+        <v>3.07</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>0.0066</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>2715100</v>
+        <v>3308600</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.59</v>
+        <v>1.02</v>
       </c>
       <c r="H68" t="n">
-        <v>43.98</v>
-      </c>
-      <c r="I68" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>81.5</v>
+      </c>
+      <c r="I68" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1.05</v>
+        <v>2.769</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0.927</v>
+        <v>2.382</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
@@ -3533,28 +3535,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>7.52</v>
-      </c>
-      <c r="E69" s="3" t="n">
-        <v>0.0027</v>
+        <v>6.46</v>
+      </c>
+      <c r="E69" s="8" t="n">
+        <v>-0.0358</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>2707000</v>
+        <v>3267900</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.18</v>
+        <v>0.59</v>
       </c>
       <c r="H69" t="n">
-        <v>45.48</v>
+        <v>56.81</v>
       </c>
       <c r="I69" s="9" t="inlineStr">
         <is>
@@ -3562,10 +3564,10 @@
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>7.582</v>
+        <v>6.107</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>7.711</v>
+        <v>5.877</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
@@ -3578,28 +3580,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>0.41</v>
+        <v>0.52</v>
       </c>
       <c r="E70" s="8" t="n">
-        <v>-0.0353</v>
+        <v>-0.03700000000000001</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>2676900</v>
+        <v>3222100</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.39</v>
+        <v>0.22</v>
       </c>
       <c r="H70" t="n">
-        <v>46.73</v>
+        <v>52.58</v>
       </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
@@ -3607,10 +3609,10 @@
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.425</v>
+        <v>0.52</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0.416</v>
+        <v>0.454</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
@@ -3623,28 +3625,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>6.33</v>
+        <v>4.57</v>
       </c>
       <c r="E71" s="8" t="n">
-        <v>-0.0016</v>
+        <v>-0.0151</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>2653900</v>
+        <v>3212300</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.43</v>
+        <v>0.33</v>
       </c>
       <c r="H71" t="n">
-        <v>41.19</v>
+        <v>42.88</v>
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
@@ -3652,10 +3654,10 @@
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>6.41</v>
+        <v>4.645</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>6.789</v>
+        <v>4.636</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
@@ -3683,10 +3685,10 @@
         <v>-0.031</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>2629100</v>
+        <v>3116700</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.44</v>
+        <v>0.52</v>
       </c>
       <c r="H72" t="n">
         <v>41.91</v>
@@ -3713,28 +3715,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0370</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>XPB</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>0.4</v>
+        <v>0.185</v>
       </c>
       <c r="E73" s="8" t="n">
-        <v>-0.0244</v>
+        <v>-0.09759999999999999</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>2587900</v>
+        <v>3017700</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>1.39</v>
+        <v>1.72</v>
       </c>
       <c r="H73" t="n">
-        <v>33.55</v>
+        <v>38.29</v>
       </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
@@ -3742,10 +3744,10 @@
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.417</v>
+        <v>0.209</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0.436</v>
+        <v>0.193</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
@@ -3758,28 +3760,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>0.79</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="E74" s="8" t="n">
-        <v>-0.0186</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>2473300</v>
+        <v>3017200</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.66</v>
+        <v>0.58</v>
       </c>
       <c r="H74" t="n">
-        <v>45.85</v>
+        <v>54.07</v>
       </c>
       <c r="I74" s="6" t="inlineStr">
         <is>
@@ -3787,10 +3789,10 @@
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.822</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0.773</v>
+        <v>0.51</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr"/>
@@ -3803,28 +3805,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>1.03</v>
+        <v>7.31</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>-0.0463</v>
+        <v>-0.0027</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>2468400</v>
+        <v>2970100</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.61</v>
+        <v>0.29</v>
       </c>
       <c r="H75" t="n">
-        <v>52</v>
+        <v>33.47</v>
       </c>
       <c r="I75" s="6" t="inlineStr">
         <is>
@@ -3832,10 +3834,10 @@
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1.042</v>
+        <v>7.5</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0.895</v>
+        <v>8.003</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr"/>
@@ -3848,28 +3850,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>1.16</v>
+        <v>0.75</v>
       </c>
       <c r="E76" s="8" t="n">
-        <v>-0.0252</v>
+        <v>-0.026</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>2410100</v>
+        <v>2938900</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.59</v>
+        <v>0.35</v>
       </c>
       <c r="H76" t="n">
-        <v>52.79</v>
+        <v>42.4</v>
       </c>
       <c r="I76" s="6" t="inlineStr">
         <is>
@@ -3877,10 +3879,10 @@
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1.163</v>
+        <v>0.776</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>1.091</v>
+        <v>0.773</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
@@ -3893,28 +3895,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>0.575</v>
+        <v>1.02</v>
       </c>
       <c r="E77" s="8" t="n">
-        <v>-0.0496</v>
+        <v>-0.0556</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>2374600</v>
+        <v>2914400</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.46</v>
+        <v>0.72</v>
       </c>
       <c r="H77" t="n">
-        <v>56.68</v>
+        <v>51.06</v>
       </c>
       <c r="I77" s="6" t="inlineStr">
         <is>
@@ -3922,10 +3924,10 @@
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.5620000000000001</v>
+        <v>1.041</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0.51</v>
+        <v>0.895</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
@@ -3938,28 +3940,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E78" s="3" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.735</v>
+      </c>
+      <c r="E78" s="8" t="n">
+        <v>-0.0329</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>2366200</v>
+        <v>2902900</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.57</v>
+        <v>0.41</v>
       </c>
       <c r="H78" t="n">
-        <v>25.55</v>
+        <v>51.56</v>
       </c>
       <c r="I78" s="6" t="inlineStr">
         <is>
@@ -3967,10 +3969,10 @@
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.425</v>
+        <v>0.743</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>1.58</v>
+        <v>0.669</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
@@ -3983,28 +3985,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>5218</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>VANTNRG</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E79" s="8" t="n">
-        <v>-0.0328</v>
+        <v>2.8</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>0.0036</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>2363500</v>
+        <v>2889700</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.74</v>
+        <v>0.59</v>
       </c>
       <c r="H79" t="n">
-        <v>26.9</v>
+        <v>56.38</v>
       </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
@@ -4012,10 +4014,10 @@
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.323</v>
+        <v>2.766</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0.332</v>
+        <v>2.158</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
@@ -4028,40 +4030,38 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>0.49</v>
+        <v>0.35</v>
       </c>
       <c r="E80" s="8" t="n">
-        <v>-0.0101</v>
+        <v>-0.0141</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>2353100</v>
+        <v>2855000</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
       <c r="H80" t="n">
-        <v>40.63</v>
-      </c>
-      <c r="I80" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.15</v>
+      </c>
+      <c r="I80" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.514</v>
-      </c>
-      <c r="K80" s="2" t="n">
-        <v>0.527</v>
-      </c>
+        <v>0.311</v>
+      </c>
+      <c r="K80" s="2" t="n"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
     </row>
@@ -4073,39 +4073,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>2.09</v>
+        <v>0.98</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>-0.0142</v>
+        <v>-0.0392</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>2303700</v>
+        <v>2816000</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.11</v>
+        <v>0.61</v>
       </c>
       <c r="H81" t="n">
-        <v>47.7</v>
-      </c>
-      <c r="I81" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.38</v>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>2.108</v>
+        <v>1.049</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>2.097</v>
+        <v>0.927</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
@@ -4118,28 +4118,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>2.42</v>
+        <v>0.785</v>
       </c>
       <c r="E82" s="8" t="n">
-        <v>-0.0163</v>
+        <v>-0.0248</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>2264500</v>
+        <v>2725900</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.18</v>
+        <v>0.73</v>
       </c>
       <c r="H82" t="n">
-        <v>46.53</v>
+        <v>45.07</v>
       </c>
       <c r="I82" s="6" t="inlineStr">
         <is>
@@ -4147,10 +4147,10 @@
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>2.457</v>
+        <v>0.822</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>2.374</v>
+        <v>0.773</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr"/>
@@ -4163,28 +4163,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>2.62</v>
+        <v>0.4</v>
       </c>
       <c r="E83" s="8" t="n">
-        <v>-0.0296</v>
+        <v>-0.0244</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>2255000</v>
+        <v>2587900</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.45</v>
+        <v>1.39</v>
       </c>
       <c r="H83" t="n">
-        <v>35.88</v>
+        <v>33.55</v>
       </c>
       <c r="I83" s="6" t="inlineStr">
         <is>
@@ -4192,10 +4192,10 @@
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>2.879</v>
+        <v>0.417</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>2.87</v>
+        <v>0.436</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
@@ -4208,39 +4208,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>7.29</v>
-      </c>
-      <c r="E84" s="8" t="n">
-        <v>-0.005500000000000001</v>
+        <v>0.805</v>
+      </c>
+      <c r="E84" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>2225100</v>
+        <v>2466700</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.22</v>
+        <v>0.42</v>
       </c>
       <c r="H84" t="n">
-        <v>32.77</v>
-      </c>
-      <c r="I84" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.89</v>
+      </c>
+      <c r="I84" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>7.499</v>
+        <v>0.792</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>8.003</v>
+        <v>0.769</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
@@ -4253,28 +4253,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="E85" s="8" t="n">
-        <v>-0.0488</v>
+        <v>1.26</v>
+      </c>
+      <c r="E85" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>2208900</v>
+        <v>2462800</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.52</v>
+        <v>0.59</v>
       </c>
       <c r="H85" t="n">
-        <v>47.76</v>
+        <v>23.74</v>
       </c>
       <c r="I85" s="6" t="inlineStr">
         <is>
@@ -4282,10 +4282,10 @@
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.6</v>
+        <v>1.424</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0.585</v>
+        <v>1.58</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr"/>
@@ -4298,39 +4298,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.495</v>
       </c>
       <c r="E86" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>2180200</v>
+        <v>2456200</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.92</v>
+        <v>0.29</v>
       </c>
       <c r="H86" t="n">
-        <v>66.36</v>
-      </c>
-      <c r="I86" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.03</v>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.642</v>
+        <v>0.515</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0.548</v>
+        <v>0.527</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
@@ -4343,28 +4343,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="E87" s="10" t="n">
-        <v>0</v>
+        <v>1.16</v>
+      </c>
+      <c r="E87" s="8" t="n">
+        <v>-0.0252</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>2175200</v>
+        <v>2428200</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.45</v>
+        <v>0.6</v>
       </c>
       <c r="H87" t="n">
-        <v>56.06</v>
+        <v>52.79</v>
       </c>
       <c r="I87" s="6" t="inlineStr">
         <is>
@@ -4372,10 +4372,10 @@
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>2.765</v>
+        <v>1.163</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>2.158</v>
+        <v>1.091</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
@@ -4388,39 +4388,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>VANTNRG</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>13.04</v>
-      </c>
-      <c r="E88" s="3" t="n">
-        <v>0.0046</v>
+        <v>0.295</v>
+      </c>
+      <c r="E88" s="8" t="n">
+        <v>-0.0328</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>2164200</v>
+        <v>2418500</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.24</v>
+        <v>0.76</v>
       </c>
       <c r="H88" t="n">
-        <v>47.07</v>
-      </c>
-      <c r="I88" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>26.9</v>
+      </c>
+      <c r="I88" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>13.027</v>
+        <v>0.323</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>13.469</v>
+        <v>0.332</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr"/>
@@ -4442,19 +4442,19 @@
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="E89" s="8" t="n">
-        <v>-0.021</v>
+        <v>-0.028</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>2140800</v>
+        <v>2414000</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.65</v>
+        <v>0.74</v>
       </c>
       <c r="H89" t="n">
-        <v>39.49</v>
+        <v>38.44</v>
       </c>
       <c r="I89" s="6" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>2.927</v>
+        <v>2.925</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>3.024</v>
@@ -4478,28 +4478,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E90" s="10" t="n">
-        <v>0</v>
+        <v>0.655</v>
+      </c>
+      <c r="E90" s="8" t="n">
+        <v>-0.0296</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>1992800</v>
+        <v>2345300</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.64</v>
+        <v>0.26</v>
       </c>
       <c r="H90" t="n">
-        <v>51.9</v>
+        <v>43.84</v>
       </c>
       <c r="I90" s="6" t="inlineStr">
         <is>
@@ -4507,10 +4507,10 @@
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.865</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0.859</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr"/>
@@ -4523,28 +4523,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>0.66</v>
+        <v>2.62</v>
       </c>
       <c r="E91" s="8" t="n">
-        <v>-0.0222</v>
+        <v>-0.0296</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>1973400</v>
+        <v>2338300</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.22</v>
+        <v>0.47</v>
       </c>
       <c r="H91" t="n">
-        <v>44.67</v>
+        <v>35.88</v>
       </c>
       <c r="I91" s="6" t="inlineStr">
         <is>
@@ -4552,10 +4552,10 @@
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.6879999999999999</v>
+        <v>2.879</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0.6879999999999999</v>
+        <v>2.87</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr"/>
@@ -4568,39 +4568,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E92" s="8" t="n">
-        <v>-0.0062</v>
+        <v>6.79</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>0.0074</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>1931700</v>
+        <v>2332600</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0.33</v>
+        <v>0.53</v>
       </c>
       <c r="H92" t="n">
-        <v>61.65</v>
-      </c>
-      <c r="I92" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.86</v>
+      </c>
+      <c r="I92" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.792</v>
+        <v>6.762</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0.769</v>
+        <v>6.835</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="7" t="inlineStr"/>
@@ -4613,28 +4613,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>1.18</v>
+        <v>0.77</v>
       </c>
       <c r="E93" s="8" t="n">
-        <v>-0.0328</v>
+        <v>-0.0552</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>1916600</v>
+        <v>2304500</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.26</v>
+        <v>0.37</v>
       </c>
       <c r="H93" t="n">
-        <v>52.34</v>
+        <v>54.55</v>
       </c>
       <c r="I93" s="6" t="inlineStr">
         <is>
@@ -4642,10 +4642,10 @@
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>1.168</v>
+        <v>0.766</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>1.13</v>
+        <v>0.68</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="7" t="inlineStr"/>
@@ -4658,39 +4658,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>0.9350000000000001</v>
-      </c>
-      <c r="E94" s="8" t="n">
-        <v>-0.0106</v>
+        <v>13.02</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>0.0031</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>1912000</v>
+        <v>2299600</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>0.5</v>
+        <v>0.26</v>
       </c>
       <c r="H94" t="n">
-        <v>27.89</v>
-      </c>
-      <c r="I94" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.11</v>
+      </c>
+      <c r="I94" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.979</v>
+        <v>13.025</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>1.059</v>
+        <v>13.468</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="7" t="inlineStr"/>
@@ -4703,28 +4703,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>3.74</v>
+        <v>0.585</v>
       </c>
       <c r="E95" s="8" t="n">
-        <v>-0.026</v>
+        <v>-0.0488</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>1904200</v>
+        <v>2265200</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.67</v>
+        <v>0.53</v>
       </c>
       <c r="H95" t="n">
-        <v>45.59</v>
+        <v>47.76</v>
       </c>
       <c r="I95" s="6" t="inlineStr">
         <is>
@@ -4732,10 +4732,10 @@
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>3.86</v>
+        <v>0.6</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>3.646</v>
+        <v>0.585</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="7" t="inlineStr"/>
@@ -4748,39 +4748,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E96" s="8" t="n">
-        <v>-0.0491</v>
+        <v>0.695</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>0.0072</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>1860600</v>
+        <v>2202700</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.3</v>
+        <v>0.93</v>
       </c>
       <c r="H96" t="n">
-        <v>55.55</v>
-      </c>
-      <c r="I96" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.11</v>
+      </c>
+      <c r="I96" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.767</v>
+        <v>0.642</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0.68</v>
+        <v>0.548</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="7" t="inlineStr"/>
@@ -4793,39 +4793,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="E97" s="10" t="n">
-        <v>0</v>
+        <v>3.74</v>
+      </c>
+      <c r="E97" s="8" t="n">
+        <v>-0.026</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>1854600</v>
+        <v>2111300</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>0.3</v>
+        <v>0.74</v>
       </c>
       <c r="H97" t="n">
-        <v>49.34</v>
-      </c>
-      <c r="I97" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.59</v>
+      </c>
+      <c r="I97" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>1.926</v>
+        <v>3.86</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>1.953</v>
+        <v>3.646</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="7" t="inlineStr"/>
@@ -4838,28 +4838,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E98" s="3" t="n">
-        <v>0.0154</v>
+        <v>1.18</v>
+      </c>
+      <c r="E98" s="8" t="n">
+        <v>-0.0328</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>1821800</v>
+        <v>2088300</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>0.35</v>
+        <v>0.28</v>
       </c>
       <c r="H98" t="n">
-        <v>41.84</v>
+        <v>52.34</v>
       </c>
       <c r="I98" s="6" t="inlineStr">
         <is>
@@ -4867,10 +4867,10 @@
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.335</v>
+        <v>1.168</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0.343</v>
+        <v>1.13</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr"/>
@@ -4883,39 +4883,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E99" s="8" t="n">
-        <v>-0.0052</v>
+        <v>0.62</v>
+      </c>
+      <c r="E99" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>1820100</v>
+        <v>2060400</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0.33</v>
+        <v>0.66</v>
       </c>
       <c r="H99" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="I99" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.44</v>
+      </c>
+      <c r="I99" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.917</v>
+        <v>0.615</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0.871</v>
+        <v>0.603</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="7" t="inlineStr"/>
@@ -4928,28 +4928,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>FEYTECH</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>3.74</v>
+        <v>0.205</v>
       </c>
       <c r="E100" s="8" t="n">
-        <v>-0.0106</v>
+        <v>-0.04650000000000001</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>1738100</v>
+        <v>2047400</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>0.18</v>
+        <v>1.74</v>
       </c>
       <c r="H100" t="n">
-        <v>56.45</v>
+        <v>36.09</v>
       </c>
       <c r="I100" s="6" t="inlineStr">
         <is>
@@ -4957,10 +4957,10 @@
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>3.625</v>
+        <v>0.225</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>2.918</v>
+        <v>0.233</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr"/>
@@ -4973,28 +4973,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>1.44</v>
+        <v>0.33</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.0154</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>1725500</v>
+        <v>2046700</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="H101" t="n">
-        <v>44.83</v>
+        <v>41.84</v>
       </c>
       <c r="I101" s="6" t="inlineStr">
         <is>
@@ -5002,10 +5002,10 @@
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.452</v>
+        <v>0.335</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>1.466</v>
+        <v>0.343</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="7" t="inlineStr"/>
@@ -5018,39 +5018,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>7173</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>TOYOVEN</t>
+          <t>BIMB</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>0.255</v>
+        <v>2.02</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>0.0851</v>
+        <v>0.01</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>1665100</v>
+        <v>1993800</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>2.57</v>
+        <v>2.34</v>
       </c>
       <c r="H102" t="n">
-        <v>75.08</v>
-      </c>
-      <c r="I102" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.32</v>
+      </c>
+      <c r="I102" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.217</v>
+        <v>2.045</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0.209</v>
+        <v>2.087</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="7" t="inlineStr"/>
@@ -5063,28 +5063,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="E103" s="8" t="n">
-        <v>-0.0195</v>
+        <v>0.865</v>
+      </c>
+      <c r="E103" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>1661600</v>
+        <v>1992800</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>0.2</v>
+        <v>0.64</v>
       </c>
       <c r="H103" t="n">
-        <v>43.62</v>
+        <v>51.9</v>
       </c>
       <c r="I103" s="6" t="inlineStr">
         <is>
@@ -5092,10 +5092,10 @@
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.776</v>
+        <v>0.865</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0.773</v>
+        <v>0.859</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="7" t="inlineStr"/>
@@ -5108,28 +5108,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>1.26</v>
+        <v>3.72</v>
       </c>
       <c r="E104" s="8" t="n">
-        <v>-0.0526</v>
+        <v>-0.0159</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>1654400</v>
+        <v>1970500</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>0.73</v>
+        <v>0.2</v>
       </c>
       <c r="H104" t="n">
-        <v>53.76</v>
+        <v>55.89</v>
       </c>
       <c r="I104" s="6" t="inlineStr">
         <is>
@@ -5137,10 +5137,10 @@
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>1.248</v>
+        <v>3.623</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>1.167</v>
+        <v>2.918</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="7" t="inlineStr"/>
@@ -5153,39 +5153,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>2.98</v>
+        <v>1.9</v>
       </c>
       <c r="E105" s="8" t="n">
-        <v>-0.0387</v>
+        <v>-0.0155</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>1628400</v>
+        <v>1966800</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>0.52</v>
+        <v>0.32</v>
       </c>
       <c r="H105" t="n">
-        <v>50.16</v>
-      </c>
-      <c r="I105" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.31</v>
+      </c>
+      <c r="I105" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>3.026</v>
+        <v>1.923</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>2.846</v>
+        <v>1.952</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="7" t="inlineStr"/>
@@ -5198,28 +5198,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>3.79</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="E106" s="8" t="n">
-        <v>-0.0207</v>
+        <v>-0.0106</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>1613500</v>
+        <v>1954600</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>0.16</v>
+        <v>0.51</v>
       </c>
       <c r="H106" t="n">
-        <v>46.67</v>
+        <v>27.89</v>
       </c>
       <c r="I106" s="6" t="inlineStr">
         <is>
@@ -5227,10 +5227,10 @@
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>3.969</v>
+        <v>0.979</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>3.522</v>
+        <v>1.059</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="7" t="inlineStr"/>
@@ -5243,39 +5243,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E107" s="10" t="n">
-        <v>0</v>
+        <v>1.23</v>
+      </c>
+      <c r="E107" s="8" t="n">
+        <v>-0.0315</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>1569000</v>
+        <v>1934900</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>0.73</v>
+        <v>0.6</v>
       </c>
       <c r="H107" t="n">
-        <v>48.26</v>
-      </c>
-      <c r="I107" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.1</v>
+      </c>
+      <c r="I107" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.5620000000000001</v>
+        <v>1.287</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0.5620000000000001</v>
+        <v>1.217</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="7" t="inlineStr"/>
@@ -5288,39 +5288,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="E108" s="3" t="n">
-        <v>0.0062</v>
+        <v>0.945</v>
+      </c>
+      <c r="E108" s="8" t="n">
+        <v>-0.0105</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>1541300</v>
+        <v>1911400</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>0.23</v>
+        <v>0.34</v>
       </c>
       <c r="H108" t="n">
-        <v>49.49</v>
-      </c>
-      <c r="I108" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>61.73</v>
+      </c>
+      <c r="I108" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>1.615</v>
+        <v>0.916</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>1.703</v>
+        <v>0.871</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="7" t="inlineStr"/>
@@ -5333,28 +5333,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="E109" s="8" t="n">
-        <v>-0.0236</v>
+        <v>-0.0602</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>1537500</v>
+        <v>1865700</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>0.48</v>
+        <v>0.82</v>
       </c>
       <c r="H109" t="n">
-        <v>46.92</v>
+        <v>52.74</v>
       </c>
       <c r="I109" s="6" t="inlineStr">
         <is>
@@ -5362,10 +5362,10 @@
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.288</v>
+        <v>1.247</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>1.217</v>
+        <v>1.167</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="7" t="inlineStr"/>
@@ -5378,28 +5378,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0272</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>TTVHB</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>0.235</v>
+        <v>3.76</v>
       </c>
       <c r="E110" s="8" t="n">
-        <v>-0.0208</v>
+        <v>-0.0284</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>1519200</v>
+        <v>1804200</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>0.63</v>
+        <v>0.18</v>
       </c>
       <c r="H110" t="n">
-        <v>44.1</v>
+        <v>45.75</v>
       </c>
       <c r="I110" s="6" t="inlineStr">
         <is>
@@ -5407,10 +5407,10 @@
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.248</v>
+        <v>3.967</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0.255</v>
+        <v>3.521</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="7" t="inlineStr"/>
@@ -5423,39 +5423,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>2.51</v>
+        <v>1.43</v>
       </c>
       <c r="E111" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>1517600</v>
+        <v>1790500</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>0.48</v>
+        <v>0.44</v>
       </c>
       <c r="H111" t="n">
-        <v>37.53</v>
-      </c>
-      <c r="I111" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.01</v>
+      </c>
+      <c r="I111" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>2.561</v>
+        <v>1.451</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>2.7</v>
+        <v>1.465</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="7" t="inlineStr"/>
@@ -5468,28 +5468,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="E112" s="3" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.735</v>
+      </c>
+      <c r="E112" s="8" t="n">
+        <v>-0.05769999999999999</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>1512700</v>
+        <v>1754000</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>0.99</v>
+        <v>0.76</v>
       </c>
       <c r="H112" t="n">
-        <v>49.82</v>
+        <v>52.63</v>
       </c>
       <c r="I112" s="6" t="inlineStr">
         <is>
@@ -5497,10 +5497,10 @@
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.916</v>
+        <v>0.728</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0.866</v>
+        <v>0.701</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="7" t="inlineStr"/>
@@ -5513,39 +5513,39 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="E113" s="8" t="n">
-        <v>-0.0274</v>
+        <v>1.63</v>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>0.0062</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>1509500</v>
+        <v>1745900</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>0.1</v>
+        <v>0.26</v>
       </c>
       <c r="H113" t="n">
-        <v>43.13</v>
-      </c>
-      <c r="I113" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.49</v>
+      </c>
+      <c r="I113" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.764</v>
+        <v>1.615</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0.722</v>
+        <v>1.703</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="7" t="inlineStr"/>
@@ -5558,39 +5558,39 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>8524</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>TALIWRK</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>0.23</v>
+        <v>2.5</v>
       </c>
       <c r="E114" s="8" t="n">
-        <v>-0.0213</v>
+        <v>-0.004</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>1479500</v>
+        <v>1721700</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>0.72</v>
+        <v>0.54</v>
       </c>
       <c r="H114" t="n">
-        <v>37.06</v>
-      </c>
-      <c r="I114" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>36.45</v>
+      </c>
+      <c r="I114" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.247</v>
+        <v>2.56</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0.258</v>
+        <v>2.7</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="7" t="inlineStr"/>
@@ -5603,28 +5603,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>0.3</v>
+        <v>2.97</v>
       </c>
       <c r="E115" s="8" t="n">
-        <v>-0.0164</v>
+        <v>-0.04190000000000001</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>1468700</v>
+        <v>1716600</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>0.24</v>
+        <v>0.55</v>
       </c>
       <c r="H115" t="n">
-        <v>38.46</v>
+        <v>49.72</v>
       </c>
       <c r="I115" s="6" t="inlineStr">
         <is>
@@ -5632,10 +5632,10 @@
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.319</v>
+        <v>3.025</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0.338</v>
+        <v>2.846</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="7" t="inlineStr"/>
@@ -5648,28 +5648,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>1.69</v>
+        <v>0.865</v>
       </c>
       <c r="E116" s="8" t="n">
-        <v>-0.0174</v>
+        <v>-0.0226</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>1464600</v>
+        <v>1708400</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>0.3</v>
+        <v>0.66</v>
       </c>
       <c r="H116" t="n">
-        <v>41.59</v>
+        <v>19.71</v>
       </c>
       <c r="I116" s="6" t="inlineStr">
         <is>
@@ -5677,10 +5677,10 @@
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>1.742</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>1.772</v>
+        <v>0.979</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="7" t="inlineStr"/>
@@ -5693,39 +5693,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E117" s="8" t="n">
-        <v>-0.0385</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E117" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>1415500</v>
+        <v>1696000</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="H117" t="n">
-        <v>55.01</v>
-      </c>
-      <c r="I117" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.26</v>
+      </c>
+      <c r="I117" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.729</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>0.701</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="7" t="inlineStr"/>
@@ -5738,28 +5738,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>0.67</v>
+        <v>10.34</v>
       </c>
       <c r="E118" s="8" t="n">
-        <v>-0.036</v>
+        <v>-0.0282</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>1412000</v>
+        <v>1688200</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="H118" t="n">
-        <v>35.17</v>
+        <v>52.72</v>
       </c>
       <c r="I118" s="6" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.738</v>
+        <v>10.39</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>0.746</v>
+        <v>9.693</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="7" t="inlineStr"/>
@@ -5783,39 +5783,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>7173</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>TOYOVEN</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E119" s="8" t="n">
-        <v>-0.0156</v>
+        <v>0.255</v>
+      </c>
+      <c r="E119" s="3" t="n">
+        <v>0.0851</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>1408900</v>
+        <v>1675100</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>0.59</v>
+        <v>2.59</v>
       </c>
       <c r="H119" t="n">
-        <v>48.11</v>
-      </c>
-      <c r="I119" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.08</v>
+      </c>
+      <c r="I119" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.637</v>
+        <v>0.217</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>0.619</v>
+        <v>0.209</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="7" t="inlineStr"/>
@@ -5828,28 +5828,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>TDM</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E120" s="10" t="n">
-        <v>0</v>
+        <v>0.9</v>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>0.0588</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>1383200</v>
+        <v>1648100</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>2.81</v>
+        <v>1.08</v>
       </c>
       <c r="H120" t="n">
-        <v>27.29</v>
+        <v>49.12</v>
       </c>
       <c r="I120" s="6" t="inlineStr">
         <is>
@@ -5857,10 +5857,10 @@
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.208</v>
+        <v>0.915</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0.217</v>
+        <v>0.866</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="7" t="inlineStr"/>
@@ -5873,28 +5873,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>0.875</v>
+        <v>1.68</v>
       </c>
       <c r="E121" s="8" t="n">
-        <v>-0.0113</v>
+        <v>-0.0233</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>1369700</v>
+        <v>1640900</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>0.53</v>
+        <v>0.34</v>
       </c>
       <c r="H121" t="n">
-        <v>21.19</v>
+        <v>40.51</v>
       </c>
       <c r="I121" s="6" t="inlineStr">
         <is>
@@ -5902,10 +5902,10 @@
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.9330000000000001</v>
+        <v>1.741</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0.98</v>
+        <v>1.772</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="7" t="inlineStr"/>
@@ -5918,28 +5918,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>TALIWRK</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>1.2</v>
+        <v>0.23</v>
       </c>
       <c r="E122" s="8" t="n">
-        <v>-0.0323</v>
+        <v>-0.0213</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>1350400</v>
+        <v>1620600</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>0.38</v>
+        <v>0.79</v>
       </c>
       <c r="H122" t="n">
-        <v>49.35</v>
+        <v>37.06</v>
       </c>
       <c r="I122" s="6" t="inlineStr">
         <is>
@@ -5947,10 +5947,10 @@
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>1.25</v>
+        <v>0.247</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>1.05</v>
+        <v>0.258</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="7" t="inlineStr"/>
@@ -5963,28 +5963,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>6181</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>MALTON</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>0.205</v>
+        <v>0.3</v>
       </c>
       <c r="E123" s="8" t="n">
-        <v>-0.04650000000000001</v>
+        <v>-0.0164</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>1339300</v>
+        <v>1618700</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>1.92</v>
+        <v>0.26</v>
       </c>
       <c r="H123" t="n">
-        <v>35.59</v>
+        <v>38.46</v>
       </c>
       <c r="I123" s="6" t="inlineStr">
         <is>
@@ -5992,10 +5992,10 @@
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.218</v>
+        <v>0.319</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>0.226</v>
+        <v>0.338</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="7" t="inlineStr"/>
@@ -6008,28 +6008,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0466</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>SRKKAI</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>0.485</v>
+        <v>7.2</v>
       </c>
       <c r="E124" s="8" t="n">
-        <v>-0.049</v>
+        <v>-0.0014</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>1328200</v>
+        <v>1601900</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>1.12</v>
+        <v>0.21</v>
       </c>
       <c r="H124" t="n">
-        <v>36.4</v>
+        <v>36.49</v>
       </c>
       <c r="I124" s="6" t="inlineStr">
         <is>
@@ -6037,10 +6037,10 @@
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.517</v>
+        <v>7.348</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>0.531</v>
+        <v>7.67</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="7" t="inlineStr"/>
@@ -6053,28 +6053,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="E125" s="10" t="n">
-        <v>0</v>
+        <v>0.71</v>
+      </c>
+      <c r="E125" s="8" t="n">
+        <v>-0.0274</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>1291700</v>
+        <v>1597100</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>0.14</v>
+        <v>0.11</v>
       </c>
       <c r="H125" t="n">
-        <v>52.59</v>
+        <v>43.13</v>
       </c>
       <c r="I125" s="6" t="inlineStr">
         <is>
@@ -6082,10 +6082,10 @@
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.356</v>
+        <v>0.764</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>0.326</v>
+        <v>0.722</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="7" t="inlineStr"/>
@@ -6098,28 +6098,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>0272</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>TTVHB</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>10.42</v>
+        <v>0.235</v>
       </c>
       <c r="E126" s="8" t="n">
-        <v>-0.0207</v>
+        <v>-0.0208</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>1289700</v>
+        <v>1519200</v>
       </c>
       <c r="G126" s="5" t="n">
-        <v>0.36</v>
+        <v>0.63</v>
       </c>
       <c r="H126" t="n">
-        <v>54.34</v>
+        <v>44.1</v>
       </c>
       <c r="I126" s="6" t="inlineStr">
         <is>
@@ -6127,10 +6127,10 @@
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>10.397</v>
+        <v>0.248</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>9.694000000000001</v>
+        <v>0.255</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="7" t="inlineStr"/>
@@ -6143,28 +6143,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="E127" s="8" t="n">
-        <v>-0.0354</v>
+        <v>-0.0484</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>1258900</v>
+        <v>1478100</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>0.53</v>
+        <v>0.41</v>
       </c>
       <c r="H127" t="n">
-        <v>34.68</v>
+        <v>47.61</v>
       </c>
       <c r="I127" s="6" t="inlineStr">
         <is>
@@ -6172,10 +6172,10 @@
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>1.232</v>
+        <v>1.248</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>1.303</v>
+        <v>1.05</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="7" t="inlineStr"/>
@@ -6188,28 +6188,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>BPURI</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>0.21</v>
+        <v>0.35</v>
       </c>
       <c r="E128" s="8" t="n">
-        <v>-0.0455</v>
+        <v>-0.0141</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>1229000</v>
+        <v>1470400</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>2.36</v>
+        <v>0.16</v>
       </c>
       <c r="H128" t="n">
-        <v>37.42</v>
+        <v>50.37</v>
       </c>
       <c r="I128" s="6" t="inlineStr">
         <is>
@@ -6217,10 +6217,10 @@
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.224</v>
+        <v>0.355</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>0.233</v>
+        <v>0.326</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="7" t="inlineStr"/>
@@ -6233,31 +6233,40 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>9776</t>
+          <t>0466</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>RSSB</t>
+          <t>SRKKAI</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E129" s="10" t="n">
-        <v>0</v>
+        <v>0.49</v>
+      </c>
+      <c r="E129" s="8" t="n">
+        <v>-0.0392</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>1208800</v>
-      </c>
-      <c r="G129" s="5" t="n"/>
+        <v>1444500</v>
+      </c>
+      <c r="G129" s="5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="H129" t="n">
+        <v>37.73</v>
+      </c>
       <c r="I129" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J129" s="2" t="n"/>
-      <c r="K129" s="2" t="n"/>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="K129" s="2" t="n">
+        <v>0.531</v>
+      </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="7" t="inlineStr"/>
     </row>
@@ -6269,28 +6278,28 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>BAUTO</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>0.885</v>
+        <v>0.665</v>
       </c>
       <c r="E130" s="8" t="n">
-        <v>-0.0112</v>
+        <v>-0.0432</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>1206900</v>
+        <v>1431800</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>0.77</v>
+        <v>0.45</v>
       </c>
       <c r="H130" t="n">
-        <v>35.62</v>
+        <v>34.5</v>
       </c>
       <c r="I130" s="6" t="inlineStr">
         <is>
@@ -6298,10 +6307,10 @@
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>0.914</v>
+        <v>0.738</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>0.931</v>
+        <v>0.746</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="7" t="inlineStr"/>
@@ -6314,39 +6323,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>BAUTO</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>2.28</v>
+        <v>0.885</v>
       </c>
       <c r="E131" s="8" t="n">
-        <v>-0.013</v>
+        <v>-0.0112</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>1198100</v>
+        <v>1416700</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>0.32</v>
+        <v>0.9</v>
       </c>
       <c r="H131" t="n">
-        <v>57.14</v>
-      </c>
-      <c r="I131" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.62</v>
+      </c>
+      <c r="I131" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>2.208</v>
+        <v>0.914</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>2.152</v>
+        <v>0.931</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="7" t="inlineStr"/>
@@ -6359,39 +6368,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E132" s="3" t="n">
-        <v>0.0175</v>
+        <v>0.63</v>
+      </c>
+      <c r="E132" s="8" t="n">
+        <v>-0.0156</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>1184300</v>
+        <v>1408900</v>
       </c>
       <c r="G132" s="5" t="n">
-        <v>1.24</v>
+        <v>0.59</v>
       </c>
       <c r="H132" t="n">
-        <v>63.79</v>
-      </c>
-      <c r="I132" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.11</v>
+      </c>
+      <c r="I132" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>0.275</v>
+        <v>0.637</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>0.267</v>
+        <v>0.619</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="7" t="inlineStr"/>
@@ -6404,28 +6413,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>2054</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>TDM</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="E133" s="8" t="n">
-        <v>-0.0167</v>
+        <v>0.2</v>
+      </c>
+      <c r="E133" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>1179400</v>
+        <v>1383200</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>0.15</v>
+        <v>2.81</v>
       </c>
       <c r="H133" t="n">
-        <v>34.37</v>
+        <v>27.29</v>
       </c>
       <c r="I133" s="6" t="inlineStr">
         <is>
@@ -6433,10 +6442,10 @@
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>1.24</v>
+        <v>0.208</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>1.334</v>
+        <v>0.217</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="7" t="inlineStr"/>
@@ -6449,28 +6458,28 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>5315</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>SKYWLD</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>7.17</v>
+        <v>0.36</v>
       </c>
       <c r="E134" s="8" t="n">
-        <v>-0.005500000000000001</v>
+        <v>-0.07690000000000001</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>1130900</v>
+        <v>1363400</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>0.15</v>
+        <v>1.37</v>
       </c>
       <c r="H134" t="n">
-        <v>35.27</v>
+        <v>31.27</v>
       </c>
       <c r="I134" s="6" t="inlineStr">
         <is>
@@ -6478,10 +6487,10 @@
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>7.345</v>
+        <v>0.387</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>7.669</v>
+        <v>0.395</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="7" t="inlineStr"/>
@@ -6494,39 +6503,39 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>6.78</v>
-      </c>
-      <c r="E135" s="3" t="n">
-        <v>0.0059</v>
+        <v>4.28</v>
+      </c>
+      <c r="E135" s="8" t="n">
+        <v>-0.0339</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>1122100</v>
+        <v>1351200</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>0.26</v>
+        <v>0.21</v>
       </c>
       <c r="H135" t="n">
-        <v>51.24</v>
-      </c>
-      <c r="I135" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.92</v>
+      </c>
+      <c r="I135" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>6.761</v>
+        <v>4.356</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>6.835</v>
+        <v>4.437</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="7" t="inlineStr"/>
@@ -6539,39 +6548,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>5120</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>AMFIRST</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>0.335</v>
+        <v>2.25</v>
       </c>
       <c r="E136" s="8" t="n">
-        <v>-0.0147</v>
+        <v>-0.026</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>1121100</v>
+        <v>1339500</v>
       </c>
       <c r="G136" s="5" t="n">
-        <v>3.82</v>
+        <v>0.35</v>
       </c>
       <c r="H136" t="n">
-        <v>31.64</v>
-      </c>
-      <c r="I136" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.5</v>
+      </c>
+      <c r="I136" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>0.344</v>
+        <v>2.205</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>0.345</v>
+        <v>2.151</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="7" t="inlineStr"/>
@@ -6584,28 +6593,28 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>6181</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>MALTON</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>0.225</v>
+        <v>0.205</v>
       </c>
       <c r="E137" s="8" t="n">
-        <v>-0.0426</v>
+        <v>-0.04650000000000001</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>1110700</v>
+        <v>1339300</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>0.23</v>
+        <v>1.92</v>
       </c>
       <c r="H137" t="n">
-        <v>41.8</v>
+        <v>35.59</v>
       </c>
       <c r="I137" s="6" t="inlineStr">
         <is>
@@ -6613,10 +6622,10 @@
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>0.247</v>
+        <v>0.218</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>0.223</v>
+        <v>0.226</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="7" t="inlineStr"/>
@@ -6629,39 +6638,39 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E138" s="8" t="n">
-        <v>-0.0305</v>
+        <v>10.08</v>
+      </c>
+      <c r="E138" s="3" t="n">
+        <v>0.01</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>1098100</v>
+        <v>1312700</v>
       </c>
       <c r="G138" s="5" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H138" t="n">
-        <v>64.23999999999999</v>
-      </c>
-      <c r="I138" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.11</v>
+      </c>
+      <c r="I138" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>0.5629999999999999</v>
+        <v>10.014</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>0.463</v>
+        <v>10.169</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="7" t="inlineStr"/>
@@ -6674,39 +6683,39 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0337</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>0.24</v>
+        <v>1.08</v>
       </c>
       <c r="E139" s="8" t="n">
-        <v>-0.04</v>
+        <v>-0.0442</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>1093300</v>
+        <v>1291700</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="H139" t="n">
-        <v>50.37</v>
-      </c>
-      <c r="I139" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.06</v>
+      </c>
+      <c r="I139" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>0.24</v>
+        <v>1.231</v>
       </c>
       <c r="K139" s="2" t="n">
-        <v>0.243</v>
+        <v>1.303</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="7" t="inlineStr"/>
@@ -6719,39 +6728,39 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0328</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>3REN</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>0.39</v>
+        <v>1.18</v>
       </c>
       <c r="E140" s="8" t="n">
-        <v>-0.0127</v>
+        <v>-0.0167</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>1070700</v>
+        <v>1279300</v>
       </c>
       <c r="G140" s="5" t="n">
-        <v>0.47</v>
+        <v>0.17</v>
       </c>
       <c r="H140" t="n">
-        <v>50.92</v>
-      </c>
-      <c r="I140" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.37</v>
+      </c>
+      <c r="I140" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>0.388</v>
+        <v>1.24</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>0.391</v>
+        <v>1.334</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="7" t="inlineStr"/>
@@ -6764,28 +6773,28 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>4634</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>POS</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E141" s="3" t="n">
-        <v>0.0408</v>
+        <v>0.44</v>
+      </c>
+      <c r="E141" s="8" t="n">
+        <v>-0.0222</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>1025300</v>
+        <v>1256700</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="H141" t="n">
-        <v>53.86</v>
+        <v>24.7</v>
       </c>
       <c r="I141" s="6" t="inlineStr">
         <is>
@@ -6793,11 +6802,9 @@
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>0.249</v>
-      </c>
-      <c r="K141" s="2" t="n">
-        <v>0.251</v>
-      </c>
+        <v>0.469</v>
+      </c>
+      <c r="K141" s="2" t="n"/>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="7" t="inlineStr"/>
     </row>
@@ -6809,28 +6816,28 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>0291</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>CHB</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>2.52</v>
+        <v>0.635</v>
       </c>
       <c r="E142" s="8" t="n">
-        <v>-0.0345</v>
+        <v>-0.0305</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>1023500</v>
+        <v>1230900</v>
       </c>
       <c r="G142" s="5" t="n">
-        <v>0.62</v>
+        <v>0.23</v>
       </c>
       <c r="H142" t="n">
-        <v>53.41</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="I142" s="6" t="inlineStr">
         <is>
@@ -6838,10 +6845,10 @@
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>2.529</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="K142" s="2" t="n">
-        <v>2.224</v>
+        <v>0.463</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="7" t="inlineStr"/>
@@ -6854,28 +6861,28 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>BPURI</t>
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>10.04</v>
-      </c>
-      <c r="E143" s="3" t="n">
-        <v>0.006</v>
+        <v>0.21</v>
+      </c>
+      <c r="E143" s="8" t="n">
+        <v>-0.0455</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>1017700</v>
+        <v>1229800</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>0.08</v>
+        <v>2.36</v>
       </c>
       <c r="H143" t="n">
-        <v>49.55</v>
+        <v>37.42</v>
       </c>
       <c r="I143" s="6" t="inlineStr">
         <is>
@@ -6883,10 +6890,10 @@
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>10.01</v>
+        <v>0.224</v>
       </c>
       <c r="K143" s="2" t="n">
-        <v>10.168</v>
+        <v>0.233</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="7" t="inlineStr"/>
@@ -6899,40 +6906,31 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>9776</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>THMY</t>
+          <t>RSSB</t>
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="E144" s="8" t="n">
-        <v>-0.033</v>
+        <v>0.33</v>
+      </c>
+      <c r="E144" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>1015800</v>
-      </c>
-      <c r="G144" s="5" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="H144" t="n">
-        <v>48.24</v>
-      </c>
+        <v>1208800</v>
+      </c>
+      <c r="G144" s="5" t="n"/>
       <c r="I144" s="6" t="inlineStr">
         <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J144" s="2" t="n">
-        <v>2.112</v>
-      </c>
-      <c r="K144" s="2" t="n">
-        <v>1.984</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="n"/>
+      <c r="K144" s="2" t="n"/>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="7" t="inlineStr"/>
     </row>
@@ -6953,19 +6951,19 @@
         </is>
       </c>
       <c r="D145" s="2" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="E145" s="3" t="n">
-        <v>0.0203</v>
+        <v>0.0305</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>1000700</v>
+        <v>1207600</v>
       </c>
       <c r="G145" s="5" t="n">
-        <v>0.88</v>
+        <v>1.06</v>
       </c>
       <c r="H145" t="n">
-        <v>37.84</v>
+        <v>39.55</v>
       </c>
       <c r="I145" s="6" t="inlineStr">
         <is>
@@ -6973,7 +6971,7 @@
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>2.136</v>
+        <v>2.138</v>
       </c>
       <c r="K145" s="2" t="n">
         <v>2.291</v>
@@ -6989,39 +6987,39 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D146" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>5.36</v>
       </c>
       <c r="E146" s="8" t="n">
-        <v>-0.0072</v>
+        <v>-0.0377</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>989900</v>
+        <v>1188800</v>
       </c>
       <c r="G146" s="5" t="n">
-        <v>0.14</v>
+        <v>0.33</v>
       </c>
       <c r="H146" t="n">
-        <v>30.53</v>
-      </c>
-      <c r="I146" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.43</v>
+      </c>
+      <c r="I146" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>0.735</v>
+        <v>5.501</v>
       </c>
       <c r="K146" s="2" t="n">
-        <v>0.801</v>
+        <v>5.391</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="7" t="inlineStr"/>
@@ -7034,39 +7032,39 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>NGGB</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D147" s="2" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="E147" s="3" t="n">
-        <v>0.0066</v>
+        <v>0.285</v>
+      </c>
+      <c r="E147" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>980100</v>
+        <v>1184400</v>
       </c>
       <c r="G147" s="5" t="n">
-        <v>0.63</v>
+        <v>1.24</v>
       </c>
       <c r="H147" t="n">
-        <v>61.61</v>
-      </c>
-      <c r="I147" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.9</v>
+      </c>
+      <c r="I147" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>0.742</v>
+        <v>0.275</v>
       </c>
       <c r="K147" s="2" t="n">
-        <v>0.718</v>
+        <v>0.267</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="7" t="inlineStr"/>
@@ -7079,39 +7077,39 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>0291</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>CHB</t>
         </is>
       </c>
       <c r="D148" s="2" t="n">
-        <v>4.32</v>
+        <v>2.49</v>
       </c>
       <c r="E148" s="8" t="n">
-        <v>-0.0248</v>
+        <v>-0.046</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>948300</v>
+        <v>1141200</v>
       </c>
       <c r="G148" s="5" t="n">
-        <v>0.15</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H148" t="n">
-        <v>47.32</v>
-      </c>
-      <c r="I148" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.83</v>
+      </c>
+      <c r="I148" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>4.36</v>
+        <v>2.527</v>
       </c>
       <c r="K148" s="2" t="n">
-        <v>4.438</v>
+        <v>2.223</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="7" t="inlineStr"/>
@@ -7124,39 +7122,39 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>5106</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>AXREIT</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D149" s="2" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="E149" s="10" t="n">
-        <v>0</v>
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="E149" s="8" t="n">
+        <v>-0.0144</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>891700</v>
+        <v>1134600</v>
       </c>
       <c r="G149" s="5" t="n">
-        <v>0.7</v>
+        <v>0.16</v>
       </c>
       <c r="H149" t="n">
-        <v>53.66</v>
-      </c>
-      <c r="I149" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.64</v>
+      </c>
+      <c r="I149" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>1.831</v>
+        <v>0.734</v>
       </c>
       <c r="K149" s="2" t="n">
-        <v>1.829</v>
+        <v>0.801</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="7" t="inlineStr"/>
@@ -7169,28 +7167,28 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D150" s="2" t="n">
-        <v>5.09</v>
+        <v>0.23</v>
       </c>
       <c r="E150" s="8" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.0213</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>866500</v>
+        <v>1125700</v>
       </c>
       <c r="G150" s="5" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="H150" t="n">
-        <v>52.38</v>
+        <v>43.72</v>
       </c>
       <c r="I150" s="6" t="inlineStr">
         <is>
@@ -7198,10 +7196,10 @@
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>5.07</v>
+        <v>0.247</v>
       </c>
       <c r="K150" s="2" t="n">
-        <v>5.064</v>
+        <v>0.223</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="7" t="inlineStr"/>
@@ -7214,39 +7212,39 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>0151</t>
+          <t>0337</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>KGB</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="D151" s="2" t="n">
-        <v>8.449999999999999</v>
+        <v>0.24</v>
       </c>
       <c r="E151" s="8" t="n">
-        <v>-0.0265</v>
+        <v>-0.04</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>845800</v>
+        <v>1125300</v>
       </c>
       <c r="G151" s="5" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="H151" t="n">
-        <v>44.52</v>
-      </c>
-      <c r="I151" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.37</v>
+      </c>
+      <c r="I151" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>8.683999999999999</v>
+        <v>0.24</v>
       </c>
       <c r="K151" s="2" t="n">
-        <v>8.708</v>
+        <v>0.243</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="7" t="inlineStr"/>
@@ -7259,39 +7257,39 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>5120</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>AMFIRST</t>
         </is>
       </c>
       <c r="D152" s="2" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E152" s="3" t="n">
-        <v>0.0091</v>
+        <v>0.335</v>
+      </c>
+      <c r="E152" s="8" t="n">
+        <v>-0.0147</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>842000</v>
+        <v>1121100</v>
       </c>
       <c r="G152" s="5" t="n">
-        <v>0.75</v>
+        <v>3.82</v>
       </c>
       <c r="H152" t="n">
-        <v>39.65</v>
-      </c>
-      <c r="I152" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.64</v>
+      </c>
+      <c r="I152" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>0.573</v>
+        <v>0.344</v>
       </c>
       <c r="K152" s="2" t="n">
-        <v>0.615</v>
+        <v>0.345</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="7" t="inlineStr"/>
@@ -7304,39 +7302,39 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D153" s="2" t="n">
-        <v>5.41</v>
-      </c>
-      <c r="E153" s="8" t="n">
-        <v>-0.0287</v>
+        <v>5.97</v>
+      </c>
+      <c r="E153" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>834600</v>
+        <v>1110300</v>
       </c>
       <c r="G153" s="5" t="n">
-        <v>0.23</v>
+        <v>0.13</v>
       </c>
       <c r="H153" t="n">
-        <v>48.62</v>
-      </c>
-      <c r="I153" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.65</v>
+      </c>
+      <c r="I153" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J153" s="2" t="n">
-        <v>5.506</v>
+        <v>6.094</v>
       </c>
       <c r="K153" s="2" t="n">
-        <v>5.392</v>
+        <v>6.351</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="7" t="inlineStr"/>
@@ -7349,39 +7347,39 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>NGGB</t>
         </is>
       </c>
       <c r="D154" s="2" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="E154" s="8" t="n">
-        <v>-0.0187</v>
+        <v>0.77</v>
+      </c>
+      <c r="E154" s="3" t="n">
+        <v>0.0199</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>828900</v>
+        <v>1098100</v>
       </c>
       <c r="G154" s="5" t="n">
-        <v>0.22</v>
+        <v>0.7</v>
       </c>
       <c r="H154" t="n">
-        <v>61.14</v>
-      </c>
-      <c r="I154" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>64.87</v>
+      </c>
+      <c r="I154" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>0.494</v>
+        <v>0.743</v>
       </c>
       <c r="K154" s="2" t="n">
-        <v>0.461</v>
+        <v>0.718</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="7" t="inlineStr"/>
@@ -7394,39 +7392,39 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>0293</t>
+          <t>8206</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>KJTS</t>
+          <t>ECOWLD</t>
         </is>
       </c>
       <c r="D155" s="2" t="n">
-        <v>0.88</v>
+        <v>1.92</v>
       </c>
       <c r="E155" s="8" t="n">
-        <v>-0.0435</v>
+        <v>-0.0154</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>820100</v>
+        <v>1083800</v>
       </c>
       <c r="G155" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="H155" t="n">
-        <v>34.48</v>
-      </c>
-      <c r="I155" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.56</v>
+      </c>
+      <c r="I155" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>0.979</v>
+        <v>1.908</v>
       </c>
       <c r="K155" s="2" t="n">
-        <v>1.028</v>
+        <v>1.958</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="7" t="inlineStr"/>
@@ -7439,28 +7437,28 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>0375</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>THMY</t>
         </is>
       </c>
       <c r="D156" s="2" t="n">
-        <v>1.29</v>
+        <v>2.05</v>
       </c>
       <c r="E156" s="8" t="n">
-        <v>-0.0515</v>
+        <v>-0.033</v>
       </c>
       <c r="F156" s="4" t="n">
-        <v>775000</v>
+        <v>1075400</v>
       </c>
       <c r="G156" s="5" t="n">
-        <v>0.33</v>
+        <v>0.45</v>
       </c>
       <c r="H156" t="n">
-        <v>45.56</v>
+        <v>48.24</v>
       </c>
       <c r="I156" s="6" t="inlineStr">
         <is>
@@ -7468,10 +7466,10 @@
         </is>
       </c>
       <c r="J156" s="2" t="n">
-        <v>1.338</v>
+        <v>2.112</v>
       </c>
       <c r="K156" s="2" t="n">
-        <v>1.273</v>
+        <v>1.984</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="7" t="inlineStr"/>
@@ -7484,28 +7482,28 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>0325</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="D157" s="2" t="n">
-        <v>3.24</v>
+        <v>1</v>
       </c>
       <c r="E157" s="8" t="n">
-        <v>-0.0122</v>
+        <v>-0.0291</v>
       </c>
       <c r="F157" s="4" t="n">
-        <v>758900</v>
+        <v>1073900</v>
       </c>
       <c r="G157" s="5" t="n">
-        <v>0.12</v>
+        <v>0.67</v>
       </c>
       <c r="H157" t="n">
-        <v>29.99</v>
+        <v>36.21</v>
       </c>
       <c r="I157" s="6" t="inlineStr">
         <is>
@@ -7513,10 +7511,10 @@
         </is>
       </c>
       <c r="J157" s="2" t="n">
-        <v>3.406</v>
+        <v>1.091</v>
       </c>
       <c r="K157" s="2" t="n">
-        <v>3.624</v>
+        <v>1.095</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="7" t="inlineStr"/>
@@ -7529,39 +7527,39 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>0328</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>3REN</t>
         </is>
       </c>
       <c r="D158" s="2" t="n">
-        <v>2.5</v>
+        <v>0.39</v>
       </c>
       <c r="E158" s="8" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0127</v>
       </c>
       <c r="F158" s="4" t="n">
-        <v>755200</v>
+        <v>1070700</v>
       </c>
       <c r="G158" s="5" t="n">
-        <v>0.14</v>
+        <v>0.47</v>
       </c>
       <c r="H158" t="n">
-        <v>41.47</v>
-      </c>
-      <c r="I158" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.92</v>
+      </c>
+      <c r="I158" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J158" s="2" t="n">
-        <v>2.565</v>
+        <v>0.388</v>
       </c>
       <c r="K158" s="2" t="n">
-        <v>2.739</v>
+        <v>0.391</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="7" t="inlineStr"/>
@@ -7574,28 +7572,28 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D159" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E159" s="3" t="n">
-        <v>0.005</v>
+        <v>0.4</v>
+      </c>
+      <c r="E159" s="8" t="n">
+        <v>-0.0361</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v>662300</v>
+        <v>1070000</v>
       </c>
       <c r="G159" s="5" t="n">
-        <v>0.08</v>
+        <v>0.29</v>
       </c>
       <c r="H159" t="n">
-        <v>40.06</v>
+        <v>48.09</v>
       </c>
       <c r="I159" s="6" t="inlineStr">
         <is>
@@ -7603,10 +7601,10 @@
         </is>
       </c>
       <c r="J159" s="2" t="n">
-        <v>6.097</v>
+        <v>0.417</v>
       </c>
       <c r="K159" s="2" t="n">
-        <v>6.351</v>
+        <v>0.378</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="7" t="inlineStr"/>
@@ -7619,28 +7617,28 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>4634</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>POS</t>
         </is>
       </c>
       <c r="D160" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E160" s="8" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.25</v>
+      </c>
+      <c r="E160" s="3" t="n">
+        <v>0.0204</v>
       </c>
       <c r="F160" s="4" t="n">
-        <v>610800</v>
+        <v>1036300</v>
       </c>
       <c r="G160" s="5" t="n">
-        <v>0.53</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H160" t="n">
-        <v>35.74</v>
+        <v>50.21</v>
       </c>
       <c r="I160" s="6" t="inlineStr">
         <is>
@@ -7648,10 +7646,10 @@
         </is>
       </c>
       <c r="J160" s="2" t="n">
-        <v>0.631</v>
+        <v>0.249</v>
       </c>
       <c r="K160" s="2" t="n">
-        <v>0.63</v>
+        <v>0.251</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="7" t="inlineStr"/>
@@ -7664,28 +7662,28 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D161" s="2" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E161" s="10" t="n">
-        <v>0</v>
+        <v>0.82</v>
+      </c>
+      <c r="E161" s="8" t="n">
+        <v>-0.0296</v>
       </c>
       <c r="F161" s="4" t="n">
-        <v>606800</v>
+        <v>1032700</v>
       </c>
       <c r="G161" s="5" t="n">
-        <v>0.18</v>
+        <v>0.48</v>
       </c>
       <c r="H161" t="n">
-        <v>39.4</v>
+        <v>17.47</v>
       </c>
       <c r="I161" s="6" t="inlineStr">
         <is>
@@ -7693,10 +7691,10 @@
         </is>
       </c>
       <c r="J161" s="2" t="n">
-        <v>0.547</v>
+        <v>0.971</v>
       </c>
       <c r="K161" s="2" t="n">
-        <v>0.575</v>
+        <v>1.093</v>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" s="7" t="inlineStr"/>
@@ -7709,28 +7707,28 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>0398</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>GDGROUP</t>
         </is>
       </c>
       <c r="D162" s="2" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="E162" s="8" t="n">
-        <v>-0.0225</v>
+        <v>0.38</v>
+      </c>
+      <c r="E162" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F162" s="4" t="n">
-        <v>602300</v>
+        <v>1031100</v>
       </c>
       <c r="G162" s="5" t="n">
-        <v>0.11</v>
+        <v>1</v>
       </c>
       <c r="H162" t="n">
-        <v>39.04</v>
+        <v>49.68</v>
       </c>
       <c r="I162" s="9" t="inlineStr">
         <is>
@@ -7738,10 +7736,10 @@
         </is>
       </c>
       <c r="J162" s="2" t="n">
-        <v>4.463</v>
+        <v>0.38</v>
       </c>
       <c r="K162" s="2" t="n">
-        <v>4.758</v>
+        <v>0.379</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="7" t="inlineStr"/>
@@ -7754,28 +7752,28 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>0151</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>LWSABAH</t>
+          <t>KGB</t>
         </is>
       </c>
       <c r="D163" s="2" t="n">
-        <v>1.51</v>
+        <v>8.44</v>
       </c>
       <c r="E163" s="8" t="n">
-        <v>-0.0208</v>
+        <v>-0.0276</v>
       </c>
       <c r="F163" s="4" t="n">
-        <v>590100</v>
+        <v>975800</v>
       </c>
       <c r="G163" s="5" t="n">
-        <v>0.55</v>
+        <v>0.46</v>
       </c>
       <c r="H163" t="n">
-        <v>33.47</v>
+        <v>44.32</v>
       </c>
       <c r="I163" s="6" t="inlineStr">
         <is>
@@ -7783,10 +7781,10 @@
         </is>
       </c>
       <c r="J163" s="2" t="n">
-        <v>1.626</v>
+        <v>8.683</v>
       </c>
       <c r="K163" s="2" t="n">
-        <v>1.632</v>
+        <v>8.708</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="7" t="inlineStr"/>
@@ -7799,28 +7797,28 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D164" s="2" t="n">
-        <v>2.67</v>
+        <v>2.49</v>
       </c>
       <c r="E164" s="8" t="n">
-        <v>-0.0037</v>
+        <v>-0.0119</v>
       </c>
       <c r="F164" s="4" t="n">
-        <v>589200</v>
+        <v>966000</v>
       </c>
       <c r="G164" s="5" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="H164" t="n">
-        <v>55.04</v>
+        <v>40.83</v>
       </c>
       <c r="I164" s="6" t="inlineStr">
         <is>
@@ -7828,10 +7826,10 @@
         </is>
       </c>
       <c r="J164" s="2" t="n">
-        <v>2.67</v>
+        <v>2.564</v>
       </c>
       <c r="K164" s="2" t="n">
-        <v>2.225</v>
+        <v>2.739</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="7" t="inlineStr"/>
@@ -7844,39 +7842,39 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>5121</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>HEKTAR</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D165" s="2" t="n">
-        <v>0.505</v>
+        <v>5.08</v>
       </c>
       <c r="E165" s="8" t="n">
-        <v>-0.0098</v>
+        <v>-0.0097</v>
       </c>
       <c r="F165" s="4" t="n">
-        <v>586700</v>
+        <v>942800</v>
       </c>
       <c r="G165" s="5" t="n">
-        <v>0.78</v>
+        <v>0.22</v>
       </c>
       <c r="H165" t="n">
-        <v>54.4</v>
-      </c>
-      <c r="I165" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.69</v>
+      </c>
+      <c r="I165" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J165" s="2" t="n">
-        <v>0.502</v>
+        <v>5.069</v>
       </c>
       <c r="K165" s="2" t="n">
-        <v>0.488</v>
+        <v>5.064</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="7" t="inlineStr"/>
@@ -7889,28 +7887,28 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>0293</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>KJTS</t>
         </is>
       </c>
       <c r="D166" s="2" t="n">
-        <v>1.69</v>
+        <v>0.875</v>
       </c>
       <c r="E166" s="8" t="n">
-        <v>-0.0117</v>
+        <v>-0.0489</v>
       </c>
       <c r="F166" s="4" t="n">
-        <v>584700</v>
+        <v>930400</v>
       </c>
       <c r="G166" s="5" t="n">
-        <v>0.09</v>
+        <v>0.79</v>
       </c>
       <c r="H166" t="n">
-        <v>33.7</v>
+        <v>34.02</v>
       </c>
       <c r="I166" s="6" t="inlineStr">
         <is>
@@ -7918,10 +7916,10 @@
         </is>
       </c>
       <c r="J166" s="2" t="n">
-        <v>1.785</v>
+        <v>0.978</v>
       </c>
       <c r="K166" s="2" t="n">
-        <v>1.902</v>
+        <v>1.028</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="7" t="inlineStr"/>
@@ -7934,39 +7932,39 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>IHH</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D167" s="2" t="n">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="E167" s="3" t="n">
-        <v>0.005</v>
+        <v>1.7</v>
+      </c>
+      <c r="E167" s="8" t="n">
+        <v>-0.0058</v>
       </c>
       <c r="F167" s="4" t="n">
-        <v>575200</v>
+        <v>928400</v>
       </c>
       <c r="G167" s="5" t="n">
         <v>0.14</v>
       </c>
       <c r="H167" t="n">
-        <v>58.53</v>
-      </c>
-      <c r="I167" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.58</v>
+      </c>
+      <c r="I167" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J167" s="2" t="n">
-        <v>7.908</v>
+        <v>1.786</v>
       </c>
       <c r="K167" s="2" t="n">
-        <v>7.984</v>
+        <v>1.902</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="7" t="inlineStr"/>
@@ -7979,39 +7977,39 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D168" s="2" t="n">
-        <v>0.895</v>
+        <v>0.525</v>
       </c>
       <c r="E168" s="8" t="n">
-        <v>-0.011</v>
+        <v>-0.0187</v>
       </c>
       <c r="F168" s="4" t="n">
-        <v>573000</v>
+        <v>902900</v>
       </c>
       <c r="G168" s="5" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="H168" t="n">
-        <v>41.27</v>
-      </c>
-      <c r="I168" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.14</v>
+      </c>
+      <c r="I168" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J168" s="2" t="n">
-        <v>0.909</v>
+        <v>0.494</v>
       </c>
       <c r="K168" s="2" t="n">
-        <v>0.958</v>
+        <v>0.461</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="7" t="inlineStr"/>
@@ -8024,39 +8022,39 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D169" s="2" t="n">
-        <v>0.785</v>
+        <v>1.28</v>
       </c>
       <c r="E169" s="8" t="n">
-        <v>-0.0248</v>
+        <v>-0.0588</v>
       </c>
       <c r="F169" s="4" t="n">
-        <v>567300</v>
+        <v>902200</v>
       </c>
       <c r="G169" s="5" t="n">
-        <v>0.25</v>
+        <v>0.38</v>
       </c>
       <c r="H169" t="n">
-        <v>52.65</v>
-      </c>
-      <c r="I169" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.54</v>
+      </c>
+      <c r="I169" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J169" s="2" t="n">
-        <v>0.778</v>
+        <v>1.337</v>
       </c>
       <c r="K169" s="2" t="n">
-        <v>0.767</v>
+        <v>1.273</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="7" t="inlineStr"/>
@@ -8069,39 +8067,39 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>5106</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>AXREIT</t>
         </is>
       </c>
       <c r="D170" s="2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="E170" s="8" t="n">
-        <v>-0.008399999999999999</v>
+        <v>1.85</v>
+      </c>
+      <c r="E170" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F170" s="4" t="n">
-        <v>565900</v>
+        <v>893800</v>
       </c>
       <c r="G170" s="5" t="n">
-        <v>0.24</v>
+        <v>0.7</v>
       </c>
       <c r="H170" t="n">
-        <v>31.79</v>
-      </c>
-      <c r="I170" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.66</v>
+      </c>
+      <c r="I170" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J170" s="2" t="n">
-        <v>1.254</v>
+        <v>1.831</v>
       </c>
       <c r="K170" s="2" t="n">
-        <v>1.309</v>
+        <v>1.829</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" s="7" t="inlineStr"/>
@@ -8114,39 +8112,39 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>0325</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D171" s="2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="E171" s="8" t="n">
-        <v>-0.0194</v>
+        <v>0.555</v>
+      </c>
+      <c r="E171" s="3" t="n">
+        <v>0.0091</v>
       </c>
       <c r="F171" s="4" t="n">
-        <v>565400</v>
+        <v>842000</v>
       </c>
       <c r="G171" s="5" t="n">
-        <v>0.35</v>
+        <v>0.75</v>
       </c>
       <c r="H171" t="n">
-        <v>37.27</v>
-      </c>
-      <c r="I171" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>39.65</v>
+      </c>
+      <c r="I171" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J171" s="2" t="n">
-        <v>1.092</v>
+        <v>0.573</v>
       </c>
       <c r="K171" s="2" t="n">
-        <v>1.095</v>
+        <v>0.615</v>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" s="7" t="inlineStr"/>
@@ -8159,39 +8157,39 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D172" s="2" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="E172" s="3" t="n">
-        <v>0.0141</v>
+        <v>0.535</v>
+      </c>
+      <c r="E172" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F172" s="4" t="n">
-        <v>564200</v>
+        <v>842000</v>
       </c>
       <c r="G172" s="5" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="H172" t="n">
-        <v>58.07</v>
-      </c>
-      <c r="I172" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.4</v>
+      </c>
+      <c r="I172" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J172" s="2" t="n">
-        <v>2.107</v>
+        <v>0.547</v>
       </c>
       <c r="K172" s="2" t="n">
-        <v>2.055</v>
+        <v>0.575</v>
       </c>
       <c r="L172" t="inlineStr"/>
       <c r="M172" s="7" t="inlineStr"/>
@@ -8204,39 +8202,39 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>MATRIX</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D173" s="2" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E173" s="3" t="n">
-        <v>0.009300000000000001</v>
+        <v>3.22</v>
+      </c>
+      <c r="E173" s="8" t="n">
+        <v>-0.0183</v>
       </c>
       <c r="F173" s="4" t="n">
-        <v>561800</v>
+        <v>786800</v>
       </c>
       <c r="G173" s="5" t="n">
-        <v>0.44</v>
+        <v>0.12</v>
       </c>
       <c r="H173" t="n">
-        <v>45.93</v>
-      </c>
-      <c r="I173" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.97</v>
+      </c>
+      <c r="I173" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J173" s="2" t="n">
-        <v>1.096</v>
+        <v>3.404</v>
       </c>
       <c r="K173" s="2" t="n">
-        <v>1.138</v>
+        <v>3.623</v>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" s="7" t="inlineStr"/>
@@ -8249,39 +8247,39 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D174" s="2" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="E174" s="8" t="n">
-        <v>-0.0178</v>
+        <v>1.39</v>
+      </c>
+      <c r="E174" s="3" t="n">
+        <v>0.0072</v>
       </c>
       <c r="F174" s="4" t="n">
-        <v>556200</v>
+        <v>766700</v>
       </c>
       <c r="G174" s="5" t="n">
-        <v>0.26</v>
+        <v>0.41</v>
       </c>
       <c r="H174" t="n">
-        <v>18.08</v>
-      </c>
-      <c r="I174" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.2</v>
+      </c>
+      <c r="I174" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J174" s="2" t="n">
-        <v>0.972</v>
+        <v>1.374</v>
       </c>
       <c r="K174" s="2" t="n">
-        <v>1.093</v>
+        <v>1.342</v>
       </c>
       <c r="L174" t="inlineStr"/>
       <c r="M174" s="7" t="inlineStr"/>
@@ -8294,28 +8292,28 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>MULPHA</t>
+          <t>LWSABAH</t>
         </is>
       </c>
       <c r="D175" s="2" t="n">
-        <v>2.65</v>
+        <v>1.54</v>
       </c>
       <c r="E175" s="8" t="n">
-        <v>-0.0112</v>
+        <v>-0.0013</v>
       </c>
       <c r="F175" s="4" t="n">
-        <v>551300</v>
+        <v>764700</v>
       </c>
       <c r="G175" s="5" t="n">
-        <v>67.81</v>
+        <v>0.71</v>
       </c>
       <c r="H175" t="n">
-        <v>37.45</v>
+        <v>36.26</v>
       </c>
       <c r="I175" s="6" t="inlineStr">
         <is>
@@ -8323,10 +8321,10 @@
         </is>
       </c>
       <c r="J175" s="2" t="n">
-        <v>2.728</v>
+        <v>1.629</v>
       </c>
       <c r="K175" s="2" t="n">
-        <v>2.822</v>
+        <v>1.632</v>
       </c>
       <c r="L175" t="inlineStr"/>
       <c r="M175" s="7" t="inlineStr"/>
@@ -8339,39 +8337,39 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>FFB</t>
         </is>
       </c>
       <c r="D176" s="2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E176" s="3" t="n">
-        <v>0.0145</v>
+        <v>1.76</v>
+      </c>
+      <c r="E176" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F176" s="4" t="n">
-        <v>510200</v>
+        <v>746400</v>
       </c>
       <c r="G176" s="5" t="n">
-        <v>0.27</v>
+        <v>0.23</v>
       </c>
       <c r="H176" t="n">
-        <v>63.39</v>
-      </c>
-      <c r="I176" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.77</v>
+      </c>
+      <c r="I176" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J176" s="2" t="n">
-        <v>1.375</v>
+        <v>1.843</v>
       </c>
       <c r="K176" s="2" t="n">
-        <v>1.343</v>
+        <v>1.981</v>
       </c>
       <c r="L176" t="inlineStr"/>
       <c r="M176" s="7" t="inlineStr"/>
@@ -8384,45 +8382,900 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>0249</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>LGMS</t>
+          <t>IHH</t>
         </is>
       </c>
       <c r="D177" s="2" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="E177" s="8" t="n">
-        <v>-0.0374</v>
+        <v>8.029999999999999</v>
+      </c>
+      <c r="E177" s="3" t="n">
+        <v>0.0025</v>
       </c>
       <c r="F177" s="4" t="n">
-        <v>507400</v>
+        <v>712000</v>
       </c>
       <c r="G177" s="5" t="n">
-        <v>0.47</v>
+        <v>0.18</v>
       </c>
       <c r="H177" t="n">
-        <v>47.7</v>
-      </c>
-      <c r="I177" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.52</v>
+      </c>
+      <c r="I177" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J177" s="2" t="n">
-        <v>0.527</v>
+        <v>7.906</v>
       </c>
       <c r="K177" s="2" t="n">
-        <v>0.506</v>
+        <v>7.984</v>
       </c>
       <c r="L177" t="inlineStr"/>
       <c r="M177" s="7" t="inlineStr"/>
     </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>5288</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>SIMEPROP</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E178" s="8" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="F178" s="4" t="n">
+        <v>690900</v>
+      </c>
+      <c r="G178" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H178" t="n">
+        <v>52.25</v>
+      </c>
+      <c r="I178" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="n">
+        <v>1.255</v>
+      </c>
+      <c r="K178" s="2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" s="7" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>5211</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>SUNWAY</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="E179" s="8" t="n">
+        <v>-0.0292</v>
+      </c>
+      <c r="F179" s="4" t="n">
+        <v>685500</v>
+      </c>
+      <c r="G179" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H179" t="n">
+        <v>37.69</v>
+      </c>
+      <c r="I179" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="K179" s="2" t="n">
+        <v>4.757</v>
+      </c>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" s="7" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>0233</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>PEKAT</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="E180" s="8" t="n">
+        <v>-0.0112</v>
+      </c>
+      <c r="F180" s="4" t="n">
+        <v>635800</v>
+      </c>
+      <c r="G180" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H180" t="n">
+        <v>53.91</v>
+      </c>
+      <c r="I180" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="n">
+        <v>2.668</v>
+      </c>
+      <c r="K180" s="2" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" s="7" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E181" s="8" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="F181" s="4" t="n">
+        <v>635000</v>
+      </c>
+      <c r="G181" s="5" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H181" t="n">
+        <v>35.74</v>
+      </c>
+      <c r="I181" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="K181" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" s="7" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>9059</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>TSH</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="E182" s="8" t="n">
+        <v>-0.008399999999999999</v>
+      </c>
+      <c r="F182" s="4" t="n">
+        <v>614600</v>
+      </c>
+      <c r="G182" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H182" t="n">
+        <v>31.79</v>
+      </c>
+      <c r="I182" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="n">
+        <v>1.254</v>
+      </c>
+      <c r="K182" s="2" t="n">
+        <v>1.309</v>
+      </c>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" s="7" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>5121</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>HEKTAR</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="E183" s="8" t="n">
+        <v>-0.0098</v>
+      </c>
+      <c r="F183" s="4" t="n">
+        <v>606700</v>
+      </c>
+      <c r="G183" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H183" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="I183" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="K183" s="2" t="n">
+        <v>0.488</v>
+      </c>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" s="7" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>0338</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>KOPI</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="E184" s="8" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="F184" s="4" t="n">
+        <v>595400</v>
+      </c>
+      <c r="G184" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H184" t="n">
+        <v>41.27</v>
+      </c>
+      <c r="I184" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="K184" s="2" t="n">
+        <v>0.958</v>
+      </c>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" s="7" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>0099</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>SCICOM</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="E185" s="8" t="n">
+        <v>-0.0469</v>
+      </c>
+      <c r="F185" s="4" t="n">
+        <v>595000</v>
+      </c>
+      <c r="G185" s="5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H185" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="I185" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="n">
+        <v>2.222</v>
+      </c>
+      <c r="K185" s="2" t="n">
+        <v>2.232</v>
+      </c>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" s="7" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>5326</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>99SMART</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="E186" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F186" s="4" t="n">
+        <v>589400</v>
+      </c>
+      <c r="G186" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H186" t="n">
+        <v>39.75</v>
+      </c>
+      <c r="I186" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="n">
+        <v>3.164</v>
+      </c>
+      <c r="K186" s="2" t="n">
+        <v>3.347</v>
+      </c>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" s="7" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>4383</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>JTIASA</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="E187" s="8" t="n">
+        <v>-0.0053</v>
+      </c>
+      <c r="F187" s="4" t="n">
+        <v>583700</v>
+      </c>
+      <c r="G187" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H187" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="I187" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="n">
+        <v>0.954</v>
+      </c>
+      <c r="K187" s="2" t="n">
+        <v>1.008</v>
+      </c>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" s="7" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>5236</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>MATRIX</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="E188" s="3" t="n">
+        <v>0.009300000000000001</v>
+      </c>
+      <c r="F188" s="4" t="n">
+        <v>578900</v>
+      </c>
+      <c r="G188" s="5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H188" t="n">
+        <v>45.93</v>
+      </c>
+      <c r="I188" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J188" s="2" t="n">
+        <v>1.096</v>
+      </c>
+      <c r="K188" s="2" t="n">
+        <v>1.138</v>
+      </c>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" s="7" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>5302</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>ATECH</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="E189" s="8" t="n">
+        <v>-0.0248</v>
+      </c>
+      <c r="F189" s="4" t="n">
+        <v>576900</v>
+      </c>
+      <c r="G189" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H189" t="n">
+        <v>52.65</v>
+      </c>
+      <c r="I189" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J189" s="2" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="K189" s="2" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" s="7" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>7293</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>YINSON</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="E190" s="3" t="n">
+        <v>0.009399999999999999</v>
+      </c>
+      <c r="F190" s="4" t="n">
+        <v>573300</v>
+      </c>
+      <c r="G190" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H190" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="I190" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J190" s="2" t="n">
+        <v>2.106</v>
+      </c>
+      <c r="K190" s="2" t="n">
+        <v>2.055</v>
+      </c>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" s="7" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>5141</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>DAYANG</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E191" s="8" t="n">
+        <v>-0.0146</v>
+      </c>
+      <c r="F191" s="4" t="n">
+        <v>557100</v>
+      </c>
+      <c r="G191" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H191" t="n">
+        <v>31.19</v>
+      </c>
+      <c r="I191" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J191" s="2" t="n">
+        <v>1.424</v>
+      </c>
+      <c r="K191" s="2" t="n">
+        <v>1.476</v>
+      </c>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" s="7" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>3905</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>MULPHA</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E192" s="8" t="n">
+        <v>-0.0299</v>
+      </c>
+      <c r="F192" s="4" t="n">
+        <v>553400</v>
+      </c>
+      <c r="G192" s="5" t="n">
+        <v>68.06999999999999</v>
+      </c>
+      <c r="H192" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="I192" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J192" s="2" t="n">
+        <v>2.724</v>
+      </c>
+      <c r="K192" s="2" t="n">
+        <v>2.821</v>
+      </c>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" s="7" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>0366</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>ICENTS</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="E193" s="8" t="n">
+        <v>-0.0491</v>
+      </c>
+      <c r="F193" s="4" t="n">
+        <v>550500</v>
+      </c>
+      <c r="G193" s="5" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H193" t="n">
+        <v>40.31</v>
+      </c>
+      <c r="I193" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J193" s="2" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="K193" s="2" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" s="7" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>LGMS</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="E194" s="8" t="n">
+        <v>-0.0374</v>
+      </c>
+      <c r="F194" s="4" t="n">
+        <v>541800</v>
+      </c>
+      <c r="G194" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H194" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="I194" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J194" s="2" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="K194" s="2" t="n">
+        <v>0.506</v>
+      </c>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" s="7" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>5263</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>SUNCON</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="E195" s="8" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="F195" s="4" t="n">
+        <v>527500</v>
+      </c>
+      <c r="G195" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H195" t="n">
+        <v>44.83</v>
+      </c>
+      <c r="I195" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J195" s="2" t="n">
+        <v>7.593</v>
+      </c>
+      <c r="K195" s="2" t="n">
+        <v>7.788</v>
+      </c>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" s="7" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>5005</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>UNISEM</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="E196" s="8" t="n">
+        <v>-0.0368</v>
+      </c>
+      <c r="F196" s="4" t="n">
+        <v>520800</v>
+      </c>
+      <c r="G196" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H196" t="n">
+        <v>45.15</v>
+      </c>
+      <c r="I196" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J196" s="2" t="n">
+        <v>4.312</v>
+      </c>
+      <c r="K196" s="2" t="n">
+        <v>4.341</v>
+      </c>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M177"/>
+  <autoFilter ref="A1:M196"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>